--- a/ჟურნალი/5. N301 front-end დეველოპმენტი (ინტეგრირებული მიდგომით) - Git.xlsx
+++ b/ჟურნალი/5. N301 front-end დეველოპმენტი (ინტეგრირებული მიდგომით) - Git.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\3Daudiece\Desktop\Front-end (არ წაშალოთ!!!)\0. ready\ჟურნალი\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\3Daudiece\Desktop\Front-end!!\0. ready\ჟურნალი\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18977694-BBBC-4CE2-9970-32B7A7E35CF2}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBD158D9-70DA-442B-AD74-59ABFCC7CC83}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-122" yWindow="-122" windowWidth="29045" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="51">
   <si>
     <t xml:space="preserve">პროგრამა                     </t>
   </si>
@@ -387,6 +387,9 @@
   </si>
   <si>
     <t>მოდული:  ვერსიების კონტროლი git ტექნოლოგიის გამოყენებით; N 06.1.1.7</t>
+  </si>
+  <si>
+    <t>სტატუსი შეუწყდა 09.07.2026-დან</t>
   </si>
 </sst>
 </file>
@@ -678,7 +681,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -729,6 +732,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -777,6 +789,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -815,9 +830,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1046,43 +1058,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="40"/>
-      <c r="D1" s="41"/>
-      <c r="F1" s="25">
+      <c r="A1" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="44"/>
+      <c r="D1" s="45"/>
+      <c r="F1" s="28">
         <v>4</v>
       </c>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="37">
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="40">
         <v>2</v>
       </c>
-      <c r="K1" s="38"/>
-      <c r="L1" s="37">
+      <c r="K1" s="42"/>
+      <c r="L1" s="40">
         <v>5</v>
       </c>
-      <c r="M1" s="51"/>
-      <c r="N1" s="51"/>
-      <c r="O1" s="51"/>
-      <c r="P1" s="38"/>
-      <c r="Q1" s="37">
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+      <c r="P1" s="42"/>
+      <c r="Q1" s="40">
         <v>5</v>
       </c>
-      <c r="R1" s="51"/>
-      <c r="S1" s="51"/>
-      <c r="T1" s="51"/>
-      <c r="U1" s="38"/>
-      <c r="V1" s="17"/>
-      <c r="W1" s="17"/>
-      <c r="X1" s="17"/>
-      <c r="Y1" s="17"/>
-      <c r="Z1" s="17"/>
+      <c r="R1" s="41"/>
+      <c r="S1" s="41"/>
+      <c r="T1" s="41"/>
+      <c r="U1" s="42"/>
+      <c r="V1" s="40">
+        <v>5</v>
+      </c>
+      <c r="W1" s="41"/>
+      <c r="X1" s="41"/>
+      <c r="Y1" s="41"/>
+      <c r="Z1" s="42"/>
       <c r="AA1" s="17"/>
       <c r="AB1" s="17"/>
       <c r="AC1" s="18"/>
@@ -1139,877 +1153,887 @@
       <c r="CB1" s="17"/>
     </row>
     <row r="2" spans="1:85" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="39"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="44" t="s">
+      <c r="A2" s="43"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="33">
+      <c r="F2" s="36">
         <v>46202</v>
       </c>
-      <c r="G2" s="33">
+      <c r="G2" s="36">
         <v>46202</v>
       </c>
-      <c r="H2" s="33">
+      <c r="H2" s="36">
         <v>46202</v>
       </c>
-      <c r="I2" s="33">
+      <c r="I2" s="36">
         <v>46202</v>
       </c>
-      <c r="J2" s="33">
+      <c r="J2" s="36">
         <v>46206</v>
       </c>
-      <c r="K2" s="33">
+      <c r="K2" s="36">
         <v>46206</v>
       </c>
-      <c r="L2" s="33">
+      <c r="L2" s="36">
         <v>46209</v>
       </c>
-      <c r="M2" s="33">
+      <c r="M2" s="36">
         <v>46209</v>
       </c>
-      <c r="N2" s="33">
+      <c r="N2" s="36">
         <v>46209</v>
       </c>
-      <c r="O2" s="33">
+      <c r="O2" s="36">
         <v>46209</v>
       </c>
-      <c r="P2" s="33">
+      <c r="P2" s="36">
         <v>46209</v>
       </c>
-      <c r="Q2" s="33">
+      <c r="Q2" s="36">
         <v>46216</v>
       </c>
-      <c r="R2" s="33">
+      <c r="R2" s="36">
         <v>46216</v>
       </c>
-      <c r="S2" s="33">
+      <c r="S2" s="36">
         <v>46216</v>
       </c>
-      <c r="T2" s="33">
+      <c r="T2" s="36">
         <v>46216</v>
       </c>
-      <c r="U2" s="33">
+      <c r="U2" s="36">
         <v>46216</v>
       </c>
-      <c r="V2" s="33"/>
-      <c r="W2" s="33"/>
-      <c r="X2" s="33"/>
-      <c r="Y2" s="33"/>
-      <c r="Z2" s="33"/>
-      <c r="AA2" s="33"/>
-      <c r="AB2" s="33"/>
-      <c r="AC2" s="33"/>
-      <c r="AD2" s="33"/>
-      <c r="AE2" s="33"/>
-      <c r="AF2" s="33"/>
-      <c r="AG2" s="33"/>
-      <c r="AH2" s="33"/>
-      <c r="AI2" s="33"/>
-      <c r="AJ2" s="33"/>
-      <c r="AK2" s="33"/>
-      <c r="AL2" s="33"/>
-      <c r="AM2" s="33"/>
-      <c r="AN2" s="33"/>
-      <c r="AO2" s="33"/>
-      <c r="AP2" s="33"/>
-      <c r="AQ2" s="33"/>
-      <c r="AR2" s="33"/>
-      <c r="AS2" s="33"/>
-      <c r="AT2" s="33"/>
-      <c r="AU2" s="33"/>
-      <c r="AV2" s="33"/>
-      <c r="AW2" s="33"/>
-      <c r="AX2" s="33"/>
-      <c r="AY2" s="33"/>
-      <c r="AZ2" s="33"/>
-      <c r="BA2" s="33"/>
-      <c r="BB2" s="33"/>
-      <c r="BC2" s="33"/>
-      <c r="BD2" s="33"/>
-      <c r="BE2" s="33"/>
-      <c r="BF2" s="33"/>
-      <c r="BG2" s="33"/>
-      <c r="BH2" s="33"/>
-      <c r="BI2" s="33"/>
-      <c r="BJ2" s="33"/>
-      <c r="BK2" s="33"/>
-      <c r="BL2" s="33"/>
-      <c r="BM2" s="33"/>
-      <c r="BN2" s="33"/>
-      <c r="BO2" s="33"/>
-      <c r="BP2" s="33"/>
-      <c r="BQ2" s="33"/>
-      <c r="BR2" s="33"/>
-      <c r="BS2" s="33"/>
-      <c r="BT2" s="33"/>
-      <c r="BU2" s="33"/>
-      <c r="BV2" s="33"/>
-      <c r="BW2" s="33"/>
-      <c r="BX2" s="33"/>
-      <c r="BY2" s="33"/>
-      <c r="BZ2" s="33"/>
-      <c r="CA2" s="33"/>
-      <c r="CB2" s="33"/>
+      <c r="V2" s="36">
+        <v>46223</v>
+      </c>
+      <c r="W2" s="36">
+        <v>46223</v>
+      </c>
+      <c r="X2" s="36">
+        <v>46223</v>
+      </c>
+      <c r="Y2" s="36">
+        <v>46223</v>
+      </c>
+      <c r="Z2" s="36">
+        <v>46223</v>
+      </c>
+      <c r="AA2" s="36"/>
+      <c r="AB2" s="36"/>
+      <c r="AC2" s="36"/>
+      <c r="AD2" s="36"/>
+      <c r="AE2" s="36"/>
+      <c r="AF2" s="36"/>
+      <c r="AG2" s="36"/>
+      <c r="AH2" s="36"/>
+      <c r="AI2" s="36"/>
+      <c r="AJ2" s="36"/>
+      <c r="AK2" s="36"/>
+      <c r="AL2" s="36"/>
+      <c r="AM2" s="36"/>
+      <c r="AN2" s="36"/>
+      <c r="AO2" s="36"/>
+      <c r="AP2" s="36"/>
+      <c r="AQ2" s="36"/>
+      <c r="AR2" s="36"/>
+      <c r="AS2" s="36"/>
+      <c r="AT2" s="36"/>
+      <c r="AU2" s="36"/>
+      <c r="AV2" s="36"/>
+      <c r="AW2" s="36"/>
+      <c r="AX2" s="36"/>
+      <c r="AY2" s="36"/>
+      <c r="AZ2" s="36"/>
+      <c r="BA2" s="36"/>
+      <c r="BB2" s="36"/>
+      <c r="BC2" s="36"/>
+      <c r="BD2" s="36"/>
+      <c r="BE2" s="36"/>
+      <c r="BF2" s="36"/>
+      <c r="BG2" s="36"/>
+      <c r="BH2" s="36"/>
+      <c r="BI2" s="36"/>
+      <c r="BJ2" s="36"/>
+      <c r="BK2" s="36"/>
+      <c r="BL2" s="36"/>
+      <c r="BM2" s="36"/>
+      <c r="BN2" s="36"/>
+      <c r="BO2" s="36"/>
+      <c r="BP2" s="36"/>
+      <c r="BQ2" s="36"/>
+      <c r="BR2" s="36"/>
+      <c r="BS2" s="36"/>
+      <c r="BT2" s="36"/>
+      <c r="BU2" s="36"/>
+      <c r="BV2" s="36"/>
+      <c r="BW2" s="36"/>
+      <c r="BX2" s="36"/>
+      <c r="BY2" s="36"/>
+      <c r="BZ2" s="36"/>
+      <c r="CA2" s="36"/>
+      <c r="CB2" s="36"/>
     </row>
     <row r="3" spans="1:85" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="51" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="33"/>
-      <c r="J3" s="33"/>
-      <c r="K3" s="33"/>
-      <c r="L3" s="33"/>
-      <c r="M3" s="33"/>
-      <c r="N3" s="33"/>
-      <c r="O3" s="33"/>
-      <c r="P3" s="33"/>
-      <c r="Q3" s="33"/>
-      <c r="R3" s="33"/>
-      <c r="S3" s="33"/>
-      <c r="T3" s="33"/>
-      <c r="U3" s="33"/>
-      <c r="V3" s="33"/>
-      <c r="W3" s="33"/>
-      <c r="X3" s="33"/>
-      <c r="Y3" s="33"/>
-      <c r="Z3" s="33"/>
-      <c r="AA3" s="33"/>
-      <c r="AB3" s="33"/>
-      <c r="AC3" s="33"/>
-      <c r="AD3" s="33"/>
-      <c r="AE3" s="33"/>
-      <c r="AF3" s="33"/>
-      <c r="AG3" s="33"/>
-      <c r="AH3" s="33"/>
-      <c r="AI3" s="33"/>
-      <c r="AJ3" s="33"/>
-      <c r="AK3" s="33"/>
-      <c r="AL3" s="33"/>
-      <c r="AM3" s="33"/>
-      <c r="AN3" s="33"/>
-      <c r="AO3" s="33"/>
-      <c r="AP3" s="33"/>
-      <c r="AQ3" s="33"/>
-      <c r="AR3" s="33"/>
-      <c r="AS3" s="33"/>
-      <c r="AT3" s="33"/>
-      <c r="AU3" s="33"/>
-      <c r="AV3" s="33"/>
-      <c r="AW3" s="33"/>
-      <c r="AX3" s="33"/>
-      <c r="AY3" s="33"/>
-      <c r="AZ3" s="33"/>
-      <c r="BA3" s="33"/>
-      <c r="BB3" s="33"/>
-      <c r="BC3" s="33"/>
-      <c r="BD3" s="33"/>
-      <c r="BE3" s="33"/>
-      <c r="BF3" s="33"/>
-      <c r="BG3" s="33"/>
-      <c r="BH3" s="33"/>
-      <c r="BI3" s="33"/>
-      <c r="BJ3" s="33"/>
-      <c r="BK3" s="33"/>
-      <c r="BL3" s="33"/>
-      <c r="BM3" s="33"/>
-      <c r="BN3" s="33"/>
-      <c r="BO3" s="33"/>
-      <c r="BP3" s="33"/>
-      <c r="BQ3" s="33"/>
-      <c r="BR3" s="33"/>
-      <c r="BS3" s="33"/>
-      <c r="BT3" s="33"/>
-      <c r="BU3" s="33"/>
-      <c r="BV3" s="33"/>
-      <c r="BW3" s="33"/>
-      <c r="BX3" s="33"/>
-      <c r="BY3" s="33"/>
-      <c r="BZ3" s="33"/>
-      <c r="CA3" s="33"/>
-      <c r="CB3" s="33"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="36"/>
+      <c r="J3" s="36"/>
+      <c r="K3" s="36"/>
+      <c r="L3" s="36"/>
+      <c r="M3" s="36"/>
+      <c r="N3" s="36"/>
+      <c r="O3" s="36"/>
+      <c r="P3" s="36"/>
+      <c r="Q3" s="36"/>
+      <c r="R3" s="36"/>
+      <c r="S3" s="36"/>
+      <c r="T3" s="36"/>
+      <c r="U3" s="36"/>
+      <c r="V3" s="36"/>
+      <c r="W3" s="36"/>
+      <c r="X3" s="36"/>
+      <c r="Y3" s="36"/>
+      <c r="Z3" s="36"/>
+      <c r="AA3" s="36"/>
+      <c r="AB3" s="36"/>
+      <c r="AC3" s="36"/>
+      <c r="AD3" s="36"/>
+      <c r="AE3" s="36"/>
+      <c r="AF3" s="36"/>
+      <c r="AG3" s="36"/>
+      <c r="AH3" s="36"/>
+      <c r="AI3" s="36"/>
+      <c r="AJ3" s="36"/>
+      <c r="AK3" s="36"/>
+      <c r="AL3" s="36"/>
+      <c r="AM3" s="36"/>
+      <c r="AN3" s="36"/>
+      <c r="AO3" s="36"/>
+      <c r="AP3" s="36"/>
+      <c r="AQ3" s="36"/>
+      <c r="AR3" s="36"/>
+      <c r="AS3" s="36"/>
+      <c r="AT3" s="36"/>
+      <c r="AU3" s="36"/>
+      <c r="AV3" s="36"/>
+      <c r="AW3" s="36"/>
+      <c r="AX3" s="36"/>
+      <c r="AY3" s="36"/>
+      <c r="AZ3" s="36"/>
+      <c r="BA3" s="36"/>
+      <c r="BB3" s="36"/>
+      <c r="BC3" s="36"/>
+      <c r="BD3" s="36"/>
+      <c r="BE3" s="36"/>
+      <c r="BF3" s="36"/>
+      <c r="BG3" s="36"/>
+      <c r="BH3" s="36"/>
+      <c r="BI3" s="36"/>
+      <c r="BJ3" s="36"/>
+      <c r="BK3" s="36"/>
+      <c r="BL3" s="36"/>
+      <c r="BM3" s="36"/>
+      <c r="BN3" s="36"/>
+      <c r="BO3" s="36"/>
+      <c r="BP3" s="36"/>
+      <c r="BQ3" s="36"/>
+      <c r="BR3" s="36"/>
+      <c r="BS3" s="36"/>
+      <c r="BT3" s="36"/>
+      <c r="BU3" s="36"/>
+      <c r="BV3" s="36"/>
+      <c r="BW3" s="36"/>
+      <c r="BX3" s="36"/>
+      <c r="BY3" s="36"/>
+      <c r="BZ3" s="36"/>
+      <c r="CA3" s="36"/>
+      <c r="CB3" s="36"/>
     </row>
     <row r="4" spans="1:85" ht="24.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="47" t="s">
+      <c r="A4" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="47"/>
-      <c r="C4" s="48" t="s">
+      <c r="B4" s="51"/>
+      <c r="C4" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="32"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="33"/>
-      <c r="K4" s="33"/>
-      <c r="L4" s="33"/>
-      <c r="M4" s="33"/>
-      <c r="N4" s="33"/>
-      <c r="O4" s="33"/>
-      <c r="P4" s="33"/>
-      <c r="Q4" s="33"/>
-      <c r="R4" s="33"/>
-      <c r="S4" s="33"/>
-      <c r="T4" s="33"/>
-      <c r="U4" s="33"/>
-      <c r="V4" s="33"/>
-      <c r="W4" s="33"/>
-      <c r="X4" s="33"/>
-      <c r="Y4" s="33"/>
-      <c r="Z4" s="33"/>
-      <c r="AA4" s="33"/>
-      <c r="AB4" s="33"/>
-      <c r="AC4" s="33"/>
-      <c r="AD4" s="33"/>
-      <c r="AE4" s="33"/>
-      <c r="AF4" s="33"/>
-      <c r="AG4" s="33"/>
-      <c r="AH4" s="33"/>
-      <c r="AI4" s="33"/>
-      <c r="AJ4" s="33"/>
-      <c r="AK4" s="33"/>
-      <c r="AL4" s="33"/>
-      <c r="AM4" s="33"/>
-      <c r="AN4" s="33"/>
-      <c r="AO4" s="33"/>
-      <c r="AP4" s="33"/>
-      <c r="AQ4" s="33"/>
-      <c r="AR4" s="33"/>
-      <c r="AS4" s="33"/>
-      <c r="AT4" s="33"/>
-      <c r="AU4" s="33"/>
-      <c r="AV4" s="33"/>
-      <c r="AW4" s="33"/>
-      <c r="AX4" s="33"/>
-      <c r="AY4" s="33"/>
-      <c r="AZ4" s="33"/>
-      <c r="BA4" s="33"/>
-      <c r="BB4" s="33"/>
-      <c r="BC4" s="33"/>
-      <c r="BD4" s="33"/>
-      <c r="BE4" s="33"/>
-      <c r="BF4" s="33"/>
-      <c r="BG4" s="33"/>
-      <c r="BH4" s="33"/>
-      <c r="BI4" s="33"/>
-      <c r="BJ4" s="33"/>
-      <c r="BK4" s="33"/>
-      <c r="BL4" s="33"/>
-      <c r="BM4" s="33"/>
-      <c r="BN4" s="33"/>
-      <c r="BO4" s="33"/>
-      <c r="BP4" s="33"/>
-      <c r="BQ4" s="33"/>
-      <c r="BR4" s="33"/>
-      <c r="BS4" s="33"/>
-      <c r="BT4" s="33"/>
-      <c r="BU4" s="33"/>
-      <c r="BV4" s="33"/>
-      <c r="BW4" s="33"/>
-      <c r="BX4" s="33"/>
-      <c r="BY4" s="33"/>
-      <c r="BZ4" s="33"/>
-      <c r="CA4" s="33"/>
-      <c r="CB4" s="33"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="36"/>
+      <c r="K4" s="36"/>
+      <c r="L4" s="36"/>
+      <c r="M4" s="36"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
+      <c r="S4" s="36"/>
+      <c r="T4" s="36"/>
+      <c r="U4" s="36"/>
+      <c r="V4" s="36"/>
+      <c r="W4" s="36"/>
+      <c r="X4" s="36"/>
+      <c r="Y4" s="36"/>
+      <c r="Z4" s="36"/>
+      <c r="AA4" s="36"/>
+      <c r="AB4" s="36"/>
+      <c r="AC4" s="36"/>
+      <c r="AD4" s="36"/>
+      <c r="AE4" s="36"/>
+      <c r="AF4" s="36"/>
+      <c r="AG4" s="36"/>
+      <c r="AH4" s="36"/>
+      <c r="AI4" s="36"/>
+      <c r="AJ4" s="36"/>
+      <c r="AK4" s="36"/>
+      <c r="AL4" s="36"/>
+      <c r="AM4" s="36"/>
+      <c r="AN4" s="36"/>
+      <c r="AO4" s="36"/>
+      <c r="AP4" s="36"/>
+      <c r="AQ4" s="36"/>
+      <c r="AR4" s="36"/>
+      <c r="AS4" s="36"/>
+      <c r="AT4" s="36"/>
+      <c r="AU4" s="36"/>
+      <c r="AV4" s="36"/>
+      <c r="AW4" s="36"/>
+      <c r="AX4" s="36"/>
+      <c r="AY4" s="36"/>
+      <c r="AZ4" s="36"/>
+      <c r="BA4" s="36"/>
+      <c r="BB4" s="36"/>
+      <c r="BC4" s="36"/>
+      <c r="BD4" s="36"/>
+      <c r="BE4" s="36"/>
+      <c r="BF4" s="36"/>
+      <c r="BG4" s="36"/>
+      <c r="BH4" s="36"/>
+      <c r="BI4" s="36"/>
+      <c r="BJ4" s="36"/>
+      <c r="BK4" s="36"/>
+      <c r="BL4" s="36"/>
+      <c r="BM4" s="36"/>
+      <c r="BN4" s="36"/>
+      <c r="BO4" s="36"/>
+      <c r="BP4" s="36"/>
+      <c r="BQ4" s="36"/>
+      <c r="BR4" s="36"/>
+      <c r="BS4" s="36"/>
+      <c r="BT4" s="36"/>
+      <c r="BU4" s="36"/>
+      <c r="BV4" s="36"/>
+      <c r="BW4" s="36"/>
+      <c r="BX4" s="36"/>
+      <c r="BY4" s="36"/>
+      <c r="BZ4" s="36"/>
+      <c r="CA4" s="36"/>
+      <c r="CB4" s="36"/>
     </row>
     <row r="5" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="49" t="s">
+      <c r="A5" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="49"/>
-      <c r="C5" s="35">
+      <c r="B5" s="53"/>
+      <c r="C5" s="38">
         <v>60</v>
       </c>
-      <c r="D5" s="36"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="33"/>
-      <c r="H5" s="33"/>
-      <c r="I5" s="33"/>
-      <c r="J5" s="33"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="33"/>
-      <c r="M5" s="33"/>
-      <c r="N5" s="33"/>
-      <c r="O5" s="33"/>
-      <c r="P5" s="33"/>
-      <c r="Q5" s="33"/>
-      <c r="R5" s="33"/>
-      <c r="S5" s="33"/>
-      <c r="T5" s="33"/>
-      <c r="U5" s="33"/>
-      <c r="V5" s="33"/>
-      <c r="W5" s="33"/>
-      <c r="X5" s="33"/>
-      <c r="Y5" s="33"/>
-      <c r="Z5" s="33"/>
-      <c r="AA5" s="33"/>
-      <c r="AB5" s="33"/>
-      <c r="AC5" s="33"/>
-      <c r="AD5" s="33"/>
-      <c r="AE5" s="33"/>
-      <c r="AF5" s="33"/>
-      <c r="AG5" s="33"/>
-      <c r="AH5" s="33"/>
-      <c r="AI5" s="33"/>
-      <c r="AJ5" s="33"/>
-      <c r="AK5" s="33"/>
-      <c r="AL5" s="33"/>
-      <c r="AM5" s="33"/>
-      <c r="AN5" s="33"/>
-      <c r="AO5" s="33"/>
-      <c r="AP5" s="33"/>
-      <c r="AQ5" s="33"/>
-      <c r="AR5" s="33"/>
-      <c r="AS5" s="33"/>
-      <c r="AT5" s="33"/>
-      <c r="AU5" s="33"/>
-      <c r="AV5" s="33"/>
-      <c r="AW5" s="33"/>
-      <c r="AX5" s="33"/>
-      <c r="AY5" s="33"/>
-      <c r="AZ5" s="33"/>
-      <c r="BA5" s="33"/>
-      <c r="BB5" s="33"/>
-      <c r="BC5" s="33"/>
-      <c r="BD5" s="33"/>
-      <c r="BE5" s="33"/>
-      <c r="BF5" s="33"/>
-      <c r="BG5" s="33"/>
-      <c r="BH5" s="33"/>
-      <c r="BI5" s="33"/>
-      <c r="BJ5" s="33"/>
-      <c r="BK5" s="33"/>
-      <c r="BL5" s="33"/>
-      <c r="BM5" s="33"/>
-      <c r="BN5" s="33"/>
-      <c r="BO5" s="33"/>
-      <c r="BP5" s="33"/>
-      <c r="BQ5" s="33"/>
-      <c r="BR5" s="33"/>
-      <c r="BS5" s="33"/>
-      <c r="BT5" s="33"/>
-      <c r="BU5" s="33"/>
-      <c r="BV5" s="33"/>
-      <c r="BW5" s="33"/>
-      <c r="BX5" s="33"/>
-      <c r="BY5" s="33"/>
-      <c r="BZ5" s="33"/>
-      <c r="CA5" s="33"/>
-      <c r="CB5" s="33"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="36"/>
+      <c r="J5" s="36"/>
+      <c r="K5" s="36"/>
+      <c r="L5" s="36"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="36"/>
+      <c r="S5" s="36"/>
+      <c r="T5" s="36"/>
+      <c r="U5" s="36"/>
+      <c r="V5" s="36"/>
+      <c r="W5" s="36"/>
+      <c r="X5" s="36"/>
+      <c r="Y5" s="36"/>
+      <c r="Z5" s="36"/>
+      <c r="AA5" s="36"/>
+      <c r="AB5" s="36"/>
+      <c r="AC5" s="36"/>
+      <c r="AD5" s="36"/>
+      <c r="AE5" s="36"/>
+      <c r="AF5" s="36"/>
+      <c r="AG5" s="36"/>
+      <c r="AH5" s="36"/>
+      <c r="AI5" s="36"/>
+      <c r="AJ5" s="36"/>
+      <c r="AK5" s="36"/>
+      <c r="AL5" s="36"/>
+      <c r="AM5" s="36"/>
+      <c r="AN5" s="36"/>
+      <c r="AO5" s="36"/>
+      <c r="AP5" s="36"/>
+      <c r="AQ5" s="36"/>
+      <c r="AR5" s="36"/>
+      <c r="AS5" s="36"/>
+      <c r="AT5" s="36"/>
+      <c r="AU5" s="36"/>
+      <c r="AV5" s="36"/>
+      <c r="AW5" s="36"/>
+      <c r="AX5" s="36"/>
+      <c r="AY5" s="36"/>
+      <c r="AZ5" s="36"/>
+      <c r="BA5" s="36"/>
+      <c r="BB5" s="36"/>
+      <c r="BC5" s="36"/>
+      <c r="BD5" s="36"/>
+      <c r="BE5" s="36"/>
+      <c r="BF5" s="36"/>
+      <c r="BG5" s="36"/>
+      <c r="BH5" s="36"/>
+      <c r="BI5" s="36"/>
+      <c r="BJ5" s="36"/>
+      <c r="BK5" s="36"/>
+      <c r="BL5" s="36"/>
+      <c r="BM5" s="36"/>
+      <c r="BN5" s="36"/>
+      <c r="BO5" s="36"/>
+      <c r="BP5" s="36"/>
+      <c r="BQ5" s="36"/>
+      <c r="BR5" s="36"/>
+      <c r="BS5" s="36"/>
+      <c r="BT5" s="36"/>
+      <c r="BU5" s="36"/>
+      <c r="BV5" s="36"/>
+      <c r="BW5" s="36"/>
+      <c r="BX5" s="36"/>
+      <c r="BY5" s="36"/>
+      <c r="BZ5" s="36"/>
+      <c r="CA5" s="36"/>
+      <c r="CB5" s="36"/>
     </row>
     <row r="6" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="49" t="s">
+      <c r="A6" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="49"/>
-      <c r="C6" s="35">
+      <c r="B6" s="53"/>
+      <c r="C6" s="38">
         <v>6</v>
       </c>
-      <c r="D6" s="36"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="33"/>
-      <c r="K6" s="33"/>
-      <c r="L6" s="33"/>
-      <c r="M6" s="33"/>
-      <c r="N6" s="33"/>
-      <c r="O6" s="33"/>
-      <c r="P6" s="33"/>
-      <c r="Q6" s="33"/>
-      <c r="R6" s="33"/>
-      <c r="S6" s="33"/>
-      <c r="T6" s="33"/>
-      <c r="U6" s="33"/>
-      <c r="V6" s="33"/>
-      <c r="W6" s="33"/>
-      <c r="X6" s="33"/>
-      <c r="Y6" s="33"/>
-      <c r="Z6" s="33"/>
-      <c r="AA6" s="33"/>
-      <c r="AB6" s="33"/>
-      <c r="AC6" s="33"/>
-      <c r="AD6" s="33"/>
-      <c r="AE6" s="33"/>
-      <c r="AF6" s="33"/>
-      <c r="AG6" s="33"/>
-      <c r="AH6" s="33"/>
-      <c r="AI6" s="33"/>
-      <c r="AJ6" s="33"/>
-      <c r="AK6" s="33"/>
-      <c r="AL6" s="33"/>
-      <c r="AM6" s="33"/>
-      <c r="AN6" s="33"/>
-      <c r="AO6" s="33"/>
-      <c r="AP6" s="33"/>
-      <c r="AQ6" s="33"/>
-      <c r="AR6" s="33"/>
-      <c r="AS6" s="33"/>
-      <c r="AT6" s="33"/>
-      <c r="AU6" s="33"/>
-      <c r="AV6" s="33"/>
-      <c r="AW6" s="33"/>
-      <c r="AX6" s="33"/>
-      <c r="AY6" s="33"/>
-      <c r="AZ6" s="33"/>
-      <c r="BA6" s="33"/>
-      <c r="BB6" s="33"/>
-      <c r="BC6" s="33"/>
-      <c r="BD6" s="33"/>
-      <c r="BE6" s="33"/>
-      <c r="BF6" s="33"/>
-      <c r="BG6" s="33"/>
-      <c r="BH6" s="33"/>
-      <c r="BI6" s="33"/>
-      <c r="BJ6" s="33"/>
-      <c r="BK6" s="33"/>
-      <c r="BL6" s="33"/>
-      <c r="BM6" s="33"/>
-      <c r="BN6" s="33"/>
-      <c r="BO6" s="33"/>
-      <c r="BP6" s="33"/>
-      <c r="BQ6" s="33"/>
-      <c r="BR6" s="33"/>
-      <c r="BS6" s="33"/>
-      <c r="BT6" s="33"/>
-      <c r="BU6" s="33"/>
-      <c r="BV6" s="33"/>
-      <c r="BW6" s="33"/>
-      <c r="BX6" s="33"/>
-      <c r="BY6" s="33"/>
-      <c r="BZ6" s="33"/>
-      <c r="CA6" s="33"/>
-      <c r="CB6" s="33"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="36"/>
+      <c r="H6" s="36"/>
+      <c r="I6" s="36"/>
+      <c r="J6" s="36"/>
+      <c r="K6" s="36"/>
+      <c r="L6" s="36"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
+      <c r="S6" s="36"/>
+      <c r="T6" s="36"/>
+      <c r="U6" s="36"/>
+      <c r="V6" s="36"/>
+      <c r="W6" s="36"/>
+      <c r="X6" s="36"/>
+      <c r="Y6" s="36"/>
+      <c r="Z6" s="36"/>
+      <c r="AA6" s="36"/>
+      <c r="AB6" s="36"/>
+      <c r="AC6" s="36"/>
+      <c r="AD6" s="36"/>
+      <c r="AE6" s="36"/>
+      <c r="AF6" s="36"/>
+      <c r="AG6" s="36"/>
+      <c r="AH6" s="36"/>
+      <c r="AI6" s="36"/>
+      <c r="AJ6" s="36"/>
+      <c r="AK6" s="36"/>
+      <c r="AL6" s="36"/>
+      <c r="AM6" s="36"/>
+      <c r="AN6" s="36"/>
+      <c r="AO6" s="36"/>
+      <c r="AP6" s="36"/>
+      <c r="AQ6" s="36"/>
+      <c r="AR6" s="36"/>
+      <c r="AS6" s="36"/>
+      <c r="AT6" s="36"/>
+      <c r="AU6" s="36"/>
+      <c r="AV6" s="36"/>
+      <c r="AW6" s="36"/>
+      <c r="AX6" s="36"/>
+      <c r="AY6" s="36"/>
+      <c r="AZ6" s="36"/>
+      <c r="BA6" s="36"/>
+      <c r="BB6" s="36"/>
+      <c r="BC6" s="36"/>
+      <c r="BD6" s="36"/>
+      <c r="BE6" s="36"/>
+      <c r="BF6" s="36"/>
+      <c r="BG6" s="36"/>
+      <c r="BH6" s="36"/>
+      <c r="BI6" s="36"/>
+      <c r="BJ6" s="36"/>
+      <c r="BK6" s="36"/>
+      <c r="BL6" s="36"/>
+      <c r="BM6" s="36"/>
+      <c r="BN6" s="36"/>
+      <c r="BO6" s="36"/>
+      <c r="BP6" s="36"/>
+      <c r="BQ6" s="36"/>
+      <c r="BR6" s="36"/>
+      <c r="BS6" s="36"/>
+      <c r="BT6" s="36"/>
+      <c r="BU6" s="36"/>
+      <c r="BV6" s="36"/>
+      <c r="BW6" s="36"/>
+      <c r="BX6" s="36"/>
+      <c r="BY6" s="36"/>
+      <c r="BZ6" s="36"/>
+      <c r="CA6" s="36"/>
+      <c r="CB6" s="36"/>
     </row>
     <row r="7" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="50" t="s">
+      <c r="A7" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="50"/>
-      <c r="C7" s="35">
+      <c r="B7" s="54"/>
+      <c r="C7" s="38">
         <v>9</v>
       </c>
-      <c r="D7" s="36"/>
-      <c r="E7" s="46"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="34"/>
-      <c r="I7" s="34"/>
-      <c r="J7" s="34"/>
-      <c r="K7" s="34"/>
-      <c r="L7" s="34"/>
-      <c r="M7" s="34"/>
-      <c r="N7" s="34"/>
-      <c r="O7" s="34"/>
-      <c r="P7" s="34"/>
-      <c r="Q7" s="34"/>
-      <c r="R7" s="34"/>
-      <c r="S7" s="34"/>
-      <c r="T7" s="34"/>
-      <c r="U7" s="34"/>
-      <c r="V7" s="34"/>
-      <c r="W7" s="34"/>
-      <c r="X7" s="34"/>
-      <c r="Y7" s="34"/>
-      <c r="Z7" s="34"/>
-      <c r="AA7" s="34"/>
-      <c r="AB7" s="34"/>
-      <c r="AC7" s="34"/>
-      <c r="AD7" s="34"/>
-      <c r="AE7" s="34"/>
-      <c r="AF7" s="34"/>
-      <c r="AG7" s="34"/>
-      <c r="AH7" s="34"/>
-      <c r="AI7" s="34"/>
-      <c r="AJ7" s="34"/>
-      <c r="AK7" s="34"/>
-      <c r="AL7" s="34"/>
-      <c r="AM7" s="34"/>
-      <c r="AN7" s="34"/>
-      <c r="AO7" s="34"/>
-      <c r="AP7" s="34"/>
-      <c r="AQ7" s="34"/>
-      <c r="AR7" s="34"/>
-      <c r="AS7" s="34"/>
-      <c r="AT7" s="34"/>
-      <c r="AU7" s="34"/>
-      <c r="AV7" s="34"/>
-      <c r="AW7" s="34"/>
-      <c r="AX7" s="34"/>
-      <c r="AY7" s="34"/>
-      <c r="AZ7" s="34"/>
-      <c r="BA7" s="34"/>
-      <c r="BB7" s="34"/>
-      <c r="BC7" s="34"/>
-      <c r="BD7" s="34"/>
-      <c r="BE7" s="34"/>
-      <c r="BF7" s="34"/>
-      <c r="BG7" s="34"/>
-      <c r="BH7" s="34"/>
-      <c r="BI7" s="34"/>
-      <c r="BJ7" s="34"/>
-      <c r="BK7" s="34"/>
-      <c r="BL7" s="34"/>
-      <c r="BM7" s="34"/>
-      <c r="BN7" s="34"/>
-      <c r="BO7" s="34"/>
-      <c r="BP7" s="34"/>
-      <c r="BQ7" s="34"/>
-      <c r="BR7" s="34"/>
-      <c r="BS7" s="34"/>
-      <c r="BT7" s="34"/>
-      <c r="BU7" s="34"/>
-      <c r="BV7" s="34"/>
-      <c r="BW7" s="34"/>
-      <c r="BX7" s="34"/>
-      <c r="BY7" s="34"/>
-      <c r="BZ7" s="34"/>
-      <c r="CA7" s="34"/>
-      <c r="CB7" s="34"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="50"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="37"/>
+      <c r="I7" s="37"/>
+      <c r="J7" s="37"/>
+      <c r="K7" s="37"/>
+      <c r="L7" s="37"/>
+      <c r="M7" s="37"/>
+      <c r="N7" s="37"/>
+      <c r="O7" s="37"/>
+      <c r="P7" s="37"/>
+      <c r="Q7" s="37"/>
+      <c r="R7" s="37"/>
+      <c r="S7" s="37"/>
+      <c r="T7" s="37"/>
+      <c r="U7" s="37"/>
+      <c r="V7" s="37"/>
+      <c r="W7" s="37"/>
+      <c r="X7" s="37"/>
+      <c r="Y7" s="37"/>
+      <c r="Z7" s="37"/>
+      <c r="AA7" s="37"/>
+      <c r="AB7" s="37"/>
+      <c r="AC7" s="37"/>
+      <c r="AD7" s="37"/>
+      <c r="AE7" s="37"/>
+      <c r="AF7" s="37"/>
+      <c r="AG7" s="37"/>
+      <c r="AH7" s="37"/>
+      <c r="AI7" s="37"/>
+      <c r="AJ7" s="37"/>
+      <c r="AK7" s="37"/>
+      <c r="AL7" s="37"/>
+      <c r="AM7" s="37"/>
+      <c r="AN7" s="37"/>
+      <c r="AO7" s="37"/>
+      <c r="AP7" s="37"/>
+      <c r="AQ7" s="37"/>
+      <c r="AR7" s="37"/>
+      <c r="AS7" s="37"/>
+      <c r="AT7" s="37"/>
+      <c r="AU7" s="37"/>
+      <c r="AV7" s="37"/>
+      <c r="AW7" s="37"/>
+      <c r="AX7" s="37"/>
+      <c r="AY7" s="37"/>
+      <c r="AZ7" s="37"/>
+      <c r="BA7" s="37"/>
+      <c r="BB7" s="37"/>
+      <c r="BC7" s="37"/>
+      <c r="BD7" s="37"/>
+      <c r="BE7" s="37"/>
+      <c r="BF7" s="37"/>
+      <c r="BG7" s="37"/>
+      <c r="BH7" s="37"/>
+      <c r="BI7" s="37"/>
+      <c r="BJ7" s="37"/>
+      <c r="BK7" s="37"/>
+      <c r="BL7" s="37"/>
+      <c r="BM7" s="37"/>
+      <c r="BN7" s="37"/>
+      <c r="BO7" s="37"/>
+      <c r="BP7" s="37"/>
+      <c r="BQ7" s="37"/>
+      <c r="BR7" s="37"/>
+      <c r="BS7" s="37"/>
+      <c r="BT7" s="37"/>
+      <c r="BU7" s="37"/>
+      <c r="BV7" s="37"/>
+      <c r="BW7" s="37"/>
+      <c r="BX7" s="37"/>
+      <c r="BY7" s="37"/>
+      <c r="BZ7" s="37"/>
+      <c r="CA7" s="37"/>
+      <c r="CB7" s="37"/>
     </row>
     <row r="8" spans="1:85" ht="23.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="30"/>
-      <c r="C8" s="31">
+      <c r="B8" s="33"/>
+      <c r="C8" s="34">
         <f>SUM(C5:D7)</f>
         <v>75</v>
       </c>
-      <c r="D8" s="32"/>
+      <c r="D8" s="35"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="22">
-        <v>1</v>
-      </c>
-      <c r="G8" s="22">
+      <c r="F8" s="25">
+        <v>1</v>
+      </c>
+      <c r="G8" s="25">
         <v>2</v>
       </c>
-      <c r="H8" s="22">
+      <c r="H8" s="25">
         <v>3</v>
       </c>
-      <c r="I8" s="22">
+      <c r="I8" s="25">
         <v>4</v>
       </c>
-      <c r="J8" s="22">
+      <c r="J8" s="25">
         <v>5</v>
       </c>
-      <c r="K8" s="22">
+      <c r="K8" s="25">
         <v>6</v>
       </c>
-      <c r="L8" s="22">
+      <c r="L8" s="25">
         <v>7</v>
       </c>
-      <c r="M8" s="22">
+      <c r="M8" s="25">
         <v>8</v>
       </c>
-      <c r="N8" s="22">
+      <c r="N8" s="25">
         <v>9</v>
       </c>
-      <c r="O8" s="22">
+      <c r="O8" s="25">
         <v>10</v>
       </c>
-      <c r="P8" s="22">
+      <c r="P8" s="25">
         <v>11</v>
       </c>
-      <c r="Q8" s="22">
+      <c r="Q8" s="25">
         <v>12</v>
       </c>
-      <c r="R8" s="22">
+      <c r="R8" s="25">
         <v>13</v>
       </c>
-      <c r="S8" s="22">
+      <c r="S8" s="25">
         <v>14</v>
       </c>
-      <c r="T8" s="22">
+      <c r="T8" s="25">
         <v>15</v>
       </c>
-      <c r="U8" s="22">
+      <c r="U8" s="25">
         <v>16</v>
       </c>
-      <c r="V8" s="22">
+      <c r="V8" s="25">
         <v>17</v>
       </c>
-      <c r="W8" s="22">
+      <c r="W8" s="25">
         <v>18</v>
       </c>
-      <c r="X8" s="22">
+      <c r="X8" s="25">
         <v>19</v>
       </c>
-      <c r="Y8" s="22">
+      <c r="Y8" s="25">
         <v>20</v>
       </c>
-      <c r="Z8" s="22">
+      <c r="Z8" s="25">
         <v>21</v>
       </c>
-      <c r="AA8" s="22">
+      <c r="AA8" s="25">
         <v>22</v>
       </c>
-      <c r="AB8" s="22">
+      <c r="AB8" s="25">
         <v>23</v>
       </c>
-      <c r="AC8" s="22">
+      <c r="AC8" s="25">
         <v>24</v>
       </c>
-      <c r="AD8" s="22">
+      <c r="AD8" s="25">
         <v>25</v>
       </c>
-      <c r="AE8" s="22">
+      <c r="AE8" s="25">
         <v>26</v>
       </c>
-      <c r="AF8" s="22">
+      <c r="AF8" s="25">
         <v>27</v>
       </c>
-      <c r="AG8" s="22">
+      <c r="AG8" s="25">
         <v>28</v>
       </c>
-      <c r="AH8" s="22">
+      <c r="AH8" s="25">
         <v>29</v>
       </c>
-      <c r="AI8" s="22">
+      <c r="AI8" s="25">
         <v>30</v>
       </c>
-      <c r="AJ8" s="22">
+      <c r="AJ8" s="25">
         <v>31</v>
       </c>
-      <c r="AK8" s="22">
+      <c r="AK8" s="25">
         <v>32</v>
       </c>
-      <c r="AL8" s="22">
+      <c r="AL8" s="25">
         <v>33</v>
       </c>
-      <c r="AM8" s="22">
+      <c r="AM8" s="25">
         <v>34</v>
       </c>
-      <c r="AN8" s="22">
+      <c r="AN8" s="25">
         <v>35</v>
       </c>
-      <c r="AO8" s="22">
+      <c r="AO8" s="25">
         <v>36</v>
       </c>
-      <c r="AP8" s="22">
+      <c r="AP8" s="25">
         <v>37</v>
       </c>
-      <c r="AQ8" s="22">
+      <c r="AQ8" s="25">
         <v>38</v>
       </c>
-      <c r="AR8" s="22">
+      <c r="AR8" s="25">
         <v>39</v>
       </c>
-      <c r="AS8" s="22">
+      <c r="AS8" s="25">
         <v>40</v>
       </c>
-      <c r="AT8" s="22">
+      <c r="AT8" s="25">
         <v>41</v>
       </c>
-      <c r="AU8" s="22">
+      <c r="AU8" s="25">
         <v>42</v>
       </c>
-      <c r="AV8" s="22">
+      <c r="AV8" s="25">
         <v>43</v>
       </c>
-      <c r="AW8" s="22">
+      <c r="AW8" s="25">
         <v>44</v>
       </c>
-      <c r="AX8" s="22">
+      <c r="AX8" s="25">
         <v>45</v>
       </c>
-      <c r="AY8" s="22">
+      <c r="AY8" s="25">
         <v>46</v>
       </c>
-      <c r="AZ8" s="22">
+      <c r="AZ8" s="25">
         <v>47</v>
       </c>
-      <c r="BA8" s="22">
+      <c r="BA8" s="25">
         <v>48</v>
       </c>
-      <c r="BB8" s="22">
+      <c r="BB8" s="25">
         <v>49</v>
       </c>
-      <c r="BC8" s="22">
+      <c r="BC8" s="25">
         <v>50</v>
       </c>
-      <c r="BD8" s="22">
+      <c r="BD8" s="25">
         <v>51</v>
       </c>
-      <c r="BE8" s="22">
+      <c r="BE8" s="25">
         <v>52</v>
       </c>
-      <c r="BF8" s="22">
+      <c r="BF8" s="25">
         <v>53</v>
       </c>
-      <c r="BG8" s="22">
+      <c r="BG8" s="25">
         <v>54</v>
       </c>
-      <c r="BH8" s="22">
+      <c r="BH8" s="25">
         <v>55</v>
       </c>
-      <c r="BI8" s="22">
+      <c r="BI8" s="25">
         <v>56</v>
       </c>
-      <c r="BJ8" s="22">
+      <c r="BJ8" s="25">
         <v>57</v>
       </c>
-      <c r="BK8" s="22">
+      <c r="BK8" s="25">
         <v>58</v>
       </c>
-      <c r="BL8" s="22">
+      <c r="BL8" s="25">
         <v>59</v>
       </c>
-      <c r="BM8" s="22">
+      <c r="BM8" s="25">
         <v>60</v>
       </c>
-      <c r="BN8" s="22">
+      <c r="BN8" s="25">
         <v>61</v>
       </c>
-      <c r="BO8" s="22">
+      <c r="BO8" s="25">
         <v>62</v>
       </c>
-      <c r="BP8" s="22">
+      <c r="BP8" s="25">
         <v>63</v>
       </c>
-      <c r="BQ8" s="22">
+      <c r="BQ8" s="25">
         <v>64</v>
       </c>
-      <c r="BR8" s="22">
+      <c r="BR8" s="25">
         <v>65</v>
       </c>
-      <c r="BS8" s="22">
+      <c r="BS8" s="25">
         <v>66</v>
       </c>
-      <c r="BT8" s="22">
+      <c r="BT8" s="25">
         <v>67</v>
       </c>
-      <c r="BU8" s="22">
+      <c r="BU8" s="25">
         <v>68</v>
       </c>
-      <c r="BV8" s="22">
+      <c r="BV8" s="25">
         <v>69</v>
       </c>
-      <c r="BW8" s="22">
+      <c r="BW8" s="25">
         <v>70</v>
       </c>
-      <c r="BX8" s="22">
+      <c r="BX8" s="25">
         <v>71</v>
       </c>
-      <c r="BY8" s="22">
+      <c r="BY8" s="25">
         <v>72</v>
       </c>
-      <c r="BZ8" s="22">
+      <c r="BZ8" s="25">
         <v>73</v>
       </c>
-      <c r="CA8" s="22">
+      <c r="CA8" s="25">
         <v>74</v>
       </c>
-      <c r="CB8" s="22">
+      <c r="CB8" s="25">
         <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="28"/>
+      <c r="D9" s="31"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="23"/>
-      <c r="J9" s="23"/>
-      <c r="K9" s="23"/>
-      <c r="L9" s="23"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="23"/>
-      <c r="O9" s="23"/>
-      <c r="P9" s="23"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="23"/>
-      <c r="S9" s="23"/>
-      <c r="T9" s="23"/>
-      <c r="U9" s="23"/>
-      <c r="V9" s="23"/>
-      <c r="W9" s="23"/>
-      <c r="X9" s="23"/>
-      <c r="Y9" s="23"/>
-      <c r="Z9" s="23"/>
-      <c r="AA9" s="23"/>
-      <c r="AB9" s="23"/>
-      <c r="AC9" s="23"/>
-      <c r="AD9" s="23"/>
-      <c r="AE9" s="23"/>
-      <c r="AF9" s="23"/>
-      <c r="AG9" s="23"/>
-      <c r="AH9" s="23"/>
-      <c r="AI9" s="23"/>
-      <c r="AJ9" s="23"/>
-      <c r="AK9" s="23"/>
-      <c r="AL9" s="23"/>
-      <c r="AM9" s="23"/>
-      <c r="AN9" s="23"/>
-      <c r="AO9" s="23"/>
-      <c r="AP9" s="23"/>
-      <c r="AQ9" s="23"/>
-      <c r="AR9" s="23"/>
-      <c r="AS9" s="23"/>
-      <c r="AT9" s="23"/>
-      <c r="AU9" s="23"/>
-      <c r="AV9" s="23"/>
-      <c r="AW9" s="23"/>
-      <c r="AX9" s="23"/>
-      <c r="AY9" s="23"/>
-      <c r="AZ9" s="23"/>
-      <c r="BA9" s="23"/>
-      <c r="BB9" s="23"/>
-      <c r="BC9" s="23"/>
-      <c r="BD9" s="23"/>
-      <c r="BE9" s="23"/>
-      <c r="BF9" s="23"/>
-      <c r="BG9" s="23"/>
-      <c r="BH9" s="23"/>
-      <c r="BI9" s="23"/>
-      <c r="BJ9" s="23"/>
-      <c r="BK9" s="23"/>
-      <c r="BL9" s="23"/>
-      <c r="BM9" s="23"/>
-      <c r="BN9" s="23"/>
-      <c r="BO9" s="23"/>
-      <c r="BP9" s="23"/>
-      <c r="BQ9" s="23"/>
-      <c r="BR9" s="23"/>
-      <c r="BS9" s="23"/>
-      <c r="BT9" s="23"/>
-      <c r="BU9" s="23"/>
-      <c r="BV9" s="23"/>
-      <c r="BW9" s="23"/>
-      <c r="BX9" s="23"/>
-      <c r="BY9" s="23"/>
-      <c r="BZ9" s="23"/>
-      <c r="CA9" s="23"/>
-      <c r="CB9" s="23"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="26"/>
+      <c r="L9" s="26"/>
+      <c r="M9" s="26"/>
+      <c r="N9" s="26"/>
+      <c r="O9" s="26"/>
+      <c r="P9" s="26"/>
+      <c r="Q9" s="26"/>
+      <c r="R9" s="26"/>
+      <c r="S9" s="26"/>
+      <c r="T9" s="26"/>
+      <c r="U9" s="26"/>
+      <c r="V9" s="26"/>
+      <c r="W9" s="26"/>
+      <c r="X9" s="26"/>
+      <c r="Y9" s="26"/>
+      <c r="Z9" s="26"/>
+      <c r="AA9" s="26"/>
+      <c r="AB9" s="26"/>
+      <c r="AC9" s="26"/>
+      <c r="AD9" s="26"/>
+      <c r="AE9" s="26"/>
+      <c r="AF9" s="26"/>
+      <c r="AG9" s="26"/>
+      <c r="AH9" s="26"/>
+      <c r="AI9" s="26"/>
+      <c r="AJ9" s="26"/>
+      <c r="AK9" s="26"/>
+      <c r="AL9" s="26"/>
+      <c r="AM9" s="26"/>
+      <c r="AN9" s="26"/>
+      <c r="AO9" s="26"/>
+      <c r="AP9" s="26"/>
+      <c r="AQ9" s="26"/>
+      <c r="AR9" s="26"/>
+      <c r="AS9" s="26"/>
+      <c r="AT9" s="26"/>
+      <c r="AU9" s="26"/>
+      <c r="AV9" s="26"/>
+      <c r="AW9" s="26"/>
+      <c r="AX9" s="26"/>
+      <c r="AY9" s="26"/>
+      <c r="AZ9" s="26"/>
+      <c r="BA9" s="26"/>
+      <c r="BB9" s="26"/>
+      <c r="BC9" s="26"/>
+      <c r="BD9" s="26"/>
+      <c r="BE9" s="26"/>
+      <c r="BF9" s="26"/>
+      <c r="BG9" s="26"/>
+      <c r="BH9" s="26"/>
+      <c r="BI9" s="26"/>
+      <c r="BJ9" s="26"/>
+      <c r="BK9" s="26"/>
+      <c r="BL9" s="26"/>
+      <c r="BM9" s="26"/>
+      <c r="BN9" s="26"/>
+      <c r="BO9" s="26"/>
+      <c r="BP9" s="26"/>
+      <c r="BQ9" s="26"/>
+      <c r="BR9" s="26"/>
+      <c r="BS9" s="26"/>
+      <c r="BT9" s="26"/>
+      <c r="BU9" s="26"/>
+      <c r="BV9" s="26"/>
+      <c r="BW9" s="26"/>
+      <c r="BX9" s="26"/>
+      <c r="BY9" s="26"/>
+      <c r="BZ9" s="26"/>
+      <c r="CA9" s="26"/>
+      <c r="CB9" s="26"/>
     </row>
     <row r="10" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="27"/>
-      <c r="B10" s="28"/>
+      <c r="A10" s="30"/>
+      <c r="B10" s="31"/>
       <c r="C10" s="6"/>
       <c r="D10" s="4" t="s">
         <v>12</v>
@@ -2439,7 +2463,7 @@
       </c>
       <c r="D13" s="11">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E13" s="12"/>
       <c r="F13" s="8"/>
@@ -2460,11 +2484,21 @@
       <c r="S13" s="8"/>
       <c r="T13" s="8"/>
       <c r="U13" s="8"/>
-      <c r="V13" s="8"/>
-      <c r="W13" s="8"/>
-      <c r="X13" s="8"/>
-      <c r="Y13" s="8"/>
-      <c r="Z13" s="8"/>
+      <c r="V13" s="8">
+        <v>0</v>
+      </c>
+      <c r="W13" s="8">
+        <v>0</v>
+      </c>
+      <c r="X13" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="8">
+        <v>0</v>
+      </c>
       <c r="AA13" s="8"/>
       <c r="AB13" s="8"/>
       <c r="AC13" s="8"/>
@@ -2536,7 +2570,7 @@
       </c>
       <c r="D14" s="11">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E14" s="12"/>
       <c r="F14" s="8">
@@ -2575,8 +2609,12 @@
       <c r="S14" s="8"/>
       <c r="T14" s="8"/>
       <c r="U14" s="8"/>
-      <c r="V14" s="8"/>
-      <c r="W14" s="8"/>
+      <c r="V14" s="8">
+        <v>0</v>
+      </c>
+      <c r="W14" s="8">
+        <v>0</v>
+      </c>
       <c r="X14" s="8"/>
       <c r="Y14" s="8"/>
       <c r="Z14" s="8"/>
@@ -2647,7 +2685,7 @@
       </c>
       <c r="D15" s="11">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E15" s="12"/>
       <c r="F15" s="8">
@@ -2688,11 +2726,21 @@
       <c r="S15" s="8"/>
       <c r="T15" s="8"/>
       <c r="U15" s="8"/>
-      <c r="V15" s="8"/>
-      <c r="W15" s="8"/>
-      <c r="X15" s="8"/>
-      <c r="Y15" s="8"/>
-      <c r="Z15" s="8"/>
+      <c r="V15" s="8">
+        <v>0</v>
+      </c>
+      <c r="W15" s="8">
+        <v>0</v>
+      </c>
+      <c r="X15" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="8">
+        <v>0</v>
+      </c>
       <c r="AA15" s="8"/>
       <c r="AB15" s="8"/>
       <c r="AC15" s="8"/>
@@ -2887,70 +2935,72 @@
       <c r="P17" s="8">
         <v>0</v>
       </c>
-      <c r="Q17" s="8"/>
-      <c r="R17" s="8"/>
-      <c r="S17" s="8"/>
-      <c r="T17" s="8"/>
-      <c r="U17" s="8"/>
-      <c r="V17" s="8"/>
-      <c r="W17" s="8"/>
-      <c r="X17" s="8"/>
-      <c r="Y17" s="8"/>
-      <c r="Z17" s="8"/>
-      <c r="AA17" s="8"/>
-      <c r="AB17" s="8"/>
-      <c r="AC17" s="8"/>
-      <c r="AD17" s="8"/>
-      <c r="AE17" s="8"/>
-      <c r="AF17" s="8"/>
-      <c r="AG17" s="8"/>
-      <c r="AH17" s="8"/>
-      <c r="AI17" s="8"/>
-      <c r="AJ17" s="8"/>
-      <c r="AK17" s="8"/>
-      <c r="AL17" s="8"/>
-      <c r="AM17" s="8"/>
-      <c r="AN17" s="8"/>
-      <c r="AO17" s="8"/>
-      <c r="AP17" s="8"/>
-      <c r="AQ17" s="8"/>
-      <c r="AR17" s="8"/>
-      <c r="AS17" s="8"/>
-      <c r="AT17" s="8"/>
-      <c r="AU17" s="8"/>
-      <c r="AV17" s="8"/>
-      <c r="AW17" s="8"/>
-      <c r="AX17" s="8"/>
-      <c r="AY17" s="8"/>
-      <c r="AZ17" s="8"/>
-      <c r="BA17" s="8"/>
-      <c r="BB17" s="8"/>
-      <c r="BC17" s="8"/>
-      <c r="BD17" s="8"/>
-      <c r="BE17" s="8"/>
-      <c r="BF17" s="8"/>
-      <c r="BG17" s="8"/>
-      <c r="BH17" s="8"/>
-      <c r="BI17" s="8"/>
-      <c r="BJ17" s="8"/>
-      <c r="BK17" s="8"/>
-      <c r="BL17" s="8"/>
-      <c r="BM17" s="8"/>
-      <c r="BN17" s="8"/>
-      <c r="BO17" s="8"/>
-      <c r="BP17" s="8"/>
-      <c r="BQ17" s="8"/>
-      <c r="BR17" s="8"/>
-      <c r="BS17" s="8"/>
-      <c r="BT17" s="8"/>
-      <c r="BU17" s="8"/>
-      <c r="BV17" s="8"/>
-      <c r="BW17" s="8"/>
-      <c r="BX17" s="8"/>
-      <c r="BY17" s="8"/>
-      <c r="BZ17" s="8"/>
-      <c r="CA17" s="8"/>
-      <c r="CB17" s="8"/>
+      <c r="Q17" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="R17" s="23"/>
+      <c r="S17" s="23"/>
+      <c r="T17" s="23"/>
+      <c r="U17" s="23"/>
+      <c r="V17" s="23"/>
+      <c r="W17" s="23"/>
+      <c r="X17" s="23"/>
+      <c r="Y17" s="23"/>
+      <c r="Z17" s="23"/>
+      <c r="AA17" s="23"/>
+      <c r="AB17" s="23"/>
+      <c r="AC17" s="23"/>
+      <c r="AD17" s="23"/>
+      <c r="AE17" s="23"/>
+      <c r="AF17" s="23"/>
+      <c r="AG17" s="23"/>
+      <c r="AH17" s="23"/>
+      <c r="AI17" s="23"/>
+      <c r="AJ17" s="23"/>
+      <c r="AK17" s="23"/>
+      <c r="AL17" s="23"/>
+      <c r="AM17" s="23"/>
+      <c r="AN17" s="23"/>
+      <c r="AO17" s="23"/>
+      <c r="AP17" s="23"/>
+      <c r="AQ17" s="23"/>
+      <c r="AR17" s="23"/>
+      <c r="AS17" s="23"/>
+      <c r="AT17" s="23"/>
+      <c r="AU17" s="23"/>
+      <c r="AV17" s="23"/>
+      <c r="AW17" s="23"/>
+      <c r="AX17" s="23"/>
+      <c r="AY17" s="23"/>
+      <c r="AZ17" s="23"/>
+      <c r="BA17" s="23"/>
+      <c r="BB17" s="23"/>
+      <c r="BC17" s="23"/>
+      <c r="BD17" s="23"/>
+      <c r="BE17" s="23"/>
+      <c r="BF17" s="23"/>
+      <c r="BG17" s="23"/>
+      <c r="BH17" s="23"/>
+      <c r="BI17" s="23"/>
+      <c r="BJ17" s="23"/>
+      <c r="BK17" s="23"/>
+      <c r="BL17" s="23"/>
+      <c r="BM17" s="23"/>
+      <c r="BN17" s="23"/>
+      <c r="BO17" s="23"/>
+      <c r="BP17" s="23"/>
+      <c r="BQ17" s="23"/>
+      <c r="BR17" s="23"/>
+      <c r="BS17" s="23"/>
+      <c r="BT17" s="23"/>
+      <c r="BU17" s="23"/>
+      <c r="BV17" s="23"/>
+      <c r="BW17" s="23"/>
+      <c r="BX17" s="23"/>
+      <c r="BY17" s="23"/>
+      <c r="BZ17" s="23"/>
+      <c r="CA17" s="23"/>
+      <c r="CB17" s="24"/>
     </row>
     <row r="18" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9">
@@ -2964,7 +3014,7 @@
       </c>
       <c r="D18" s="11">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E18" s="12"/>
       <c r="F18" s="8"/>
@@ -2989,11 +3039,21 @@
       <c r="S18" s="8"/>
       <c r="T18" s="8"/>
       <c r="U18" s="8"/>
-      <c r="V18" s="8"/>
-      <c r="W18" s="8"/>
-      <c r="X18" s="8"/>
-      <c r="Y18" s="8"/>
-      <c r="Z18" s="8"/>
+      <c r="V18" s="8">
+        <v>0</v>
+      </c>
+      <c r="W18" s="8">
+        <v>0</v>
+      </c>
+      <c r="X18" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="8">
+        <v>0</v>
+      </c>
       <c r="AA18" s="8"/>
       <c r="AB18" s="8"/>
       <c r="AC18" s="8"/>
@@ -3061,7 +3121,7 @@
       </c>
       <c r="D19" s="11">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E19" s="12"/>
       <c r="F19" s="8">
@@ -3090,8 +3150,12 @@
       <c r="S19" s="8"/>
       <c r="T19" s="8"/>
       <c r="U19" s="8"/>
-      <c r="V19" s="8"/>
-      <c r="W19" s="8"/>
+      <c r="V19" s="8">
+        <v>0</v>
+      </c>
+      <c r="W19" s="8">
+        <v>0</v>
+      </c>
       <c r="X19" s="8"/>
       <c r="Y19" s="8"/>
       <c r="Z19" s="8"/>
@@ -3162,7 +3226,7 @@
       </c>
       <c r="D20" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E20" s="12"/>
       <c r="F20" s="8"/>
@@ -3181,11 +3245,21 @@
       <c r="S20" s="8"/>
       <c r="T20" s="8"/>
       <c r="U20" s="8"/>
-      <c r="V20" s="8"/>
-      <c r="W20" s="8"/>
-      <c r="X20" s="8"/>
-      <c r="Y20" s="8"/>
-      <c r="Z20" s="8"/>
+      <c r="V20" s="8">
+        <v>0</v>
+      </c>
+      <c r="W20" s="8">
+        <v>0</v>
+      </c>
+      <c r="X20" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="8">
+        <v>0</v>
+      </c>
       <c r="AA20" s="8"/>
       <c r="AB20" s="8"/>
       <c r="AC20" s="8"/>
@@ -3253,7 +3327,7 @@
       </c>
       <c r="D21" s="11">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E21" s="12"/>
       <c r="F21" s="8">
@@ -3289,16 +3363,36 @@
       <c r="P21" s="8">
         <v>0</v>
       </c>
-      <c r="Q21" s="8"/>
-      <c r="R21" s="8"/>
-      <c r="S21" s="8"/>
-      <c r="T21" s="8"/>
-      <c r="U21" s="8"/>
-      <c r="V21" s="8"/>
-      <c r="W21" s="8"/>
-      <c r="X21" s="8"/>
-      <c r="Y21" s="8"/>
-      <c r="Z21" s="8"/>
+      <c r="Q21" s="8">
+        <v>0</v>
+      </c>
+      <c r="R21" s="8">
+        <v>0</v>
+      </c>
+      <c r="S21" s="8">
+        <v>0</v>
+      </c>
+      <c r="T21" s="8">
+        <v>0</v>
+      </c>
+      <c r="U21" s="8">
+        <v>0</v>
+      </c>
+      <c r="V21" s="8">
+        <v>0</v>
+      </c>
+      <c r="W21" s="8">
+        <v>0</v>
+      </c>
+      <c r="X21" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="8">
+        <v>0</v>
+      </c>
       <c r="AA21" s="8"/>
       <c r="AB21" s="8"/>
       <c r="AC21" s="8"/>
@@ -3459,7 +3553,7 @@
       </c>
       <c r="D23" s="11">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E23" s="12"/>
       <c r="F23" s="8">
@@ -3495,16 +3589,36 @@
       <c r="P23" s="8">
         <v>0</v>
       </c>
-      <c r="Q23" s="8"/>
-      <c r="R23" s="8"/>
-      <c r="S23" s="8"/>
-      <c r="T23" s="8"/>
-      <c r="U23" s="8"/>
-      <c r="V23" s="8"/>
-      <c r="W23" s="8"/>
-      <c r="X23" s="8"/>
-      <c r="Y23" s="8"/>
-      <c r="Z23" s="8"/>
+      <c r="Q23" s="8">
+        <v>0</v>
+      </c>
+      <c r="R23" s="8">
+        <v>0</v>
+      </c>
+      <c r="S23" s="8">
+        <v>0</v>
+      </c>
+      <c r="T23" s="8">
+        <v>0</v>
+      </c>
+      <c r="U23" s="8">
+        <v>0</v>
+      </c>
+      <c r="V23" s="8">
+        <v>0</v>
+      </c>
+      <c r="W23" s="8">
+        <v>0</v>
+      </c>
+      <c r="X23" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="8">
+        <v>0</v>
+      </c>
       <c r="AA23" s="8"/>
       <c r="AB23" s="8"/>
       <c r="AC23" s="8"/>
@@ -3681,7 +3795,7 @@
       </c>
       <c r="D25" s="11">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E25" s="12"/>
       <c r="F25" s="8">
@@ -3710,11 +3824,21 @@
       <c r="S25" s="8"/>
       <c r="T25" s="8"/>
       <c r="U25" s="8"/>
-      <c r="V25" s="8"/>
-      <c r="W25" s="8"/>
-      <c r="X25" s="8"/>
-      <c r="Y25" s="8"/>
-      <c r="Z25" s="8"/>
+      <c r="V25" s="8">
+        <v>0</v>
+      </c>
+      <c r="W25" s="8">
+        <v>0</v>
+      </c>
+      <c r="X25" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="8">
+        <v>0</v>
+      </c>
       <c r="AA25" s="8"/>
       <c r="AB25" s="8"/>
       <c r="AC25" s="8"/>
@@ -3782,7 +3906,7 @@
       </c>
       <c r="D26" s="11">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E26" s="12"/>
       <c r="F26" s="8">
@@ -3823,11 +3947,21 @@
       <c r="S26" s="8"/>
       <c r="T26" s="8"/>
       <c r="U26" s="8"/>
-      <c r="V26" s="8"/>
-      <c r="W26" s="8"/>
-      <c r="X26" s="8"/>
-      <c r="Y26" s="8"/>
-      <c r="Z26" s="8"/>
+      <c r="V26" s="8">
+        <v>0</v>
+      </c>
+      <c r="W26" s="8">
+        <v>0</v>
+      </c>
+      <c r="X26" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="8">
+        <v>0</v>
+      </c>
       <c r="AA26" s="8"/>
       <c r="AB26" s="8"/>
       <c r="AC26" s="8"/>
@@ -3895,7 +4029,7 @@
       </c>
       <c r="D27" s="11">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E27" s="15"/>
       <c r="F27" s="8">
@@ -3931,16 +4065,36 @@
       <c r="P27" s="8">
         <v>0</v>
       </c>
-      <c r="Q27" s="8"/>
-      <c r="R27" s="8"/>
-      <c r="S27" s="8"/>
-      <c r="T27" s="8"/>
-      <c r="U27" s="8"/>
-      <c r="V27" s="8"/>
-      <c r="W27" s="8"/>
-      <c r="X27" s="8"/>
-      <c r="Y27" s="8"/>
-      <c r="Z27" s="8"/>
+      <c r="Q27" s="8">
+        <v>0</v>
+      </c>
+      <c r="R27" s="8">
+        <v>0</v>
+      </c>
+      <c r="S27" s="8">
+        <v>0</v>
+      </c>
+      <c r="T27" s="8">
+        <v>0</v>
+      </c>
+      <c r="U27" s="8">
+        <v>0</v>
+      </c>
+      <c r="V27" s="8">
+        <v>0</v>
+      </c>
+      <c r="W27" s="8">
+        <v>0</v>
+      </c>
+      <c r="X27" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="8">
+        <v>0</v>
+      </c>
       <c r="AA27" s="8"/>
       <c r="AB27" s="8"/>
       <c r="AC27" s="8"/>
@@ -4010,88 +4164,87 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E28" s="24" t="s">
+      <c r="E28" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="F28" s="24"/>
-      <c r="G28" s="24"/>
-      <c r="H28" s="24"/>
-      <c r="I28" s="24"/>
-      <c r="J28" s="24"/>
-      <c r="K28" s="24"/>
-      <c r="L28" s="24"/>
-      <c r="M28" s="24"/>
-      <c r="N28" s="24"/>
-      <c r="O28" s="24"/>
-      <c r="P28" s="24"/>
-      <c r="Q28" s="24"/>
-      <c r="R28" s="24"/>
-      <c r="S28" s="24"/>
-      <c r="T28" s="24"/>
-      <c r="U28" s="24"/>
-      <c r="V28" s="24"/>
-      <c r="W28" s="24"/>
-      <c r="X28" s="24"/>
-      <c r="Y28" s="24"/>
-      <c r="Z28" s="24"/>
-      <c r="AA28" s="24"/>
-      <c r="AB28" s="24"/>
-      <c r="AC28" s="24"/>
-      <c r="AD28" s="24"/>
-      <c r="AE28" s="24"/>
-      <c r="AF28" s="24"/>
-      <c r="AG28" s="24"/>
-      <c r="AH28" s="24"/>
-      <c r="AI28" s="24"/>
-      <c r="AJ28" s="24"/>
-      <c r="AK28" s="24"/>
-      <c r="AL28" s="24"/>
-      <c r="AM28" s="24"/>
-      <c r="AN28" s="24"/>
-      <c r="AO28" s="24"/>
-      <c r="AP28" s="24"/>
-      <c r="AQ28" s="24"/>
-      <c r="AR28" s="24"/>
-      <c r="AS28" s="24"/>
-      <c r="AT28" s="24"/>
-      <c r="AU28" s="24"/>
-      <c r="AV28" s="24"/>
-      <c r="AW28" s="24"/>
-      <c r="AX28" s="24"/>
-      <c r="AY28" s="24"/>
-      <c r="AZ28" s="24"/>
-      <c r="BA28" s="24"/>
-      <c r="BB28" s="24"/>
-      <c r="BC28" s="24"/>
-      <c r="BD28" s="24"/>
-      <c r="BE28" s="24"/>
-      <c r="BF28" s="24"/>
-      <c r="BG28" s="24"/>
-      <c r="BH28" s="24"/>
-      <c r="BI28" s="24"/>
-      <c r="BJ28" s="24"/>
-      <c r="BK28" s="24"/>
-      <c r="BL28" s="24"/>
-      <c r="BM28" s="24"/>
-      <c r="BN28" s="24"/>
-      <c r="BO28" s="24"/>
-      <c r="BP28" s="24"/>
-      <c r="BQ28" s="24"/>
-      <c r="BR28" s="24"/>
-      <c r="BS28" s="24"/>
-      <c r="BT28" s="24"/>
-      <c r="BU28" s="24"/>
-      <c r="BV28" s="24"/>
-      <c r="BW28" s="24"/>
-      <c r="BX28" s="24"/>
-      <c r="BY28" s="24"/>
-      <c r="BZ28" s="24"/>
-      <c r="CA28" s="24"/>
-      <c r="CB28" s="24"/>
+      <c r="F28" s="27"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="27"/>
+      <c r="I28" s="27"/>
+      <c r="J28" s="27"/>
+      <c r="K28" s="27"/>
+      <c r="L28" s="27"/>
+      <c r="M28" s="27"/>
+      <c r="N28" s="27"/>
+      <c r="O28" s="27"/>
+      <c r="P28" s="27"/>
+      <c r="Q28" s="27"/>
+      <c r="R28" s="27"/>
+      <c r="S28" s="27"/>
+      <c r="T28" s="27"/>
+      <c r="U28" s="27"/>
+      <c r="V28" s="27"/>
+      <c r="W28" s="27"/>
+      <c r="X28" s="27"/>
+      <c r="Y28" s="27"/>
+      <c r="Z28" s="27"/>
+      <c r="AA28" s="27"/>
+      <c r="AB28" s="27"/>
+      <c r="AC28" s="27"/>
+      <c r="AD28" s="27"/>
+      <c r="AE28" s="27"/>
+      <c r="AF28" s="27"/>
+      <c r="AG28" s="27"/>
+      <c r="AH28" s="27"/>
+      <c r="AI28" s="27"/>
+      <c r="AJ28" s="27"/>
+      <c r="AK28" s="27"/>
+      <c r="AL28" s="27"/>
+      <c r="AM28" s="27"/>
+      <c r="AN28" s="27"/>
+      <c r="AO28" s="27"/>
+      <c r="AP28" s="27"/>
+      <c r="AQ28" s="27"/>
+      <c r="AR28" s="27"/>
+      <c r="AS28" s="27"/>
+      <c r="AT28" s="27"/>
+      <c r="AU28" s="27"/>
+      <c r="AV28" s="27"/>
+      <c r="AW28" s="27"/>
+      <c r="AX28" s="27"/>
+      <c r="AY28" s="27"/>
+      <c r="AZ28" s="27"/>
+      <c r="BA28" s="27"/>
+      <c r="BB28" s="27"/>
+      <c r="BC28" s="27"/>
+      <c r="BD28" s="27"/>
+      <c r="BE28" s="27"/>
+      <c r="BF28" s="27"/>
+      <c r="BG28" s="27"/>
+      <c r="BH28" s="27"/>
+      <c r="BI28" s="27"/>
+      <c r="BJ28" s="27"/>
+      <c r="BK28" s="27"/>
+      <c r="BL28" s="27"/>
+      <c r="BM28" s="27"/>
+      <c r="BN28" s="27"/>
+      <c r="BO28" s="27"/>
+      <c r="BP28" s="27"/>
+      <c r="BQ28" s="27"/>
+      <c r="BR28" s="27"/>
+      <c r="BS28" s="27"/>
+      <c r="BT28" s="27"/>
+      <c r="BU28" s="27"/>
+      <c r="BV28" s="27"/>
+      <c r="BW28" s="27"/>
+      <c r="BX28" s="27"/>
+      <c r="BY28" s="27"/>
+      <c r="BZ28" s="27"/>
+      <c r="CA28" s="27"/>
+      <c r="CB28" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="172">
-    <mergeCell ref="Q1:U1"/>
+  <mergeCells count="174">
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="W2:W7"/>
     <mergeCell ref="X2:X7"/>
@@ -4115,6 +4268,7 @@
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A7:B7"/>
+    <mergeCell ref="V1:Z1"/>
     <mergeCell ref="L1:P1"/>
     <mergeCell ref="AA2:AA7"/>
     <mergeCell ref="N2:N7"/>
@@ -4126,6 +4280,7 @@
     <mergeCell ref="T2:T7"/>
     <mergeCell ref="U2:U7"/>
     <mergeCell ref="V2:V7"/>
+    <mergeCell ref="Q1:U1"/>
     <mergeCell ref="AG2:AG7"/>
     <mergeCell ref="AD2:AD7"/>
     <mergeCell ref="AE2:AE7"/>
@@ -4226,6 +4381,7 @@
     <mergeCell ref="AT8:AT9"/>
     <mergeCell ref="AU8:AU9"/>
     <mergeCell ref="AV8:AV9"/>
+    <mergeCell ref="BJ8:BJ9"/>
     <mergeCell ref="BK8:BK9"/>
     <mergeCell ref="BL8:BL9"/>
     <mergeCell ref="BM8:BM9"/>
@@ -4239,6 +4395,7 @@
     <mergeCell ref="BC8:BC9"/>
     <mergeCell ref="BD8:BD9"/>
     <mergeCell ref="BE8:BE9"/>
+    <mergeCell ref="Q17:CB17"/>
     <mergeCell ref="BX8:BX9"/>
     <mergeCell ref="BY8:BY9"/>
     <mergeCell ref="BZ8:BZ9"/>
@@ -4262,7 +4419,6 @@
     <mergeCell ref="BG8:BG9"/>
     <mergeCell ref="BH8:BH9"/>
     <mergeCell ref="BI8:BI9"/>
-    <mergeCell ref="BJ8:BJ9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" verticalDpi="0"/>

--- a/ჟურნალი/5. N301 front-end დეველოპმენტი (ინტეგრირებული მიდგომით) - Git.xlsx
+++ b/ჟურნალი/5. N301 front-end დეველოპმენტი (ინტეგრირებული მიდგომით) - Git.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\3Daudiece\Desktop\Front-end!!\0. ready\ჟურნალი\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBD158D9-70DA-442B-AD74-59ABFCC7CC83}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C31875BB-90DC-4C38-9F09-E852376BAFB8}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-122" yWindow="-122" windowWidth="29045" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -732,6 +732,78 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -741,12 +813,6 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -764,72 +830,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1058,45 +1058,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="44"/>
-      <c r="D1" s="45"/>
-      <c r="F1" s="28">
+      <c r="A1" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="27"/>
+      <c r="D1" s="28"/>
+      <c r="F1" s="50">
         <v>4</v>
       </c>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="40">
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="22">
         <v>2</v>
       </c>
-      <c r="K1" s="42"/>
-      <c r="L1" s="40">
+      <c r="K1" s="23"/>
+      <c r="L1" s="22">
         <v>5</v>
       </c>
       <c r="M1" s="41"/>
       <c r="N1" s="41"/>
       <c r="O1" s="41"/>
-      <c r="P1" s="42"/>
-      <c r="Q1" s="40">
+      <c r="P1" s="23"/>
+      <c r="Q1" s="22">
         <v>5</v>
       </c>
       <c r="R1" s="41"/>
       <c r="S1" s="41"/>
       <c r="T1" s="41"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="40">
+      <c r="U1" s="23"/>
+      <c r="V1" s="22">
         <v>5</v>
       </c>
       <c r="W1" s="41"/>
       <c r="X1" s="41"/>
       <c r="Y1" s="41"/>
-      <c r="Z1" s="42"/>
+      <c r="Z1" s="23"/>
       <c r="AA1" s="17"/>
       <c r="AB1" s="17"/>
       <c r="AC1" s="18"/>
@@ -1151,889 +1151,893 @@
       <c r="BZ1" s="17"/>
       <c r="CA1" s="17"/>
       <c r="CB1" s="17"/>
+      <c r="CC1" s="1">
+        <f>SUM(E1:CB1)</f>
+        <v>21</v>
+      </c>
     </row>
     <row r="2" spans="1:85" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="43"/>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="48" t="s">
+      <c r="A2" s="26"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="36">
+      <c r="F2" s="24">
         <v>46202</v>
       </c>
-      <c r="G2" s="36">
+      <c r="G2" s="24">
         <v>46202</v>
       </c>
-      <c r="H2" s="36">
+      <c r="H2" s="24">
         <v>46202</v>
       </c>
-      <c r="I2" s="36">
+      <c r="I2" s="24">
         <v>46202</v>
       </c>
-      <c r="J2" s="36">
+      <c r="J2" s="24">
         <v>46206</v>
       </c>
-      <c r="K2" s="36">
+      <c r="K2" s="24">
         <v>46206</v>
       </c>
-      <c r="L2" s="36">
+      <c r="L2" s="24">
         <v>46209</v>
       </c>
-      <c r="M2" s="36">
+      <c r="M2" s="24">
         <v>46209</v>
       </c>
-      <c r="N2" s="36">
+      <c r="N2" s="24">
         <v>46209</v>
       </c>
-      <c r="O2" s="36">
+      <c r="O2" s="24">
         <v>46209</v>
       </c>
-      <c r="P2" s="36">
+      <c r="P2" s="24">
         <v>46209</v>
       </c>
-      <c r="Q2" s="36">
+      <c r="Q2" s="24">
         <v>46216</v>
       </c>
-      <c r="R2" s="36">
+      <c r="R2" s="24">
         <v>46216</v>
       </c>
-      <c r="S2" s="36">
+      <c r="S2" s="24">
         <v>46216</v>
       </c>
-      <c r="T2" s="36">
+      <c r="T2" s="24">
         <v>46216</v>
       </c>
-      <c r="U2" s="36">
+      <c r="U2" s="24">
         <v>46216</v>
       </c>
-      <c r="V2" s="36">
+      <c r="V2" s="24">
         <v>46223</v>
       </c>
-      <c r="W2" s="36">
+      <c r="W2" s="24">
         <v>46223</v>
       </c>
-      <c r="X2" s="36">
+      <c r="X2" s="24">
         <v>46223</v>
       </c>
-      <c r="Y2" s="36">
+      <c r="Y2" s="24">
         <v>46223</v>
       </c>
-      <c r="Z2" s="36">
+      <c r="Z2" s="24">
         <v>46223</v>
       </c>
-      <c r="AA2" s="36"/>
-      <c r="AB2" s="36"/>
-      <c r="AC2" s="36"/>
-      <c r="AD2" s="36"/>
-      <c r="AE2" s="36"/>
-      <c r="AF2" s="36"/>
-      <c r="AG2" s="36"/>
-      <c r="AH2" s="36"/>
-      <c r="AI2" s="36"/>
-      <c r="AJ2" s="36"/>
-      <c r="AK2" s="36"/>
-      <c r="AL2" s="36"/>
-      <c r="AM2" s="36"/>
-      <c r="AN2" s="36"/>
-      <c r="AO2" s="36"/>
-      <c r="AP2" s="36"/>
-      <c r="AQ2" s="36"/>
-      <c r="AR2" s="36"/>
-      <c r="AS2" s="36"/>
-      <c r="AT2" s="36"/>
-      <c r="AU2" s="36"/>
-      <c r="AV2" s="36"/>
-      <c r="AW2" s="36"/>
-      <c r="AX2" s="36"/>
-      <c r="AY2" s="36"/>
-      <c r="AZ2" s="36"/>
-      <c r="BA2" s="36"/>
-      <c r="BB2" s="36"/>
-      <c r="BC2" s="36"/>
-      <c r="BD2" s="36"/>
-      <c r="BE2" s="36"/>
-      <c r="BF2" s="36"/>
-      <c r="BG2" s="36"/>
-      <c r="BH2" s="36"/>
-      <c r="BI2" s="36"/>
-      <c r="BJ2" s="36"/>
-      <c r="BK2" s="36"/>
-      <c r="BL2" s="36"/>
-      <c r="BM2" s="36"/>
-      <c r="BN2" s="36"/>
-      <c r="BO2" s="36"/>
-      <c r="BP2" s="36"/>
-      <c r="BQ2" s="36"/>
-      <c r="BR2" s="36"/>
-      <c r="BS2" s="36"/>
-      <c r="BT2" s="36"/>
-      <c r="BU2" s="36"/>
-      <c r="BV2" s="36"/>
-      <c r="BW2" s="36"/>
-      <c r="BX2" s="36"/>
-      <c r="BY2" s="36"/>
-      <c r="BZ2" s="36"/>
-      <c r="CA2" s="36"/>
-      <c r="CB2" s="36"/>
+      <c r="AA2" s="24"/>
+      <c r="AB2" s="24"/>
+      <c r="AC2" s="24"/>
+      <c r="AD2" s="24"/>
+      <c r="AE2" s="24"/>
+      <c r="AF2" s="24"/>
+      <c r="AG2" s="24"/>
+      <c r="AH2" s="24"/>
+      <c r="AI2" s="24"/>
+      <c r="AJ2" s="24"/>
+      <c r="AK2" s="24"/>
+      <c r="AL2" s="24"/>
+      <c r="AM2" s="24"/>
+      <c r="AN2" s="24"/>
+      <c r="AO2" s="24"/>
+      <c r="AP2" s="24"/>
+      <c r="AQ2" s="24"/>
+      <c r="AR2" s="24"/>
+      <c r="AS2" s="24"/>
+      <c r="AT2" s="24"/>
+      <c r="AU2" s="24"/>
+      <c r="AV2" s="24"/>
+      <c r="AW2" s="24"/>
+      <c r="AX2" s="24"/>
+      <c r="AY2" s="24"/>
+      <c r="AZ2" s="24"/>
+      <c r="BA2" s="24"/>
+      <c r="BB2" s="24"/>
+      <c r="BC2" s="24"/>
+      <c r="BD2" s="24"/>
+      <c r="BE2" s="24"/>
+      <c r="BF2" s="24"/>
+      <c r="BG2" s="24"/>
+      <c r="BH2" s="24"/>
+      <c r="BI2" s="24"/>
+      <c r="BJ2" s="24"/>
+      <c r="BK2" s="24"/>
+      <c r="BL2" s="24"/>
+      <c r="BM2" s="24"/>
+      <c r="BN2" s="24"/>
+      <c r="BO2" s="24"/>
+      <c r="BP2" s="24"/>
+      <c r="BQ2" s="24"/>
+      <c r="BR2" s="24"/>
+      <c r="BS2" s="24"/>
+      <c r="BT2" s="24"/>
+      <c r="BU2" s="24"/>
+      <c r="BV2" s="24"/>
+      <c r="BW2" s="24"/>
+      <c r="BX2" s="24"/>
+      <c r="BY2" s="24"/>
+      <c r="BZ2" s="24"/>
+      <c r="CA2" s="24"/>
+      <c r="CB2" s="24"/>
     </row>
     <row r="3" spans="1:85" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="36"/>
-      <c r="K3" s="36"/>
-      <c r="L3" s="36"/>
-      <c r="M3" s="36"/>
-      <c r="N3" s="36"/>
-      <c r="O3" s="36"/>
-      <c r="P3" s="36"/>
-      <c r="Q3" s="36"/>
-      <c r="R3" s="36"/>
-      <c r="S3" s="36"/>
-      <c r="T3" s="36"/>
-      <c r="U3" s="36"/>
-      <c r="V3" s="36"/>
-      <c r="W3" s="36"/>
-      <c r="X3" s="36"/>
-      <c r="Y3" s="36"/>
-      <c r="Z3" s="36"/>
-      <c r="AA3" s="36"/>
-      <c r="AB3" s="36"/>
-      <c r="AC3" s="36"/>
-      <c r="AD3" s="36"/>
-      <c r="AE3" s="36"/>
-      <c r="AF3" s="36"/>
-      <c r="AG3" s="36"/>
-      <c r="AH3" s="36"/>
-      <c r="AI3" s="36"/>
-      <c r="AJ3" s="36"/>
-      <c r="AK3" s="36"/>
-      <c r="AL3" s="36"/>
-      <c r="AM3" s="36"/>
-      <c r="AN3" s="36"/>
-      <c r="AO3" s="36"/>
-      <c r="AP3" s="36"/>
-      <c r="AQ3" s="36"/>
-      <c r="AR3" s="36"/>
-      <c r="AS3" s="36"/>
-      <c r="AT3" s="36"/>
-      <c r="AU3" s="36"/>
-      <c r="AV3" s="36"/>
-      <c r="AW3" s="36"/>
-      <c r="AX3" s="36"/>
-      <c r="AY3" s="36"/>
-      <c r="AZ3" s="36"/>
-      <c r="BA3" s="36"/>
-      <c r="BB3" s="36"/>
-      <c r="BC3" s="36"/>
-      <c r="BD3" s="36"/>
-      <c r="BE3" s="36"/>
-      <c r="BF3" s="36"/>
-      <c r="BG3" s="36"/>
-      <c r="BH3" s="36"/>
-      <c r="BI3" s="36"/>
-      <c r="BJ3" s="36"/>
-      <c r="BK3" s="36"/>
-      <c r="BL3" s="36"/>
-      <c r="BM3" s="36"/>
-      <c r="BN3" s="36"/>
-      <c r="BO3" s="36"/>
-      <c r="BP3" s="36"/>
-      <c r="BQ3" s="36"/>
-      <c r="BR3" s="36"/>
-      <c r="BS3" s="36"/>
-      <c r="BT3" s="36"/>
-      <c r="BU3" s="36"/>
-      <c r="BV3" s="36"/>
-      <c r="BW3" s="36"/>
-      <c r="BX3" s="36"/>
-      <c r="BY3" s="36"/>
-      <c r="BZ3" s="36"/>
-      <c r="CA3" s="36"/>
-      <c r="CB3" s="36"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="24"/>
+      <c r="Q3" s="24"/>
+      <c r="R3" s="24"/>
+      <c r="S3" s="24"/>
+      <c r="T3" s="24"/>
+      <c r="U3" s="24"/>
+      <c r="V3" s="24"/>
+      <c r="W3" s="24"/>
+      <c r="X3" s="24"/>
+      <c r="Y3" s="24"/>
+      <c r="Z3" s="24"/>
+      <c r="AA3" s="24"/>
+      <c r="AB3" s="24"/>
+      <c r="AC3" s="24"/>
+      <c r="AD3" s="24"/>
+      <c r="AE3" s="24"/>
+      <c r="AF3" s="24"/>
+      <c r="AG3" s="24"/>
+      <c r="AH3" s="24"/>
+      <c r="AI3" s="24"/>
+      <c r="AJ3" s="24"/>
+      <c r="AK3" s="24"/>
+      <c r="AL3" s="24"/>
+      <c r="AM3" s="24"/>
+      <c r="AN3" s="24"/>
+      <c r="AO3" s="24"/>
+      <c r="AP3" s="24"/>
+      <c r="AQ3" s="24"/>
+      <c r="AR3" s="24"/>
+      <c r="AS3" s="24"/>
+      <c r="AT3" s="24"/>
+      <c r="AU3" s="24"/>
+      <c r="AV3" s="24"/>
+      <c r="AW3" s="24"/>
+      <c r="AX3" s="24"/>
+      <c r="AY3" s="24"/>
+      <c r="AZ3" s="24"/>
+      <c r="BA3" s="24"/>
+      <c r="BB3" s="24"/>
+      <c r="BC3" s="24"/>
+      <c r="BD3" s="24"/>
+      <c r="BE3" s="24"/>
+      <c r="BF3" s="24"/>
+      <c r="BG3" s="24"/>
+      <c r="BH3" s="24"/>
+      <c r="BI3" s="24"/>
+      <c r="BJ3" s="24"/>
+      <c r="BK3" s="24"/>
+      <c r="BL3" s="24"/>
+      <c r="BM3" s="24"/>
+      <c r="BN3" s="24"/>
+      <c r="BO3" s="24"/>
+      <c r="BP3" s="24"/>
+      <c r="BQ3" s="24"/>
+      <c r="BR3" s="24"/>
+      <c r="BS3" s="24"/>
+      <c r="BT3" s="24"/>
+      <c r="BU3" s="24"/>
+      <c r="BV3" s="24"/>
+      <c r="BW3" s="24"/>
+      <c r="BX3" s="24"/>
+      <c r="BY3" s="24"/>
+      <c r="BZ3" s="24"/>
+      <c r="CA3" s="24"/>
+      <c r="CB3" s="24"/>
     </row>
     <row r="4" spans="1:85" ht="24.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="51"/>
-      <c r="C4" s="52" t="s">
+      <c r="B4" s="34"/>
+      <c r="C4" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="35"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="36"/>
-      <c r="K4" s="36"/>
-      <c r="L4" s="36"/>
-      <c r="M4" s="36"/>
-      <c r="N4" s="36"/>
-      <c r="O4" s="36"/>
-      <c r="P4" s="36"/>
-      <c r="Q4" s="36"/>
-      <c r="R4" s="36"/>
-      <c r="S4" s="36"/>
-      <c r="T4" s="36"/>
-      <c r="U4" s="36"/>
-      <c r="V4" s="36"/>
-      <c r="W4" s="36"/>
-      <c r="X4" s="36"/>
-      <c r="Y4" s="36"/>
-      <c r="Z4" s="36"/>
-      <c r="AA4" s="36"/>
-      <c r="AB4" s="36"/>
-      <c r="AC4" s="36"/>
-      <c r="AD4" s="36"/>
-      <c r="AE4" s="36"/>
-      <c r="AF4" s="36"/>
-      <c r="AG4" s="36"/>
-      <c r="AH4" s="36"/>
-      <c r="AI4" s="36"/>
-      <c r="AJ4" s="36"/>
-      <c r="AK4" s="36"/>
-      <c r="AL4" s="36"/>
-      <c r="AM4" s="36"/>
-      <c r="AN4" s="36"/>
-      <c r="AO4" s="36"/>
-      <c r="AP4" s="36"/>
-      <c r="AQ4" s="36"/>
-      <c r="AR4" s="36"/>
-      <c r="AS4" s="36"/>
-      <c r="AT4" s="36"/>
-      <c r="AU4" s="36"/>
-      <c r="AV4" s="36"/>
-      <c r="AW4" s="36"/>
-      <c r="AX4" s="36"/>
-      <c r="AY4" s="36"/>
-      <c r="AZ4" s="36"/>
-      <c r="BA4" s="36"/>
-      <c r="BB4" s="36"/>
-      <c r="BC4" s="36"/>
-      <c r="BD4" s="36"/>
-      <c r="BE4" s="36"/>
-      <c r="BF4" s="36"/>
-      <c r="BG4" s="36"/>
-      <c r="BH4" s="36"/>
-      <c r="BI4" s="36"/>
-      <c r="BJ4" s="36"/>
-      <c r="BK4" s="36"/>
-      <c r="BL4" s="36"/>
-      <c r="BM4" s="36"/>
-      <c r="BN4" s="36"/>
-      <c r="BO4" s="36"/>
-      <c r="BP4" s="36"/>
-      <c r="BQ4" s="36"/>
-      <c r="BR4" s="36"/>
-      <c r="BS4" s="36"/>
-      <c r="BT4" s="36"/>
-      <c r="BU4" s="36"/>
-      <c r="BV4" s="36"/>
-      <c r="BW4" s="36"/>
-      <c r="BX4" s="36"/>
-      <c r="BY4" s="36"/>
-      <c r="BZ4" s="36"/>
-      <c r="CA4" s="36"/>
-      <c r="CB4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="24"/>
+      <c r="Q4" s="24"/>
+      <c r="R4" s="24"/>
+      <c r="S4" s="24"/>
+      <c r="T4" s="24"/>
+      <c r="U4" s="24"/>
+      <c r="V4" s="24"/>
+      <c r="W4" s="24"/>
+      <c r="X4" s="24"/>
+      <c r="Y4" s="24"/>
+      <c r="Z4" s="24"/>
+      <c r="AA4" s="24"/>
+      <c r="AB4" s="24"/>
+      <c r="AC4" s="24"/>
+      <c r="AD4" s="24"/>
+      <c r="AE4" s="24"/>
+      <c r="AF4" s="24"/>
+      <c r="AG4" s="24"/>
+      <c r="AH4" s="24"/>
+      <c r="AI4" s="24"/>
+      <c r="AJ4" s="24"/>
+      <c r="AK4" s="24"/>
+      <c r="AL4" s="24"/>
+      <c r="AM4" s="24"/>
+      <c r="AN4" s="24"/>
+      <c r="AO4" s="24"/>
+      <c r="AP4" s="24"/>
+      <c r="AQ4" s="24"/>
+      <c r="AR4" s="24"/>
+      <c r="AS4" s="24"/>
+      <c r="AT4" s="24"/>
+      <c r="AU4" s="24"/>
+      <c r="AV4" s="24"/>
+      <c r="AW4" s="24"/>
+      <c r="AX4" s="24"/>
+      <c r="AY4" s="24"/>
+      <c r="AZ4" s="24"/>
+      <c r="BA4" s="24"/>
+      <c r="BB4" s="24"/>
+      <c r="BC4" s="24"/>
+      <c r="BD4" s="24"/>
+      <c r="BE4" s="24"/>
+      <c r="BF4" s="24"/>
+      <c r="BG4" s="24"/>
+      <c r="BH4" s="24"/>
+      <c r="BI4" s="24"/>
+      <c r="BJ4" s="24"/>
+      <c r="BK4" s="24"/>
+      <c r="BL4" s="24"/>
+      <c r="BM4" s="24"/>
+      <c r="BN4" s="24"/>
+      <c r="BO4" s="24"/>
+      <c r="BP4" s="24"/>
+      <c r="BQ4" s="24"/>
+      <c r="BR4" s="24"/>
+      <c r="BS4" s="24"/>
+      <c r="BT4" s="24"/>
+      <c r="BU4" s="24"/>
+      <c r="BV4" s="24"/>
+      <c r="BW4" s="24"/>
+      <c r="BX4" s="24"/>
+      <c r="BY4" s="24"/>
+      <c r="BZ4" s="24"/>
+      <c r="CA4" s="24"/>
+      <c r="CB4" s="24"/>
     </row>
     <row r="5" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="53" t="s">
+      <c r="A5" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="53"/>
+      <c r="B5" s="37"/>
       <c r="C5" s="38">
         <v>60</v>
       </c>
       <c r="D5" s="39"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="36"/>
-      <c r="K5" s="36"/>
-      <c r="L5" s="36"/>
-      <c r="M5" s="36"/>
-      <c r="N5" s="36"/>
-      <c r="O5" s="36"/>
-      <c r="P5" s="36"/>
-      <c r="Q5" s="36"/>
-      <c r="R5" s="36"/>
-      <c r="S5" s="36"/>
-      <c r="T5" s="36"/>
-      <c r="U5" s="36"/>
-      <c r="V5" s="36"/>
-      <c r="W5" s="36"/>
-      <c r="X5" s="36"/>
-      <c r="Y5" s="36"/>
-      <c r="Z5" s="36"/>
-      <c r="AA5" s="36"/>
-      <c r="AB5" s="36"/>
-      <c r="AC5" s="36"/>
-      <c r="AD5" s="36"/>
-      <c r="AE5" s="36"/>
-      <c r="AF5" s="36"/>
-      <c r="AG5" s="36"/>
-      <c r="AH5" s="36"/>
-      <c r="AI5" s="36"/>
-      <c r="AJ5" s="36"/>
-      <c r="AK5" s="36"/>
-      <c r="AL5" s="36"/>
-      <c r="AM5" s="36"/>
-      <c r="AN5" s="36"/>
-      <c r="AO5" s="36"/>
-      <c r="AP5" s="36"/>
-      <c r="AQ5" s="36"/>
-      <c r="AR5" s="36"/>
-      <c r="AS5" s="36"/>
-      <c r="AT5" s="36"/>
-      <c r="AU5" s="36"/>
-      <c r="AV5" s="36"/>
-      <c r="AW5" s="36"/>
-      <c r="AX5" s="36"/>
-      <c r="AY5" s="36"/>
-      <c r="AZ5" s="36"/>
-      <c r="BA5" s="36"/>
-      <c r="BB5" s="36"/>
-      <c r="BC5" s="36"/>
-      <c r="BD5" s="36"/>
-      <c r="BE5" s="36"/>
-      <c r="BF5" s="36"/>
-      <c r="BG5" s="36"/>
-      <c r="BH5" s="36"/>
-      <c r="BI5" s="36"/>
-      <c r="BJ5" s="36"/>
-      <c r="BK5" s="36"/>
-      <c r="BL5" s="36"/>
-      <c r="BM5" s="36"/>
-      <c r="BN5" s="36"/>
-      <c r="BO5" s="36"/>
-      <c r="BP5" s="36"/>
-      <c r="BQ5" s="36"/>
-      <c r="BR5" s="36"/>
-      <c r="BS5" s="36"/>
-      <c r="BT5" s="36"/>
-      <c r="BU5" s="36"/>
-      <c r="BV5" s="36"/>
-      <c r="BW5" s="36"/>
-      <c r="BX5" s="36"/>
-      <c r="BY5" s="36"/>
-      <c r="BZ5" s="36"/>
-      <c r="CA5" s="36"/>
-      <c r="CB5" s="36"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="24"/>
+      <c r="P5" s="24"/>
+      <c r="Q5" s="24"/>
+      <c r="R5" s="24"/>
+      <c r="S5" s="24"/>
+      <c r="T5" s="24"/>
+      <c r="U5" s="24"/>
+      <c r="V5" s="24"/>
+      <c r="W5" s="24"/>
+      <c r="X5" s="24"/>
+      <c r="Y5" s="24"/>
+      <c r="Z5" s="24"/>
+      <c r="AA5" s="24"/>
+      <c r="AB5" s="24"/>
+      <c r="AC5" s="24"/>
+      <c r="AD5" s="24"/>
+      <c r="AE5" s="24"/>
+      <c r="AF5" s="24"/>
+      <c r="AG5" s="24"/>
+      <c r="AH5" s="24"/>
+      <c r="AI5" s="24"/>
+      <c r="AJ5" s="24"/>
+      <c r="AK5" s="24"/>
+      <c r="AL5" s="24"/>
+      <c r="AM5" s="24"/>
+      <c r="AN5" s="24"/>
+      <c r="AO5" s="24"/>
+      <c r="AP5" s="24"/>
+      <c r="AQ5" s="24"/>
+      <c r="AR5" s="24"/>
+      <c r="AS5" s="24"/>
+      <c r="AT5" s="24"/>
+      <c r="AU5" s="24"/>
+      <c r="AV5" s="24"/>
+      <c r="AW5" s="24"/>
+      <c r="AX5" s="24"/>
+      <c r="AY5" s="24"/>
+      <c r="AZ5" s="24"/>
+      <c r="BA5" s="24"/>
+      <c r="BB5" s="24"/>
+      <c r="BC5" s="24"/>
+      <c r="BD5" s="24"/>
+      <c r="BE5" s="24"/>
+      <c r="BF5" s="24"/>
+      <c r="BG5" s="24"/>
+      <c r="BH5" s="24"/>
+      <c r="BI5" s="24"/>
+      <c r="BJ5" s="24"/>
+      <c r="BK5" s="24"/>
+      <c r="BL5" s="24"/>
+      <c r="BM5" s="24"/>
+      <c r="BN5" s="24"/>
+      <c r="BO5" s="24"/>
+      <c r="BP5" s="24"/>
+      <c r="BQ5" s="24"/>
+      <c r="BR5" s="24"/>
+      <c r="BS5" s="24"/>
+      <c r="BT5" s="24"/>
+      <c r="BU5" s="24"/>
+      <c r="BV5" s="24"/>
+      <c r="BW5" s="24"/>
+      <c r="BX5" s="24"/>
+      <c r="BY5" s="24"/>
+      <c r="BZ5" s="24"/>
+      <c r="CA5" s="24"/>
+      <c r="CB5" s="24"/>
     </row>
     <row r="6" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="53" t="s">
+      <c r="A6" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="53"/>
+      <c r="B6" s="37"/>
       <c r="C6" s="38">
         <v>6</v>
       </c>
       <c r="D6" s="39"/>
-      <c r="E6" s="49"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="36"/>
-      <c r="K6" s="36"/>
-      <c r="L6" s="36"/>
-      <c r="M6" s="36"/>
-      <c r="N6" s="36"/>
-      <c r="O6" s="36"/>
-      <c r="P6" s="36"/>
-      <c r="Q6" s="36"/>
-      <c r="R6" s="36"/>
-      <c r="S6" s="36"/>
-      <c r="T6" s="36"/>
-      <c r="U6" s="36"/>
-      <c r="V6" s="36"/>
-      <c r="W6" s="36"/>
-      <c r="X6" s="36"/>
-      <c r="Y6" s="36"/>
-      <c r="Z6" s="36"/>
-      <c r="AA6" s="36"/>
-      <c r="AB6" s="36"/>
-      <c r="AC6" s="36"/>
-      <c r="AD6" s="36"/>
-      <c r="AE6" s="36"/>
-      <c r="AF6" s="36"/>
-      <c r="AG6" s="36"/>
-      <c r="AH6" s="36"/>
-      <c r="AI6" s="36"/>
-      <c r="AJ6" s="36"/>
-      <c r="AK6" s="36"/>
-      <c r="AL6" s="36"/>
-      <c r="AM6" s="36"/>
-      <c r="AN6" s="36"/>
-      <c r="AO6" s="36"/>
-      <c r="AP6" s="36"/>
-      <c r="AQ6" s="36"/>
-      <c r="AR6" s="36"/>
-      <c r="AS6" s="36"/>
-      <c r="AT6" s="36"/>
-      <c r="AU6" s="36"/>
-      <c r="AV6" s="36"/>
-      <c r="AW6" s="36"/>
-      <c r="AX6" s="36"/>
-      <c r="AY6" s="36"/>
-      <c r="AZ6" s="36"/>
-      <c r="BA6" s="36"/>
-      <c r="BB6" s="36"/>
-      <c r="BC6" s="36"/>
-      <c r="BD6" s="36"/>
-      <c r="BE6" s="36"/>
-      <c r="BF6" s="36"/>
-      <c r="BG6" s="36"/>
-      <c r="BH6" s="36"/>
-      <c r="BI6" s="36"/>
-      <c r="BJ6" s="36"/>
-      <c r="BK6" s="36"/>
-      <c r="BL6" s="36"/>
-      <c r="BM6" s="36"/>
-      <c r="BN6" s="36"/>
-      <c r="BO6" s="36"/>
-      <c r="BP6" s="36"/>
-      <c r="BQ6" s="36"/>
-      <c r="BR6" s="36"/>
-      <c r="BS6" s="36"/>
-      <c r="BT6" s="36"/>
-      <c r="BU6" s="36"/>
-      <c r="BV6" s="36"/>
-      <c r="BW6" s="36"/>
-      <c r="BX6" s="36"/>
-      <c r="BY6" s="36"/>
-      <c r="BZ6" s="36"/>
-      <c r="CA6" s="36"/>
-      <c r="CB6" s="36"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="24"/>
+      <c r="K6" s="24"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="24"/>
+      <c r="P6" s="24"/>
+      <c r="Q6" s="24"/>
+      <c r="R6" s="24"/>
+      <c r="S6" s="24"/>
+      <c r="T6" s="24"/>
+      <c r="U6" s="24"/>
+      <c r="V6" s="24"/>
+      <c r="W6" s="24"/>
+      <c r="X6" s="24"/>
+      <c r="Y6" s="24"/>
+      <c r="Z6" s="24"/>
+      <c r="AA6" s="24"/>
+      <c r="AB6" s="24"/>
+      <c r="AC6" s="24"/>
+      <c r="AD6" s="24"/>
+      <c r="AE6" s="24"/>
+      <c r="AF6" s="24"/>
+      <c r="AG6" s="24"/>
+      <c r="AH6" s="24"/>
+      <c r="AI6" s="24"/>
+      <c r="AJ6" s="24"/>
+      <c r="AK6" s="24"/>
+      <c r="AL6" s="24"/>
+      <c r="AM6" s="24"/>
+      <c r="AN6" s="24"/>
+      <c r="AO6" s="24"/>
+      <c r="AP6" s="24"/>
+      <c r="AQ6" s="24"/>
+      <c r="AR6" s="24"/>
+      <c r="AS6" s="24"/>
+      <c r="AT6" s="24"/>
+      <c r="AU6" s="24"/>
+      <c r="AV6" s="24"/>
+      <c r="AW6" s="24"/>
+      <c r="AX6" s="24"/>
+      <c r="AY6" s="24"/>
+      <c r="AZ6" s="24"/>
+      <c r="BA6" s="24"/>
+      <c r="BB6" s="24"/>
+      <c r="BC6" s="24"/>
+      <c r="BD6" s="24"/>
+      <c r="BE6" s="24"/>
+      <c r="BF6" s="24"/>
+      <c r="BG6" s="24"/>
+      <c r="BH6" s="24"/>
+      <c r="BI6" s="24"/>
+      <c r="BJ6" s="24"/>
+      <c r="BK6" s="24"/>
+      <c r="BL6" s="24"/>
+      <c r="BM6" s="24"/>
+      <c r="BN6" s="24"/>
+      <c r="BO6" s="24"/>
+      <c r="BP6" s="24"/>
+      <c r="BQ6" s="24"/>
+      <c r="BR6" s="24"/>
+      <c r="BS6" s="24"/>
+      <c r="BT6" s="24"/>
+      <c r="BU6" s="24"/>
+      <c r="BV6" s="24"/>
+      <c r="BW6" s="24"/>
+      <c r="BX6" s="24"/>
+      <c r="BY6" s="24"/>
+      <c r="BZ6" s="24"/>
+      <c r="CA6" s="24"/>
+      <c r="CB6" s="24"/>
     </row>
     <row r="7" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="54" t="s">
+      <c r="A7" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="54"/>
+      <c r="B7" s="40"/>
       <c r="C7" s="38">
         <v>9</v>
       </c>
       <c r="D7" s="39"/>
-      <c r="E7" s="50"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="37"/>
-      <c r="I7" s="37"/>
-      <c r="J7" s="37"/>
-      <c r="K7" s="37"/>
-      <c r="L7" s="37"/>
-      <c r="M7" s="37"/>
-      <c r="N7" s="37"/>
-      <c r="O7" s="37"/>
-      <c r="P7" s="37"/>
-      <c r="Q7" s="37"/>
-      <c r="R7" s="37"/>
-      <c r="S7" s="37"/>
-      <c r="T7" s="37"/>
-      <c r="U7" s="37"/>
-      <c r="V7" s="37"/>
-      <c r="W7" s="37"/>
-      <c r="X7" s="37"/>
-      <c r="Y7" s="37"/>
-      <c r="Z7" s="37"/>
-      <c r="AA7" s="37"/>
-      <c r="AB7" s="37"/>
-      <c r="AC7" s="37"/>
-      <c r="AD7" s="37"/>
-      <c r="AE7" s="37"/>
-      <c r="AF7" s="37"/>
-      <c r="AG7" s="37"/>
-      <c r="AH7" s="37"/>
-      <c r="AI7" s="37"/>
-      <c r="AJ7" s="37"/>
-      <c r="AK7" s="37"/>
-      <c r="AL7" s="37"/>
-      <c r="AM7" s="37"/>
-      <c r="AN7" s="37"/>
-      <c r="AO7" s="37"/>
-      <c r="AP7" s="37"/>
-      <c r="AQ7" s="37"/>
-      <c r="AR7" s="37"/>
-      <c r="AS7" s="37"/>
-      <c r="AT7" s="37"/>
-      <c r="AU7" s="37"/>
-      <c r="AV7" s="37"/>
-      <c r="AW7" s="37"/>
-      <c r="AX7" s="37"/>
-      <c r="AY7" s="37"/>
-      <c r="AZ7" s="37"/>
-      <c r="BA7" s="37"/>
-      <c r="BB7" s="37"/>
-      <c r="BC7" s="37"/>
-      <c r="BD7" s="37"/>
-      <c r="BE7" s="37"/>
-      <c r="BF7" s="37"/>
-      <c r="BG7" s="37"/>
-      <c r="BH7" s="37"/>
-      <c r="BI7" s="37"/>
-      <c r="BJ7" s="37"/>
-      <c r="BK7" s="37"/>
-      <c r="BL7" s="37"/>
-      <c r="BM7" s="37"/>
-      <c r="BN7" s="37"/>
-      <c r="BO7" s="37"/>
-      <c r="BP7" s="37"/>
-      <c r="BQ7" s="37"/>
-      <c r="BR7" s="37"/>
-      <c r="BS7" s="37"/>
-      <c r="BT7" s="37"/>
-      <c r="BU7" s="37"/>
-      <c r="BV7" s="37"/>
-      <c r="BW7" s="37"/>
-      <c r="BX7" s="37"/>
-      <c r="BY7" s="37"/>
-      <c r="BZ7" s="37"/>
-      <c r="CA7" s="37"/>
-      <c r="CB7" s="37"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
+      <c r="M7" s="25"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="25"/>
+      <c r="P7" s="25"/>
+      <c r="Q7" s="25"/>
+      <c r="R7" s="25"/>
+      <c r="S7" s="25"/>
+      <c r="T7" s="25"/>
+      <c r="U7" s="25"/>
+      <c r="V7" s="25"/>
+      <c r="W7" s="25"/>
+      <c r="X7" s="25"/>
+      <c r="Y7" s="25"/>
+      <c r="Z7" s="25"/>
+      <c r="AA7" s="25"/>
+      <c r="AB7" s="25"/>
+      <c r="AC7" s="25"/>
+      <c r="AD7" s="25"/>
+      <c r="AE7" s="25"/>
+      <c r="AF7" s="25"/>
+      <c r="AG7" s="25"/>
+      <c r="AH7" s="25"/>
+      <c r="AI7" s="25"/>
+      <c r="AJ7" s="25"/>
+      <c r="AK7" s="25"/>
+      <c r="AL7" s="25"/>
+      <c r="AM7" s="25"/>
+      <c r="AN7" s="25"/>
+      <c r="AO7" s="25"/>
+      <c r="AP7" s="25"/>
+      <c r="AQ7" s="25"/>
+      <c r="AR7" s="25"/>
+      <c r="AS7" s="25"/>
+      <c r="AT7" s="25"/>
+      <c r="AU7" s="25"/>
+      <c r="AV7" s="25"/>
+      <c r="AW7" s="25"/>
+      <c r="AX7" s="25"/>
+      <c r="AY7" s="25"/>
+      <c r="AZ7" s="25"/>
+      <c r="BA7" s="25"/>
+      <c r="BB7" s="25"/>
+      <c r="BC7" s="25"/>
+      <c r="BD7" s="25"/>
+      <c r="BE7" s="25"/>
+      <c r="BF7" s="25"/>
+      <c r="BG7" s="25"/>
+      <c r="BH7" s="25"/>
+      <c r="BI7" s="25"/>
+      <c r="BJ7" s="25"/>
+      <c r="BK7" s="25"/>
+      <c r="BL7" s="25"/>
+      <c r="BM7" s="25"/>
+      <c r="BN7" s="25"/>
+      <c r="BO7" s="25"/>
+      <c r="BP7" s="25"/>
+      <c r="BQ7" s="25"/>
+      <c r="BR7" s="25"/>
+      <c r="BS7" s="25"/>
+      <c r="BT7" s="25"/>
+      <c r="BU7" s="25"/>
+      <c r="BV7" s="25"/>
+      <c r="BW7" s="25"/>
+      <c r="BX7" s="25"/>
+      <c r="BY7" s="25"/>
+      <c r="BZ7" s="25"/>
+      <c r="CA7" s="25"/>
+      <c r="CB7" s="25"/>
     </row>
     <row r="8" spans="1:85" ht="23.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="34">
+      <c r="B8" s="42"/>
+      <c r="C8" s="43">
         <f>SUM(C5:D7)</f>
         <v>75</v>
       </c>
-      <c r="D8" s="35"/>
+      <c r="D8" s="36"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="25">
-        <v>1</v>
-      </c>
-      <c r="G8" s="25">
+      <c r="F8" s="44">
+        <v>1</v>
+      </c>
+      <c r="G8" s="44">
         <v>2</v>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="44">
         <v>3</v>
       </c>
-      <c r="I8" s="25">
+      <c r="I8" s="44">
         <v>4</v>
       </c>
-      <c r="J8" s="25">
+      <c r="J8" s="44">
         <v>5</v>
       </c>
-      <c r="K8" s="25">
+      <c r="K8" s="44">
         <v>6</v>
       </c>
-      <c r="L8" s="25">
+      <c r="L8" s="44">
         <v>7</v>
       </c>
-      <c r="M8" s="25">
+      <c r="M8" s="44">
         <v>8</v>
       </c>
-      <c r="N8" s="25">
+      <c r="N8" s="44">
         <v>9</v>
       </c>
-      <c r="O8" s="25">
+      <c r="O8" s="44">
         <v>10</v>
       </c>
-      <c r="P8" s="25">
+      <c r="P8" s="44">
         <v>11</v>
       </c>
-      <c r="Q8" s="25">
+      <c r="Q8" s="44">
         <v>12</v>
       </c>
-      <c r="R8" s="25">
+      <c r="R8" s="44">
         <v>13</v>
       </c>
-      <c r="S8" s="25">
+      <c r="S8" s="44">
         <v>14</v>
       </c>
-      <c r="T8" s="25">
+      <c r="T8" s="44">
         <v>15</v>
       </c>
-      <c r="U8" s="25">
+      <c r="U8" s="44">
         <v>16</v>
       </c>
-      <c r="V8" s="25">
+      <c r="V8" s="44">
         <v>17</v>
       </c>
-      <c r="W8" s="25">
+      <c r="W8" s="44">
         <v>18</v>
       </c>
-      <c r="X8" s="25">
+      <c r="X8" s="44">
         <v>19</v>
       </c>
-      <c r="Y8" s="25">
+      <c r="Y8" s="44">
         <v>20</v>
       </c>
-      <c r="Z8" s="25">
+      <c r="Z8" s="44">
         <v>21</v>
       </c>
-      <c r="AA8" s="25">
+      <c r="AA8" s="44">
         <v>22</v>
       </c>
-      <c r="AB8" s="25">
+      <c r="AB8" s="44">
         <v>23</v>
       </c>
-      <c r="AC8" s="25">
+      <c r="AC8" s="44">
         <v>24</v>
       </c>
-      <c r="AD8" s="25">
+      <c r="AD8" s="44">
         <v>25</v>
       </c>
-      <c r="AE8" s="25">
+      <c r="AE8" s="44">
         <v>26</v>
       </c>
-      <c r="AF8" s="25">
+      <c r="AF8" s="44">
         <v>27</v>
       </c>
-      <c r="AG8" s="25">
+      <c r="AG8" s="44">
         <v>28</v>
       </c>
-      <c r="AH8" s="25">
+      <c r="AH8" s="44">
         <v>29</v>
       </c>
-      <c r="AI8" s="25">
+      <c r="AI8" s="44">
         <v>30</v>
       </c>
-      <c r="AJ8" s="25">
+      <c r="AJ8" s="44">
         <v>31</v>
       </c>
-      <c r="AK8" s="25">
+      <c r="AK8" s="44">
         <v>32</v>
       </c>
-      <c r="AL8" s="25">
+      <c r="AL8" s="44">
         <v>33</v>
       </c>
-      <c r="AM8" s="25">
+      <c r="AM8" s="44">
         <v>34</v>
       </c>
-      <c r="AN8" s="25">
+      <c r="AN8" s="44">
         <v>35</v>
       </c>
-      <c r="AO8" s="25">
+      <c r="AO8" s="44">
         <v>36</v>
       </c>
-      <c r="AP8" s="25">
+      <c r="AP8" s="44">
         <v>37</v>
       </c>
-      <c r="AQ8" s="25">
+      <c r="AQ8" s="44">
         <v>38</v>
       </c>
-      <c r="AR8" s="25">
+      <c r="AR8" s="44">
         <v>39</v>
       </c>
-      <c r="AS8" s="25">
+      <c r="AS8" s="44">
         <v>40</v>
       </c>
-      <c r="AT8" s="25">
+      <c r="AT8" s="44">
         <v>41</v>
       </c>
-      <c r="AU8" s="25">
+      <c r="AU8" s="44">
         <v>42</v>
       </c>
-      <c r="AV8" s="25">
+      <c r="AV8" s="44">
         <v>43</v>
       </c>
-      <c r="AW8" s="25">
+      <c r="AW8" s="44">
         <v>44</v>
       </c>
-      <c r="AX8" s="25">
+      <c r="AX8" s="44">
         <v>45</v>
       </c>
-      <c r="AY8" s="25">
+      <c r="AY8" s="44">
         <v>46</v>
       </c>
-      <c r="AZ8" s="25">
+      <c r="AZ8" s="44">
         <v>47</v>
       </c>
-      <c r="BA8" s="25">
+      <c r="BA8" s="44">
         <v>48</v>
       </c>
-      <c r="BB8" s="25">
+      <c r="BB8" s="44">
         <v>49</v>
       </c>
-      <c r="BC8" s="25">
+      <c r="BC8" s="44">
         <v>50</v>
       </c>
-      <c r="BD8" s="25">
+      <c r="BD8" s="44">
         <v>51</v>
       </c>
-      <c r="BE8" s="25">
+      <c r="BE8" s="44">
         <v>52</v>
       </c>
-      <c r="BF8" s="25">
+      <c r="BF8" s="44">
         <v>53</v>
       </c>
-      <c r="BG8" s="25">
+      <c r="BG8" s="44">
         <v>54</v>
       </c>
-      <c r="BH8" s="25">
+      <c r="BH8" s="44">
         <v>55</v>
       </c>
-      <c r="BI8" s="25">
+      <c r="BI8" s="44">
         <v>56</v>
       </c>
-      <c r="BJ8" s="25">
+      <c r="BJ8" s="44">
         <v>57</v>
       </c>
-      <c r="BK8" s="25">
+      <c r="BK8" s="44">
         <v>58</v>
       </c>
-      <c r="BL8" s="25">
+      <c r="BL8" s="44">
         <v>59</v>
       </c>
-      <c r="BM8" s="25">
+      <c r="BM8" s="44">
         <v>60</v>
       </c>
-      <c r="BN8" s="25">
+      <c r="BN8" s="44">
         <v>61</v>
       </c>
-      <c r="BO8" s="25">
+      <c r="BO8" s="44">
         <v>62</v>
       </c>
-      <c r="BP8" s="25">
+      <c r="BP8" s="44">
         <v>63</v>
       </c>
-      <c r="BQ8" s="25">
+      <c r="BQ8" s="44">
         <v>64</v>
       </c>
-      <c r="BR8" s="25">
+      <c r="BR8" s="44">
         <v>65</v>
       </c>
-      <c r="BS8" s="25">
+      <c r="BS8" s="44">
         <v>66</v>
       </c>
-      <c r="BT8" s="25">
+      <c r="BT8" s="44">
         <v>67</v>
       </c>
-      <c r="BU8" s="25">
+      <c r="BU8" s="44">
         <v>68</v>
       </c>
-      <c r="BV8" s="25">
+      <c r="BV8" s="44">
         <v>69</v>
       </c>
-      <c r="BW8" s="25">
+      <c r="BW8" s="44">
         <v>70</v>
       </c>
-      <c r="BX8" s="25">
+      <c r="BX8" s="44">
         <v>71</v>
       </c>
-      <c r="BY8" s="25">
+      <c r="BY8" s="44">
         <v>72</v>
       </c>
-      <c r="BZ8" s="25">
+      <c r="BZ8" s="44">
         <v>73</v>
       </c>
-      <c r="CA8" s="25">
+      <c r="CA8" s="44">
         <v>74</v>
       </c>
-      <c r="CB8" s="25">
+      <c r="CB8" s="44">
         <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="30" t="s">
+      <c r="A9" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="32" t="s">
+      <c r="C9" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="31"/>
+      <c r="D9" s="53"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="26"/>
-      <c r="J9" s="26"/>
-      <c r="K9" s="26"/>
-      <c r="L9" s="26"/>
-      <c r="M9" s="26"/>
-      <c r="N9" s="26"/>
-      <c r="O9" s="26"/>
-      <c r="P9" s="26"/>
-      <c r="Q9" s="26"/>
-      <c r="R9" s="26"/>
-      <c r="S9" s="26"/>
-      <c r="T9" s="26"/>
-      <c r="U9" s="26"/>
-      <c r="V9" s="26"/>
-      <c r="W9" s="26"/>
-      <c r="X9" s="26"/>
-      <c r="Y9" s="26"/>
-      <c r="Z9" s="26"/>
-      <c r="AA9" s="26"/>
-      <c r="AB9" s="26"/>
-      <c r="AC9" s="26"/>
-      <c r="AD9" s="26"/>
-      <c r="AE9" s="26"/>
-      <c r="AF9" s="26"/>
-      <c r="AG9" s="26"/>
-      <c r="AH9" s="26"/>
-      <c r="AI9" s="26"/>
-      <c r="AJ9" s="26"/>
-      <c r="AK9" s="26"/>
-      <c r="AL9" s="26"/>
-      <c r="AM9" s="26"/>
-      <c r="AN9" s="26"/>
-      <c r="AO9" s="26"/>
-      <c r="AP9" s="26"/>
-      <c r="AQ9" s="26"/>
-      <c r="AR9" s="26"/>
-      <c r="AS9" s="26"/>
-      <c r="AT9" s="26"/>
-      <c r="AU9" s="26"/>
-      <c r="AV9" s="26"/>
-      <c r="AW9" s="26"/>
-      <c r="AX9" s="26"/>
-      <c r="AY9" s="26"/>
-      <c r="AZ9" s="26"/>
-      <c r="BA9" s="26"/>
-      <c r="BB9" s="26"/>
-      <c r="BC9" s="26"/>
-      <c r="BD9" s="26"/>
-      <c r="BE9" s="26"/>
-      <c r="BF9" s="26"/>
-      <c r="BG9" s="26"/>
-      <c r="BH9" s="26"/>
-      <c r="BI9" s="26"/>
-      <c r="BJ9" s="26"/>
-      <c r="BK9" s="26"/>
-      <c r="BL9" s="26"/>
-      <c r="BM9" s="26"/>
-      <c r="BN9" s="26"/>
-      <c r="BO9" s="26"/>
-      <c r="BP9" s="26"/>
-      <c r="BQ9" s="26"/>
-      <c r="BR9" s="26"/>
-      <c r="BS9" s="26"/>
-      <c r="BT9" s="26"/>
-      <c r="BU9" s="26"/>
-      <c r="BV9" s="26"/>
-      <c r="BW9" s="26"/>
-      <c r="BX9" s="26"/>
-      <c r="BY9" s="26"/>
-      <c r="BZ9" s="26"/>
-      <c r="CA9" s="26"/>
-      <c r="CB9" s="26"/>
+      <c r="F9" s="45"/>
+      <c r="G9" s="45"/>
+      <c r="H9" s="45"/>
+      <c r="I9" s="45"/>
+      <c r="J9" s="45"/>
+      <c r="K9" s="45"/>
+      <c r="L9" s="45"/>
+      <c r="M9" s="45"/>
+      <c r="N9" s="45"/>
+      <c r="O9" s="45"/>
+      <c r="P9" s="45"/>
+      <c r="Q9" s="45"/>
+      <c r="R9" s="45"/>
+      <c r="S9" s="45"/>
+      <c r="T9" s="45"/>
+      <c r="U9" s="45"/>
+      <c r="V9" s="45"/>
+      <c r="W9" s="45"/>
+      <c r="X9" s="45"/>
+      <c r="Y9" s="45"/>
+      <c r="Z9" s="45"/>
+      <c r="AA9" s="45"/>
+      <c r="AB9" s="45"/>
+      <c r="AC9" s="45"/>
+      <c r="AD9" s="45"/>
+      <c r="AE9" s="45"/>
+      <c r="AF9" s="45"/>
+      <c r="AG9" s="45"/>
+      <c r="AH9" s="45"/>
+      <c r="AI9" s="45"/>
+      <c r="AJ9" s="45"/>
+      <c r="AK9" s="45"/>
+      <c r="AL9" s="45"/>
+      <c r="AM9" s="45"/>
+      <c r="AN9" s="45"/>
+      <c r="AO9" s="45"/>
+      <c r="AP9" s="45"/>
+      <c r="AQ9" s="45"/>
+      <c r="AR9" s="45"/>
+      <c r="AS9" s="45"/>
+      <c r="AT9" s="45"/>
+      <c r="AU9" s="45"/>
+      <c r="AV9" s="45"/>
+      <c r="AW9" s="45"/>
+      <c r="AX9" s="45"/>
+      <c r="AY9" s="45"/>
+      <c r="AZ9" s="45"/>
+      <c r="BA9" s="45"/>
+      <c r="BB9" s="45"/>
+      <c r="BC9" s="45"/>
+      <c r="BD9" s="45"/>
+      <c r="BE9" s="45"/>
+      <c r="BF9" s="45"/>
+      <c r="BG9" s="45"/>
+      <c r="BH9" s="45"/>
+      <c r="BI9" s="45"/>
+      <c r="BJ9" s="45"/>
+      <c r="BK9" s="45"/>
+      <c r="BL9" s="45"/>
+      <c r="BM9" s="45"/>
+      <c r="BN9" s="45"/>
+      <c r="BO9" s="45"/>
+      <c r="BP9" s="45"/>
+      <c r="BQ9" s="45"/>
+      <c r="BR9" s="45"/>
+      <c r="BS9" s="45"/>
+      <c r="BT9" s="45"/>
+      <c r="BU9" s="45"/>
+      <c r="BV9" s="45"/>
+      <c r="BW9" s="45"/>
+      <c r="BX9" s="45"/>
+      <c r="BY9" s="45"/>
+      <c r="BZ9" s="45"/>
+      <c r="CA9" s="45"/>
+      <c r="CB9" s="45"/>
     </row>
     <row r="10" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="30"/>
-      <c r="B10" s="31"/>
+      <c r="A10" s="52"/>
+      <c r="B10" s="53"/>
       <c r="C10" s="6"/>
       <c r="D10" s="4" t="s">
         <v>12</v>
@@ -2935,72 +2939,72 @@
       <c r="P17" s="8">
         <v>0</v>
       </c>
-      <c r="Q17" s="22" t="s">
+      <c r="Q17" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="R17" s="23"/>
-      <c r="S17" s="23"/>
-      <c r="T17" s="23"/>
-      <c r="U17" s="23"/>
-      <c r="V17" s="23"/>
-      <c r="W17" s="23"/>
-      <c r="X17" s="23"/>
-      <c r="Y17" s="23"/>
-      <c r="Z17" s="23"/>
-      <c r="AA17" s="23"/>
-      <c r="AB17" s="23"/>
-      <c r="AC17" s="23"/>
-      <c r="AD17" s="23"/>
-      <c r="AE17" s="23"/>
-      <c r="AF17" s="23"/>
-      <c r="AG17" s="23"/>
-      <c r="AH17" s="23"/>
-      <c r="AI17" s="23"/>
-      <c r="AJ17" s="23"/>
-      <c r="AK17" s="23"/>
-      <c r="AL17" s="23"/>
-      <c r="AM17" s="23"/>
-      <c r="AN17" s="23"/>
-      <c r="AO17" s="23"/>
-      <c r="AP17" s="23"/>
-      <c r="AQ17" s="23"/>
-      <c r="AR17" s="23"/>
-      <c r="AS17" s="23"/>
-      <c r="AT17" s="23"/>
-      <c r="AU17" s="23"/>
-      <c r="AV17" s="23"/>
-      <c r="AW17" s="23"/>
-      <c r="AX17" s="23"/>
-      <c r="AY17" s="23"/>
-      <c r="AZ17" s="23"/>
-      <c r="BA17" s="23"/>
-      <c r="BB17" s="23"/>
-      <c r="BC17" s="23"/>
-      <c r="BD17" s="23"/>
-      <c r="BE17" s="23"/>
-      <c r="BF17" s="23"/>
-      <c r="BG17" s="23"/>
-      <c r="BH17" s="23"/>
-      <c r="BI17" s="23"/>
-      <c r="BJ17" s="23"/>
-      <c r="BK17" s="23"/>
-      <c r="BL17" s="23"/>
-      <c r="BM17" s="23"/>
-      <c r="BN17" s="23"/>
-      <c r="BO17" s="23"/>
-      <c r="BP17" s="23"/>
-      <c r="BQ17" s="23"/>
-      <c r="BR17" s="23"/>
-      <c r="BS17" s="23"/>
-      <c r="BT17" s="23"/>
-      <c r="BU17" s="23"/>
-      <c r="BV17" s="23"/>
-      <c r="BW17" s="23"/>
-      <c r="BX17" s="23"/>
-      <c r="BY17" s="23"/>
-      <c r="BZ17" s="23"/>
-      <c r="CA17" s="23"/>
-      <c r="CB17" s="24"/>
+      <c r="R17" s="47"/>
+      <c r="S17" s="47"/>
+      <c r="T17" s="47"/>
+      <c r="U17" s="47"/>
+      <c r="V17" s="47"/>
+      <c r="W17" s="47"/>
+      <c r="X17" s="47"/>
+      <c r="Y17" s="47"/>
+      <c r="Z17" s="47"/>
+      <c r="AA17" s="47"/>
+      <c r="AB17" s="47"/>
+      <c r="AC17" s="47"/>
+      <c r="AD17" s="47"/>
+      <c r="AE17" s="47"/>
+      <c r="AF17" s="47"/>
+      <c r="AG17" s="47"/>
+      <c r="AH17" s="47"/>
+      <c r="AI17" s="47"/>
+      <c r="AJ17" s="47"/>
+      <c r="AK17" s="47"/>
+      <c r="AL17" s="47"/>
+      <c r="AM17" s="47"/>
+      <c r="AN17" s="47"/>
+      <c r="AO17" s="47"/>
+      <c r="AP17" s="47"/>
+      <c r="AQ17" s="47"/>
+      <c r="AR17" s="47"/>
+      <c r="AS17" s="47"/>
+      <c r="AT17" s="47"/>
+      <c r="AU17" s="47"/>
+      <c r="AV17" s="47"/>
+      <c r="AW17" s="47"/>
+      <c r="AX17" s="47"/>
+      <c r="AY17" s="47"/>
+      <c r="AZ17" s="47"/>
+      <c r="BA17" s="47"/>
+      <c r="BB17" s="47"/>
+      <c r="BC17" s="47"/>
+      <c r="BD17" s="47"/>
+      <c r="BE17" s="47"/>
+      <c r="BF17" s="47"/>
+      <c r="BG17" s="47"/>
+      <c r="BH17" s="47"/>
+      <c r="BI17" s="47"/>
+      <c r="BJ17" s="47"/>
+      <c r="BK17" s="47"/>
+      <c r="BL17" s="47"/>
+      <c r="BM17" s="47"/>
+      <c r="BN17" s="47"/>
+      <c r="BO17" s="47"/>
+      <c r="BP17" s="47"/>
+      <c r="BQ17" s="47"/>
+      <c r="BR17" s="47"/>
+      <c r="BS17" s="47"/>
+      <c r="BT17" s="47"/>
+      <c r="BU17" s="47"/>
+      <c r="BV17" s="47"/>
+      <c r="BW17" s="47"/>
+      <c r="BX17" s="47"/>
+      <c r="BY17" s="47"/>
+      <c r="BZ17" s="47"/>
+      <c r="CA17" s="47"/>
+      <c r="CB17" s="48"/>
     </row>
     <row r="18" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9">
@@ -4164,87 +4168,237 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E28" s="27" t="s">
+      <c r="E28" s="49" t="s">
         <v>48</v>
       </c>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="27"/>
-      <c r="I28" s="27"/>
-      <c r="J28" s="27"/>
-      <c r="K28" s="27"/>
-      <c r="L28" s="27"/>
-      <c r="M28" s="27"/>
-      <c r="N28" s="27"/>
-      <c r="O28" s="27"/>
-      <c r="P28" s="27"/>
-      <c r="Q28" s="27"/>
-      <c r="R28" s="27"/>
-      <c r="S28" s="27"/>
-      <c r="T28" s="27"/>
-      <c r="U28" s="27"/>
-      <c r="V28" s="27"/>
-      <c r="W28" s="27"/>
-      <c r="X28" s="27"/>
-      <c r="Y28" s="27"/>
-      <c r="Z28" s="27"/>
-      <c r="AA28" s="27"/>
-      <c r="AB28" s="27"/>
-      <c r="AC28" s="27"/>
-      <c r="AD28" s="27"/>
-      <c r="AE28" s="27"/>
-      <c r="AF28" s="27"/>
-      <c r="AG28" s="27"/>
-      <c r="AH28" s="27"/>
-      <c r="AI28" s="27"/>
-      <c r="AJ28" s="27"/>
-      <c r="AK28" s="27"/>
-      <c r="AL28" s="27"/>
-      <c r="AM28" s="27"/>
-      <c r="AN28" s="27"/>
-      <c r="AO28" s="27"/>
-      <c r="AP28" s="27"/>
-      <c r="AQ28" s="27"/>
-      <c r="AR28" s="27"/>
-      <c r="AS28" s="27"/>
-      <c r="AT28" s="27"/>
-      <c r="AU28" s="27"/>
-      <c r="AV28" s="27"/>
-      <c r="AW28" s="27"/>
-      <c r="AX28" s="27"/>
-      <c r="AY28" s="27"/>
-      <c r="AZ28" s="27"/>
-      <c r="BA28" s="27"/>
-      <c r="BB28" s="27"/>
-      <c r="BC28" s="27"/>
-      <c r="BD28" s="27"/>
-      <c r="BE28" s="27"/>
-      <c r="BF28" s="27"/>
-      <c r="BG28" s="27"/>
-      <c r="BH28" s="27"/>
-      <c r="BI28" s="27"/>
-      <c r="BJ28" s="27"/>
-      <c r="BK28" s="27"/>
-      <c r="BL28" s="27"/>
-      <c r="BM28" s="27"/>
-      <c r="BN28" s="27"/>
-      <c r="BO28" s="27"/>
-      <c r="BP28" s="27"/>
-      <c r="BQ28" s="27"/>
-      <c r="BR28" s="27"/>
-      <c r="BS28" s="27"/>
-      <c r="BT28" s="27"/>
-      <c r="BU28" s="27"/>
-      <c r="BV28" s="27"/>
-      <c r="BW28" s="27"/>
-      <c r="BX28" s="27"/>
-      <c r="BY28" s="27"/>
-      <c r="BZ28" s="27"/>
-      <c r="CA28" s="27"/>
-      <c r="CB28" s="27"/>
+      <c r="F28" s="49"/>
+      <c r="G28" s="49"/>
+      <c r="H28" s="49"/>
+      <c r="I28" s="49"/>
+      <c r="J28" s="49"/>
+      <c r="K28" s="49"/>
+      <c r="L28" s="49"/>
+      <c r="M28" s="49"/>
+      <c r="N28" s="49"/>
+      <c r="O28" s="49"/>
+      <c r="P28" s="49"/>
+      <c r="Q28" s="49"/>
+      <c r="R28" s="49"/>
+      <c r="S28" s="49"/>
+      <c r="T28" s="49"/>
+      <c r="U28" s="49"/>
+      <c r="V28" s="49"/>
+      <c r="W28" s="49"/>
+      <c r="X28" s="49"/>
+      <c r="Y28" s="49"/>
+      <c r="Z28" s="49"/>
+      <c r="AA28" s="49"/>
+      <c r="AB28" s="49"/>
+      <c r="AC28" s="49"/>
+      <c r="AD28" s="49"/>
+      <c r="AE28" s="49"/>
+      <c r="AF28" s="49"/>
+      <c r="AG28" s="49"/>
+      <c r="AH28" s="49"/>
+      <c r="AI28" s="49"/>
+      <c r="AJ28" s="49"/>
+      <c r="AK28" s="49"/>
+      <c r="AL28" s="49"/>
+      <c r="AM28" s="49"/>
+      <c r="AN28" s="49"/>
+      <c r="AO28" s="49"/>
+      <c r="AP28" s="49"/>
+      <c r="AQ28" s="49"/>
+      <c r="AR28" s="49"/>
+      <c r="AS28" s="49"/>
+      <c r="AT28" s="49"/>
+      <c r="AU28" s="49"/>
+      <c r="AV28" s="49"/>
+      <c r="AW28" s="49"/>
+      <c r="AX28" s="49"/>
+      <c r="AY28" s="49"/>
+      <c r="AZ28" s="49"/>
+      <c r="BA28" s="49"/>
+      <c r="BB28" s="49"/>
+      <c r="BC28" s="49"/>
+      <c r="BD28" s="49"/>
+      <c r="BE28" s="49"/>
+      <c r="BF28" s="49"/>
+      <c r="BG28" s="49"/>
+      <c r="BH28" s="49"/>
+      <c r="BI28" s="49"/>
+      <c r="BJ28" s="49"/>
+      <c r="BK28" s="49"/>
+      <c r="BL28" s="49"/>
+      <c r="BM28" s="49"/>
+      <c r="BN28" s="49"/>
+      <c r="BO28" s="49"/>
+      <c r="BP28" s="49"/>
+      <c r="BQ28" s="49"/>
+      <c r="BR28" s="49"/>
+      <c r="BS28" s="49"/>
+      <c r="BT28" s="49"/>
+      <c r="BU28" s="49"/>
+      <c r="BV28" s="49"/>
+      <c r="BW28" s="49"/>
+      <c r="BX28" s="49"/>
+      <c r="BY28" s="49"/>
+      <c r="BZ28" s="49"/>
+      <c r="CA28" s="49"/>
+      <c r="CB28" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="174">
+    <mergeCell ref="Q17:CB17"/>
+    <mergeCell ref="BX8:BX9"/>
+    <mergeCell ref="BY8:BY9"/>
+    <mergeCell ref="BZ8:BZ9"/>
+    <mergeCell ref="CA8:CA9"/>
+    <mergeCell ref="CB8:CB9"/>
+    <mergeCell ref="E28:CB28"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="BO8:BO9"/>
+    <mergeCell ref="BP8:BP9"/>
+    <mergeCell ref="BQ8:BQ9"/>
+    <mergeCell ref="BR8:BR9"/>
+    <mergeCell ref="BS8:BS9"/>
+    <mergeCell ref="BT8:BT9"/>
+    <mergeCell ref="BU8:BU9"/>
+    <mergeCell ref="BV8:BV9"/>
+    <mergeCell ref="BW8:BW9"/>
+    <mergeCell ref="BF8:BF9"/>
+    <mergeCell ref="BG8:BG9"/>
+    <mergeCell ref="BH8:BH9"/>
+    <mergeCell ref="BI8:BI9"/>
+    <mergeCell ref="BJ8:BJ9"/>
+    <mergeCell ref="BK8:BK9"/>
+    <mergeCell ref="BL8:BL9"/>
+    <mergeCell ref="BM8:BM9"/>
+    <mergeCell ref="BN8:BN9"/>
+    <mergeCell ref="AW8:AW9"/>
+    <mergeCell ref="AX8:AX9"/>
+    <mergeCell ref="AY8:AY9"/>
+    <mergeCell ref="AZ8:AZ9"/>
+    <mergeCell ref="BA8:BA9"/>
+    <mergeCell ref="BB8:BB9"/>
+    <mergeCell ref="BC8:BC9"/>
+    <mergeCell ref="BD8:BD9"/>
+    <mergeCell ref="BE8:BE9"/>
+    <mergeCell ref="AN8:AN9"/>
+    <mergeCell ref="AO8:AO9"/>
+    <mergeCell ref="AP8:AP9"/>
+    <mergeCell ref="AQ8:AQ9"/>
+    <mergeCell ref="AR8:AR9"/>
+    <mergeCell ref="AS8:AS9"/>
+    <mergeCell ref="AT8:AT9"/>
+    <mergeCell ref="AU8:AU9"/>
+    <mergeCell ref="AV8:AV9"/>
+    <mergeCell ref="AE8:AE9"/>
+    <mergeCell ref="AF8:AF9"/>
+    <mergeCell ref="AG8:AG9"/>
+    <mergeCell ref="AH8:AH9"/>
+    <mergeCell ref="AI8:AI9"/>
+    <mergeCell ref="AJ8:AJ9"/>
+    <mergeCell ref="AK8:AK9"/>
+    <mergeCell ref="AL8:AL9"/>
+    <mergeCell ref="AM8:AM9"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="W8:W9"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AD8:AD9"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="BU2:BU7"/>
+    <mergeCell ref="BV2:BV7"/>
+    <mergeCell ref="BW2:BW7"/>
+    <mergeCell ref="BX2:BX7"/>
+    <mergeCell ref="BY2:BY7"/>
+    <mergeCell ref="BZ2:BZ7"/>
+    <mergeCell ref="CA2:CA7"/>
+    <mergeCell ref="CB2:CB7"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="BL2:BL7"/>
+    <mergeCell ref="BM2:BM7"/>
+    <mergeCell ref="BN2:BN7"/>
+    <mergeCell ref="BO2:BO7"/>
+    <mergeCell ref="BP2:BP7"/>
+    <mergeCell ref="BQ2:BQ7"/>
+    <mergeCell ref="BR2:BR7"/>
+    <mergeCell ref="BS2:BS7"/>
+    <mergeCell ref="BT2:BT7"/>
+    <mergeCell ref="BC2:BC7"/>
+    <mergeCell ref="BD2:BD7"/>
+    <mergeCell ref="BE2:BE7"/>
+    <mergeCell ref="BF2:BF7"/>
+    <mergeCell ref="BG2:BG7"/>
+    <mergeCell ref="BH2:BH7"/>
+    <mergeCell ref="BI2:BI7"/>
+    <mergeCell ref="BJ2:BJ7"/>
+    <mergeCell ref="BK2:BK7"/>
+    <mergeCell ref="AT2:AT7"/>
+    <mergeCell ref="AU2:AU7"/>
+    <mergeCell ref="AV2:AV7"/>
+    <mergeCell ref="AW2:AW7"/>
+    <mergeCell ref="AX2:AX7"/>
+    <mergeCell ref="AY2:AY7"/>
+    <mergeCell ref="AZ2:AZ7"/>
+    <mergeCell ref="BA2:BA7"/>
+    <mergeCell ref="BB2:BB7"/>
+    <mergeCell ref="AK2:AK7"/>
+    <mergeCell ref="AL2:AL7"/>
+    <mergeCell ref="AM2:AM7"/>
+    <mergeCell ref="AN2:AN7"/>
+    <mergeCell ref="AO2:AO7"/>
+    <mergeCell ref="AP2:AP7"/>
+    <mergeCell ref="AQ2:AQ7"/>
+    <mergeCell ref="AR2:AR7"/>
+    <mergeCell ref="AS2:AS7"/>
+    <mergeCell ref="AG2:AG7"/>
+    <mergeCell ref="AD2:AD7"/>
+    <mergeCell ref="AE2:AE7"/>
+    <mergeCell ref="AF2:AF7"/>
+    <mergeCell ref="AB2:AB7"/>
+    <mergeCell ref="AC2:AC7"/>
+    <mergeCell ref="AH2:AH7"/>
+    <mergeCell ref="AI2:AI7"/>
+    <mergeCell ref="AJ2:AJ7"/>
+    <mergeCell ref="L1:P1"/>
+    <mergeCell ref="AA2:AA7"/>
+    <mergeCell ref="N2:N7"/>
+    <mergeCell ref="O2:O7"/>
+    <mergeCell ref="P2:P7"/>
+    <mergeCell ref="Q2:Q7"/>
+    <mergeCell ref="R2:R7"/>
+    <mergeCell ref="S2:S7"/>
+    <mergeCell ref="T2:T7"/>
+    <mergeCell ref="U2:U7"/>
+    <mergeCell ref="V2:V7"/>
+    <mergeCell ref="Q1:U1"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="W2:W7"/>
     <mergeCell ref="X2:X7"/>
@@ -4269,156 +4423,6 @@
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="V1:Z1"/>
-    <mergeCell ref="L1:P1"/>
-    <mergeCell ref="AA2:AA7"/>
-    <mergeCell ref="N2:N7"/>
-    <mergeCell ref="O2:O7"/>
-    <mergeCell ref="P2:P7"/>
-    <mergeCell ref="Q2:Q7"/>
-    <mergeCell ref="R2:R7"/>
-    <mergeCell ref="S2:S7"/>
-    <mergeCell ref="T2:T7"/>
-    <mergeCell ref="U2:U7"/>
-    <mergeCell ref="V2:V7"/>
-    <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="AG2:AG7"/>
-    <mergeCell ref="AD2:AD7"/>
-    <mergeCell ref="AE2:AE7"/>
-    <mergeCell ref="AF2:AF7"/>
-    <mergeCell ref="AB2:AB7"/>
-    <mergeCell ref="AC2:AC7"/>
-    <mergeCell ref="AH2:AH7"/>
-    <mergeCell ref="AI2:AI7"/>
-    <mergeCell ref="AJ2:AJ7"/>
-    <mergeCell ref="AK2:AK7"/>
-    <mergeCell ref="AL2:AL7"/>
-    <mergeCell ref="AM2:AM7"/>
-    <mergeCell ref="AN2:AN7"/>
-    <mergeCell ref="AO2:AO7"/>
-    <mergeCell ref="AP2:AP7"/>
-    <mergeCell ref="AQ2:AQ7"/>
-    <mergeCell ref="AR2:AR7"/>
-    <mergeCell ref="AS2:AS7"/>
-    <mergeCell ref="BH2:BH7"/>
-    <mergeCell ref="BI2:BI7"/>
-    <mergeCell ref="BJ2:BJ7"/>
-    <mergeCell ref="BK2:BK7"/>
-    <mergeCell ref="AT2:AT7"/>
-    <mergeCell ref="AU2:AU7"/>
-    <mergeCell ref="AV2:AV7"/>
-    <mergeCell ref="AW2:AW7"/>
-    <mergeCell ref="AX2:AX7"/>
-    <mergeCell ref="AY2:AY7"/>
-    <mergeCell ref="AZ2:AZ7"/>
-    <mergeCell ref="BA2:BA7"/>
-    <mergeCell ref="BB2:BB7"/>
-    <mergeCell ref="BU2:BU7"/>
-    <mergeCell ref="BV2:BV7"/>
-    <mergeCell ref="BW2:BW7"/>
-    <mergeCell ref="BX2:BX7"/>
-    <mergeCell ref="BY2:BY7"/>
-    <mergeCell ref="BZ2:BZ7"/>
-    <mergeCell ref="CA2:CA7"/>
-    <mergeCell ref="CB2:CB7"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="BL2:BL7"/>
-    <mergeCell ref="BM2:BM7"/>
-    <mergeCell ref="BN2:BN7"/>
-    <mergeCell ref="BO2:BO7"/>
-    <mergeCell ref="BP2:BP7"/>
-    <mergeCell ref="BQ2:BQ7"/>
-    <mergeCell ref="BR2:BR7"/>
-    <mergeCell ref="BS2:BS7"/>
-    <mergeCell ref="BT2:BT7"/>
-    <mergeCell ref="BC2:BC7"/>
-    <mergeCell ref="BD2:BD7"/>
-    <mergeCell ref="BE2:BE7"/>
-    <mergeCell ref="BF2:BF7"/>
-    <mergeCell ref="BG2:BG7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="V8:V9"/>
-    <mergeCell ref="W8:W9"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AD8:AD9"/>
-    <mergeCell ref="AE8:AE9"/>
-    <mergeCell ref="AF8:AF9"/>
-    <mergeCell ref="AG8:AG9"/>
-    <mergeCell ref="AH8:AH9"/>
-    <mergeCell ref="AI8:AI9"/>
-    <mergeCell ref="AJ8:AJ9"/>
-    <mergeCell ref="AK8:AK9"/>
-    <mergeCell ref="AL8:AL9"/>
-    <mergeCell ref="AM8:AM9"/>
-    <mergeCell ref="AN8:AN9"/>
-    <mergeCell ref="AO8:AO9"/>
-    <mergeCell ref="AP8:AP9"/>
-    <mergeCell ref="AQ8:AQ9"/>
-    <mergeCell ref="AR8:AR9"/>
-    <mergeCell ref="AS8:AS9"/>
-    <mergeCell ref="AT8:AT9"/>
-    <mergeCell ref="AU8:AU9"/>
-    <mergeCell ref="AV8:AV9"/>
-    <mergeCell ref="BJ8:BJ9"/>
-    <mergeCell ref="BK8:BK9"/>
-    <mergeCell ref="BL8:BL9"/>
-    <mergeCell ref="BM8:BM9"/>
-    <mergeCell ref="BN8:BN9"/>
-    <mergeCell ref="AW8:AW9"/>
-    <mergeCell ref="AX8:AX9"/>
-    <mergeCell ref="AY8:AY9"/>
-    <mergeCell ref="AZ8:AZ9"/>
-    <mergeCell ref="BA8:BA9"/>
-    <mergeCell ref="BB8:BB9"/>
-    <mergeCell ref="BC8:BC9"/>
-    <mergeCell ref="BD8:BD9"/>
-    <mergeCell ref="BE8:BE9"/>
-    <mergeCell ref="Q17:CB17"/>
-    <mergeCell ref="BX8:BX9"/>
-    <mergeCell ref="BY8:BY9"/>
-    <mergeCell ref="BZ8:BZ9"/>
-    <mergeCell ref="CA8:CA9"/>
-    <mergeCell ref="CB8:CB9"/>
-    <mergeCell ref="E28:CB28"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="BO8:BO9"/>
-    <mergeCell ref="BP8:BP9"/>
-    <mergeCell ref="BQ8:BQ9"/>
-    <mergeCell ref="BR8:BR9"/>
-    <mergeCell ref="BS8:BS9"/>
-    <mergeCell ref="BT8:BT9"/>
-    <mergeCell ref="BU8:BU9"/>
-    <mergeCell ref="BV8:BV9"/>
-    <mergeCell ref="BW8:BW9"/>
-    <mergeCell ref="BF8:BF9"/>
-    <mergeCell ref="BG8:BG9"/>
-    <mergeCell ref="BH8:BH9"/>
-    <mergeCell ref="BI8:BI9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" verticalDpi="0"/>

--- a/ჟურნალი/5. N301 front-end დეველოპმენტი (ინტეგრირებული მიდგომით) - Git.xlsx
+++ b/ჟურნალი/5. N301 front-end დეველოპმენტი (ინტეგრირებული მიდგომით) - Git.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\3Daudiece\Desktop\Front-end!!\0. ready\ჟურნალი\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C31875BB-90DC-4C38-9F09-E852376BAFB8}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CEB28D3-76E0-4CD3-903D-118AEB3EC026}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-122" yWindow="-122" windowWidth="29045" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -69,6 +69,7 @@
         <sz val="11"/>
         <color indexed="63"/>
         <rFont val="Sylfaen"/>
+        <family val="1"/>
       </rPr>
       <t>არმინე</t>
     </r>
@@ -79,6 +80,7 @@
         <sz val="11"/>
         <color indexed="63"/>
         <rFont val="Sylfaen"/>
+        <family val="1"/>
       </rPr>
       <t>იორდანიან</t>
     </r>
@@ -89,6 +91,7 @@
         <sz val="11"/>
         <color indexed="63"/>
         <rFont val="Sylfaen"/>
+        <family val="1"/>
       </rPr>
       <t>ალექსეი</t>
     </r>
@@ -99,6 +102,7 @@
         <sz val="11"/>
         <color indexed="63"/>
         <rFont val="Sylfaen"/>
+        <family val="1"/>
       </rPr>
       <t>მოზაიძე</t>
     </r>
@@ -109,6 +113,7 @@
         <sz val="11"/>
         <color indexed="63"/>
         <rFont val="Sylfaen"/>
+        <family val="1"/>
       </rPr>
       <t>ზურიკო</t>
     </r>
@@ -119,6 +124,7 @@
         <sz val="11"/>
         <color indexed="63"/>
         <rFont val="Sylfaen"/>
+        <family val="1"/>
       </rPr>
       <t>კორსანტია</t>
     </r>
@@ -132,6 +138,7 @@
         <sz val="11"/>
         <color indexed="63"/>
         <rFont val="Sylfaen"/>
+        <family val="1"/>
       </rPr>
       <t>ლუკა</t>
     </r>
@@ -145,6 +152,7 @@
         <sz val="11"/>
         <color indexed="63"/>
         <rFont val="Sylfaen"/>
+        <family val="1"/>
       </rPr>
       <t>საბა</t>
     </r>
@@ -155,6 +163,7 @@
         <sz val="11"/>
         <color indexed="63"/>
         <rFont val="Sylfaen"/>
+        <family val="1"/>
       </rPr>
       <t>ლაჩაშვილი</t>
     </r>
@@ -165,6 +174,7 @@
         <sz val="11"/>
         <color indexed="63"/>
         <rFont val="Sylfaen"/>
+        <family val="1"/>
       </rPr>
       <t>ალბინა</t>
     </r>
@@ -175,6 +185,7 @@
         <sz val="11"/>
         <color indexed="63"/>
         <rFont val="Sylfaen"/>
+        <family val="1"/>
       </rPr>
       <t>ძახოევი</t>
     </r>
@@ -185,6 +196,7 @@
         <sz val="11"/>
         <color indexed="63"/>
         <rFont val="Sylfaen"/>
+        <family val="1"/>
       </rPr>
       <t>მირიან</t>
     </r>
@@ -195,6 +207,7 @@
         <sz val="11"/>
         <color indexed="63"/>
         <rFont val="Sylfaen"/>
+        <family val="1"/>
       </rPr>
       <t>ქათამაძე</t>
     </r>
@@ -205,6 +218,7 @@
         <sz val="11"/>
         <color indexed="63"/>
         <rFont val="Sylfaen"/>
+        <family val="1"/>
       </rPr>
       <t>ოდიშვილი</t>
     </r>
@@ -215,6 +229,7 @@
         <sz val="11"/>
         <color indexed="63"/>
         <rFont val="Sylfaen"/>
+        <family val="1"/>
       </rPr>
       <t>ბანძელაძე</t>
     </r>
@@ -225,6 +240,7 @@
         <sz val="11"/>
         <color indexed="63"/>
         <rFont val="Sylfaen"/>
+        <family val="1"/>
       </rPr>
       <t>მირცხულავა</t>
     </r>
@@ -235,6 +251,7 @@
         <sz val="11"/>
         <color indexed="63"/>
         <rFont val="Sylfaen"/>
+        <family val="1"/>
       </rPr>
       <t>ლევან</t>
     </r>
@@ -245,6 +262,7 @@
         <sz val="11"/>
         <color indexed="63"/>
         <rFont val="Sylfaen"/>
+        <family val="1"/>
       </rPr>
       <t>გობეჯიშვილი</t>
     </r>
@@ -258,6 +276,7 @@
         <sz val="11"/>
         <color indexed="63"/>
         <rFont val="Sylfaen"/>
+        <family val="1"/>
       </rPr>
       <t>ბერიაშვილი</t>
     </r>
@@ -268,6 +287,7 @@
         <sz val="11"/>
         <color indexed="63"/>
         <rFont val="Sylfaen"/>
+        <family val="1"/>
       </rPr>
       <t>მარტიროს</t>
     </r>
@@ -278,6 +298,7 @@
         <sz val="11"/>
         <color indexed="63"/>
         <rFont val="Sylfaen"/>
+        <family val="1"/>
       </rPr>
       <t>არუთუნიან</t>
     </r>
@@ -288,6 +309,7 @@
         <sz val="11"/>
         <color indexed="63"/>
         <rFont val="Sylfaen"/>
+        <family val="1"/>
       </rPr>
       <t>ირინა</t>
     </r>
@@ -298,6 +320,7 @@
         <sz val="11"/>
         <color indexed="63"/>
         <rFont val="Sylfaen"/>
+        <family val="1"/>
       </rPr>
       <t>მატაშოვა</t>
     </r>
@@ -308,6 +331,7 @@
         <sz val="11"/>
         <color indexed="63"/>
         <rFont val="Sylfaen"/>
+        <family val="1"/>
       </rPr>
       <t>ნიკოლოზ</t>
     </r>
@@ -318,6 +342,7 @@
         <sz val="11"/>
         <color indexed="63"/>
         <rFont val="Sylfaen"/>
+        <family val="1"/>
       </rPr>
       <t>ქისიშვილი</t>
     </r>
@@ -328,6 +353,7 @@
         <sz val="11"/>
         <color indexed="63"/>
         <rFont val="Sylfaen"/>
+        <family val="1"/>
       </rPr>
       <t>დავითი</t>
     </r>
@@ -338,6 +364,7 @@
         <sz val="11"/>
         <color indexed="63"/>
         <rFont val="Sylfaen"/>
+        <family val="1"/>
       </rPr>
       <t>ვეშაგური</t>
     </r>
@@ -348,6 +375,7 @@
         <sz val="11"/>
         <color indexed="63"/>
         <rFont val="Sylfaen"/>
+        <family val="1"/>
       </rPr>
       <t>გიორგი</t>
     </r>
@@ -358,6 +386,7 @@
         <sz val="11"/>
         <color indexed="63"/>
         <rFont val="Sylfaen"/>
+        <family val="1"/>
       </rPr>
       <t>ბენდიანიშვილი</t>
     </r>
@@ -368,6 +397,7 @@
         <sz val="11"/>
         <color indexed="63"/>
         <rFont val="Sylfaen"/>
+        <family val="1"/>
       </rPr>
       <t>ვაჟა</t>
     </r>
@@ -378,6 +408,7 @@
         <sz val="11"/>
         <color indexed="63"/>
         <rFont val="Sylfaen"/>
+        <family val="1"/>
       </rPr>
       <t>ხარაზიშვილი</t>
     </r>
@@ -410,60 +441,70 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="Sylfaen"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Sylfaen"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color indexed="2"/>
       <name val="Sylfaen"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color theme="1"/>
       <name val="Sylfaen"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Sylfaen"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color indexed="2"/>
       <name val="Sylfaen"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="63"/>
       <name val="Sylfaen"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -485,12 +526,6 @@
       <patternFill patternType="solid">
         <fgColor indexed="2"/>
         <bgColor indexed="2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor theme="9"/>
       </patternFill>
     </fill>
     <fill>
@@ -681,7 +716,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -724,13 +759,10 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1058,68 +1090,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="27"/>
-      <c r="D1" s="28"/>
-      <c r="F1" s="50">
+      <c r="A1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="26"/>
+      <c r="D1" s="27"/>
+      <c r="F1" s="49">
         <v>4</v>
       </c>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="22">
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="21">
         <v>2</v>
       </c>
-      <c r="K1" s="23"/>
-      <c r="L1" s="22">
+      <c r="K1" s="22"/>
+      <c r="L1" s="21">
         <v>5</v>
       </c>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="23"/>
-      <c r="Q1" s="22">
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
+      <c r="O1" s="40"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="21">
         <v>5</v>
       </c>
-      <c r="R1" s="41"/>
-      <c r="S1" s="41"/>
-      <c r="T1" s="41"/>
-      <c r="U1" s="23"/>
-      <c r="V1" s="22">
+      <c r="R1" s="40"/>
+      <c r="S1" s="40"/>
+      <c r="T1" s="40"/>
+      <c r="U1" s="22"/>
+      <c r="V1" s="21">
         <v>5</v>
       </c>
-      <c r="W1" s="41"/>
-      <c r="X1" s="41"/>
-      <c r="Y1" s="41"/>
-      <c r="Z1" s="23"/>
-      <c r="AA1" s="17"/>
-      <c r="AB1" s="17"/>
-      <c r="AC1" s="18"/>
-      <c r="AD1" s="19"/>
-      <c r="AE1" s="17"/>
+      <c r="W1" s="40"/>
+      <c r="X1" s="40"/>
+      <c r="Y1" s="40"/>
+      <c r="Z1" s="22"/>
+      <c r="AA1" s="21">
+        <v>5</v>
+      </c>
+      <c r="AB1" s="40"/>
+      <c r="AC1" s="40"/>
+      <c r="AD1" s="40"/>
+      <c r="AE1" s="22"/>
       <c r="AF1" s="17"/>
       <c r="AG1" s="17"/>
       <c r="AH1" s="17"/>
       <c r="AI1" s="17"/>
       <c r="AJ1" s="17"/>
-      <c r="AK1" s="19"/>
-      <c r="AL1" s="19"/>
+      <c r="AK1" s="18"/>
+      <c r="AL1" s="18"/>
       <c r="AM1" s="17"/>
       <c r="AN1" s="17"/>
       <c r="AO1" s="17"/>
       <c r="AP1" s="17"/>
       <c r="AQ1" s="17"/>
       <c r="AR1" s="17"/>
-      <c r="AS1" s="19"/>
-      <c r="AT1" s="20"/>
-      <c r="AU1" s="20"/>
-      <c r="AV1" s="20"/>
-      <c r="AW1" s="20"/>
+      <c r="AS1" s="18"/>
+      <c r="AT1" s="19"/>
+      <c r="AU1" s="19"/>
+      <c r="AV1" s="19"/>
+      <c r="AW1" s="19"/>
       <c r="AX1" s="17"/>
       <c r="AY1" s="17"/>
       <c r="AZ1" s="17"/>
@@ -1138,9 +1172,9 @@
       <c r="BM1" s="17"/>
       <c r="BN1" s="17"/>
       <c r="BO1" s="17"/>
-      <c r="BP1" s="21"/>
-      <c r="BQ1" s="21"/>
-      <c r="BR1" s="21"/>
+      <c r="BP1" s="20"/>
+      <c r="BQ1" s="20"/>
+      <c r="BR1" s="20"/>
       <c r="BS1" s="17"/>
       <c r="BT1" s="17"/>
       <c r="BU1" s="17"/>
@@ -1153,891 +1187,901 @@
       <c r="CB1" s="17"/>
       <c r="CC1" s="1">
         <f>SUM(E1:CB1)</f>
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:85" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="26"/>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="31" t="s">
+      <c r="A2" s="25"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="24">
+      <c r="F2" s="23">
         <v>46202</v>
       </c>
-      <c r="G2" s="24">
+      <c r="G2" s="23">
         <v>46202</v>
       </c>
-      <c r="H2" s="24">
+      <c r="H2" s="23">
         <v>46202</v>
       </c>
-      <c r="I2" s="24">
+      <c r="I2" s="23">
         <v>46202</v>
       </c>
-      <c r="J2" s="24">
+      <c r="J2" s="23">
         <v>46206</v>
       </c>
-      <c r="K2" s="24">
+      <c r="K2" s="23">
         <v>46206</v>
       </c>
-      <c r="L2" s="24">
+      <c r="L2" s="23">
         <v>46209</v>
       </c>
-      <c r="M2" s="24">
+      <c r="M2" s="23">
         <v>46209</v>
       </c>
-      <c r="N2" s="24">
+      <c r="N2" s="23">
         <v>46209</v>
       </c>
-      <c r="O2" s="24">
+      <c r="O2" s="23">
         <v>46209</v>
       </c>
-      <c r="P2" s="24">
+      <c r="P2" s="23">
         <v>46209</v>
       </c>
-      <c r="Q2" s="24">
+      <c r="Q2" s="23">
         <v>46216</v>
       </c>
-      <c r="R2" s="24">
+      <c r="R2" s="23">
         <v>46216</v>
       </c>
-      <c r="S2" s="24">
+      <c r="S2" s="23">
         <v>46216</v>
       </c>
-      <c r="T2" s="24">
+      <c r="T2" s="23">
         <v>46216</v>
       </c>
-      <c r="U2" s="24">
+      <c r="U2" s="23">
         <v>46216</v>
       </c>
-      <c r="V2" s="24">
+      <c r="V2" s="23">
         <v>46223</v>
       </c>
-      <c r="W2" s="24">
+      <c r="W2" s="23">
         <v>46223</v>
       </c>
-      <c r="X2" s="24">
+      <c r="X2" s="23">
         <v>46223</v>
       </c>
-      <c r="Y2" s="24">
+      <c r="Y2" s="23">
         <v>46223</v>
       </c>
-      <c r="Z2" s="24">
+      <c r="Z2" s="23">
         <v>46223</v>
       </c>
-      <c r="AA2" s="24"/>
-      <c r="AB2" s="24"/>
-      <c r="AC2" s="24"/>
-      <c r="AD2" s="24"/>
-      <c r="AE2" s="24"/>
-      <c r="AF2" s="24"/>
-      <c r="AG2" s="24"/>
-      <c r="AH2" s="24"/>
-      <c r="AI2" s="24"/>
-      <c r="AJ2" s="24"/>
-      <c r="AK2" s="24"/>
-      <c r="AL2" s="24"/>
-      <c r="AM2" s="24"/>
-      <c r="AN2" s="24"/>
-      <c r="AO2" s="24"/>
-      <c r="AP2" s="24"/>
-      <c r="AQ2" s="24"/>
-      <c r="AR2" s="24"/>
-      <c r="AS2" s="24"/>
-      <c r="AT2" s="24"/>
-      <c r="AU2" s="24"/>
-      <c r="AV2" s="24"/>
-      <c r="AW2" s="24"/>
-      <c r="AX2" s="24"/>
-      <c r="AY2" s="24"/>
-      <c r="AZ2" s="24"/>
-      <c r="BA2" s="24"/>
-      <c r="BB2" s="24"/>
-      <c r="BC2" s="24"/>
-      <c r="BD2" s="24"/>
-      <c r="BE2" s="24"/>
-      <c r="BF2" s="24"/>
-      <c r="BG2" s="24"/>
-      <c r="BH2" s="24"/>
-      <c r="BI2" s="24"/>
-      <c r="BJ2" s="24"/>
-      <c r="BK2" s="24"/>
-      <c r="BL2" s="24"/>
-      <c r="BM2" s="24"/>
-      <c r="BN2" s="24"/>
-      <c r="BO2" s="24"/>
-      <c r="BP2" s="24"/>
-      <c r="BQ2" s="24"/>
-      <c r="BR2" s="24"/>
-      <c r="BS2" s="24"/>
-      <c r="BT2" s="24"/>
-      <c r="BU2" s="24"/>
-      <c r="BV2" s="24"/>
-      <c r="BW2" s="24"/>
-      <c r="BX2" s="24"/>
-      <c r="BY2" s="24"/>
-      <c r="BZ2" s="24"/>
-      <c r="CA2" s="24"/>
-      <c r="CB2" s="24"/>
+      <c r="AA2" s="23">
+        <v>46230</v>
+      </c>
+      <c r="AB2" s="23">
+        <v>46230</v>
+      </c>
+      <c r="AC2" s="23">
+        <v>46230</v>
+      </c>
+      <c r="AD2" s="23">
+        <v>46230</v>
+      </c>
+      <c r="AE2" s="23">
+        <v>46230</v>
+      </c>
+      <c r="AF2" s="23"/>
+      <c r="AG2" s="23"/>
+      <c r="AH2" s="23"/>
+      <c r="AI2" s="23"/>
+      <c r="AJ2" s="23"/>
+      <c r="AK2" s="23"/>
+      <c r="AL2" s="23"/>
+      <c r="AM2" s="23"/>
+      <c r="AN2" s="23"/>
+      <c r="AO2" s="23"/>
+      <c r="AP2" s="23"/>
+      <c r="AQ2" s="23"/>
+      <c r="AR2" s="23"/>
+      <c r="AS2" s="23"/>
+      <c r="AT2" s="23"/>
+      <c r="AU2" s="23"/>
+      <c r="AV2" s="23"/>
+      <c r="AW2" s="23"/>
+      <c r="AX2" s="23"/>
+      <c r="AY2" s="23"/>
+      <c r="AZ2" s="23"/>
+      <c r="BA2" s="23"/>
+      <c r="BB2" s="23"/>
+      <c r="BC2" s="23"/>
+      <c r="BD2" s="23"/>
+      <c r="BE2" s="23"/>
+      <c r="BF2" s="23"/>
+      <c r="BG2" s="23"/>
+      <c r="BH2" s="23"/>
+      <c r="BI2" s="23"/>
+      <c r="BJ2" s="23"/>
+      <c r="BK2" s="23"/>
+      <c r="BL2" s="23"/>
+      <c r="BM2" s="23"/>
+      <c r="BN2" s="23"/>
+      <c r="BO2" s="23"/>
+      <c r="BP2" s="23"/>
+      <c r="BQ2" s="23"/>
+      <c r="BR2" s="23"/>
+      <c r="BS2" s="23"/>
+      <c r="BT2" s="23"/>
+      <c r="BU2" s="23"/>
+      <c r="BV2" s="23"/>
+      <c r="BW2" s="23"/>
+      <c r="BX2" s="23"/>
+      <c r="BY2" s="23"/>
+      <c r="BZ2" s="23"/>
+      <c r="CA2" s="23"/>
+      <c r="CB2" s="23"/>
     </row>
     <row r="3" spans="1:85" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="24"/>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="24"/>
-      <c r="R3" s="24"/>
-      <c r="S3" s="24"/>
-      <c r="T3" s="24"/>
-      <c r="U3" s="24"/>
-      <c r="V3" s="24"/>
-      <c r="W3" s="24"/>
-      <c r="X3" s="24"/>
-      <c r="Y3" s="24"/>
-      <c r="Z3" s="24"/>
-      <c r="AA3" s="24"/>
-      <c r="AB3" s="24"/>
-      <c r="AC3" s="24"/>
-      <c r="AD3" s="24"/>
-      <c r="AE3" s="24"/>
-      <c r="AF3" s="24"/>
-      <c r="AG3" s="24"/>
-      <c r="AH3" s="24"/>
-      <c r="AI3" s="24"/>
-      <c r="AJ3" s="24"/>
-      <c r="AK3" s="24"/>
-      <c r="AL3" s="24"/>
-      <c r="AM3" s="24"/>
-      <c r="AN3" s="24"/>
-      <c r="AO3" s="24"/>
-      <c r="AP3" s="24"/>
-      <c r="AQ3" s="24"/>
-      <c r="AR3" s="24"/>
-      <c r="AS3" s="24"/>
-      <c r="AT3" s="24"/>
-      <c r="AU3" s="24"/>
-      <c r="AV3" s="24"/>
-      <c r="AW3" s="24"/>
-      <c r="AX3" s="24"/>
-      <c r="AY3" s="24"/>
-      <c r="AZ3" s="24"/>
-      <c r="BA3" s="24"/>
-      <c r="BB3" s="24"/>
-      <c r="BC3" s="24"/>
-      <c r="BD3" s="24"/>
-      <c r="BE3" s="24"/>
-      <c r="BF3" s="24"/>
-      <c r="BG3" s="24"/>
-      <c r="BH3" s="24"/>
-      <c r="BI3" s="24"/>
-      <c r="BJ3" s="24"/>
-      <c r="BK3" s="24"/>
-      <c r="BL3" s="24"/>
-      <c r="BM3" s="24"/>
-      <c r="BN3" s="24"/>
-      <c r="BO3" s="24"/>
-      <c r="BP3" s="24"/>
-      <c r="BQ3" s="24"/>
-      <c r="BR3" s="24"/>
-      <c r="BS3" s="24"/>
-      <c r="BT3" s="24"/>
-      <c r="BU3" s="24"/>
-      <c r="BV3" s="24"/>
-      <c r="BW3" s="24"/>
-      <c r="BX3" s="24"/>
-      <c r="BY3" s="24"/>
-      <c r="BZ3" s="24"/>
-      <c r="CA3" s="24"/>
-      <c r="CB3" s="24"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="23"/>
+      <c r="L3" s="23"/>
+      <c r="M3" s="23"/>
+      <c r="N3" s="23"/>
+      <c r="O3" s="23"/>
+      <c r="P3" s="23"/>
+      <c r="Q3" s="23"/>
+      <c r="R3" s="23"/>
+      <c r="S3" s="23"/>
+      <c r="T3" s="23"/>
+      <c r="U3" s="23"/>
+      <c r="V3" s="23"/>
+      <c r="W3" s="23"/>
+      <c r="X3" s="23"/>
+      <c r="Y3" s="23"/>
+      <c r="Z3" s="23"/>
+      <c r="AA3" s="23"/>
+      <c r="AB3" s="23"/>
+      <c r="AC3" s="23"/>
+      <c r="AD3" s="23"/>
+      <c r="AE3" s="23"/>
+      <c r="AF3" s="23"/>
+      <c r="AG3" s="23"/>
+      <c r="AH3" s="23"/>
+      <c r="AI3" s="23"/>
+      <c r="AJ3" s="23"/>
+      <c r="AK3" s="23"/>
+      <c r="AL3" s="23"/>
+      <c r="AM3" s="23"/>
+      <c r="AN3" s="23"/>
+      <c r="AO3" s="23"/>
+      <c r="AP3" s="23"/>
+      <c r="AQ3" s="23"/>
+      <c r="AR3" s="23"/>
+      <c r="AS3" s="23"/>
+      <c r="AT3" s="23"/>
+      <c r="AU3" s="23"/>
+      <c r="AV3" s="23"/>
+      <c r="AW3" s="23"/>
+      <c r="AX3" s="23"/>
+      <c r="AY3" s="23"/>
+      <c r="AZ3" s="23"/>
+      <c r="BA3" s="23"/>
+      <c r="BB3" s="23"/>
+      <c r="BC3" s="23"/>
+      <c r="BD3" s="23"/>
+      <c r="BE3" s="23"/>
+      <c r="BF3" s="23"/>
+      <c r="BG3" s="23"/>
+      <c r="BH3" s="23"/>
+      <c r="BI3" s="23"/>
+      <c r="BJ3" s="23"/>
+      <c r="BK3" s="23"/>
+      <c r="BL3" s="23"/>
+      <c r="BM3" s="23"/>
+      <c r="BN3" s="23"/>
+      <c r="BO3" s="23"/>
+      <c r="BP3" s="23"/>
+      <c r="BQ3" s="23"/>
+      <c r="BR3" s="23"/>
+      <c r="BS3" s="23"/>
+      <c r="BT3" s="23"/>
+      <c r="BU3" s="23"/>
+      <c r="BV3" s="23"/>
+      <c r="BW3" s="23"/>
+      <c r="BX3" s="23"/>
+      <c r="BY3" s="23"/>
+      <c r="BZ3" s="23"/>
+      <c r="CA3" s="23"/>
+      <c r="CB3" s="23"/>
     </row>
     <row r="4" spans="1:85" ht="24.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="34"/>
-      <c r="C4" s="35" t="s">
+      <c r="B4" s="33"/>
+      <c r="C4" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="36"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
-      <c r="L4" s="24"/>
-      <c r="M4" s="24"/>
-      <c r="N4" s="24"/>
-      <c r="O4" s="24"/>
-      <c r="P4" s="24"/>
-      <c r="Q4" s="24"/>
-      <c r="R4" s="24"/>
-      <c r="S4" s="24"/>
-      <c r="T4" s="24"/>
-      <c r="U4" s="24"/>
-      <c r="V4" s="24"/>
-      <c r="W4" s="24"/>
-      <c r="X4" s="24"/>
-      <c r="Y4" s="24"/>
-      <c r="Z4" s="24"/>
-      <c r="AA4" s="24"/>
-      <c r="AB4" s="24"/>
-      <c r="AC4" s="24"/>
-      <c r="AD4" s="24"/>
-      <c r="AE4" s="24"/>
-      <c r="AF4" s="24"/>
-      <c r="AG4" s="24"/>
-      <c r="AH4" s="24"/>
-      <c r="AI4" s="24"/>
-      <c r="AJ4" s="24"/>
-      <c r="AK4" s="24"/>
-      <c r="AL4" s="24"/>
-      <c r="AM4" s="24"/>
-      <c r="AN4" s="24"/>
-      <c r="AO4" s="24"/>
-      <c r="AP4" s="24"/>
-      <c r="AQ4" s="24"/>
-      <c r="AR4" s="24"/>
-      <c r="AS4" s="24"/>
-      <c r="AT4" s="24"/>
-      <c r="AU4" s="24"/>
-      <c r="AV4" s="24"/>
-      <c r="AW4" s="24"/>
-      <c r="AX4" s="24"/>
-      <c r="AY4" s="24"/>
-      <c r="AZ4" s="24"/>
-      <c r="BA4" s="24"/>
-      <c r="BB4" s="24"/>
-      <c r="BC4" s="24"/>
-      <c r="BD4" s="24"/>
-      <c r="BE4" s="24"/>
-      <c r="BF4" s="24"/>
-      <c r="BG4" s="24"/>
-      <c r="BH4" s="24"/>
-      <c r="BI4" s="24"/>
-      <c r="BJ4" s="24"/>
-      <c r="BK4" s="24"/>
-      <c r="BL4" s="24"/>
-      <c r="BM4" s="24"/>
-      <c r="BN4" s="24"/>
-      <c r="BO4" s="24"/>
-      <c r="BP4" s="24"/>
-      <c r="BQ4" s="24"/>
-      <c r="BR4" s="24"/>
-      <c r="BS4" s="24"/>
-      <c r="BT4" s="24"/>
-      <c r="BU4" s="24"/>
-      <c r="BV4" s="24"/>
-      <c r="BW4" s="24"/>
-      <c r="BX4" s="24"/>
-      <c r="BY4" s="24"/>
-      <c r="BZ4" s="24"/>
-      <c r="CA4" s="24"/>
-      <c r="CB4" s="24"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="23"/>
+      <c r="R4" s="23"/>
+      <c r="S4" s="23"/>
+      <c r="T4" s="23"/>
+      <c r="U4" s="23"/>
+      <c r="V4" s="23"/>
+      <c r="W4" s="23"/>
+      <c r="X4" s="23"/>
+      <c r="Y4" s="23"/>
+      <c r="Z4" s="23"/>
+      <c r="AA4" s="23"/>
+      <c r="AB4" s="23"/>
+      <c r="AC4" s="23"/>
+      <c r="AD4" s="23"/>
+      <c r="AE4" s="23"/>
+      <c r="AF4" s="23"/>
+      <c r="AG4" s="23"/>
+      <c r="AH4" s="23"/>
+      <c r="AI4" s="23"/>
+      <c r="AJ4" s="23"/>
+      <c r="AK4" s="23"/>
+      <c r="AL4" s="23"/>
+      <c r="AM4" s="23"/>
+      <c r="AN4" s="23"/>
+      <c r="AO4" s="23"/>
+      <c r="AP4" s="23"/>
+      <c r="AQ4" s="23"/>
+      <c r="AR4" s="23"/>
+      <c r="AS4" s="23"/>
+      <c r="AT4" s="23"/>
+      <c r="AU4" s="23"/>
+      <c r="AV4" s="23"/>
+      <c r="AW4" s="23"/>
+      <c r="AX4" s="23"/>
+      <c r="AY4" s="23"/>
+      <c r="AZ4" s="23"/>
+      <c r="BA4" s="23"/>
+      <c r="BB4" s="23"/>
+      <c r="BC4" s="23"/>
+      <c r="BD4" s="23"/>
+      <c r="BE4" s="23"/>
+      <c r="BF4" s="23"/>
+      <c r="BG4" s="23"/>
+      <c r="BH4" s="23"/>
+      <c r="BI4" s="23"/>
+      <c r="BJ4" s="23"/>
+      <c r="BK4" s="23"/>
+      <c r="BL4" s="23"/>
+      <c r="BM4" s="23"/>
+      <c r="BN4" s="23"/>
+      <c r="BO4" s="23"/>
+      <c r="BP4" s="23"/>
+      <c r="BQ4" s="23"/>
+      <c r="BR4" s="23"/>
+      <c r="BS4" s="23"/>
+      <c r="BT4" s="23"/>
+      <c r="BU4" s="23"/>
+      <c r="BV4" s="23"/>
+      <c r="BW4" s="23"/>
+      <c r="BX4" s="23"/>
+      <c r="BY4" s="23"/>
+      <c r="BZ4" s="23"/>
+      <c r="CA4" s="23"/>
+      <c r="CB4" s="23"/>
     </row>
     <row r="5" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="37" t="s">
+      <c r="A5" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="38">
+      <c r="B5" s="36"/>
+      <c r="C5" s="37">
         <v>60</v>
       </c>
-      <c r="D5" s="39"/>
-      <c r="E5" s="32"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="24"/>
-      <c r="I5" s="24"/>
-      <c r="J5" s="24"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="24"/>
-      <c r="M5" s="24"/>
-      <c r="N5" s="24"/>
-      <c r="O5" s="24"/>
-      <c r="P5" s="24"/>
-      <c r="Q5" s="24"/>
-      <c r="R5" s="24"/>
-      <c r="S5" s="24"/>
-      <c r="T5" s="24"/>
-      <c r="U5" s="24"/>
-      <c r="V5" s="24"/>
-      <c r="W5" s="24"/>
-      <c r="X5" s="24"/>
-      <c r="Y5" s="24"/>
-      <c r="Z5" s="24"/>
-      <c r="AA5" s="24"/>
-      <c r="AB5" s="24"/>
-      <c r="AC5" s="24"/>
-      <c r="AD5" s="24"/>
-      <c r="AE5" s="24"/>
-      <c r="AF5" s="24"/>
-      <c r="AG5" s="24"/>
-      <c r="AH5" s="24"/>
-      <c r="AI5" s="24"/>
-      <c r="AJ5" s="24"/>
-      <c r="AK5" s="24"/>
-      <c r="AL5" s="24"/>
-      <c r="AM5" s="24"/>
-      <c r="AN5" s="24"/>
-      <c r="AO5" s="24"/>
-      <c r="AP5" s="24"/>
-      <c r="AQ5" s="24"/>
-      <c r="AR5" s="24"/>
-      <c r="AS5" s="24"/>
-      <c r="AT5" s="24"/>
-      <c r="AU5" s="24"/>
-      <c r="AV5" s="24"/>
-      <c r="AW5" s="24"/>
-      <c r="AX5" s="24"/>
-      <c r="AY5" s="24"/>
-      <c r="AZ5" s="24"/>
-      <c r="BA5" s="24"/>
-      <c r="BB5" s="24"/>
-      <c r="BC5" s="24"/>
-      <c r="BD5" s="24"/>
-      <c r="BE5" s="24"/>
-      <c r="BF5" s="24"/>
-      <c r="BG5" s="24"/>
-      <c r="BH5" s="24"/>
-      <c r="BI5" s="24"/>
-      <c r="BJ5" s="24"/>
-      <c r="BK5" s="24"/>
-      <c r="BL5" s="24"/>
-      <c r="BM5" s="24"/>
-      <c r="BN5" s="24"/>
-      <c r="BO5" s="24"/>
-      <c r="BP5" s="24"/>
-      <c r="BQ5" s="24"/>
-      <c r="BR5" s="24"/>
-      <c r="BS5" s="24"/>
-      <c r="BT5" s="24"/>
-      <c r="BU5" s="24"/>
-      <c r="BV5" s="24"/>
-      <c r="BW5" s="24"/>
-      <c r="BX5" s="24"/>
-      <c r="BY5" s="24"/>
-      <c r="BZ5" s="24"/>
-      <c r="CA5" s="24"/>
-      <c r="CB5" s="24"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="23"/>
+      <c r="S5" s="23"/>
+      <c r="T5" s="23"/>
+      <c r="U5" s="23"/>
+      <c r="V5" s="23"/>
+      <c r="W5" s="23"/>
+      <c r="X5" s="23"/>
+      <c r="Y5" s="23"/>
+      <c r="Z5" s="23"/>
+      <c r="AA5" s="23"/>
+      <c r="AB5" s="23"/>
+      <c r="AC5" s="23"/>
+      <c r="AD5" s="23"/>
+      <c r="AE5" s="23"/>
+      <c r="AF5" s="23"/>
+      <c r="AG5" s="23"/>
+      <c r="AH5" s="23"/>
+      <c r="AI5" s="23"/>
+      <c r="AJ5" s="23"/>
+      <c r="AK5" s="23"/>
+      <c r="AL5" s="23"/>
+      <c r="AM5" s="23"/>
+      <c r="AN5" s="23"/>
+      <c r="AO5" s="23"/>
+      <c r="AP5" s="23"/>
+      <c r="AQ5" s="23"/>
+      <c r="AR5" s="23"/>
+      <c r="AS5" s="23"/>
+      <c r="AT5" s="23"/>
+      <c r="AU5" s="23"/>
+      <c r="AV5" s="23"/>
+      <c r="AW5" s="23"/>
+      <c r="AX5" s="23"/>
+      <c r="AY5" s="23"/>
+      <c r="AZ5" s="23"/>
+      <c r="BA5" s="23"/>
+      <c r="BB5" s="23"/>
+      <c r="BC5" s="23"/>
+      <c r="BD5" s="23"/>
+      <c r="BE5" s="23"/>
+      <c r="BF5" s="23"/>
+      <c r="BG5" s="23"/>
+      <c r="BH5" s="23"/>
+      <c r="BI5" s="23"/>
+      <c r="BJ5" s="23"/>
+      <c r="BK5" s="23"/>
+      <c r="BL5" s="23"/>
+      <c r="BM5" s="23"/>
+      <c r="BN5" s="23"/>
+      <c r="BO5" s="23"/>
+      <c r="BP5" s="23"/>
+      <c r="BQ5" s="23"/>
+      <c r="BR5" s="23"/>
+      <c r="BS5" s="23"/>
+      <c r="BT5" s="23"/>
+      <c r="BU5" s="23"/>
+      <c r="BV5" s="23"/>
+      <c r="BW5" s="23"/>
+      <c r="BX5" s="23"/>
+      <c r="BY5" s="23"/>
+      <c r="BZ5" s="23"/>
+      <c r="CA5" s="23"/>
+      <c r="CB5" s="23"/>
     </row>
     <row r="6" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="37" t="s">
+      <c r="A6" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="37"/>
-      <c r="C6" s="38">
+      <c r="B6" s="36"/>
+      <c r="C6" s="37">
         <v>6</v>
       </c>
-      <c r="D6" s="39"/>
-      <c r="E6" s="32"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
-      <c r="I6" s="24"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="24"/>
-      <c r="L6" s="24"/>
-      <c r="M6" s="24"/>
-      <c r="N6" s="24"/>
-      <c r="O6" s="24"/>
-      <c r="P6" s="24"/>
-      <c r="Q6" s="24"/>
-      <c r="R6" s="24"/>
-      <c r="S6" s="24"/>
-      <c r="T6" s="24"/>
-      <c r="U6" s="24"/>
-      <c r="V6" s="24"/>
-      <c r="W6" s="24"/>
-      <c r="X6" s="24"/>
-      <c r="Y6" s="24"/>
-      <c r="Z6" s="24"/>
-      <c r="AA6" s="24"/>
-      <c r="AB6" s="24"/>
-      <c r="AC6" s="24"/>
-      <c r="AD6" s="24"/>
-      <c r="AE6" s="24"/>
-      <c r="AF6" s="24"/>
-      <c r="AG6" s="24"/>
-      <c r="AH6" s="24"/>
-      <c r="AI6" s="24"/>
-      <c r="AJ6" s="24"/>
-      <c r="AK6" s="24"/>
-      <c r="AL6" s="24"/>
-      <c r="AM6" s="24"/>
-      <c r="AN6" s="24"/>
-      <c r="AO6" s="24"/>
-      <c r="AP6" s="24"/>
-      <c r="AQ6" s="24"/>
-      <c r="AR6" s="24"/>
-      <c r="AS6" s="24"/>
-      <c r="AT6" s="24"/>
-      <c r="AU6" s="24"/>
-      <c r="AV6" s="24"/>
-      <c r="AW6" s="24"/>
-      <c r="AX6" s="24"/>
-      <c r="AY6" s="24"/>
-      <c r="AZ6" s="24"/>
-      <c r="BA6" s="24"/>
-      <c r="BB6" s="24"/>
-      <c r="BC6" s="24"/>
-      <c r="BD6" s="24"/>
-      <c r="BE6" s="24"/>
-      <c r="BF6" s="24"/>
-      <c r="BG6" s="24"/>
-      <c r="BH6" s="24"/>
-      <c r="BI6" s="24"/>
-      <c r="BJ6" s="24"/>
-      <c r="BK6" s="24"/>
-      <c r="BL6" s="24"/>
-      <c r="BM6" s="24"/>
-      <c r="BN6" s="24"/>
-      <c r="BO6" s="24"/>
-      <c r="BP6" s="24"/>
-      <c r="BQ6" s="24"/>
-      <c r="BR6" s="24"/>
-      <c r="BS6" s="24"/>
-      <c r="BT6" s="24"/>
-      <c r="BU6" s="24"/>
-      <c r="BV6" s="24"/>
-      <c r="BW6" s="24"/>
-      <c r="BX6" s="24"/>
-      <c r="BY6" s="24"/>
-      <c r="BZ6" s="24"/>
-      <c r="CA6" s="24"/>
-      <c r="CB6" s="24"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="23"/>
+      <c r="L6" s="23"/>
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
+      <c r="O6" s="23"/>
+      <c r="P6" s="23"/>
+      <c r="Q6" s="23"/>
+      <c r="R6" s="23"/>
+      <c r="S6" s="23"/>
+      <c r="T6" s="23"/>
+      <c r="U6" s="23"/>
+      <c r="V6" s="23"/>
+      <c r="W6" s="23"/>
+      <c r="X6" s="23"/>
+      <c r="Y6" s="23"/>
+      <c r="Z6" s="23"/>
+      <c r="AA6" s="23"/>
+      <c r="AB6" s="23"/>
+      <c r="AC6" s="23"/>
+      <c r="AD6" s="23"/>
+      <c r="AE6" s="23"/>
+      <c r="AF6" s="23"/>
+      <c r="AG6" s="23"/>
+      <c r="AH6" s="23"/>
+      <c r="AI6" s="23"/>
+      <c r="AJ6" s="23"/>
+      <c r="AK6" s="23"/>
+      <c r="AL6" s="23"/>
+      <c r="AM6" s="23"/>
+      <c r="AN6" s="23"/>
+      <c r="AO6" s="23"/>
+      <c r="AP6" s="23"/>
+      <c r="AQ6" s="23"/>
+      <c r="AR6" s="23"/>
+      <c r="AS6" s="23"/>
+      <c r="AT6" s="23"/>
+      <c r="AU6" s="23"/>
+      <c r="AV6" s="23"/>
+      <c r="AW6" s="23"/>
+      <c r="AX6" s="23"/>
+      <c r="AY6" s="23"/>
+      <c r="AZ6" s="23"/>
+      <c r="BA6" s="23"/>
+      <c r="BB6" s="23"/>
+      <c r="BC6" s="23"/>
+      <c r="BD6" s="23"/>
+      <c r="BE6" s="23"/>
+      <c r="BF6" s="23"/>
+      <c r="BG6" s="23"/>
+      <c r="BH6" s="23"/>
+      <c r="BI6" s="23"/>
+      <c r="BJ6" s="23"/>
+      <c r="BK6" s="23"/>
+      <c r="BL6" s="23"/>
+      <c r="BM6" s="23"/>
+      <c r="BN6" s="23"/>
+      <c r="BO6" s="23"/>
+      <c r="BP6" s="23"/>
+      <c r="BQ6" s="23"/>
+      <c r="BR6" s="23"/>
+      <c r="BS6" s="23"/>
+      <c r="BT6" s="23"/>
+      <c r="BU6" s="23"/>
+      <c r="BV6" s="23"/>
+      <c r="BW6" s="23"/>
+      <c r="BX6" s="23"/>
+      <c r="BY6" s="23"/>
+      <c r="BZ6" s="23"/>
+      <c r="CA6" s="23"/>
+      <c r="CB6" s="23"/>
     </row>
     <row r="7" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="40" t="s">
+      <c r="A7" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="40"/>
-      <c r="C7" s="38">
+      <c r="B7" s="39"/>
+      <c r="C7" s="37">
         <v>9</v>
       </c>
-      <c r="D7" s="39"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25"/>
-      <c r="I7" s="25"/>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="L7" s="25"/>
-      <c r="M7" s="25"/>
-      <c r="N7" s="25"/>
-      <c r="O7" s="25"/>
-      <c r="P7" s="25"/>
-      <c r="Q7" s="25"/>
-      <c r="R7" s="25"/>
-      <c r="S7" s="25"/>
-      <c r="T7" s="25"/>
-      <c r="U7" s="25"/>
-      <c r="V7" s="25"/>
-      <c r="W7" s="25"/>
-      <c r="X7" s="25"/>
-      <c r="Y7" s="25"/>
-      <c r="Z7" s="25"/>
-      <c r="AA7" s="25"/>
-      <c r="AB7" s="25"/>
-      <c r="AC7" s="25"/>
-      <c r="AD7" s="25"/>
-      <c r="AE7" s="25"/>
-      <c r="AF7" s="25"/>
-      <c r="AG7" s="25"/>
-      <c r="AH7" s="25"/>
-      <c r="AI7" s="25"/>
-      <c r="AJ7" s="25"/>
-      <c r="AK7" s="25"/>
-      <c r="AL7" s="25"/>
-      <c r="AM7" s="25"/>
-      <c r="AN7" s="25"/>
-      <c r="AO7" s="25"/>
-      <c r="AP7" s="25"/>
-      <c r="AQ7" s="25"/>
-      <c r="AR7" s="25"/>
-      <c r="AS7" s="25"/>
-      <c r="AT7" s="25"/>
-      <c r="AU7" s="25"/>
-      <c r="AV7" s="25"/>
-      <c r="AW7" s="25"/>
-      <c r="AX7" s="25"/>
-      <c r="AY7" s="25"/>
-      <c r="AZ7" s="25"/>
-      <c r="BA7" s="25"/>
-      <c r="BB7" s="25"/>
-      <c r="BC7" s="25"/>
-      <c r="BD7" s="25"/>
-      <c r="BE7" s="25"/>
-      <c r="BF7" s="25"/>
-      <c r="BG7" s="25"/>
-      <c r="BH7" s="25"/>
-      <c r="BI7" s="25"/>
-      <c r="BJ7" s="25"/>
-      <c r="BK7" s="25"/>
-      <c r="BL7" s="25"/>
-      <c r="BM7" s="25"/>
-      <c r="BN7" s="25"/>
-      <c r="BO7" s="25"/>
-      <c r="BP7" s="25"/>
-      <c r="BQ7" s="25"/>
-      <c r="BR7" s="25"/>
-      <c r="BS7" s="25"/>
-      <c r="BT7" s="25"/>
-      <c r="BU7" s="25"/>
-      <c r="BV7" s="25"/>
-      <c r="BW7" s="25"/>
-      <c r="BX7" s="25"/>
-      <c r="BY7" s="25"/>
-      <c r="BZ7" s="25"/>
-      <c r="CA7" s="25"/>
-      <c r="CB7" s="25"/>
+      <c r="D7" s="38"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
+      <c r="I7" s="24"/>
+      <c r="J7" s="24"/>
+      <c r="K7" s="24"/>
+      <c r="L7" s="24"/>
+      <c r="M7" s="24"/>
+      <c r="N7" s="24"/>
+      <c r="O7" s="24"/>
+      <c r="P7" s="24"/>
+      <c r="Q7" s="24"/>
+      <c r="R7" s="24"/>
+      <c r="S7" s="24"/>
+      <c r="T7" s="24"/>
+      <c r="U7" s="24"/>
+      <c r="V7" s="24"/>
+      <c r="W7" s="24"/>
+      <c r="X7" s="24"/>
+      <c r="Y7" s="24"/>
+      <c r="Z7" s="24"/>
+      <c r="AA7" s="24"/>
+      <c r="AB7" s="24"/>
+      <c r="AC7" s="24"/>
+      <c r="AD7" s="24"/>
+      <c r="AE7" s="24"/>
+      <c r="AF7" s="24"/>
+      <c r="AG7" s="24"/>
+      <c r="AH7" s="24"/>
+      <c r="AI7" s="24"/>
+      <c r="AJ7" s="24"/>
+      <c r="AK7" s="24"/>
+      <c r="AL7" s="24"/>
+      <c r="AM7" s="24"/>
+      <c r="AN7" s="24"/>
+      <c r="AO7" s="24"/>
+      <c r="AP7" s="24"/>
+      <c r="AQ7" s="24"/>
+      <c r="AR7" s="24"/>
+      <c r="AS7" s="24"/>
+      <c r="AT7" s="24"/>
+      <c r="AU7" s="24"/>
+      <c r="AV7" s="24"/>
+      <c r="AW7" s="24"/>
+      <c r="AX7" s="24"/>
+      <c r="AY7" s="24"/>
+      <c r="AZ7" s="24"/>
+      <c r="BA7" s="24"/>
+      <c r="BB7" s="24"/>
+      <c r="BC7" s="24"/>
+      <c r="BD7" s="24"/>
+      <c r="BE7" s="24"/>
+      <c r="BF7" s="24"/>
+      <c r="BG7" s="24"/>
+      <c r="BH7" s="24"/>
+      <c r="BI7" s="24"/>
+      <c r="BJ7" s="24"/>
+      <c r="BK7" s="24"/>
+      <c r="BL7" s="24"/>
+      <c r="BM7" s="24"/>
+      <c r="BN7" s="24"/>
+      <c r="BO7" s="24"/>
+      <c r="BP7" s="24"/>
+      <c r="BQ7" s="24"/>
+      <c r="BR7" s="24"/>
+      <c r="BS7" s="24"/>
+      <c r="BT7" s="24"/>
+      <c r="BU7" s="24"/>
+      <c r="BV7" s="24"/>
+      <c r="BW7" s="24"/>
+      <c r="BX7" s="24"/>
+      <c r="BY7" s="24"/>
+      <c r="BZ7" s="24"/>
+      <c r="CA7" s="24"/>
+      <c r="CB7" s="24"/>
     </row>
     <row r="8" spans="1:85" ht="23.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="42" t="s">
+      <c r="A8" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="42"/>
-      <c r="C8" s="43">
+      <c r="B8" s="41"/>
+      <c r="C8" s="42">
         <f>SUM(C5:D7)</f>
         <v>75</v>
       </c>
-      <c r="D8" s="36"/>
+      <c r="D8" s="35"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="44">
-        <v>1</v>
-      </c>
-      <c r="G8" s="44">
+      <c r="F8" s="43">
+        <v>1</v>
+      </c>
+      <c r="G8" s="43">
         <v>2</v>
       </c>
-      <c r="H8" s="44">
+      <c r="H8" s="43">
         <v>3</v>
       </c>
-      <c r="I8" s="44">
+      <c r="I8" s="43">
         <v>4</v>
       </c>
-      <c r="J8" s="44">
+      <c r="J8" s="43">
         <v>5</v>
       </c>
-      <c r="K8" s="44">
+      <c r="K8" s="43">
         <v>6</v>
       </c>
-      <c r="L8" s="44">
+      <c r="L8" s="43">
         <v>7</v>
       </c>
-      <c r="M8" s="44">
+      <c r="M8" s="43">
         <v>8</v>
       </c>
-      <c r="N8" s="44">
+      <c r="N8" s="43">
         <v>9</v>
       </c>
-      <c r="O8" s="44">
+      <c r="O8" s="43">
         <v>10</v>
       </c>
-      <c r="P8" s="44">
+      <c r="P8" s="43">
         <v>11</v>
       </c>
-      <c r="Q8" s="44">
+      <c r="Q8" s="43">
         <v>12</v>
       </c>
-      <c r="R8" s="44">
+      <c r="R8" s="43">
         <v>13</v>
       </c>
-      <c r="S8" s="44">
+      <c r="S8" s="43">
         <v>14</v>
       </c>
-      <c r="T8" s="44">
+      <c r="T8" s="43">
         <v>15</v>
       </c>
-      <c r="U8" s="44">
+      <c r="U8" s="43">
         <v>16</v>
       </c>
-      <c r="V8" s="44">
+      <c r="V8" s="43">
         <v>17</v>
       </c>
-      <c r="W8" s="44">
+      <c r="W8" s="43">
         <v>18</v>
       </c>
-      <c r="X8" s="44">
+      <c r="X8" s="43">
         <v>19</v>
       </c>
-      <c r="Y8" s="44">
+      <c r="Y8" s="43">
         <v>20</v>
       </c>
-      <c r="Z8" s="44">
+      <c r="Z8" s="43">
         <v>21</v>
       </c>
-      <c r="AA8" s="44">
+      <c r="AA8" s="43">
         <v>22</v>
       </c>
-      <c r="AB8" s="44">
+      <c r="AB8" s="43">
         <v>23</v>
       </c>
-      <c r="AC8" s="44">
+      <c r="AC8" s="43">
         <v>24</v>
       </c>
-      <c r="AD8" s="44">
+      <c r="AD8" s="43">
         <v>25</v>
       </c>
-      <c r="AE8" s="44">
+      <c r="AE8" s="43">
         <v>26</v>
       </c>
-      <c r="AF8" s="44">
+      <c r="AF8" s="43">
         <v>27</v>
       </c>
-      <c r="AG8" s="44">
+      <c r="AG8" s="43">
         <v>28</v>
       </c>
-      <c r="AH8" s="44">
+      <c r="AH8" s="43">
         <v>29</v>
       </c>
-      <c r="AI8" s="44">
+      <c r="AI8" s="43">
         <v>30</v>
       </c>
-      <c r="AJ8" s="44">
+      <c r="AJ8" s="43">
         <v>31</v>
       </c>
-      <c r="AK8" s="44">
+      <c r="AK8" s="43">
         <v>32</v>
       </c>
-      <c r="AL8" s="44">
+      <c r="AL8" s="43">
         <v>33</v>
       </c>
-      <c r="AM8" s="44">
+      <c r="AM8" s="43">
         <v>34</v>
       </c>
-      <c r="AN8" s="44">
+      <c r="AN8" s="43">
         <v>35</v>
       </c>
-      <c r="AO8" s="44">
+      <c r="AO8" s="43">
         <v>36</v>
       </c>
-      <c r="AP8" s="44">
+      <c r="AP8" s="43">
         <v>37</v>
       </c>
-      <c r="AQ8" s="44">
+      <c r="AQ8" s="43">
         <v>38</v>
       </c>
-      <c r="AR8" s="44">
+      <c r="AR8" s="43">
         <v>39</v>
       </c>
-      <c r="AS8" s="44">
+      <c r="AS8" s="43">
         <v>40</v>
       </c>
-      <c r="AT8" s="44">
+      <c r="AT8" s="43">
         <v>41</v>
       </c>
-      <c r="AU8" s="44">
+      <c r="AU8" s="43">
         <v>42</v>
       </c>
-      <c r="AV8" s="44">
+      <c r="AV8" s="43">
         <v>43</v>
       </c>
-      <c r="AW8" s="44">
+      <c r="AW8" s="43">
         <v>44</v>
       </c>
-      <c r="AX8" s="44">
+      <c r="AX8" s="43">
         <v>45</v>
       </c>
-      <c r="AY8" s="44">
+      <c r="AY8" s="43">
         <v>46</v>
       </c>
-      <c r="AZ8" s="44">
+      <c r="AZ8" s="43">
         <v>47</v>
       </c>
-      <c r="BA8" s="44">
+      <c r="BA8" s="43">
         <v>48</v>
       </c>
-      <c r="BB8" s="44">
+      <c r="BB8" s="43">
         <v>49</v>
       </c>
-      <c r="BC8" s="44">
+      <c r="BC8" s="43">
         <v>50</v>
       </c>
-      <c r="BD8" s="44">
+      <c r="BD8" s="43">
         <v>51</v>
       </c>
-      <c r="BE8" s="44">
+      <c r="BE8" s="43">
         <v>52</v>
       </c>
-      <c r="BF8" s="44">
+      <c r="BF8" s="43">
         <v>53</v>
       </c>
-      <c r="BG8" s="44">
+      <c r="BG8" s="43">
         <v>54</v>
       </c>
-      <c r="BH8" s="44">
+      <c r="BH8" s="43">
         <v>55</v>
       </c>
-      <c r="BI8" s="44">
+      <c r="BI8" s="43">
         <v>56</v>
       </c>
-      <c r="BJ8" s="44">
+      <c r="BJ8" s="43">
         <v>57</v>
       </c>
-      <c r="BK8" s="44">
+      <c r="BK8" s="43">
         <v>58</v>
       </c>
-      <c r="BL8" s="44">
+      <c r="BL8" s="43">
         <v>59</v>
       </c>
-      <c r="BM8" s="44">
+      <c r="BM8" s="43">
         <v>60</v>
       </c>
-      <c r="BN8" s="44">
+      <c r="BN8" s="43">
         <v>61</v>
       </c>
-      <c r="BO8" s="44">
+      <c r="BO8" s="43">
         <v>62</v>
       </c>
-      <c r="BP8" s="44">
+      <c r="BP8" s="43">
         <v>63</v>
       </c>
-      <c r="BQ8" s="44">
+      <c r="BQ8" s="43">
         <v>64</v>
       </c>
-      <c r="BR8" s="44">
+      <c r="BR8" s="43">
         <v>65</v>
       </c>
-      <c r="BS8" s="44">
+      <c r="BS8" s="43">
         <v>66</v>
       </c>
-      <c r="BT8" s="44">
+      <c r="BT8" s="43">
         <v>67</v>
       </c>
-      <c r="BU8" s="44">
+      <c r="BU8" s="43">
         <v>68</v>
       </c>
-      <c r="BV8" s="44">
+      <c r="BV8" s="43">
         <v>69</v>
       </c>
-      <c r="BW8" s="44">
+      <c r="BW8" s="43">
         <v>70</v>
       </c>
-      <c r="BX8" s="44">
+      <c r="BX8" s="43">
         <v>71</v>
       </c>
-      <c r="BY8" s="44">
+      <c r="BY8" s="43">
         <v>72</v>
       </c>
-      <c r="BZ8" s="44">
+      <c r="BZ8" s="43">
         <v>73</v>
       </c>
-      <c r="CA8" s="44">
+      <c r="CA8" s="43">
         <v>74</v>
       </c>
-      <c r="CB8" s="44">
+      <c r="CB8" s="43">
         <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="53" t="s">
+      <c r="B9" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="54" t="s">
+      <c r="C9" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="53"/>
+      <c r="D9" s="52"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="45"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="45"/>
-      <c r="I9" s="45"/>
-      <c r="J9" s="45"/>
-      <c r="K9" s="45"/>
-      <c r="L9" s="45"/>
-      <c r="M9" s="45"/>
-      <c r="N9" s="45"/>
-      <c r="O9" s="45"/>
-      <c r="P9" s="45"/>
-      <c r="Q9" s="45"/>
-      <c r="R9" s="45"/>
-      <c r="S9" s="45"/>
-      <c r="T9" s="45"/>
-      <c r="U9" s="45"/>
-      <c r="V9" s="45"/>
-      <c r="W9" s="45"/>
-      <c r="X9" s="45"/>
-      <c r="Y9" s="45"/>
-      <c r="Z9" s="45"/>
-      <c r="AA9" s="45"/>
-      <c r="AB9" s="45"/>
-      <c r="AC9" s="45"/>
-      <c r="AD9" s="45"/>
-      <c r="AE9" s="45"/>
-      <c r="AF9" s="45"/>
-      <c r="AG9" s="45"/>
-      <c r="AH9" s="45"/>
-      <c r="AI9" s="45"/>
-      <c r="AJ9" s="45"/>
-      <c r="AK9" s="45"/>
-      <c r="AL9" s="45"/>
-      <c r="AM9" s="45"/>
-      <c r="AN9" s="45"/>
-      <c r="AO9" s="45"/>
-      <c r="AP9" s="45"/>
-      <c r="AQ9" s="45"/>
-      <c r="AR9" s="45"/>
-      <c r="AS9" s="45"/>
-      <c r="AT9" s="45"/>
-      <c r="AU9" s="45"/>
-      <c r="AV9" s="45"/>
-      <c r="AW9" s="45"/>
-      <c r="AX9" s="45"/>
-      <c r="AY9" s="45"/>
-      <c r="AZ9" s="45"/>
-      <c r="BA9" s="45"/>
-      <c r="BB9" s="45"/>
-      <c r="BC9" s="45"/>
-      <c r="BD9" s="45"/>
-      <c r="BE9" s="45"/>
-      <c r="BF9" s="45"/>
-      <c r="BG9" s="45"/>
-      <c r="BH9" s="45"/>
-      <c r="BI9" s="45"/>
-      <c r="BJ9" s="45"/>
-      <c r="BK9" s="45"/>
-      <c r="BL9" s="45"/>
-      <c r="BM9" s="45"/>
-      <c r="BN9" s="45"/>
-      <c r="BO9" s="45"/>
-      <c r="BP9" s="45"/>
-      <c r="BQ9" s="45"/>
-      <c r="BR9" s="45"/>
-      <c r="BS9" s="45"/>
-      <c r="BT9" s="45"/>
-      <c r="BU9" s="45"/>
-      <c r="BV9" s="45"/>
-      <c r="BW9" s="45"/>
-      <c r="BX9" s="45"/>
-      <c r="BY9" s="45"/>
-      <c r="BZ9" s="45"/>
-      <c r="CA9" s="45"/>
-      <c r="CB9" s="45"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="44"/>
+      <c r="I9" s="44"/>
+      <c r="J9" s="44"/>
+      <c r="K9" s="44"/>
+      <c r="L9" s="44"/>
+      <c r="M9" s="44"/>
+      <c r="N9" s="44"/>
+      <c r="O9" s="44"/>
+      <c r="P9" s="44"/>
+      <c r="Q9" s="44"/>
+      <c r="R9" s="44"/>
+      <c r="S9" s="44"/>
+      <c r="T9" s="44"/>
+      <c r="U9" s="44"/>
+      <c r="V9" s="44"/>
+      <c r="W9" s="44"/>
+      <c r="X9" s="44"/>
+      <c r="Y9" s="44"/>
+      <c r="Z9" s="44"/>
+      <c r="AA9" s="44"/>
+      <c r="AB9" s="44"/>
+      <c r="AC9" s="44"/>
+      <c r="AD9" s="44"/>
+      <c r="AE9" s="44"/>
+      <c r="AF9" s="44"/>
+      <c r="AG9" s="44"/>
+      <c r="AH9" s="44"/>
+      <c r="AI9" s="44"/>
+      <c r="AJ9" s="44"/>
+      <c r="AK9" s="44"/>
+      <c r="AL9" s="44"/>
+      <c r="AM9" s="44"/>
+      <c r="AN9" s="44"/>
+      <c r="AO9" s="44"/>
+      <c r="AP9" s="44"/>
+      <c r="AQ9" s="44"/>
+      <c r="AR9" s="44"/>
+      <c r="AS9" s="44"/>
+      <c r="AT9" s="44"/>
+      <c r="AU9" s="44"/>
+      <c r="AV9" s="44"/>
+      <c r="AW9" s="44"/>
+      <c r="AX9" s="44"/>
+      <c r="AY9" s="44"/>
+      <c r="AZ9" s="44"/>
+      <c r="BA9" s="44"/>
+      <c r="BB9" s="44"/>
+      <c r="BC9" s="44"/>
+      <c r="BD9" s="44"/>
+      <c r="BE9" s="44"/>
+      <c r="BF9" s="44"/>
+      <c r="BG9" s="44"/>
+      <c r="BH9" s="44"/>
+      <c r="BI9" s="44"/>
+      <c r="BJ9" s="44"/>
+      <c r="BK9" s="44"/>
+      <c r="BL9" s="44"/>
+      <c r="BM9" s="44"/>
+      <c r="BN9" s="44"/>
+      <c r="BO9" s="44"/>
+      <c r="BP9" s="44"/>
+      <c r="BQ9" s="44"/>
+      <c r="BR9" s="44"/>
+      <c r="BS9" s="44"/>
+      <c r="BT9" s="44"/>
+      <c r="BU9" s="44"/>
+      <c r="BV9" s="44"/>
+      <c r="BW9" s="44"/>
+      <c r="BX9" s="44"/>
+      <c r="BY9" s="44"/>
+      <c r="BZ9" s="44"/>
+      <c r="CA9" s="44"/>
+      <c r="CB9" s="44"/>
     </row>
     <row r="10" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="52"/>
-      <c r="B10" s="53"/>
+      <c r="A10" s="51"/>
+      <c r="B10" s="52"/>
       <c r="C10" s="6"/>
       <c r="D10" s="4" t="s">
         <v>12</v>
@@ -2467,7 +2511,7 @@
       </c>
       <c r="D13" s="11">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E13" s="12"/>
       <c r="F13" s="8"/>
@@ -2503,11 +2547,21 @@
       <c r="Z13" s="8">
         <v>0</v>
       </c>
-      <c r="AA13" s="8"/>
-      <c r="AB13" s="8"/>
-      <c r="AC13" s="8"/>
-      <c r="AD13" s="8"/>
-      <c r="AE13" s="8"/>
+      <c r="AA13" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="8">
+        <v>0</v>
+      </c>
       <c r="AF13" s="8"/>
       <c r="AG13" s="8"/>
       <c r="AH13" s="8"/>
@@ -2574,7 +2628,7 @@
       </c>
       <c r="D14" s="11">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E14" s="12"/>
       <c r="F14" s="8">
@@ -2622,11 +2676,21 @@
       <c r="X14" s="8"/>
       <c r="Y14" s="8"/>
       <c r="Z14" s="8"/>
-      <c r="AA14" s="8"/>
-      <c r="AB14" s="8"/>
-      <c r="AC14" s="8"/>
-      <c r="AD14" s="8"/>
-      <c r="AE14" s="8"/>
+      <c r="AA14" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="8">
+        <v>0</v>
+      </c>
       <c r="AF14" s="8"/>
       <c r="AG14" s="8"/>
       <c r="AH14" s="8"/>
@@ -2689,7 +2753,7 @@
       </c>
       <c r="D15" s="11">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E15" s="12"/>
       <c r="F15" s="8">
@@ -2745,11 +2809,21 @@
       <c r="Z15" s="8">
         <v>0</v>
       </c>
-      <c r="AA15" s="8"/>
-      <c r="AB15" s="8"/>
-      <c r="AC15" s="8"/>
-      <c r="AD15" s="8"/>
-      <c r="AE15" s="8"/>
+      <c r="AA15" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="8">
+        <v>0</v>
+      </c>
       <c r="AF15" s="8"/>
       <c r="AG15" s="8"/>
       <c r="AH15" s="8"/>
@@ -2812,7 +2886,7 @@
       </c>
       <c r="D16" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E16" s="12"/>
       <c r="F16" s="8"/>
@@ -2836,11 +2910,21 @@
       <c r="X16" s="8"/>
       <c r="Y16" s="8"/>
       <c r="Z16" s="8"/>
-      <c r="AA16" s="8"/>
-      <c r="AB16" s="8"/>
-      <c r="AC16" s="8"/>
-      <c r="AD16" s="8"/>
-      <c r="AE16" s="8"/>
+      <c r="AA16" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="8">
+        <v>0</v>
+      </c>
       <c r="AF16" s="8"/>
       <c r="AG16" s="8"/>
       <c r="AH16" s="8"/>
@@ -2939,72 +3023,72 @@
       <c r="P17" s="8">
         <v>0</v>
       </c>
-      <c r="Q17" s="46" t="s">
+      <c r="Q17" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="R17" s="47"/>
-      <c r="S17" s="47"/>
-      <c r="T17" s="47"/>
-      <c r="U17" s="47"/>
-      <c r="V17" s="47"/>
-      <c r="W17" s="47"/>
-      <c r="X17" s="47"/>
-      <c r="Y17" s="47"/>
-      <c r="Z17" s="47"/>
-      <c r="AA17" s="47"/>
-      <c r="AB17" s="47"/>
-      <c r="AC17" s="47"/>
-      <c r="AD17" s="47"/>
-      <c r="AE17" s="47"/>
-      <c r="AF17" s="47"/>
-      <c r="AG17" s="47"/>
-      <c r="AH17" s="47"/>
-      <c r="AI17" s="47"/>
-      <c r="AJ17" s="47"/>
-      <c r="AK17" s="47"/>
-      <c r="AL17" s="47"/>
-      <c r="AM17" s="47"/>
-      <c r="AN17" s="47"/>
-      <c r="AO17" s="47"/>
-      <c r="AP17" s="47"/>
-      <c r="AQ17" s="47"/>
-      <c r="AR17" s="47"/>
-      <c r="AS17" s="47"/>
-      <c r="AT17" s="47"/>
-      <c r="AU17" s="47"/>
-      <c r="AV17" s="47"/>
-      <c r="AW17" s="47"/>
-      <c r="AX17" s="47"/>
-      <c r="AY17" s="47"/>
-      <c r="AZ17" s="47"/>
-      <c r="BA17" s="47"/>
-      <c r="BB17" s="47"/>
-      <c r="BC17" s="47"/>
-      <c r="BD17" s="47"/>
-      <c r="BE17" s="47"/>
-      <c r="BF17" s="47"/>
-      <c r="BG17" s="47"/>
-      <c r="BH17" s="47"/>
-      <c r="BI17" s="47"/>
-      <c r="BJ17" s="47"/>
-      <c r="BK17" s="47"/>
-      <c r="BL17" s="47"/>
-      <c r="BM17" s="47"/>
-      <c r="BN17" s="47"/>
-      <c r="BO17" s="47"/>
-      <c r="BP17" s="47"/>
-      <c r="BQ17" s="47"/>
-      <c r="BR17" s="47"/>
-      <c r="BS17" s="47"/>
-      <c r="BT17" s="47"/>
-      <c r="BU17" s="47"/>
-      <c r="BV17" s="47"/>
-      <c r="BW17" s="47"/>
-      <c r="BX17" s="47"/>
-      <c r="BY17" s="47"/>
-      <c r="BZ17" s="47"/>
-      <c r="CA17" s="47"/>
-      <c r="CB17" s="48"/>
+      <c r="R17" s="46"/>
+      <c r="S17" s="46"/>
+      <c r="T17" s="46"/>
+      <c r="U17" s="46"/>
+      <c r="V17" s="46"/>
+      <c r="W17" s="46"/>
+      <c r="X17" s="46"/>
+      <c r="Y17" s="46"/>
+      <c r="Z17" s="46"/>
+      <c r="AA17" s="46"/>
+      <c r="AB17" s="46"/>
+      <c r="AC17" s="46"/>
+      <c r="AD17" s="46"/>
+      <c r="AE17" s="46"/>
+      <c r="AF17" s="46"/>
+      <c r="AG17" s="46"/>
+      <c r="AH17" s="46"/>
+      <c r="AI17" s="46"/>
+      <c r="AJ17" s="46"/>
+      <c r="AK17" s="46"/>
+      <c r="AL17" s="46"/>
+      <c r="AM17" s="46"/>
+      <c r="AN17" s="46"/>
+      <c r="AO17" s="46"/>
+      <c r="AP17" s="46"/>
+      <c r="AQ17" s="46"/>
+      <c r="AR17" s="46"/>
+      <c r="AS17" s="46"/>
+      <c r="AT17" s="46"/>
+      <c r="AU17" s="46"/>
+      <c r="AV17" s="46"/>
+      <c r="AW17" s="46"/>
+      <c r="AX17" s="46"/>
+      <c r="AY17" s="46"/>
+      <c r="AZ17" s="46"/>
+      <c r="BA17" s="46"/>
+      <c r="BB17" s="46"/>
+      <c r="BC17" s="46"/>
+      <c r="BD17" s="46"/>
+      <c r="BE17" s="46"/>
+      <c r="BF17" s="46"/>
+      <c r="BG17" s="46"/>
+      <c r="BH17" s="46"/>
+      <c r="BI17" s="46"/>
+      <c r="BJ17" s="46"/>
+      <c r="BK17" s="46"/>
+      <c r="BL17" s="46"/>
+      <c r="BM17" s="46"/>
+      <c r="BN17" s="46"/>
+      <c r="BO17" s="46"/>
+      <c r="BP17" s="46"/>
+      <c r="BQ17" s="46"/>
+      <c r="BR17" s="46"/>
+      <c r="BS17" s="46"/>
+      <c r="BT17" s="46"/>
+      <c r="BU17" s="46"/>
+      <c r="BV17" s="46"/>
+      <c r="BW17" s="46"/>
+      <c r="BX17" s="46"/>
+      <c r="BY17" s="46"/>
+      <c r="BZ17" s="46"/>
+      <c r="CA17" s="46"/>
+      <c r="CB17" s="47"/>
     </row>
     <row r="18" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9">
@@ -3125,7 +3209,7 @@
       </c>
       <c r="D19" s="11">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E19" s="12"/>
       <c r="F19" s="8">
@@ -3163,11 +3247,21 @@
       <c r="X19" s="8"/>
       <c r="Y19" s="8"/>
       <c r="Z19" s="8"/>
-      <c r="AA19" s="8"/>
-      <c r="AB19" s="8"/>
-      <c r="AC19" s="8"/>
-      <c r="AD19" s="8"/>
-      <c r="AE19" s="8"/>
+      <c r="AA19" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE19" s="8">
+        <v>0</v>
+      </c>
       <c r="AF19" s="8"/>
       <c r="AG19" s="8"/>
       <c r="AH19" s="8"/>
@@ -3230,7 +3324,7 @@
       </c>
       <c r="D20" s="11">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E20" s="12"/>
       <c r="F20" s="8"/>
@@ -3264,11 +3358,21 @@
       <c r="Z20" s="8">
         <v>0</v>
       </c>
-      <c r="AA20" s="8"/>
-      <c r="AB20" s="8"/>
-      <c r="AC20" s="8"/>
-      <c r="AD20" s="8"/>
-      <c r="AE20" s="8"/>
+      <c r="AA20" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="8">
+        <v>0</v>
+      </c>
       <c r="AF20" s="8"/>
       <c r="AG20" s="8"/>
       <c r="AH20" s="8"/>
@@ -3331,7 +3435,7 @@
       </c>
       <c r="D21" s="11">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E21" s="12"/>
       <c r="F21" s="8">
@@ -3397,11 +3501,21 @@
       <c r="Z21" s="8">
         <v>0</v>
       </c>
-      <c r="AA21" s="8"/>
-      <c r="AB21" s="8"/>
-      <c r="AC21" s="8"/>
-      <c r="AD21" s="8"/>
-      <c r="AE21" s="8"/>
+      <c r="AA21" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="8">
+        <v>0</v>
+      </c>
       <c r="AF21" s="8"/>
       <c r="AG21" s="8"/>
       <c r="AH21" s="8"/>
@@ -3464,7 +3578,7 @@
       </c>
       <c r="D22" s="11">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E22" s="12"/>
       <c r="F22" s="8"/>
@@ -3490,11 +3604,21 @@
       <c r="X22" s="8"/>
       <c r="Y22" s="8"/>
       <c r="Z22" s="8"/>
-      <c r="AA22" s="8"/>
-      <c r="AB22" s="8"/>
-      <c r="AC22" s="8"/>
-      <c r="AD22" s="8"/>
-      <c r="AE22" s="8"/>
+      <c r="AA22" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="8">
+        <v>0</v>
+      </c>
       <c r="AF22" s="8"/>
       <c r="AG22" s="8"/>
       <c r="AH22" s="8"/>
@@ -3557,7 +3681,7 @@
       </c>
       <c r="D23" s="11">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E23" s="12"/>
       <c r="F23" s="8">
@@ -3623,11 +3747,21 @@
       <c r="Z23" s="8">
         <v>0</v>
       </c>
-      <c r="AA23" s="8"/>
-      <c r="AB23" s="8"/>
-      <c r="AC23" s="8"/>
-      <c r="AD23" s="8"/>
-      <c r="AE23" s="8"/>
+      <c r="AA23" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="8">
+        <v>0</v>
+      </c>
       <c r="AF23" s="8"/>
       <c r="AG23" s="8"/>
       <c r="AH23" s="8"/>
@@ -3690,7 +3824,7 @@
       </c>
       <c r="D24" s="11">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E24" s="12"/>
       <c r="F24" s="8">
@@ -3732,11 +3866,21 @@
       <c r="X24" s="8"/>
       <c r="Y24" s="8"/>
       <c r="Z24" s="8"/>
-      <c r="AA24" s="8"/>
-      <c r="AB24" s="8"/>
-      <c r="AC24" s="8"/>
-      <c r="AD24" s="8"/>
-      <c r="AE24" s="8"/>
+      <c r="AA24" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="8">
+        <v>0</v>
+      </c>
       <c r="AF24" s="8"/>
       <c r="AG24" s="8"/>
       <c r="AH24" s="8"/>
@@ -3799,7 +3943,7 @@
       </c>
       <c r="D25" s="11">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E25" s="12"/>
       <c r="F25" s="8">
@@ -3843,11 +3987,21 @@
       <c r="Z25" s="8">
         <v>0</v>
       </c>
-      <c r="AA25" s="8"/>
-      <c r="AB25" s="8"/>
-      <c r="AC25" s="8"/>
-      <c r="AD25" s="8"/>
-      <c r="AE25" s="8"/>
+      <c r="AA25" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="8">
+        <v>0</v>
+      </c>
       <c r="AF25" s="8"/>
       <c r="AG25" s="8"/>
       <c r="AH25" s="8"/>
@@ -3910,7 +4064,7 @@
       </c>
       <c r="D26" s="11">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E26" s="12"/>
       <c r="F26" s="8">
@@ -3966,11 +4120,21 @@
       <c r="Z26" s="8">
         <v>0</v>
       </c>
-      <c r="AA26" s="8"/>
-      <c r="AB26" s="8"/>
-      <c r="AC26" s="8"/>
-      <c r="AD26" s="8"/>
-      <c r="AE26" s="8"/>
+      <c r="AA26" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE26" s="8">
+        <v>0</v>
+      </c>
       <c r="AF26" s="8"/>
       <c r="AG26" s="8"/>
       <c r="AH26" s="8"/>
@@ -4033,7 +4197,7 @@
       </c>
       <c r="D27" s="11">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E27" s="15"/>
       <c r="F27" s="8">
@@ -4099,11 +4263,21 @@
       <c r="Z27" s="8">
         <v>0</v>
       </c>
-      <c r="AA27" s="8"/>
-      <c r="AB27" s="8"/>
-      <c r="AC27" s="8"/>
-      <c r="AD27" s="8"/>
-      <c r="AE27" s="8"/>
+      <c r="AA27" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE27" s="8">
+        <v>0</v>
+      </c>
       <c r="AF27" s="8"/>
       <c r="AG27" s="8"/>
       <c r="AH27" s="8"/>
@@ -4168,87 +4342,87 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E28" s="49" t="s">
+      <c r="E28" s="48" t="s">
         <v>48</v>
       </c>
-      <c r="F28" s="49"/>
-      <c r="G28" s="49"/>
-      <c r="H28" s="49"/>
-      <c r="I28" s="49"/>
-      <c r="J28" s="49"/>
-      <c r="K28" s="49"/>
-      <c r="L28" s="49"/>
-      <c r="M28" s="49"/>
-      <c r="N28" s="49"/>
-      <c r="O28" s="49"/>
-      <c r="P28" s="49"/>
-      <c r="Q28" s="49"/>
-      <c r="R28" s="49"/>
-      <c r="S28" s="49"/>
-      <c r="T28" s="49"/>
-      <c r="U28" s="49"/>
-      <c r="V28" s="49"/>
-      <c r="W28" s="49"/>
-      <c r="X28" s="49"/>
-      <c r="Y28" s="49"/>
-      <c r="Z28" s="49"/>
-      <c r="AA28" s="49"/>
-      <c r="AB28" s="49"/>
-      <c r="AC28" s="49"/>
-      <c r="AD28" s="49"/>
-      <c r="AE28" s="49"/>
-      <c r="AF28" s="49"/>
-      <c r="AG28" s="49"/>
-      <c r="AH28" s="49"/>
-      <c r="AI28" s="49"/>
-      <c r="AJ28" s="49"/>
-      <c r="AK28" s="49"/>
-      <c r="AL28" s="49"/>
-      <c r="AM28" s="49"/>
-      <c r="AN28" s="49"/>
-      <c r="AO28" s="49"/>
-      <c r="AP28" s="49"/>
-      <c r="AQ28" s="49"/>
-      <c r="AR28" s="49"/>
-      <c r="AS28" s="49"/>
-      <c r="AT28" s="49"/>
-      <c r="AU28" s="49"/>
-      <c r="AV28" s="49"/>
-      <c r="AW28" s="49"/>
-      <c r="AX28" s="49"/>
-      <c r="AY28" s="49"/>
-      <c r="AZ28" s="49"/>
-      <c r="BA28" s="49"/>
-      <c r="BB28" s="49"/>
-      <c r="BC28" s="49"/>
-      <c r="BD28" s="49"/>
-      <c r="BE28" s="49"/>
-      <c r="BF28" s="49"/>
-      <c r="BG28" s="49"/>
-      <c r="BH28" s="49"/>
-      <c r="BI28" s="49"/>
-      <c r="BJ28" s="49"/>
-      <c r="BK28" s="49"/>
-      <c r="BL28" s="49"/>
-      <c r="BM28" s="49"/>
-      <c r="BN28" s="49"/>
-      <c r="BO28" s="49"/>
-      <c r="BP28" s="49"/>
-      <c r="BQ28" s="49"/>
-      <c r="BR28" s="49"/>
-      <c r="BS28" s="49"/>
-      <c r="BT28" s="49"/>
-      <c r="BU28" s="49"/>
-      <c r="BV28" s="49"/>
-      <c r="BW28" s="49"/>
-      <c r="BX28" s="49"/>
-      <c r="BY28" s="49"/>
-      <c r="BZ28" s="49"/>
-      <c r="CA28" s="49"/>
-      <c r="CB28" s="49"/>
+      <c r="F28" s="48"/>
+      <c r="G28" s="48"/>
+      <c r="H28" s="48"/>
+      <c r="I28" s="48"/>
+      <c r="J28" s="48"/>
+      <c r="K28" s="48"/>
+      <c r="L28" s="48"/>
+      <c r="M28" s="48"/>
+      <c r="N28" s="48"/>
+      <c r="O28" s="48"/>
+      <c r="P28" s="48"/>
+      <c r="Q28" s="48"/>
+      <c r="R28" s="48"/>
+      <c r="S28" s="48"/>
+      <c r="T28" s="48"/>
+      <c r="U28" s="48"/>
+      <c r="V28" s="48"/>
+      <c r="W28" s="48"/>
+      <c r="X28" s="48"/>
+      <c r="Y28" s="48"/>
+      <c r="Z28" s="48"/>
+      <c r="AA28" s="48"/>
+      <c r="AB28" s="48"/>
+      <c r="AC28" s="48"/>
+      <c r="AD28" s="48"/>
+      <c r="AE28" s="48"/>
+      <c r="AF28" s="48"/>
+      <c r="AG28" s="48"/>
+      <c r="AH28" s="48"/>
+      <c r="AI28" s="48"/>
+      <c r="AJ28" s="48"/>
+      <c r="AK28" s="48"/>
+      <c r="AL28" s="48"/>
+      <c r="AM28" s="48"/>
+      <c r="AN28" s="48"/>
+      <c r="AO28" s="48"/>
+      <c r="AP28" s="48"/>
+      <c r="AQ28" s="48"/>
+      <c r="AR28" s="48"/>
+      <c r="AS28" s="48"/>
+      <c r="AT28" s="48"/>
+      <c r="AU28" s="48"/>
+      <c r="AV28" s="48"/>
+      <c r="AW28" s="48"/>
+      <c r="AX28" s="48"/>
+      <c r="AY28" s="48"/>
+      <c r="AZ28" s="48"/>
+      <c r="BA28" s="48"/>
+      <c r="BB28" s="48"/>
+      <c r="BC28" s="48"/>
+      <c r="BD28" s="48"/>
+      <c r="BE28" s="48"/>
+      <c r="BF28" s="48"/>
+      <c r="BG28" s="48"/>
+      <c r="BH28" s="48"/>
+      <c r="BI28" s="48"/>
+      <c r="BJ28" s="48"/>
+      <c r="BK28" s="48"/>
+      <c r="BL28" s="48"/>
+      <c r="BM28" s="48"/>
+      <c r="BN28" s="48"/>
+      <c r="BO28" s="48"/>
+      <c r="BP28" s="48"/>
+      <c r="BQ28" s="48"/>
+      <c r="BR28" s="48"/>
+      <c r="BS28" s="48"/>
+      <c r="BT28" s="48"/>
+      <c r="BU28" s="48"/>
+      <c r="BV28" s="48"/>
+      <c r="BW28" s="48"/>
+      <c r="BX28" s="48"/>
+      <c r="BY28" s="48"/>
+      <c r="BZ28" s="48"/>
+      <c r="CA28" s="48"/>
+      <c r="CB28" s="48"/>
     </row>
   </sheetData>
-  <mergeCells count="174">
+  <mergeCells count="175">
     <mergeCell ref="Q17:CB17"/>
     <mergeCell ref="BX8:BX9"/>
     <mergeCell ref="BY8:BY9"/>
@@ -4399,6 +4573,7 @@
     <mergeCell ref="U2:U7"/>
     <mergeCell ref="V2:V7"/>
     <mergeCell ref="Q1:U1"/>
+    <mergeCell ref="AA1:AE1"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="W2:W7"/>
     <mergeCell ref="X2:X7"/>

--- a/ჟურნალი/5. N301 front-end დეველოპმენტი (ინტეგრირებული მიდგომით) - Git.xlsx
+++ b/ჟურნალი/5. N301 front-end დეველოპმენტი (ინტეგრირებული მიდგომით) - Git.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\3Daudiece\Desktop\Front-end!!\0. ready\ჟურნალი\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\designer\Desktop\Front\01. - Front-end-docs\ჟურნალი\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CEB28D3-76E0-4CD3-903D-118AEB3EC026}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A24ADD-B2FE-4B84-B899-5A341C224CC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-122" yWindow="-122" windowWidth="29045" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="301 ინტეგრირებული" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="52">
   <si>
     <t xml:space="preserve">პროგრამა                     </t>
   </si>
@@ -421,6 +434,9 @@
   </si>
   <si>
     <t>სტატუსი შეუწყდა 09.07.2026-დან</t>
+  </si>
+  <si>
+    <t>სტატუსი შეუწყდა</t>
   </si>
 </sst>
 </file>
@@ -758,23 +774,74 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
@@ -806,62 +873,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1080,67 +1096,69 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:CG28"/>
-  <sheetFormatPr defaultColWidth="3.625" defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="3.5703125" defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.625" style="2"/>
+    <col min="1" max="1" width="3.5703125" style="2"/>
     <col min="2" max="3" width="21" style="1" customWidth="1"/>
     <col min="4" max="4" width="8" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="3.625" style="1"/>
+    <col min="5" max="5" width="5.5703125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="3.5703125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="26"/>
-      <c r="D1" s="27"/>
-      <c r="F1" s="49">
+      <c r="A1" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="43"/>
+      <c r="D1" s="44"/>
+      <c r="F1" s="27">
         <v>4</v>
       </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="21">
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="39">
         <v>2</v>
       </c>
-      <c r="K1" s="22"/>
-      <c r="L1" s="21">
+      <c r="K1" s="41"/>
+      <c r="L1" s="39">
         <v>5</v>
       </c>
       <c r="M1" s="40"/>
       <c r="N1" s="40"/>
       <c r="O1" s="40"/>
-      <c r="P1" s="22"/>
-      <c r="Q1" s="21">
+      <c r="P1" s="41"/>
+      <c r="Q1" s="39">
         <v>5</v>
       </c>
       <c r="R1" s="40"/>
       <c r="S1" s="40"/>
       <c r="T1" s="40"/>
-      <c r="U1" s="22"/>
-      <c r="V1" s="21">
+      <c r="U1" s="41"/>
+      <c r="V1" s="39">
         <v>5</v>
       </c>
       <c r="W1" s="40"/>
       <c r="X1" s="40"/>
       <c r="Y1" s="40"/>
-      <c r="Z1" s="22"/>
-      <c r="AA1" s="21">
+      <c r="Z1" s="41"/>
+      <c r="AA1" s="39">
         <v>5</v>
       </c>
       <c r="AB1" s="40"/>
       <c r="AC1" s="40"/>
       <c r="AD1" s="40"/>
-      <c r="AE1" s="22"/>
-      <c r="AF1" s="17"/>
-      <c r="AG1" s="17"/>
-      <c r="AH1" s="17"/>
-      <c r="AI1" s="17"/>
-      <c r="AJ1" s="17"/>
+      <c r="AE1" s="41"/>
+      <c r="AF1" s="39">
+        <v>5</v>
+      </c>
+      <c r="AG1" s="40"/>
+      <c r="AH1" s="40"/>
+      <c r="AI1" s="40"/>
+      <c r="AJ1" s="41"/>
       <c r="AK1" s="18"/>
       <c r="AL1" s="18"/>
       <c r="AM1" s="17"/>
@@ -1187,901 +1205,911 @@
       <c r="CB1" s="17"/>
       <c r="CC1" s="1">
         <f>SUM(E1:CB1)</f>
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:85" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="25"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="30" t="s">
+      <c r="A2" s="42"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="23">
+      <c r="F2" s="35">
         <v>46202</v>
       </c>
-      <c r="G2" s="23">
+      <c r="G2" s="35">
         <v>46202</v>
       </c>
-      <c r="H2" s="23">
+      <c r="H2" s="35">
         <v>46202</v>
       </c>
-      <c r="I2" s="23">
+      <c r="I2" s="35">
         <v>46202</v>
       </c>
-      <c r="J2" s="23">
+      <c r="J2" s="35">
         <v>46206</v>
       </c>
-      <c r="K2" s="23">
+      <c r="K2" s="35">
         <v>46206</v>
       </c>
-      <c r="L2" s="23">
+      <c r="L2" s="35">
         <v>46209</v>
       </c>
-      <c r="M2" s="23">
+      <c r="M2" s="35">
         <v>46209</v>
       </c>
-      <c r="N2" s="23">
+      <c r="N2" s="35">
         <v>46209</v>
       </c>
-      <c r="O2" s="23">
+      <c r="O2" s="35">
         <v>46209</v>
       </c>
-      <c r="P2" s="23">
+      <c r="P2" s="35">
         <v>46209</v>
       </c>
-      <c r="Q2" s="23">
+      <c r="Q2" s="35">
         <v>46216</v>
       </c>
-      <c r="R2" s="23">
+      <c r="R2" s="35">
         <v>46216</v>
       </c>
-      <c r="S2" s="23">
+      <c r="S2" s="35">
         <v>46216</v>
       </c>
-      <c r="T2" s="23">
+      <c r="T2" s="35">
         <v>46216</v>
       </c>
-      <c r="U2" s="23">
+      <c r="U2" s="35">
         <v>46216</v>
       </c>
-      <c r="V2" s="23">
+      <c r="V2" s="35">
         <v>46223</v>
       </c>
-      <c r="W2" s="23">
+      <c r="W2" s="35">
         <v>46223</v>
       </c>
-      <c r="X2" s="23">
+      <c r="X2" s="35">
         <v>46223</v>
       </c>
-      <c r="Y2" s="23">
+      <c r="Y2" s="35">
         <v>46223</v>
       </c>
-      <c r="Z2" s="23">
+      <c r="Z2" s="35">
         <v>46223</v>
       </c>
-      <c r="AA2" s="23">
+      <c r="AA2" s="35">
         <v>46230</v>
       </c>
-      <c r="AB2" s="23">
+      <c r="AB2" s="35">
         <v>46230</v>
       </c>
-      <c r="AC2" s="23">
+      <c r="AC2" s="35">
         <v>46230</v>
       </c>
-      <c r="AD2" s="23">
+      <c r="AD2" s="35">
         <v>46230</v>
       </c>
-      <c r="AE2" s="23">
+      <c r="AE2" s="35">
         <v>46230</v>
       </c>
-      <c r="AF2" s="23"/>
-      <c r="AG2" s="23"/>
-      <c r="AH2" s="23"/>
-      <c r="AI2" s="23"/>
-      <c r="AJ2" s="23"/>
-      <c r="AK2" s="23"/>
-      <c r="AL2" s="23"/>
-      <c r="AM2" s="23"/>
-      <c r="AN2" s="23"/>
-      <c r="AO2" s="23"/>
-      <c r="AP2" s="23"/>
-      <c r="AQ2" s="23"/>
-      <c r="AR2" s="23"/>
-      <c r="AS2" s="23"/>
-      <c r="AT2" s="23"/>
-      <c r="AU2" s="23"/>
-      <c r="AV2" s="23"/>
-      <c r="AW2" s="23"/>
-      <c r="AX2" s="23"/>
-      <c r="AY2" s="23"/>
-      <c r="AZ2" s="23"/>
-      <c r="BA2" s="23"/>
-      <c r="BB2" s="23"/>
-      <c r="BC2" s="23"/>
-      <c r="BD2" s="23"/>
-      <c r="BE2" s="23"/>
-      <c r="BF2" s="23"/>
-      <c r="BG2" s="23"/>
-      <c r="BH2" s="23"/>
-      <c r="BI2" s="23"/>
-      <c r="BJ2" s="23"/>
-      <c r="BK2" s="23"/>
-      <c r="BL2" s="23"/>
-      <c r="BM2" s="23"/>
-      <c r="BN2" s="23"/>
-      <c r="BO2" s="23"/>
-      <c r="BP2" s="23"/>
-      <c r="BQ2" s="23"/>
-      <c r="BR2" s="23"/>
-      <c r="BS2" s="23"/>
-      <c r="BT2" s="23"/>
-      <c r="BU2" s="23"/>
-      <c r="BV2" s="23"/>
-      <c r="BW2" s="23"/>
-      <c r="BX2" s="23"/>
-      <c r="BY2" s="23"/>
-      <c r="BZ2" s="23"/>
-      <c r="CA2" s="23"/>
-      <c r="CB2" s="23"/>
+      <c r="AF2" s="35">
+        <v>46279</v>
+      </c>
+      <c r="AG2" s="35">
+        <v>46279</v>
+      </c>
+      <c r="AH2" s="35">
+        <v>46279</v>
+      </c>
+      <c r="AI2" s="35">
+        <v>46279</v>
+      </c>
+      <c r="AJ2" s="35">
+        <v>46279</v>
+      </c>
+      <c r="AK2" s="35"/>
+      <c r="AL2" s="35"/>
+      <c r="AM2" s="35"/>
+      <c r="AN2" s="35"/>
+      <c r="AO2" s="35"/>
+      <c r="AP2" s="35"/>
+      <c r="AQ2" s="35"/>
+      <c r="AR2" s="35"/>
+      <c r="AS2" s="35"/>
+      <c r="AT2" s="35"/>
+      <c r="AU2" s="35"/>
+      <c r="AV2" s="35"/>
+      <c r="AW2" s="35"/>
+      <c r="AX2" s="35"/>
+      <c r="AY2" s="35"/>
+      <c r="AZ2" s="35"/>
+      <c r="BA2" s="35"/>
+      <c r="BB2" s="35"/>
+      <c r="BC2" s="35"/>
+      <c r="BD2" s="35"/>
+      <c r="BE2" s="35"/>
+      <c r="BF2" s="35"/>
+      <c r="BG2" s="35"/>
+      <c r="BH2" s="35"/>
+      <c r="BI2" s="35"/>
+      <c r="BJ2" s="35"/>
+      <c r="BK2" s="35"/>
+      <c r="BL2" s="35"/>
+      <c r="BM2" s="35"/>
+      <c r="BN2" s="35"/>
+      <c r="BO2" s="35"/>
+      <c r="BP2" s="35"/>
+      <c r="BQ2" s="35"/>
+      <c r="BR2" s="35"/>
+      <c r="BS2" s="35"/>
+      <c r="BT2" s="35"/>
+      <c r="BU2" s="35"/>
+      <c r="BV2" s="35"/>
+      <c r="BW2" s="35"/>
+      <c r="BX2" s="35"/>
+      <c r="BY2" s="35"/>
+      <c r="BZ2" s="35"/>
+      <c r="CA2" s="35"/>
+      <c r="CB2" s="35"/>
     </row>
-    <row r="3" spans="1:85" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="33" t="s">
+    <row r="3" spans="1:85" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="33"/>
-      <c r="C3" s="33"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="23"/>
-      <c r="K3" s="23"/>
-      <c r="L3" s="23"/>
-      <c r="M3" s="23"/>
-      <c r="N3" s="23"/>
-      <c r="O3" s="23"/>
-      <c r="P3" s="23"/>
-      <c r="Q3" s="23"/>
-      <c r="R3" s="23"/>
-      <c r="S3" s="23"/>
-      <c r="T3" s="23"/>
-      <c r="U3" s="23"/>
-      <c r="V3" s="23"/>
-      <c r="W3" s="23"/>
-      <c r="X3" s="23"/>
-      <c r="Y3" s="23"/>
-      <c r="Z3" s="23"/>
-      <c r="AA3" s="23"/>
-      <c r="AB3" s="23"/>
-      <c r="AC3" s="23"/>
-      <c r="AD3" s="23"/>
-      <c r="AE3" s="23"/>
-      <c r="AF3" s="23"/>
-      <c r="AG3" s="23"/>
-      <c r="AH3" s="23"/>
-      <c r="AI3" s="23"/>
-      <c r="AJ3" s="23"/>
-      <c r="AK3" s="23"/>
-      <c r="AL3" s="23"/>
-      <c r="AM3" s="23"/>
-      <c r="AN3" s="23"/>
-      <c r="AO3" s="23"/>
-      <c r="AP3" s="23"/>
-      <c r="AQ3" s="23"/>
-      <c r="AR3" s="23"/>
-      <c r="AS3" s="23"/>
-      <c r="AT3" s="23"/>
-      <c r="AU3" s="23"/>
-      <c r="AV3" s="23"/>
-      <c r="AW3" s="23"/>
-      <c r="AX3" s="23"/>
-      <c r="AY3" s="23"/>
-      <c r="AZ3" s="23"/>
-      <c r="BA3" s="23"/>
-      <c r="BB3" s="23"/>
-      <c r="BC3" s="23"/>
-      <c r="BD3" s="23"/>
-      <c r="BE3" s="23"/>
-      <c r="BF3" s="23"/>
-      <c r="BG3" s="23"/>
-      <c r="BH3" s="23"/>
-      <c r="BI3" s="23"/>
-      <c r="BJ3" s="23"/>
-      <c r="BK3" s="23"/>
-      <c r="BL3" s="23"/>
-      <c r="BM3" s="23"/>
-      <c r="BN3" s="23"/>
-      <c r="BO3" s="23"/>
-      <c r="BP3" s="23"/>
-      <c r="BQ3" s="23"/>
-      <c r="BR3" s="23"/>
-      <c r="BS3" s="23"/>
-      <c r="BT3" s="23"/>
-      <c r="BU3" s="23"/>
-      <c r="BV3" s="23"/>
-      <c r="BW3" s="23"/>
-      <c r="BX3" s="23"/>
-      <c r="BY3" s="23"/>
-      <c r="BZ3" s="23"/>
-      <c r="CA3" s="23"/>
-      <c r="CB3" s="23"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="35"/>
+      <c r="M3" s="35"/>
+      <c r="N3" s="35"/>
+      <c r="O3" s="35"/>
+      <c r="P3" s="35"/>
+      <c r="Q3" s="35"/>
+      <c r="R3" s="35"/>
+      <c r="S3" s="35"/>
+      <c r="T3" s="35"/>
+      <c r="U3" s="35"/>
+      <c r="V3" s="35"/>
+      <c r="W3" s="35"/>
+      <c r="X3" s="35"/>
+      <c r="Y3" s="35"/>
+      <c r="Z3" s="35"/>
+      <c r="AA3" s="35"/>
+      <c r="AB3" s="35"/>
+      <c r="AC3" s="35"/>
+      <c r="AD3" s="35"/>
+      <c r="AE3" s="35"/>
+      <c r="AF3" s="35"/>
+      <c r="AG3" s="35"/>
+      <c r="AH3" s="35"/>
+      <c r="AI3" s="35"/>
+      <c r="AJ3" s="35"/>
+      <c r="AK3" s="35"/>
+      <c r="AL3" s="35"/>
+      <c r="AM3" s="35"/>
+      <c r="AN3" s="35"/>
+      <c r="AO3" s="35"/>
+      <c r="AP3" s="35"/>
+      <c r="AQ3" s="35"/>
+      <c r="AR3" s="35"/>
+      <c r="AS3" s="35"/>
+      <c r="AT3" s="35"/>
+      <c r="AU3" s="35"/>
+      <c r="AV3" s="35"/>
+      <c r="AW3" s="35"/>
+      <c r="AX3" s="35"/>
+      <c r="AY3" s="35"/>
+      <c r="AZ3" s="35"/>
+      <c r="BA3" s="35"/>
+      <c r="BB3" s="35"/>
+      <c r="BC3" s="35"/>
+      <c r="BD3" s="35"/>
+      <c r="BE3" s="35"/>
+      <c r="BF3" s="35"/>
+      <c r="BG3" s="35"/>
+      <c r="BH3" s="35"/>
+      <c r="BI3" s="35"/>
+      <c r="BJ3" s="35"/>
+      <c r="BK3" s="35"/>
+      <c r="BL3" s="35"/>
+      <c r="BM3" s="35"/>
+      <c r="BN3" s="35"/>
+      <c r="BO3" s="35"/>
+      <c r="BP3" s="35"/>
+      <c r="BQ3" s="35"/>
+      <c r="BR3" s="35"/>
+      <c r="BS3" s="35"/>
+      <c r="BT3" s="35"/>
+      <c r="BU3" s="35"/>
+      <c r="BV3" s="35"/>
+      <c r="BW3" s="35"/>
+      <c r="BX3" s="35"/>
+      <c r="BY3" s="35"/>
+      <c r="BZ3" s="35"/>
+      <c r="CA3" s="35"/>
+      <c r="CB3" s="35"/>
     </row>
-    <row r="4" spans="1:85" ht="24.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="33" t="s">
+    <row r="4" spans="1:85" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="33"/>
-      <c r="C4" s="34" t="s">
+      <c r="B4" s="50"/>
+      <c r="C4" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="35"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
-      <c r="N4" s="23"/>
-      <c r="O4" s="23"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="23"/>
-      <c r="R4" s="23"/>
-      <c r="S4" s="23"/>
-      <c r="T4" s="23"/>
-      <c r="U4" s="23"/>
-      <c r="V4" s="23"/>
-      <c r="W4" s="23"/>
-      <c r="X4" s="23"/>
-      <c r="Y4" s="23"/>
-      <c r="Z4" s="23"/>
-      <c r="AA4" s="23"/>
-      <c r="AB4" s="23"/>
-      <c r="AC4" s="23"/>
-      <c r="AD4" s="23"/>
-      <c r="AE4" s="23"/>
-      <c r="AF4" s="23"/>
-      <c r="AG4" s="23"/>
-      <c r="AH4" s="23"/>
-      <c r="AI4" s="23"/>
-      <c r="AJ4" s="23"/>
-      <c r="AK4" s="23"/>
-      <c r="AL4" s="23"/>
-      <c r="AM4" s="23"/>
-      <c r="AN4" s="23"/>
-      <c r="AO4" s="23"/>
-      <c r="AP4" s="23"/>
-      <c r="AQ4" s="23"/>
-      <c r="AR4" s="23"/>
-      <c r="AS4" s="23"/>
-      <c r="AT4" s="23"/>
-      <c r="AU4" s="23"/>
-      <c r="AV4" s="23"/>
-      <c r="AW4" s="23"/>
-      <c r="AX4" s="23"/>
-      <c r="AY4" s="23"/>
-      <c r="AZ4" s="23"/>
-      <c r="BA4" s="23"/>
-      <c r="BB4" s="23"/>
-      <c r="BC4" s="23"/>
-      <c r="BD4" s="23"/>
-      <c r="BE4" s="23"/>
-      <c r="BF4" s="23"/>
-      <c r="BG4" s="23"/>
-      <c r="BH4" s="23"/>
-      <c r="BI4" s="23"/>
-      <c r="BJ4" s="23"/>
-      <c r="BK4" s="23"/>
-      <c r="BL4" s="23"/>
-      <c r="BM4" s="23"/>
-      <c r="BN4" s="23"/>
-      <c r="BO4" s="23"/>
-      <c r="BP4" s="23"/>
-      <c r="BQ4" s="23"/>
-      <c r="BR4" s="23"/>
-      <c r="BS4" s="23"/>
-      <c r="BT4" s="23"/>
-      <c r="BU4" s="23"/>
-      <c r="BV4" s="23"/>
-      <c r="BW4" s="23"/>
-      <c r="BX4" s="23"/>
-      <c r="BY4" s="23"/>
-      <c r="BZ4" s="23"/>
-      <c r="CA4" s="23"/>
-      <c r="CB4" s="23"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="35"/>
+      <c r="M4" s="35"/>
+      <c r="N4" s="35"/>
+      <c r="O4" s="35"/>
+      <c r="P4" s="35"/>
+      <c r="Q4" s="35"/>
+      <c r="R4" s="35"/>
+      <c r="S4" s="35"/>
+      <c r="T4" s="35"/>
+      <c r="U4" s="35"/>
+      <c r="V4" s="35"/>
+      <c r="W4" s="35"/>
+      <c r="X4" s="35"/>
+      <c r="Y4" s="35"/>
+      <c r="Z4" s="35"/>
+      <c r="AA4" s="35"/>
+      <c r="AB4" s="35"/>
+      <c r="AC4" s="35"/>
+      <c r="AD4" s="35"/>
+      <c r="AE4" s="35"/>
+      <c r="AF4" s="35"/>
+      <c r="AG4" s="35"/>
+      <c r="AH4" s="35"/>
+      <c r="AI4" s="35"/>
+      <c r="AJ4" s="35"/>
+      <c r="AK4" s="35"/>
+      <c r="AL4" s="35"/>
+      <c r="AM4" s="35"/>
+      <c r="AN4" s="35"/>
+      <c r="AO4" s="35"/>
+      <c r="AP4" s="35"/>
+      <c r="AQ4" s="35"/>
+      <c r="AR4" s="35"/>
+      <c r="AS4" s="35"/>
+      <c r="AT4" s="35"/>
+      <c r="AU4" s="35"/>
+      <c r="AV4" s="35"/>
+      <c r="AW4" s="35"/>
+      <c r="AX4" s="35"/>
+      <c r="AY4" s="35"/>
+      <c r="AZ4" s="35"/>
+      <c r="BA4" s="35"/>
+      <c r="BB4" s="35"/>
+      <c r="BC4" s="35"/>
+      <c r="BD4" s="35"/>
+      <c r="BE4" s="35"/>
+      <c r="BF4" s="35"/>
+      <c r="BG4" s="35"/>
+      <c r="BH4" s="35"/>
+      <c r="BI4" s="35"/>
+      <c r="BJ4" s="35"/>
+      <c r="BK4" s="35"/>
+      <c r="BL4" s="35"/>
+      <c r="BM4" s="35"/>
+      <c r="BN4" s="35"/>
+      <c r="BO4" s="35"/>
+      <c r="BP4" s="35"/>
+      <c r="BQ4" s="35"/>
+      <c r="BR4" s="35"/>
+      <c r="BS4" s="35"/>
+      <c r="BT4" s="35"/>
+      <c r="BU4" s="35"/>
+      <c r="BV4" s="35"/>
+      <c r="BW4" s="35"/>
+      <c r="BX4" s="35"/>
+      <c r="BY4" s="35"/>
+      <c r="BZ4" s="35"/>
+      <c r="CA4" s="35"/>
+      <c r="CB4" s="35"/>
     </row>
-    <row r="5" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="36" t="s">
+    <row r="5" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="36"/>
+      <c r="B5" s="52"/>
       <c r="C5" s="37">
         <v>60</v>
       </c>
       <c r="D5" s="38"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="23"/>
-      <c r="H5" s="23"/>
-      <c r="I5" s="23"/>
-      <c r="J5" s="23"/>
-      <c r="K5" s="23"/>
-      <c r="L5" s="23"/>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23"/>
-      <c r="O5" s="23"/>
-      <c r="P5" s="23"/>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="23"/>
-      <c r="S5" s="23"/>
-      <c r="T5" s="23"/>
-      <c r="U5" s="23"/>
-      <c r="V5" s="23"/>
-      <c r="W5" s="23"/>
-      <c r="X5" s="23"/>
-      <c r="Y5" s="23"/>
-      <c r="Z5" s="23"/>
-      <c r="AA5" s="23"/>
-      <c r="AB5" s="23"/>
-      <c r="AC5" s="23"/>
-      <c r="AD5" s="23"/>
-      <c r="AE5" s="23"/>
-      <c r="AF5" s="23"/>
-      <c r="AG5" s="23"/>
-      <c r="AH5" s="23"/>
-      <c r="AI5" s="23"/>
-      <c r="AJ5" s="23"/>
-      <c r="AK5" s="23"/>
-      <c r="AL5" s="23"/>
-      <c r="AM5" s="23"/>
-      <c r="AN5" s="23"/>
-      <c r="AO5" s="23"/>
-      <c r="AP5" s="23"/>
-      <c r="AQ5" s="23"/>
-      <c r="AR5" s="23"/>
-      <c r="AS5" s="23"/>
-      <c r="AT5" s="23"/>
-      <c r="AU5" s="23"/>
-      <c r="AV5" s="23"/>
-      <c r="AW5" s="23"/>
-      <c r="AX5" s="23"/>
-      <c r="AY5" s="23"/>
-      <c r="AZ5" s="23"/>
-      <c r="BA5" s="23"/>
-      <c r="BB5" s="23"/>
-      <c r="BC5" s="23"/>
-      <c r="BD5" s="23"/>
-      <c r="BE5" s="23"/>
-      <c r="BF5" s="23"/>
-      <c r="BG5" s="23"/>
-      <c r="BH5" s="23"/>
-      <c r="BI5" s="23"/>
-      <c r="BJ5" s="23"/>
-      <c r="BK5" s="23"/>
-      <c r="BL5" s="23"/>
-      <c r="BM5" s="23"/>
-      <c r="BN5" s="23"/>
-      <c r="BO5" s="23"/>
-      <c r="BP5" s="23"/>
-      <c r="BQ5" s="23"/>
-      <c r="BR5" s="23"/>
-      <c r="BS5" s="23"/>
-      <c r="BT5" s="23"/>
-      <c r="BU5" s="23"/>
-      <c r="BV5" s="23"/>
-      <c r="BW5" s="23"/>
-      <c r="BX5" s="23"/>
-      <c r="BY5" s="23"/>
-      <c r="BZ5" s="23"/>
-      <c r="CA5" s="23"/>
-      <c r="CB5" s="23"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="35"/>
+      <c r="J5" s="35"/>
+      <c r="K5" s="35"/>
+      <c r="L5" s="35"/>
+      <c r="M5" s="35"/>
+      <c r="N5" s="35"/>
+      <c r="O5" s="35"/>
+      <c r="P5" s="35"/>
+      <c r="Q5" s="35"/>
+      <c r="R5" s="35"/>
+      <c r="S5" s="35"/>
+      <c r="T5" s="35"/>
+      <c r="U5" s="35"/>
+      <c r="V5" s="35"/>
+      <c r="W5" s="35"/>
+      <c r="X5" s="35"/>
+      <c r="Y5" s="35"/>
+      <c r="Z5" s="35"/>
+      <c r="AA5" s="35"/>
+      <c r="AB5" s="35"/>
+      <c r="AC5" s="35"/>
+      <c r="AD5" s="35"/>
+      <c r="AE5" s="35"/>
+      <c r="AF5" s="35"/>
+      <c r="AG5" s="35"/>
+      <c r="AH5" s="35"/>
+      <c r="AI5" s="35"/>
+      <c r="AJ5" s="35"/>
+      <c r="AK5" s="35"/>
+      <c r="AL5" s="35"/>
+      <c r="AM5" s="35"/>
+      <c r="AN5" s="35"/>
+      <c r="AO5" s="35"/>
+      <c r="AP5" s="35"/>
+      <c r="AQ5" s="35"/>
+      <c r="AR5" s="35"/>
+      <c r="AS5" s="35"/>
+      <c r="AT5" s="35"/>
+      <c r="AU5" s="35"/>
+      <c r="AV5" s="35"/>
+      <c r="AW5" s="35"/>
+      <c r="AX5" s="35"/>
+      <c r="AY5" s="35"/>
+      <c r="AZ5" s="35"/>
+      <c r="BA5" s="35"/>
+      <c r="BB5" s="35"/>
+      <c r="BC5" s="35"/>
+      <c r="BD5" s="35"/>
+      <c r="BE5" s="35"/>
+      <c r="BF5" s="35"/>
+      <c r="BG5" s="35"/>
+      <c r="BH5" s="35"/>
+      <c r="BI5" s="35"/>
+      <c r="BJ5" s="35"/>
+      <c r="BK5" s="35"/>
+      <c r="BL5" s="35"/>
+      <c r="BM5" s="35"/>
+      <c r="BN5" s="35"/>
+      <c r="BO5" s="35"/>
+      <c r="BP5" s="35"/>
+      <c r="BQ5" s="35"/>
+      <c r="BR5" s="35"/>
+      <c r="BS5" s="35"/>
+      <c r="BT5" s="35"/>
+      <c r="BU5" s="35"/>
+      <c r="BV5" s="35"/>
+      <c r="BW5" s="35"/>
+      <c r="BX5" s="35"/>
+      <c r="BY5" s="35"/>
+      <c r="BZ5" s="35"/>
+      <c r="CA5" s="35"/>
+      <c r="CB5" s="35"/>
     </row>
-    <row r="6" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="36" t="s">
+    <row r="6" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="36"/>
+      <c r="B6" s="52"/>
       <c r="C6" s="37">
         <v>6</v>
       </c>
       <c r="D6" s="38"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="23"/>
-      <c r="K6" s="23"/>
-      <c r="L6" s="23"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
-      <c r="O6" s="23"/>
-      <c r="P6" s="23"/>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="23"/>
-      <c r="S6" s="23"/>
-      <c r="T6" s="23"/>
-      <c r="U6" s="23"/>
-      <c r="V6" s="23"/>
-      <c r="W6" s="23"/>
-      <c r="X6" s="23"/>
-      <c r="Y6" s="23"/>
-      <c r="Z6" s="23"/>
-      <c r="AA6" s="23"/>
-      <c r="AB6" s="23"/>
-      <c r="AC6" s="23"/>
-      <c r="AD6" s="23"/>
-      <c r="AE6" s="23"/>
-      <c r="AF6" s="23"/>
-      <c r="AG6" s="23"/>
-      <c r="AH6" s="23"/>
-      <c r="AI6" s="23"/>
-      <c r="AJ6" s="23"/>
-      <c r="AK6" s="23"/>
-      <c r="AL6" s="23"/>
-      <c r="AM6" s="23"/>
-      <c r="AN6" s="23"/>
-      <c r="AO6" s="23"/>
-      <c r="AP6" s="23"/>
-      <c r="AQ6" s="23"/>
-      <c r="AR6" s="23"/>
-      <c r="AS6" s="23"/>
-      <c r="AT6" s="23"/>
-      <c r="AU6" s="23"/>
-      <c r="AV6" s="23"/>
-      <c r="AW6" s="23"/>
-      <c r="AX6" s="23"/>
-      <c r="AY6" s="23"/>
-      <c r="AZ6" s="23"/>
-      <c r="BA6" s="23"/>
-      <c r="BB6" s="23"/>
-      <c r="BC6" s="23"/>
-      <c r="BD6" s="23"/>
-      <c r="BE6" s="23"/>
-      <c r="BF6" s="23"/>
-      <c r="BG6" s="23"/>
-      <c r="BH6" s="23"/>
-      <c r="BI6" s="23"/>
-      <c r="BJ6" s="23"/>
-      <c r="BK6" s="23"/>
-      <c r="BL6" s="23"/>
-      <c r="BM6" s="23"/>
-      <c r="BN6" s="23"/>
-      <c r="BO6" s="23"/>
-      <c r="BP6" s="23"/>
-      <c r="BQ6" s="23"/>
-      <c r="BR6" s="23"/>
-      <c r="BS6" s="23"/>
-      <c r="BT6" s="23"/>
-      <c r="BU6" s="23"/>
-      <c r="BV6" s="23"/>
-      <c r="BW6" s="23"/>
-      <c r="BX6" s="23"/>
-      <c r="BY6" s="23"/>
-      <c r="BZ6" s="23"/>
-      <c r="CA6" s="23"/>
-      <c r="CB6" s="23"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="35"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="35"/>
+      <c r="L6" s="35"/>
+      <c r="M6" s="35"/>
+      <c r="N6" s="35"/>
+      <c r="O6" s="35"/>
+      <c r="P6" s="35"/>
+      <c r="Q6" s="35"/>
+      <c r="R6" s="35"/>
+      <c r="S6" s="35"/>
+      <c r="T6" s="35"/>
+      <c r="U6" s="35"/>
+      <c r="V6" s="35"/>
+      <c r="W6" s="35"/>
+      <c r="X6" s="35"/>
+      <c r="Y6" s="35"/>
+      <c r="Z6" s="35"/>
+      <c r="AA6" s="35"/>
+      <c r="AB6" s="35"/>
+      <c r="AC6" s="35"/>
+      <c r="AD6" s="35"/>
+      <c r="AE6" s="35"/>
+      <c r="AF6" s="35"/>
+      <c r="AG6" s="35"/>
+      <c r="AH6" s="35"/>
+      <c r="AI6" s="35"/>
+      <c r="AJ6" s="35"/>
+      <c r="AK6" s="35"/>
+      <c r="AL6" s="35"/>
+      <c r="AM6" s="35"/>
+      <c r="AN6" s="35"/>
+      <c r="AO6" s="35"/>
+      <c r="AP6" s="35"/>
+      <c r="AQ6" s="35"/>
+      <c r="AR6" s="35"/>
+      <c r="AS6" s="35"/>
+      <c r="AT6" s="35"/>
+      <c r="AU6" s="35"/>
+      <c r="AV6" s="35"/>
+      <c r="AW6" s="35"/>
+      <c r="AX6" s="35"/>
+      <c r="AY6" s="35"/>
+      <c r="AZ6" s="35"/>
+      <c r="BA6" s="35"/>
+      <c r="BB6" s="35"/>
+      <c r="BC6" s="35"/>
+      <c r="BD6" s="35"/>
+      <c r="BE6" s="35"/>
+      <c r="BF6" s="35"/>
+      <c r="BG6" s="35"/>
+      <c r="BH6" s="35"/>
+      <c r="BI6" s="35"/>
+      <c r="BJ6" s="35"/>
+      <c r="BK6" s="35"/>
+      <c r="BL6" s="35"/>
+      <c r="BM6" s="35"/>
+      <c r="BN6" s="35"/>
+      <c r="BO6" s="35"/>
+      <c r="BP6" s="35"/>
+      <c r="BQ6" s="35"/>
+      <c r="BR6" s="35"/>
+      <c r="BS6" s="35"/>
+      <c r="BT6" s="35"/>
+      <c r="BU6" s="35"/>
+      <c r="BV6" s="35"/>
+      <c r="BW6" s="35"/>
+      <c r="BX6" s="35"/>
+      <c r="BY6" s="35"/>
+      <c r="BZ6" s="35"/>
+      <c r="CA6" s="35"/>
+      <c r="CB6" s="35"/>
     </row>
-    <row r="7" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="39" t="s">
+    <row r="7" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="39"/>
+      <c r="B7" s="53"/>
       <c r="C7" s="37">
         <v>9</v>
       </c>
       <c r="D7" s="38"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="24"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="24"/>
-      <c r="L7" s="24"/>
-      <c r="M7" s="24"/>
-      <c r="N7" s="24"/>
-      <c r="O7" s="24"/>
-      <c r="P7" s="24"/>
-      <c r="Q7" s="24"/>
-      <c r="R7" s="24"/>
-      <c r="S7" s="24"/>
-      <c r="T7" s="24"/>
-      <c r="U7" s="24"/>
-      <c r="V7" s="24"/>
-      <c r="W7" s="24"/>
-      <c r="X7" s="24"/>
-      <c r="Y7" s="24"/>
-      <c r="Z7" s="24"/>
-      <c r="AA7" s="24"/>
-      <c r="AB7" s="24"/>
-      <c r="AC7" s="24"/>
-      <c r="AD7" s="24"/>
-      <c r="AE7" s="24"/>
-      <c r="AF7" s="24"/>
-      <c r="AG7" s="24"/>
-      <c r="AH7" s="24"/>
-      <c r="AI7" s="24"/>
-      <c r="AJ7" s="24"/>
-      <c r="AK7" s="24"/>
-      <c r="AL7" s="24"/>
-      <c r="AM7" s="24"/>
-      <c r="AN7" s="24"/>
-      <c r="AO7" s="24"/>
-      <c r="AP7" s="24"/>
-      <c r="AQ7" s="24"/>
-      <c r="AR7" s="24"/>
-      <c r="AS7" s="24"/>
-      <c r="AT7" s="24"/>
-      <c r="AU7" s="24"/>
-      <c r="AV7" s="24"/>
-      <c r="AW7" s="24"/>
-      <c r="AX7" s="24"/>
-      <c r="AY7" s="24"/>
-      <c r="AZ7" s="24"/>
-      <c r="BA7" s="24"/>
-      <c r="BB7" s="24"/>
-      <c r="BC7" s="24"/>
-      <c r="BD7" s="24"/>
-      <c r="BE7" s="24"/>
-      <c r="BF7" s="24"/>
-      <c r="BG7" s="24"/>
-      <c r="BH7" s="24"/>
-      <c r="BI7" s="24"/>
-      <c r="BJ7" s="24"/>
-      <c r="BK7" s="24"/>
-      <c r="BL7" s="24"/>
-      <c r="BM7" s="24"/>
-      <c r="BN7" s="24"/>
-      <c r="BO7" s="24"/>
-      <c r="BP7" s="24"/>
-      <c r="BQ7" s="24"/>
-      <c r="BR7" s="24"/>
-      <c r="BS7" s="24"/>
-      <c r="BT7" s="24"/>
-      <c r="BU7" s="24"/>
-      <c r="BV7" s="24"/>
-      <c r="BW7" s="24"/>
-      <c r="BX7" s="24"/>
-      <c r="BY7" s="24"/>
-      <c r="BZ7" s="24"/>
-      <c r="CA7" s="24"/>
-      <c r="CB7" s="24"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="36"/>
+      <c r="K7" s="36"/>
+      <c r="L7" s="36"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="36"/>
+      <c r="O7" s="36"/>
+      <c r="P7" s="36"/>
+      <c r="Q7" s="36"/>
+      <c r="R7" s="36"/>
+      <c r="S7" s="36"/>
+      <c r="T7" s="36"/>
+      <c r="U7" s="36"/>
+      <c r="V7" s="36"/>
+      <c r="W7" s="36"/>
+      <c r="X7" s="36"/>
+      <c r="Y7" s="36"/>
+      <c r="Z7" s="36"/>
+      <c r="AA7" s="36"/>
+      <c r="AB7" s="36"/>
+      <c r="AC7" s="36"/>
+      <c r="AD7" s="36"/>
+      <c r="AE7" s="36"/>
+      <c r="AF7" s="36"/>
+      <c r="AG7" s="36"/>
+      <c r="AH7" s="36"/>
+      <c r="AI7" s="36"/>
+      <c r="AJ7" s="36"/>
+      <c r="AK7" s="36"/>
+      <c r="AL7" s="36"/>
+      <c r="AM7" s="36"/>
+      <c r="AN7" s="36"/>
+      <c r="AO7" s="36"/>
+      <c r="AP7" s="36"/>
+      <c r="AQ7" s="36"/>
+      <c r="AR7" s="36"/>
+      <c r="AS7" s="36"/>
+      <c r="AT7" s="36"/>
+      <c r="AU7" s="36"/>
+      <c r="AV7" s="36"/>
+      <c r="AW7" s="36"/>
+      <c r="AX7" s="36"/>
+      <c r="AY7" s="36"/>
+      <c r="AZ7" s="36"/>
+      <c r="BA7" s="36"/>
+      <c r="BB7" s="36"/>
+      <c r="BC7" s="36"/>
+      <c r="BD7" s="36"/>
+      <c r="BE7" s="36"/>
+      <c r="BF7" s="36"/>
+      <c r="BG7" s="36"/>
+      <c r="BH7" s="36"/>
+      <c r="BI7" s="36"/>
+      <c r="BJ7" s="36"/>
+      <c r="BK7" s="36"/>
+      <c r="BL7" s="36"/>
+      <c r="BM7" s="36"/>
+      <c r="BN7" s="36"/>
+      <c r="BO7" s="36"/>
+      <c r="BP7" s="36"/>
+      <c r="BQ7" s="36"/>
+      <c r="BR7" s="36"/>
+      <c r="BS7" s="36"/>
+      <c r="BT7" s="36"/>
+      <c r="BU7" s="36"/>
+      <c r="BV7" s="36"/>
+      <c r="BW7" s="36"/>
+      <c r="BX7" s="36"/>
+      <c r="BY7" s="36"/>
+      <c r="BZ7" s="36"/>
+      <c r="CA7" s="36"/>
+      <c r="CB7" s="36"/>
     </row>
-    <row r="8" spans="1:85" ht="23.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="41" t="s">
+    <row r="8" spans="1:85" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="41"/>
-      <c r="C8" s="42">
+      <c r="B8" s="32"/>
+      <c r="C8" s="33">
         <f>SUM(C5:D7)</f>
         <v>75</v>
       </c>
-      <c r="D8" s="35"/>
+      <c r="D8" s="34"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="43">
-        <v>1</v>
-      </c>
-      <c r="G8" s="43">
+      <c r="F8" s="24">
+        <v>1</v>
+      </c>
+      <c r="G8" s="24">
         <v>2</v>
       </c>
-      <c r="H8" s="43">
+      <c r="H8" s="24">
         <v>3</v>
       </c>
-      <c r="I8" s="43">
+      <c r="I8" s="24">
         <v>4</v>
       </c>
-      <c r="J8" s="43">
+      <c r="J8" s="24">
         <v>5</v>
       </c>
-      <c r="K8" s="43">
+      <c r="K8" s="24">
         <v>6</v>
       </c>
-      <c r="L8" s="43">
+      <c r="L8" s="24">
         <v>7</v>
       </c>
-      <c r="M8" s="43">
+      <c r="M8" s="24">
         <v>8</v>
       </c>
-      <c r="N8" s="43">
+      <c r="N8" s="24">
         <v>9</v>
       </c>
-      <c r="O8" s="43">
+      <c r="O8" s="24">
         <v>10</v>
       </c>
-      <c r="P8" s="43">
+      <c r="P8" s="24">
         <v>11</v>
       </c>
-      <c r="Q8" s="43">
+      <c r="Q8" s="24">
         <v>12</v>
       </c>
-      <c r="R8" s="43">
+      <c r="R8" s="24">
         <v>13</v>
       </c>
-      <c r="S8" s="43">
+      <c r="S8" s="24">
         <v>14</v>
       </c>
-      <c r="T8" s="43">
+      <c r="T8" s="24">
         <v>15</v>
       </c>
-      <c r="U8" s="43">
+      <c r="U8" s="24">
         <v>16</v>
       </c>
-      <c r="V8" s="43">
+      <c r="V8" s="24">
         <v>17</v>
       </c>
-      <c r="W8" s="43">
+      <c r="W8" s="24">
         <v>18</v>
       </c>
-      <c r="X8" s="43">
+      <c r="X8" s="24">
         <v>19</v>
       </c>
-      <c r="Y8" s="43">
+      <c r="Y8" s="24">
         <v>20</v>
       </c>
-      <c r="Z8" s="43">
+      <c r="Z8" s="24">
         <v>21</v>
       </c>
-      <c r="AA8" s="43">
+      <c r="AA8" s="24">
         <v>22</v>
       </c>
-      <c r="AB8" s="43">
+      <c r="AB8" s="24">
         <v>23</v>
       </c>
-      <c r="AC8" s="43">
+      <c r="AC8" s="24">
         <v>24</v>
       </c>
-      <c r="AD8" s="43">
+      <c r="AD8" s="24">
         <v>25</v>
       </c>
-      <c r="AE8" s="43">
+      <c r="AE8" s="24">
         <v>26</v>
       </c>
-      <c r="AF8" s="43">
+      <c r="AF8" s="24">
         <v>27</v>
       </c>
-      <c r="AG8" s="43">
+      <c r="AG8" s="24">
         <v>28</v>
       </c>
-      <c r="AH8" s="43">
+      <c r="AH8" s="24">
         <v>29</v>
       </c>
-      <c r="AI8" s="43">
+      <c r="AI8" s="24">
         <v>30</v>
       </c>
-      <c r="AJ8" s="43">
+      <c r="AJ8" s="24">
         <v>31</v>
       </c>
-      <c r="AK8" s="43">
+      <c r="AK8" s="24">
         <v>32</v>
       </c>
-      <c r="AL8" s="43">
+      <c r="AL8" s="24">
         <v>33</v>
       </c>
-      <c r="AM8" s="43">
+      <c r="AM8" s="24">
         <v>34</v>
       </c>
-      <c r="AN8" s="43">
+      <c r="AN8" s="24">
         <v>35</v>
       </c>
-      <c r="AO8" s="43">
+      <c r="AO8" s="24">
         <v>36</v>
       </c>
-      <c r="AP8" s="43">
+      <c r="AP8" s="24">
         <v>37</v>
       </c>
-      <c r="AQ8" s="43">
+      <c r="AQ8" s="24">
         <v>38</v>
       </c>
-      <c r="AR8" s="43">
+      <c r="AR8" s="24">
         <v>39</v>
       </c>
-      <c r="AS8" s="43">
+      <c r="AS8" s="24">
         <v>40</v>
       </c>
-      <c r="AT8" s="43">
+      <c r="AT8" s="24">
         <v>41</v>
       </c>
-      <c r="AU8" s="43">
+      <c r="AU8" s="24">
         <v>42</v>
       </c>
-      <c r="AV8" s="43">
+      <c r="AV8" s="24">
         <v>43</v>
       </c>
-      <c r="AW8" s="43">
+      <c r="AW8" s="24">
         <v>44</v>
       </c>
-      <c r="AX8" s="43">
+      <c r="AX8" s="24">
         <v>45</v>
       </c>
-      <c r="AY8" s="43">
+      <c r="AY8" s="24">
         <v>46</v>
       </c>
-      <c r="AZ8" s="43">
+      <c r="AZ8" s="24">
         <v>47</v>
       </c>
-      <c r="BA8" s="43">
+      <c r="BA8" s="24">
         <v>48</v>
       </c>
-      <c r="BB8" s="43">
+      <c r="BB8" s="24">
         <v>49</v>
       </c>
-      <c r="BC8" s="43">
+      <c r="BC8" s="24">
         <v>50</v>
       </c>
-      <c r="BD8" s="43">
+      <c r="BD8" s="24">
         <v>51</v>
       </c>
-      <c r="BE8" s="43">
+      <c r="BE8" s="24">
         <v>52</v>
       </c>
-      <c r="BF8" s="43">
+      <c r="BF8" s="24">
         <v>53</v>
       </c>
-      <c r="BG8" s="43">
+      <c r="BG8" s="24">
         <v>54</v>
       </c>
-      <c r="BH8" s="43">
+      <c r="BH8" s="24">
         <v>55</v>
       </c>
-      <c r="BI8" s="43">
+      <c r="BI8" s="24">
         <v>56</v>
       </c>
-      <c r="BJ8" s="43">
+      <c r="BJ8" s="24">
         <v>57</v>
       </c>
-      <c r="BK8" s="43">
+      <c r="BK8" s="24">
         <v>58</v>
       </c>
-      <c r="BL8" s="43">
+      <c r="BL8" s="24">
         <v>59</v>
       </c>
-      <c r="BM8" s="43">
+      <c r="BM8" s="24">
         <v>60</v>
       </c>
-      <c r="BN8" s="43">
+      <c r="BN8" s="24">
         <v>61</v>
       </c>
-      <c r="BO8" s="43">
+      <c r="BO8" s="24">
         <v>62</v>
       </c>
-      <c r="BP8" s="43">
+      <c r="BP8" s="24">
         <v>63</v>
       </c>
-      <c r="BQ8" s="43">
+      <c r="BQ8" s="24">
         <v>64</v>
       </c>
-      <c r="BR8" s="43">
+      <c r="BR8" s="24">
         <v>65</v>
       </c>
-      <c r="BS8" s="43">
+      <c r="BS8" s="24">
         <v>66</v>
       </c>
-      <c r="BT8" s="43">
+      <c r="BT8" s="24">
         <v>67</v>
       </c>
-      <c r="BU8" s="43">
+      <c r="BU8" s="24">
         <v>68</v>
       </c>
-      <c r="BV8" s="43">
+      <c r="BV8" s="24">
         <v>69</v>
       </c>
-      <c r="BW8" s="43">
+      <c r="BW8" s="24">
         <v>70</v>
       </c>
-      <c r="BX8" s="43">
+      <c r="BX8" s="24">
         <v>71</v>
       </c>
-      <c r="BY8" s="43">
+      <c r="BY8" s="24">
         <v>72</v>
       </c>
-      <c r="BZ8" s="43">
+      <c r="BZ8" s="24">
         <v>73</v>
       </c>
-      <c r="CA8" s="43">
+      <c r="CA8" s="24">
         <v>74</v>
       </c>
-      <c r="CB8" s="43">
+      <c r="CB8" s="24">
         <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="51" t="s">
+      <c r="A9" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="52" t="s">
+      <c r="B9" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="53" t="s">
+      <c r="C9" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="52"/>
+      <c r="D9" s="30"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="44"/>
-      <c r="J9" s="44"/>
-      <c r="K9" s="44"/>
-      <c r="L9" s="44"/>
-      <c r="M9" s="44"/>
-      <c r="N9" s="44"/>
-      <c r="O9" s="44"/>
-      <c r="P9" s="44"/>
-      <c r="Q9" s="44"/>
-      <c r="R9" s="44"/>
-      <c r="S9" s="44"/>
-      <c r="T9" s="44"/>
-      <c r="U9" s="44"/>
-      <c r="V9" s="44"/>
-      <c r="W9" s="44"/>
-      <c r="X9" s="44"/>
-      <c r="Y9" s="44"/>
-      <c r="Z9" s="44"/>
-      <c r="AA9" s="44"/>
-      <c r="AB9" s="44"/>
-      <c r="AC9" s="44"/>
-      <c r="AD9" s="44"/>
-      <c r="AE9" s="44"/>
-      <c r="AF9" s="44"/>
-      <c r="AG9" s="44"/>
-      <c r="AH9" s="44"/>
-      <c r="AI9" s="44"/>
-      <c r="AJ9" s="44"/>
-      <c r="AK9" s="44"/>
-      <c r="AL9" s="44"/>
-      <c r="AM9" s="44"/>
-      <c r="AN9" s="44"/>
-      <c r="AO9" s="44"/>
-      <c r="AP9" s="44"/>
-      <c r="AQ9" s="44"/>
-      <c r="AR9" s="44"/>
-      <c r="AS9" s="44"/>
-      <c r="AT9" s="44"/>
-      <c r="AU9" s="44"/>
-      <c r="AV9" s="44"/>
-      <c r="AW9" s="44"/>
-      <c r="AX9" s="44"/>
-      <c r="AY9" s="44"/>
-      <c r="AZ9" s="44"/>
-      <c r="BA9" s="44"/>
-      <c r="BB9" s="44"/>
-      <c r="BC9" s="44"/>
-      <c r="BD9" s="44"/>
-      <c r="BE9" s="44"/>
-      <c r="BF9" s="44"/>
-      <c r="BG9" s="44"/>
-      <c r="BH9" s="44"/>
-      <c r="BI9" s="44"/>
-      <c r="BJ9" s="44"/>
-      <c r="BK9" s="44"/>
-      <c r="BL9" s="44"/>
-      <c r="BM9" s="44"/>
-      <c r="BN9" s="44"/>
-      <c r="BO9" s="44"/>
-      <c r="BP9" s="44"/>
-      <c r="BQ9" s="44"/>
-      <c r="BR9" s="44"/>
-      <c r="BS9" s="44"/>
-      <c r="BT9" s="44"/>
-      <c r="BU9" s="44"/>
-      <c r="BV9" s="44"/>
-      <c r="BW9" s="44"/>
-      <c r="BX9" s="44"/>
-      <c r="BY9" s="44"/>
-      <c r="BZ9" s="44"/>
-      <c r="CA9" s="44"/>
-      <c r="CB9" s="44"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="25"/>
+      <c r="I9" s="25"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="25"/>
+      <c r="M9" s="25"/>
+      <c r="N9" s="25"/>
+      <c r="O9" s="25"/>
+      <c r="P9" s="25"/>
+      <c r="Q9" s="25"/>
+      <c r="R9" s="25"/>
+      <c r="S9" s="25"/>
+      <c r="T9" s="25"/>
+      <c r="U9" s="25"/>
+      <c r="V9" s="25"/>
+      <c r="W9" s="25"/>
+      <c r="X9" s="25"/>
+      <c r="Y9" s="25"/>
+      <c r="Z9" s="25"/>
+      <c r="AA9" s="25"/>
+      <c r="AB9" s="25"/>
+      <c r="AC9" s="25"/>
+      <c r="AD9" s="25"/>
+      <c r="AE9" s="25"/>
+      <c r="AF9" s="25"/>
+      <c r="AG9" s="25"/>
+      <c r="AH9" s="25"/>
+      <c r="AI9" s="25"/>
+      <c r="AJ9" s="25"/>
+      <c r="AK9" s="25"/>
+      <c r="AL9" s="25"/>
+      <c r="AM9" s="25"/>
+      <c r="AN9" s="25"/>
+      <c r="AO9" s="25"/>
+      <c r="AP9" s="25"/>
+      <c r="AQ9" s="25"/>
+      <c r="AR9" s="25"/>
+      <c r="AS9" s="25"/>
+      <c r="AT9" s="25"/>
+      <c r="AU9" s="25"/>
+      <c r="AV9" s="25"/>
+      <c r="AW9" s="25"/>
+      <c r="AX9" s="25"/>
+      <c r="AY9" s="25"/>
+      <c r="AZ9" s="25"/>
+      <c r="BA9" s="25"/>
+      <c r="BB9" s="25"/>
+      <c r="BC9" s="25"/>
+      <c r="BD9" s="25"/>
+      <c r="BE9" s="25"/>
+      <c r="BF9" s="25"/>
+      <c r="BG9" s="25"/>
+      <c r="BH9" s="25"/>
+      <c r="BI9" s="25"/>
+      <c r="BJ9" s="25"/>
+      <c r="BK9" s="25"/>
+      <c r="BL9" s="25"/>
+      <c r="BM9" s="25"/>
+      <c r="BN9" s="25"/>
+      <c r="BO9" s="25"/>
+      <c r="BP9" s="25"/>
+      <c r="BQ9" s="25"/>
+      <c r="BR9" s="25"/>
+      <c r="BS9" s="25"/>
+      <c r="BT9" s="25"/>
+      <c r="BU9" s="25"/>
+      <c r="BV9" s="25"/>
+      <c r="BW9" s="25"/>
+      <c r="BX9" s="25"/>
+      <c r="BY9" s="25"/>
+      <c r="BZ9" s="25"/>
+      <c r="CA9" s="25"/>
+      <c r="CB9" s="25"/>
     </row>
     <row r="10" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="51"/>
-      <c r="B10" s="52"/>
+      <c r="A10" s="29"/>
+      <c r="B10" s="30"/>
       <c r="C10" s="6"/>
       <c r="D10" s="4" t="s">
         <v>12</v>
@@ -2315,7 +2343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
         <v>1</v>
       </c>
@@ -2408,7 +2436,7 @@
       <c r="CA11" s="8"/>
       <c r="CB11" s="8"/>
     </row>
-    <row r="12" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
         <v>2</v>
       </c>
@@ -2499,7 +2527,7 @@
       <c r="CA12" s="8"/>
       <c r="CB12" s="8"/>
     </row>
-    <row r="13" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
         <v>3</v>
       </c>
@@ -2511,7 +2539,7 @@
       </c>
       <c r="D13" s="11">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13" s="12"/>
       <c r="F13" s="8"/>
@@ -2562,7 +2590,9 @@
       <c r="AE13" s="8">
         <v>0</v>
       </c>
-      <c r="AF13" s="8"/>
+      <c r="AF13" s="8">
+        <v>0</v>
+      </c>
       <c r="AG13" s="8"/>
       <c r="AH13" s="8"/>
       <c r="AI13" s="8"/>
@@ -2616,7 +2646,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
         <v>4</v>
       </c>
@@ -2628,7 +2658,7 @@
       </c>
       <c r="D14" s="11">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E14" s="12"/>
       <c r="F14" s="8">
@@ -2691,11 +2721,21 @@
       <c r="AE14" s="8">
         <v>0</v>
       </c>
-      <c r="AF14" s="8"/>
-      <c r="AG14" s="8"/>
-      <c r="AH14" s="8"/>
-      <c r="AI14" s="8"/>
-      <c r="AJ14" s="8"/>
+      <c r="AF14" s="8">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="8">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="8">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="8">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="8">
+        <v>0</v>
+      </c>
       <c r="AK14" s="8"/>
       <c r="AL14" s="8"/>
       <c r="AM14" s="8"/>
@@ -2741,7 +2781,7 @@
       <c r="CA14" s="8"/>
       <c r="CB14" s="8"/>
     </row>
-    <row r="15" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
         <v>5</v>
       </c>
@@ -2874,7 +2914,7 @@
       <c r="CA15" s="8"/>
       <c r="CB15" s="8"/>
     </row>
-    <row r="16" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
         <v>6</v>
       </c>
@@ -2975,7 +3015,7 @@
       <c r="CA16" s="8"/>
       <c r="CB16" s="8"/>
     </row>
-    <row r="17" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
         <v>7</v>
       </c>
@@ -3023,74 +3063,74 @@
       <c r="P17" s="8">
         <v>0</v>
       </c>
-      <c r="Q17" s="45" t="s">
+      <c r="Q17" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="R17" s="46"/>
-      <c r="S17" s="46"/>
-      <c r="T17" s="46"/>
-      <c r="U17" s="46"/>
-      <c r="V17" s="46"/>
-      <c r="W17" s="46"/>
-      <c r="X17" s="46"/>
-      <c r="Y17" s="46"/>
-      <c r="Z17" s="46"/>
-      <c r="AA17" s="46"/>
-      <c r="AB17" s="46"/>
-      <c r="AC17" s="46"/>
-      <c r="AD17" s="46"/>
-      <c r="AE17" s="46"/>
-      <c r="AF17" s="46"/>
-      <c r="AG17" s="46"/>
-      <c r="AH17" s="46"/>
-      <c r="AI17" s="46"/>
-      <c r="AJ17" s="46"/>
-      <c r="AK17" s="46"/>
-      <c r="AL17" s="46"/>
-      <c r="AM17" s="46"/>
-      <c r="AN17" s="46"/>
-      <c r="AO17" s="46"/>
-      <c r="AP17" s="46"/>
-      <c r="AQ17" s="46"/>
-      <c r="AR17" s="46"/>
-      <c r="AS17" s="46"/>
-      <c r="AT17" s="46"/>
-      <c r="AU17" s="46"/>
-      <c r="AV17" s="46"/>
-      <c r="AW17" s="46"/>
-      <c r="AX17" s="46"/>
-      <c r="AY17" s="46"/>
-      <c r="AZ17" s="46"/>
-      <c r="BA17" s="46"/>
-      <c r="BB17" s="46"/>
-      <c r="BC17" s="46"/>
-      <c r="BD17" s="46"/>
-      <c r="BE17" s="46"/>
-      <c r="BF17" s="46"/>
-      <c r="BG17" s="46"/>
-      <c r="BH17" s="46"/>
-      <c r="BI17" s="46"/>
-      <c r="BJ17" s="46"/>
-      <c r="BK17" s="46"/>
-      <c r="BL17" s="46"/>
-      <c r="BM17" s="46"/>
-      <c r="BN17" s="46"/>
-      <c r="BO17" s="46"/>
-      <c r="BP17" s="46"/>
-      <c r="BQ17" s="46"/>
-      <c r="BR17" s="46"/>
-      <c r="BS17" s="46"/>
-      <c r="BT17" s="46"/>
-      <c r="BU17" s="46"/>
-      <c r="BV17" s="46"/>
-      <c r="BW17" s="46"/>
-      <c r="BX17" s="46"/>
-      <c r="BY17" s="46"/>
-      <c r="BZ17" s="46"/>
-      <c r="CA17" s="46"/>
-      <c r="CB17" s="47"/>
+      <c r="R17" s="22"/>
+      <c r="S17" s="22"/>
+      <c r="T17" s="22"/>
+      <c r="U17" s="22"/>
+      <c r="V17" s="22"/>
+      <c r="W17" s="22"/>
+      <c r="X17" s="22"/>
+      <c r="Y17" s="22"/>
+      <c r="Z17" s="22"/>
+      <c r="AA17" s="22"/>
+      <c r="AB17" s="22"/>
+      <c r="AC17" s="22"/>
+      <c r="AD17" s="22"/>
+      <c r="AE17" s="22"/>
+      <c r="AF17" s="22"/>
+      <c r="AG17" s="22"/>
+      <c r="AH17" s="22"/>
+      <c r="AI17" s="22"/>
+      <c r="AJ17" s="22"/>
+      <c r="AK17" s="22"/>
+      <c r="AL17" s="22"/>
+      <c r="AM17" s="22"/>
+      <c r="AN17" s="22"/>
+      <c r="AO17" s="22"/>
+      <c r="AP17" s="22"/>
+      <c r="AQ17" s="22"/>
+      <c r="AR17" s="22"/>
+      <c r="AS17" s="22"/>
+      <c r="AT17" s="22"/>
+      <c r="AU17" s="22"/>
+      <c r="AV17" s="22"/>
+      <c r="AW17" s="22"/>
+      <c r="AX17" s="22"/>
+      <c r="AY17" s="22"/>
+      <c r="AZ17" s="22"/>
+      <c r="BA17" s="22"/>
+      <c r="BB17" s="22"/>
+      <c r="BC17" s="22"/>
+      <c r="BD17" s="22"/>
+      <c r="BE17" s="22"/>
+      <c r="BF17" s="22"/>
+      <c r="BG17" s="22"/>
+      <c r="BH17" s="22"/>
+      <c r="BI17" s="22"/>
+      <c r="BJ17" s="22"/>
+      <c r="BK17" s="22"/>
+      <c r="BL17" s="22"/>
+      <c r="BM17" s="22"/>
+      <c r="BN17" s="22"/>
+      <c r="BO17" s="22"/>
+      <c r="BP17" s="22"/>
+      <c r="BQ17" s="22"/>
+      <c r="BR17" s="22"/>
+      <c r="BS17" s="22"/>
+      <c r="BT17" s="22"/>
+      <c r="BU17" s="22"/>
+      <c r="BV17" s="22"/>
+      <c r="BW17" s="22"/>
+      <c r="BX17" s="22"/>
+      <c r="BY17" s="22"/>
+      <c r="BZ17" s="22"/>
+      <c r="CA17" s="22"/>
+      <c r="CB17" s="23"/>
     </row>
-    <row r="18" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
         <v>8</v>
       </c>
@@ -3197,7 +3237,7 @@
       <c r="CA18" s="8"/>
       <c r="CB18" s="8"/>
     </row>
-    <row r="19" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
         <v>9</v>
       </c>
@@ -3209,7 +3249,7 @@
       </c>
       <c r="D19" s="11">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E19" s="12"/>
       <c r="F19" s="8">
@@ -3262,7 +3302,9 @@
       <c r="AE19" s="8">
         <v>0</v>
       </c>
-      <c r="AF19" s="8"/>
+      <c r="AF19" s="8">
+        <v>0</v>
+      </c>
       <c r="AG19" s="8"/>
       <c r="AH19" s="8"/>
       <c r="AI19" s="8"/>
@@ -3312,7 +3354,7 @@
       <c r="CA19" s="8"/>
       <c r="CB19" s="8"/>
     </row>
-    <row r="20" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
         <v>10</v>
       </c>
@@ -3324,7 +3366,7 @@
       </c>
       <c r="D20" s="11">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E20" s="12"/>
       <c r="F20" s="8"/>
@@ -3373,7 +3415,9 @@
       <c r="AE20" s="8">
         <v>0</v>
       </c>
-      <c r="AF20" s="8"/>
+      <c r="AF20" s="8">
+        <v>0</v>
+      </c>
       <c r="AG20" s="8"/>
       <c r="AH20" s="8"/>
       <c r="AI20" s="8"/>
@@ -3423,7 +3467,7 @@
       <c r="CA20" s="8"/>
       <c r="CB20" s="8"/>
     </row>
-    <row r="21" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
         <v>11</v>
       </c>
@@ -3516,57 +3560,59 @@
       <c r="AE21" s="8">
         <v>0</v>
       </c>
-      <c r="AF21" s="8"/>
-      <c r="AG21" s="8"/>
-      <c r="AH21" s="8"/>
-      <c r="AI21" s="8"/>
-      <c r="AJ21" s="8"/>
-      <c r="AK21" s="8"/>
-      <c r="AL21" s="8"/>
-      <c r="AM21" s="8"/>
-      <c r="AN21" s="8"/>
-      <c r="AO21" s="8"/>
-      <c r="AP21" s="8"/>
-      <c r="AQ21" s="8"/>
-      <c r="AR21" s="8"/>
-      <c r="AS21" s="8"/>
-      <c r="AT21" s="8"/>
-      <c r="AU21" s="8"/>
-      <c r="AV21" s="8"/>
-      <c r="AW21" s="8"/>
-      <c r="AX21" s="8"/>
-      <c r="AY21" s="8"/>
-      <c r="AZ21" s="8"/>
-      <c r="BA21" s="8"/>
-      <c r="BB21" s="8"/>
-      <c r="BC21" s="8"/>
-      <c r="BD21" s="8"/>
-      <c r="BE21" s="8"/>
-      <c r="BF21" s="8"/>
-      <c r="BG21" s="8"/>
-      <c r="BH21" s="8"/>
-      <c r="BI21" s="8"/>
-      <c r="BJ21" s="8"/>
-      <c r="BK21" s="8"/>
-      <c r="BL21" s="8"/>
-      <c r="BM21" s="8"/>
-      <c r="BN21" s="8"/>
-      <c r="BO21" s="8"/>
-      <c r="BP21" s="8"/>
-      <c r="BQ21" s="8"/>
-      <c r="BR21" s="8"/>
-      <c r="BS21" s="8"/>
-      <c r="BT21" s="8"/>
-      <c r="BU21" s="8"/>
-      <c r="BV21" s="8"/>
-      <c r="BW21" s="8"/>
-      <c r="BX21" s="8"/>
-      <c r="BY21" s="8"/>
-      <c r="BZ21" s="8"/>
-      <c r="CA21" s="8"/>
-      <c r="CB21" s="8"/>
+      <c r="AF21" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="AG21" s="22"/>
+      <c r="AH21" s="22"/>
+      <c r="AI21" s="22"/>
+      <c r="AJ21" s="22"/>
+      <c r="AK21" s="22"/>
+      <c r="AL21" s="22"/>
+      <c r="AM21" s="22"/>
+      <c r="AN21" s="22"/>
+      <c r="AO21" s="22"/>
+      <c r="AP21" s="22"/>
+      <c r="AQ21" s="22"/>
+      <c r="AR21" s="22"/>
+      <c r="AS21" s="22"/>
+      <c r="AT21" s="22"/>
+      <c r="AU21" s="22"/>
+      <c r="AV21" s="22"/>
+      <c r="AW21" s="22"/>
+      <c r="AX21" s="22"/>
+      <c r="AY21" s="22"/>
+      <c r="AZ21" s="22"/>
+      <c r="BA21" s="22"/>
+      <c r="BB21" s="22"/>
+      <c r="BC21" s="22"/>
+      <c r="BD21" s="22"/>
+      <c r="BE21" s="22"/>
+      <c r="BF21" s="22"/>
+      <c r="BG21" s="22"/>
+      <c r="BH21" s="22"/>
+      <c r="BI21" s="22"/>
+      <c r="BJ21" s="22"/>
+      <c r="BK21" s="22"/>
+      <c r="BL21" s="22"/>
+      <c r="BM21" s="22"/>
+      <c r="BN21" s="22"/>
+      <c r="BO21" s="22"/>
+      <c r="BP21" s="22"/>
+      <c r="BQ21" s="22"/>
+      <c r="BR21" s="22"/>
+      <c r="BS21" s="22"/>
+      <c r="BT21" s="22"/>
+      <c r="BU21" s="22"/>
+      <c r="BV21" s="22"/>
+      <c r="BW21" s="22"/>
+      <c r="BX21" s="22"/>
+      <c r="BY21" s="22"/>
+      <c r="BZ21" s="22"/>
+      <c r="CA21" s="22"/>
+      <c r="CB21" s="23"/>
     </row>
-    <row r="22" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9">
         <v>12</v>
       </c>
@@ -3669,7 +3715,7 @@
       <c r="CA22" s="8"/>
       <c r="CB22" s="8"/>
     </row>
-    <row r="23" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="9">
         <v>13</v>
       </c>
@@ -3762,57 +3808,59 @@
       <c r="AE23" s="8">
         <v>0</v>
       </c>
-      <c r="AF23" s="8"/>
-      <c r="AG23" s="8"/>
-      <c r="AH23" s="8"/>
-      <c r="AI23" s="8"/>
-      <c r="AJ23" s="8"/>
-      <c r="AK23" s="8"/>
-      <c r="AL23" s="8"/>
-      <c r="AM23" s="8"/>
-      <c r="AN23" s="8"/>
-      <c r="AO23" s="8"/>
-      <c r="AP23" s="8"/>
-      <c r="AQ23" s="8"/>
-      <c r="AR23" s="8"/>
-      <c r="AS23" s="8"/>
-      <c r="AT23" s="8"/>
-      <c r="AU23" s="8"/>
-      <c r="AV23" s="8"/>
-      <c r="AW23" s="8"/>
-      <c r="AX23" s="8"/>
-      <c r="AY23" s="8"/>
-      <c r="AZ23" s="8"/>
-      <c r="BA23" s="8"/>
-      <c r="BB23" s="8"/>
-      <c r="BC23" s="8"/>
-      <c r="BD23" s="8"/>
-      <c r="BE23" s="8"/>
-      <c r="BF23" s="8"/>
-      <c r="BG23" s="8"/>
-      <c r="BH23" s="8"/>
-      <c r="BI23" s="8"/>
-      <c r="BJ23" s="8"/>
-      <c r="BK23" s="8"/>
-      <c r="BL23" s="8"/>
-      <c r="BM23" s="8"/>
-      <c r="BN23" s="8"/>
-      <c r="BO23" s="8"/>
-      <c r="BP23" s="8"/>
-      <c r="BQ23" s="8"/>
-      <c r="BR23" s="8"/>
-      <c r="BS23" s="8"/>
-      <c r="BT23" s="8"/>
-      <c r="BU23" s="8"/>
-      <c r="BV23" s="8"/>
-      <c r="BW23" s="8"/>
-      <c r="BX23" s="8"/>
-      <c r="BY23" s="8"/>
-      <c r="BZ23" s="8"/>
-      <c r="CA23" s="8"/>
-      <c r="CB23" s="8"/>
+      <c r="AF23" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="AG23" s="22"/>
+      <c r="AH23" s="22"/>
+      <c r="AI23" s="22"/>
+      <c r="AJ23" s="22"/>
+      <c r="AK23" s="22"/>
+      <c r="AL23" s="22"/>
+      <c r="AM23" s="22"/>
+      <c r="AN23" s="22"/>
+      <c r="AO23" s="22"/>
+      <c r="AP23" s="22"/>
+      <c r="AQ23" s="22"/>
+      <c r="AR23" s="22"/>
+      <c r="AS23" s="22"/>
+      <c r="AT23" s="22"/>
+      <c r="AU23" s="22"/>
+      <c r="AV23" s="22"/>
+      <c r="AW23" s="22"/>
+      <c r="AX23" s="22"/>
+      <c r="AY23" s="22"/>
+      <c r="AZ23" s="22"/>
+      <c r="BA23" s="22"/>
+      <c r="BB23" s="22"/>
+      <c r="BC23" s="22"/>
+      <c r="BD23" s="22"/>
+      <c r="BE23" s="22"/>
+      <c r="BF23" s="22"/>
+      <c r="BG23" s="22"/>
+      <c r="BH23" s="22"/>
+      <c r="BI23" s="22"/>
+      <c r="BJ23" s="22"/>
+      <c r="BK23" s="22"/>
+      <c r="BL23" s="22"/>
+      <c r="BM23" s="22"/>
+      <c r="BN23" s="22"/>
+      <c r="BO23" s="22"/>
+      <c r="BP23" s="22"/>
+      <c r="BQ23" s="22"/>
+      <c r="BR23" s="22"/>
+      <c r="BS23" s="22"/>
+      <c r="BT23" s="22"/>
+      <c r="BU23" s="22"/>
+      <c r="BV23" s="22"/>
+      <c r="BW23" s="22"/>
+      <c r="BX23" s="22"/>
+      <c r="BY23" s="22"/>
+      <c r="BZ23" s="22"/>
+      <c r="CA23" s="22"/>
+      <c r="CB23" s="23"/>
     </row>
-    <row r="24" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="9">
         <v>14</v>
       </c>
@@ -3931,7 +3979,7 @@
       <c r="CA24" s="8"/>
       <c r="CB24" s="8"/>
     </row>
-    <row r="25" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="9">
         <v>15</v>
       </c>
@@ -3943,7 +3991,7 @@
       </c>
       <c r="D25" s="11">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E25" s="12"/>
       <c r="F25" s="8">
@@ -4002,11 +4050,21 @@
       <c r="AE25" s="8">
         <v>0</v>
       </c>
-      <c r="AF25" s="8"/>
-      <c r="AG25" s="8"/>
-      <c r="AH25" s="8"/>
-      <c r="AI25" s="8"/>
-      <c r="AJ25" s="8"/>
+      <c r="AF25" s="8">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="8">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="8">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="8">
+        <v>0</v>
+      </c>
+      <c r="AJ25" s="8">
+        <v>0</v>
+      </c>
       <c r="AK25" s="8"/>
       <c r="AL25" s="8"/>
       <c r="AM25" s="8"/>
@@ -4052,7 +4110,7 @@
       <c r="CA25" s="8"/>
       <c r="CB25" s="8"/>
     </row>
-    <row r="26" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="9">
         <v>16</v>
       </c>
@@ -4064,7 +4122,7 @@
       </c>
       <c r="D26" s="11">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E26" s="12"/>
       <c r="F26" s="8">
@@ -4135,7 +4193,9 @@
       <c r="AE26" s="8">
         <v>0</v>
       </c>
-      <c r="AF26" s="8"/>
+      <c r="AF26" s="8">
+        <v>0</v>
+      </c>
       <c r="AG26" s="8"/>
       <c r="AH26" s="8"/>
       <c r="AI26" s="8"/>
@@ -4185,7 +4245,7 @@
       <c r="CA26" s="8"/>
       <c r="CB26" s="8"/>
     </row>
-    <row r="27" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="9">
         <v>17</v>
       </c>
@@ -4197,7 +4257,7 @@
       </c>
       <c r="D27" s="11">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E27" s="15"/>
       <c r="F27" s="8">
@@ -4278,11 +4338,21 @@
       <c r="AE27" s="8">
         <v>0</v>
       </c>
-      <c r="AF27" s="8"/>
-      <c r="AG27" s="8"/>
-      <c r="AH27" s="8"/>
-      <c r="AI27" s="8"/>
-      <c r="AJ27" s="8"/>
+      <c r="AF27" s="8">
+        <v>0</v>
+      </c>
+      <c r="AG27" s="8">
+        <v>0</v>
+      </c>
+      <c r="AH27" s="8">
+        <v>0</v>
+      </c>
+      <c r="AI27" s="8">
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="8">
+        <v>0</v>
+      </c>
       <c r="AK27" s="8"/>
       <c r="AL27" s="8"/>
       <c r="AM27" s="8"/>
@@ -4328,7 +4398,7 @@
       <c r="CA27" s="8"/>
       <c r="CB27" s="8"/>
     </row>
-    <row r="28" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="9">
         <v>18</v>
       </c>
@@ -4342,170 +4412,157 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E28" s="48" t="s">
+      <c r="E28" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="F28" s="48"/>
-      <c r="G28" s="48"/>
-      <c r="H28" s="48"/>
-      <c r="I28" s="48"/>
-      <c r="J28" s="48"/>
-      <c r="K28" s="48"/>
-      <c r="L28" s="48"/>
-      <c r="M28" s="48"/>
-      <c r="N28" s="48"/>
-      <c r="O28" s="48"/>
-      <c r="P28" s="48"/>
-      <c r="Q28" s="48"/>
-      <c r="R28" s="48"/>
-      <c r="S28" s="48"/>
-      <c r="T28" s="48"/>
-      <c r="U28" s="48"/>
-      <c r="V28" s="48"/>
-      <c r="W28" s="48"/>
-      <c r="X28" s="48"/>
-      <c r="Y28" s="48"/>
-      <c r="Z28" s="48"/>
-      <c r="AA28" s="48"/>
-      <c r="AB28" s="48"/>
-      <c r="AC28" s="48"/>
-      <c r="AD28" s="48"/>
-      <c r="AE28" s="48"/>
-      <c r="AF28" s="48"/>
-      <c r="AG28" s="48"/>
-      <c r="AH28" s="48"/>
-      <c r="AI28" s="48"/>
-      <c r="AJ28" s="48"/>
-      <c r="AK28" s="48"/>
-      <c r="AL28" s="48"/>
-      <c r="AM28" s="48"/>
-      <c r="AN28" s="48"/>
-      <c r="AO28" s="48"/>
-      <c r="AP28" s="48"/>
-      <c r="AQ28" s="48"/>
-      <c r="AR28" s="48"/>
-      <c r="AS28" s="48"/>
-      <c r="AT28" s="48"/>
-      <c r="AU28" s="48"/>
-      <c r="AV28" s="48"/>
-      <c r="AW28" s="48"/>
-      <c r="AX28" s="48"/>
-      <c r="AY28" s="48"/>
-      <c r="AZ28" s="48"/>
-      <c r="BA28" s="48"/>
-      <c r="BB28" s="48"/>
-      <c r="BC28" s="48"/>
-      <c r="BD28" s="48"/>
-      <c r="BE28" s="48"/>
-      <c r="BF28" s="48"/>
-      <c r="BG28" s="48"/>
-      <c r="BH28" s="48"/>
-      <c r="BI28" s="48"/>
-      <c r="BJ28" s="48"/>
-      <c r="BK28" s="48"/>
-      <c r="BL28" s="48"/>
-      <c r="BM28" s="48"/>
-      <c r="BN28" s="48"/>
-      <c r="BO28" s="48"/>
-      <c r="BP28" s="48"/>
-      <c r="BQ28" s="48"/>
-      <c r="BR28" s="48"/>
-      <c r="BS28" s="48"/>
-      <c r="BT28" s="48"/>
-      <c r="BU28" s="48"/>
-      <c r="BV28" s="48"/>
-      <c r="BW28" s="48"/>
-      <c r="BX28" s="48"/>
-      <c r="BY28" s="48"/>
-      <c r="BZ28" s="48"/>
-      <c r="CA28" s="48"/>
-      <c r="CB28" s="48"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="26"/>
+      <c r="I28" s="26"/>
+      <c r="J28" s="26"/>
+      <c r="K28" s="26"/>
+      <c r="L28" s="26"/>
+      <c r="M28" s="26"/>
+      <c r="N28" s="26"/>
+      <c r="O28" s="26"/>
+      <c r="P28" s="26"/>
+      <c r="Q28" s="26"/>
+      <c r="R28" s="26"/>
+      <c r="S28" s="26"/>
+      <c r="T28" s="26"/>
+      <c r="U28" s="26"/>
+      <c r="V28" s="26"/>
+      <c r="W28" s="26"/>
+      <c r="X28" s="26"/>
+      <c r="Y28" s="26"/>
+      <c r="Z28" s="26"/>
+      <c r="AA28" s="26"/>
+      <c r="AB28" s="26"/>
+      <c r="AC28" s="26"/>
+      <c r="AD28" s="26"/>
+      <c r="AE28" s="26"/>
+      <c r="AF28" s="26"/>
+      <c r="AG28" s="26"/>
+      <c r="AH28" s="26"/>
+      <c r="AI28" s="26"/>
+      <c r="AJ28" s="26"/>
+      <c r="AK28" s="26"/>
+      <c r="AL28" s="26"/>
+      <c r="AM28" s="26"/>
+      <c r="AN28" s="26"/>
+      <c r="AO28" s="26"/>
+      <c r="AP28" s="26"/>
+      <c r="AQ28" s="26"/>
+      <c r="AR28" s="26"/>
+      <c r="AS28" s="26"/>
+      <c r="AT28" s="26"/>
+      <c r="AU28" s="26"/>
+      <c r="AV28" s="26"/>
+      <c r="AW28" s="26"/>
+      <c r="AX28" s="26"/>
+      <c r="AY28" s="26"/>
+      <c r="AZ28" s="26"/>
+      <c r="BA28" s="26"/>
+      <c r="BB28" s="26"/>
+      <c r="BC28" s="26"/>
+      <c r="BD28" s="26"/>
+      <c r="BE28" s="26"/>
+      <c r="BF28" s="26"/>
+      <c r="BG28" s="26"/>
+      <c r="BH28" s="26"/>
+      <c r="BI28" s="26"/>
+      <c r="BJ28" s="26"/>
+      <c r="BK28" s="26"/>
+      <c r="BL28" s="26"/>
+      <c r="BM28" s="26"/>
+      <c r="BN28" s="26"/>
+      <c r="BO28" s="26"/>
+      <c r="BP28" s="26"/>
+      <c r="BQ28" s="26"/>
+      <c r="BR28" s="26"/>
+      <c r="BS28" s="26"/>
+      <c r="BT28" s="26"/>
+      <c r="BU28" s="26"/>
+      <c r="BV28" s="26"/>
+      <c r="BW28" s="26"/>
+      <c r="BX28" s="26"/>
+      <c r="BY28" s="26"/>
+      <c r="BZ28" s="26"/>
+      <c r="CA28" s="26"/>
+      <c r="CB28" s="26"/>
     </row>
   </sheetData>
-  <mergeCells count="175">
-    <mergeCell ref="Q17:CB17"/>
-    <mergeCell ref="BX8:BX9"/>
-    <mergeCell ref="BY8:BY9"/>
-    <mergeCell ref="BZ8:BZ9"/>
-    <mergeCell ref="CA8:CA9"/>
-    <mergeCell ref="CB8:CB9"/>
-    <mergeCell ref="E28:CB28"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="BO8:BO9"/>
-    <mergeCell ref="BP8:BP9"/>
-    <mergeCell ref="BQ8:BQ9"/>
-    <mergeCell ref="BR8:BR9"/>
-    <mergeCell ref="BS8:BS9"/>
-    <mergeCell ref="BT8:BT9"/>
-    <mergeCell ref="BU8:BU9"/>
-    <mergeCell ref="BV8:BV9"/>
-    <mergeCell ref="BW8:BW9"/>
-    <mergeCell ref="BF8:BF9"/>
-    <mergeCell ref="BG8:BG9"/>
-    <mergeCell ref="BH8:BH9"/>
-    <mergeCell ref="BI8:BI9"/>
-    <mergeCell ref="BJ8:BJ9"/>
-    <mergeCell ref="BK8:BK9"/>
-    <mergeCell ref="BL8:BL9"/>
-    <mergeCell ref="BM8:BM9"/>
-    <mergeCell ref="BN8:BN9"/>
-    <mergeCell ref="AW8:AW9"/>
-    <mergeCell ref="AX8:AX9"/>
-    <mergeCell ref="AY8:AY9"/>
-    <mergeCell ref="AZ8:AZ9"/>
-    <mergeCell ref="BA8:BA9"/>
-    <mergeCell ref="BB8:BB9"/>
-    <mergeCell ref="BC8:BC9"/>
-    <mergeCell ref="BD8:BD9"/>
-    <mergeCell ref="BE8:BE9"/>
-    <mergeCell ref="AN8:AN9"/>
-    <mergeCell ref="AO8:AO9"/>
-    <mergeCell ref="AP8:AP9"/>
-    <mergeCell ref="AQ8:AQ9"/>
-    <mergeCell ref="AR8:AR9"/>
-    <mergeCell ref="AS8:AS9"/>
-    <mergeCell ref="AT8:AT9"/>
-    <mergeCell ref="AU8:AU9"/>
-    <mergeCell ref="AV8:AV9"/>
-    <mergeCell ref="AE8:AE9"/>
-    <mergeCell ref="AF8:AF9"/>
-    <mergeCell ref="AG8:AG9"/>
-    <mergeCell ref="AH8:AH9"/>
-    <mergeCell ref="AI8:AI9"/>
-    <mergeCell ref="AJ8:AJ9"/>
-    <mergeCell ref="AK8:AK9"/>
-    <mergeCell ref="AL8:AL9"/>
-    <mergeCell ref="AM8:AM9"/>
-    <mergeCell ref="V8:V9"/>
-    <mergeCell ref="W8:W9"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AD8:AD9"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
+  <mergeCells count="178">
+    <mergeCell ref="AF1:AJ1"/>
+    <mergeCell ref="AF21:CB21"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="W2:W7"/>
+    <mergeCell ref="X2:X7"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:D2"/>
+    <mergeCell ref="Y2:Y7"/>
+    <mergeCell ref="Z2:Z7"/>
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="F2:F7"/>
+    <mergeCell ref="G2:G7"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="I2:I7"/>
+    <mergeCell ref="J2:J7"/>
+    <mergeCell ref="K2:K7"/>
+    <mergeCell ref="L2:L7"/>
+    <mergeCell ref="M2:M7"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="V1:Z1"/>
+    <mergeCell ref="L1:P1"/>
+    <mergeCell ref="AA2:AA7"/>
+    <mergeCell ref="N2:N7"/>
+    <mergeCell ref="O2:O7"/>
+    <mergeCell ref="P2:P7"/>
+    <mergeCell ref="Q2:Q7"/>
+    <mergeCell ref="R2:R7"/>
+    <mergeCell ref="S2:S7"/>
+    <mergeCell ref="T2:T7"/>
+    <mergeCell ref="U2:U7"/>
+    <mergeCell ref="V2:V7"/>
+    <mergeCell ref="Q1:U1"/>
+    <mergeCell ref="AA1:AE1"/>
+    <mergeCell ref="AG2:AG7"/>
+    <mergeCell ref="AD2:AD7"/>
+    <mergeCell ref="AE2:AE7"/>
+    <mergeCell ref="AF2:AF7"/>
+    <mergeCell ref="AB2:AB7"/>
+    <mergeCell ref="AC2:AC7"/>
+    <mergeCell ref="AH2:AH7"/>
+    <mergeCell ref="AI2:AI7"/>
+    <mergeCell ref="AJ2:AJ7"/>
+    <mergeCell ref="AK2:AK7"/>
+    <mergeCell ref="AL2:AL7"/>
+    <mergeCell ref="AM2:AM7"/>
+    <mergeCell ref="AN2:AN7"/>
+    <mergeCell ref="AO2:AO7"/>
+    <mergeCell ref="AP2:AP7"/>
+    <mergeCell ref="AQ2:AQ7"/>
+    <mergeCell ref="AR2:AR7"/>
+    <mergeCell ref="AS2:AS7"/>
+    <mergeCell ref="BH2:BH7"/>
+    <mergeCell ref="BI2:BI7"/>
+    <mergeCell ref="BJ2:BJ7"/>
+    <mergeCell ref="BK2:BK7"/>
+    <mergeCell ref="AT2:AT7"/>
+    <mergeCell ref="AU2:AU7"/>
+    <mergeCell ref="AV2:AV7"/>
+    <mergeCell ref="AW2:AW7"/>
+    <mergeCell ref="AX2:AX7"/>
+    <mergeCell ref="AY2:AY7"/>
+    <mergeCell ref="AZ2:AZ7"/>
+    <mergeCell ref="BA2:BA7"/>
+    <mergeCell ref="BB2:BB7"/>
     <mergeCell ref="BU2:BU7"/>
     <mergeCell ref="BV2:BV7"/>
     <mergeCell ref="BW2:BW7"/>
@@ -4530,74 +4587,90 @@
     <mergeCell ref="BE2:BE7"/>
     <mergeCell ref="BF2:BF7"/>
     <mergeCell ref="BG2:BG7"/>
-    <mergeCell ref="BH2:BH7"/>
-    <mergeCell ref="BI2:BI7"/>
-    <mergeCell ref="BJ2:BJ7"/>
-    <mergeCell ref="BK2:BK7"/>
-    <mergeCell ref="AT2:AT7"/>
-    <mergeCell ref="AU2:AU7"/>
-    <mergeCell ref="AV2:AV7"/>
-    <mergeCell ref="AW2:AW7"/>
-    <mergeCell ref="AX2:AX7"/>
-    <mergeCell ref="AY2:AY7"/>
-    <mergeCell ref="AZ2:AZ7"/>
-    <mergeCell ref="BA2:BA7"/>
-    <mergeCell ref="BB2:BB7"/>
-    <mergeCell ref="AK2:AK7"/>
-    <mergeCell ref="AL2:AL7"/>
-    <mergeCell ref="AM2:AM7"/>
-    <mergeCell ref="AN2:AN7"/>
-    <mergeCell ref="AO2:AO7"/>
-    <mergeCell ref="AP2:AP7"/>
-    <mergeCell ref="AQ2:AQ7"/>
-    <mergeCell ref="AR2:AR7"/>
-    <mergeCell ref="AS2:AS7"/>
-    <mergeCell ref="AG2:AG7"/>
-    <mergeCell ref="AD2:AD7"/>
-    <mergeCell ref="AE2:AE7"/>
-    <mergeCell ref="AF2:AF7"/>
-    <mergeCell ref="AB2:AB7"/>
-    <mergeCell ref="AC2:AC7"/>
-    <mergeCell ref="AH2:AH7"/>
-    <mergeCell ref="AI2:AI7"/>
-    <mergeCell ref="AJ2:AJ7"/>
-    <mergeCell ref="L1:P1"/>
-    <mergeCell ref="AA2:AA7"/>
-    <mergeCell ref="N2:N7"/>
-    <mergeCell ref="O2:O7"/>
-    <mergeCell ref="P2:P7"/>
-    <mergeCell ref="Q2:Q7"/>
-    <mergeCell ref="R2:R7"/>
-    <mergeCell ref="S2:S7"/>
-    <mergeCell ref="T2:T7"/>
-    <mergeCell ref="U2:U7"/>
-    <mergeCell ref="V2:V7"/>
-    <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="AA1:AE1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="W2:W7"/>
-    <mergeCell ref="X2:X7"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:D2"/>
-    <mergeCell ref="Y2:Y7"/>
-    <mergeCell ref="Z2:Z7"/>
-    <mergeCell ref="E2:E7"/>
-    <mergeCell ref="F2:F7"/>
-    <mergeCell ref="G2:G7"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="I2:I7"/>
-    <mergeCell ref="J2:J7"/>
-    <mergeCell ref="K2:K7"/>
-    <mergeCell ref="L2:L7"/>
-    <mergeCell ref="M2:M7"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="V1:Z1"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="W8:W9"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AD8:AD9"/>
+    <mergeCell ref="AE8:AE9"/>
+    <mergeCell ref="AF8:AF9"/>
+    <mergeCell ref="AG8:AG9"/>
+    <mergeCell ref="AH8:AH9"/>
+    <mergeCell ref="AI8:AI9"/>
+    <mergeCell ref="AJ8:AJ9"/>
+    <mergeCell ref="AK8:AK9"/>
+    <mergeCell ref="AL8:AL9"/>
+    <mergeCell ref="AM8:AM9"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="BO8:BO9"/>
+    <mergeCell ref="BP8:BP9"/>
+    <mergeCell ref="BQ8:BQ9"/>
+    <mergeCell ref="BR8:BR9"/>
+    <mergeCell ref="BS8:BS9"/>
+    <mergeCell ref="BT8:BT9"/>
+    <mergeCell ref="BF8:BF9"/>
+    <mergeCell ref="BG8:BG9"/>
+    <mergeCell ref="BH8:BH9"/>
+    <mergeCell ref="BI8:BI9"/>
+    <mergeCell ref="BJ8:BJ9"/>
+    <mergeCell ref="BK8:BK9"/>
+    <mergeCell ref="BL8:BL9"/>
+    <mergeCell ref="BM8:BM9"/>
+    <mergeCell ref="BN8:BN9"/>
+    <mergeCell ref="AW8:AW9"/>
+    <mergeCell ref="AX8:AX9"/>
+    <mergeCell ref="AY8:AY9"/>
+    <mergeCell ref="AZ8:AZ9"/>
+    <mergeCell ref="BA8:BA9"/>
+    <mergeCell ref="BB8:BB9"/>
+    <mergeCell ref="AF23:CB23"/>
+    <mergeCell ref="Q17:CB17"/>
+    <mergeCell ref="BX8:BX9"/>
+    <mergeCell ref="BY8:BY9"/>
+    <mergeCell ref="BZ8:BZ9"/>
+    <mergeCell ref="CA8:CA9"/>
+    <mergeCell ref="CB8:CB9"/>
+    <mergeCell ref="E28:CB28"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="BU8:BU9"/>
+    <mergeCell ref="BV8:BV9"/>
+    <mergeCell ref="BW8:BW9"/>
+    <mergeCell ref="BC8:BC9"/>
+    <mergeCell ref="BD8:BD9"/>
+    <mergeCell ref="BE8:BE9"/>
+    <mergeCell ref="AN8:AN9"/>
+    <mergeCell ref="AO8:AO9"/>
+    <mergeCell ref="AP8:AP9"/>
+    <mergeCell ref="AQ8:AQ9"/>
+    <mergeCell ref="AR8:AR9"/>
+    <mergeCell ref="AS8:AS9"/>
+    <mergeCell ref="AT8:AT9"/>
+    <mergeCell ref="AU8:AU9"/>
+    <mergeCell ref="AV8:AV9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" verticalDpi="0"/>

--- a/ჟურნალი/5. N301 front-end დეველოპმენტი (ინტეგრირებული მიდგომით) - Git.xlsx
+++ b/ჟურნალი/5. N301 front-end დეველოპმენტი (ინტეგრირებული მიდგომით) - Git.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\designer\Desktop\Front\01. - Front-end-docs\ჟურნალი\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A24ADD-B2FE-4B84-B899-5A341C224CC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45870C8D-CA3E-4307-B6B2-F826904F6D0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -780,6 +780,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -789,59 +798,11 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
@@ -873,11 +834,50 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1106,65 +1106,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="42" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="43"/>
-      <c r="D1" s="44"/>
-      <c r="F1" s="27">
+      <c r="A1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="30"/>
+      <c r="D1" s="31"/>
+      <c r="F1" s="52">
         <v>4</v>
       </c>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="39">
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="21">
         <v>2</v>
       </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="39">
+      <c r="K1" s="23"/>
+      <c r="L1" s="21">
         <v>5</v>
       </c>
-      <c r="M1" s="40"/>
-      <c r="N1" s="40"/>
-      <c r="O1" s="40"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="39">
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="21">
         <v>5</v>
       </c>
-      <c r="R1" s="40"/>
-      <c r="S1" s="40"/>
-      <c r="T1" s="40"/>
-      <c r="U1" s="41"/>
-      <c r="V1" s="39">
+      <c r="R1" s="22"/>
+      <c r="S1" s="22"/>
+      <c r="T1" s="22"/>
+      <c r="U1" s="23"/>
+      <c r="V1" s="21">
         <v>5</v>
       </c>
-      <c r="W1" s="40"/>
-      <c r="X1" s="40"/>
-      <c r="Y1" s="40"/>
-      <c r="Z1" s="41"/>
-      <c r="AA1" s="39">
+      <c r="W1" s="22"/>
+      <c r="X1" s="22"/>
+      <c r="Y1" s="22"/>
+      <c r="Z1" s="23"/>
+      <c r="AA1" s="21">
         <v>5</v>
       </c>
-      <c r="AB1" s="40"/>
-      <c r="AC1" s="40"/>
-      <c r="AD1" s="40"/>
-      <c r="AE1" s="41"/>
-      <c r="AF1" s="39">
+      <c r="AB1" s="22"/>
+      <c r="AC1" s="22"/>
+      <c r="AD1" s="22"/>
+      <c r="AE1" s="23"/>
+      <c r="AF1" s="21">
         <v>5</v>
       </c>
-      <c r="AG1" s="40"/>
-      <c r="AH1" s="40"/>
-      <c r="AI1" s="40"/>
-      <c r="AJ1" s="41"/>
-      <c r="AK1" s="18"/>
-      <c r="AL1" s="18"/>
-      <c r="AM1" s="17"/>
-      <c r="AN1" s="17"/>
-      <c r="AO1" s="17"/>
-      <c r="AP1" s="17"/>
+      <c r="AG1" s="22"/>
+      <c r="AH1" s="22"/>
+      <c r="AI1" s="22"/>
+      <c r="AJ1" s="23"/>
+      <c r="AK1" s="21">
+        <v>6</v>
+      </c>
+      <c r="AL1" s="22"/>
+      <c r="AM1" s="22"/>
+      <c r="AN1" s="22"/>
+      <c r="AO1" s="22"/>
+      <c r="AP1" s="23"/>
       <c r="AQ1" s="17"/>
       <c r="AR1" s="17"/>
       <c r="AS1" s="18"/>
@@ -1205,911 +1207,923 @@
       <c r="CB1" s="17"/>
       <c r="CC1" s="1">
         <f>SUM(E1:CB1)</f>
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:85" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="42"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="47" t="s">
+      <c r="A2" s="29"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="35">
+      <c r="F2" s="27">
         <v>46202</v>
       </c>
-      <c r="G2" s="35">
+      <c r="G2" s="27">
         <v>46202</v>
       </c>
-      <c r="H2" s="35">
+      <c r="H2" s="27">
         <v>46202</v>
       </c>
-      <c r="I2" s="35">
+      <c r="I2" s="27">
         <v>46202</v>
       </c>
-      <c r="J2" s="35">
+      <c r="J2" s="27">
         <v>46206</v>
       </c>
-      <c r="K2" s="35">
+      <c r="K2" s="27">
         <v>46206</v>
       </c>
-      <c r="L2" s="35">
+      <c r="L2" s="27">
         <v>46209</v>
       </c>
-      <c r="M2" s="35">
+      <c r="M2" s="27">
         <v>46209</v>
       </c>
-      <c r="N2" s="35">
+      <c r="N2" s="27">
         <v>46209</v>
       </c>
-      <c r="O2" s="35">
+      <c r="O2" s="27">
         <v>46209</v>
       </c>
-      <c r="P2" s="35">
+      <c r="P2" s="27">
         <v>46209</v>
       </c>
-      <c r="Q2" s="35">
+      <c r="Q2" s="27">
         <v>46216</v>
       </c>
-      <c r="R2" s="35">
+      <c r="R2" s="27">
         <v>46216</v>
       </c>
-      <c r="S2" s="35">
+      <c r="S2" s="27">
         <v>46216</v>
       </c>
-      <c r="T2" s="35">
+      <c r="T2" s="27">
         <v>46216</v>
       </c>
-      <c r="U2" s="35">
+      <c r="U2" s="27">
         <v>46216</v>
       </c>
-      <c r="V2" s="35">
+      <c r="V2" s="27">
         <v>46223</v>
       </c>
-      <c r="W2" s="35">
+      <c r="W2" s="27">
         <v>46223</v>
       </c>
-      <c r="X2" s="35">
+      <c r="X2" s="27">
         <v>46223</v>
       </c>
-      <c r="Y2" s="35">
+      <c r="Y2" s="27">
         <v>46223</v>
       </c>
-      <c r="Z2" s="35">
+      <c r="Z2" s="27">
         <v>46223</v>
       </c>
-      <c r="AA2" s="35">
+      <c r="AA2" s="27">
         <v>46230</v>
       </c>
-      <c r="AB2" s="35">
+      <c r="AB2" s="27">
         <v>46230</v>
       </c>
-      <c r="AC2" s="35">
+      <c r="AC2" s="27">
         <v>46230</v>
       </c>
-      <c r="AD2" s="35">
+      <c r="AD2" s="27">
         <v>46230</v>
       </c>
-      <c r="AE2" s="35">
+      <c r="AE2" s="27">
         <v>46230</v>
       </c>
-      <c r="AF2" s="35">
+      <c r="AF2" s="27">
         <v>46279</v>
       </c>
-      <c r="AG2" s="35">
+      <c r="AG2" s="27">
         <v>46279</v>
       </c>
-      <c r="AH2" s="35">
+      <c r="AH2" s="27">
         <v>46279</v>
       </c>
-      <c r="AI2" s="35">
+      <c r="AI2" s="27">
         <v>46279</v>
       </c>
-      <c r="AJ2" s="35">
+      <c r="AJ2" s="27">
         <v>46279</v>
       </c>
-      <c r="AK2" s="35"/>
-      <c r="AL2" s="35"/>
-      <c r="AM2" s="35"/>
-      <c r="AN2" s="35"/>
-      <c r="AO2" s="35"/>
-      <c r="AP2" s="35"/>
-      <c r="AQ2" s="35"/>
-      <c r="AR2" s="35"/>
-      <c r="AS2" s="35"/>
-      <c r="AT2" s="35"/>
-      <c r="AU2" s="35"/>
-      <c r="AV2" s="35"/>
-      <c r="AW2" s="35"/>
-      <c r="AX2" s="35"/>
-      <c r="AY2" s="35"/>
-      <c r="AZ2" s="35"/>
-      <c r="BA2" s="35"/>
-      <c r="BB2" s="35"/>
-      <c r="BC2" s="35"/>
-      <c r="BD2" s="35"/>
-      <c r="BE2" s="35"/>
-      <c r="BF2" s="35"/>
-      <c r="BG2" s="35"/>
-      <c r="BH2" s="35"/>
-      <c r="BI2" s="35"/>
-      <c r="BJ2" s="35"/>
-      <c r="BK2" s="35"/>
-      <c r="BL2" s="35"/>
-      <c r="BM2" s="35"/>
-      <c r="BN2" s="35"/>
-      <c r="BO2" s="35"/>
-      <c r="BP2" s="35"/>
-      <c r="BQ2" s="35"/>
-      <c r="BR2" s="35"/>
-      <c r="BS2" s="35"/>
-      <c r="BT2" s="35"/>
-      <c r="BU2" s="35"/>
-      <c r="BV2" s="35"/>
-      <c r="BW2" s="35"/>
-      <c r="BX2" s="35"/>
-      <c r="BY2" s="35"/>
-      <c r="BZ2" s="35"/>
-      <c r="CA2" s="35"/>
-      <c r="CB2" s="35"/>
+      <c r="AK2" s="27">
+        <v>46286</v>
+      </c>
+      <c r="AL2" s="27">
+        <v>46286</v>
+      </c>
+      <c r="AM2" s="27">
+        <v>46286</v>
+      </c>
+      <c r="AN2" s="27">
+        <v>46286</v>
+      </c>
+      <c r="AO2" s="27">
+        <v>46286</v>
+      </c>
+      <c r="AP2" s="27">
+        <v>46286</v>
+      </c>
+      <c r="AQ2" s="27"/>
+      <c r="AR2" s="27"/>
+      <c r="AS2" s="27"/>
+      <c r="AT2" s="27"/>
+      <c r="AU2" s="27"/>
+      <c r="AV2" s="27"/>
+      <c r="AW2" s="27"/>
+      <c r="AX2" s="27"/>
+      <c r="AY2" s="27"/>
+      <c r="AZ2" s="27"/>
+      <c r="BA2" s="27"/>
+      <c r="BB2" s="27"/>
+      <c r="BC2" s="27"/>
+      <c r="BD2" s="27"/>
+      <c r="BE2" s="27"/>
+      <c r="BF2" s="27"/>
+      <c r="BG2" s="27"/>
+      <c r="BH2" s="27"/>
+      <c r="BI2" s="27"/>
+      <c r="BJ2" s="27"/>
+      <c r="BK2" s="27"/>
+      <c r="BL2" s="27"/>
+      <c r="BM2" s="27"/>
+      <c r="BN2" s="27"/>
+      <c r="BO2" s="27"/>
+      <c r="BP2" s="27"/>
+      <c r="BQ2" s="27"/>
+      <c r="BR2" s="27"/>
+      <c r="BS2" s="27"/>
+      <c r="BT2" s="27"/>
+      <c r="BU2" s="27"/>
+      <c r="BV2" s="27"/>
+      <c r="BW2" s="27"/>
+      <c r="BX2" s="27"/>
+      <c r="BY2" s="27"/>
+      <c r="BZ2" s="27"/>
+      <c r="CA2" s="27"/>
+      <c r="CB2" s="27"/>
     </row>
     <row r="3" spans="1:85" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="37" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="35"/>
-      <c r="I3" s="35"/>
-      <c r="J3" s="35"/>
-      <c r="K3" s="35"/>
-      <c r="L3" s="35"/>
-      <c r="M3" s="35"/>
-      <c r="N3" s="35"/>
-      <c r="O3" s="35"/>
-      <c r="P3" s="35"/>
-      <c r="Q3" s="35"/>
-      <c r="R3" s="35"/>
-      <c r="S3" s="35"/>
-      <c r="T3" s="35"/>
-      <c r="U3" s="35"/>
-      <c r="V3" s="35"/>
-      <c r="W3" s="35"/>
-      <c r="X3" s="35"/>
-      <c r="Y3" s="35"/>
-      <c r="Z3" s="35"/>
-      <c r="AA3" s="35"/>
-      <c r="AB3" s="35"/>
-      <c r="AC3" s="35"/>
-      <c r="AD3" s="35"/>
-      <c r="AE3" s="35"/>
-      <c r="AF3" s="35"/>
-      <c r="AG3" s="35"/>
-      <c r="AH3" s="35"/>
-      <c r="AI3" s="35"/>
-      <c r="AJ3" s="35"/>
-      <c r="AK3" s="35"/>
-      <c r="AL3" s="35"/>
-      <c r="AM3" s="35"/>
-      <c r="AN3" s="35"/>
-      <c r="AO3" s="35"/>
-      <c r="AP3" s="35"/>
-      <c r="AQ3" s="35"/>
-      <c r="AR3" s="35"/>
-      <c r="AS3" s="35"/>
-      <c r="AT3" s="35"/>
-      <c r="AU3" s="35"/>
-      <c r="AV3" s="35"/>
-      <c r="AW3" s="35"/>
-      <c r="AX3" s="35"/>
-      <c r="AY3" s="35"/>
-      <c r="AZ3" s="35"/>
-      <c r="BA3" s="35"/>
-      <c r="BB3" s="35"/>
-      <c r="BC3" s="35"/>
-      <c r="BD3" s="35"/>
-      <c r="BE3" s="35"/>
-      <c r="BF3" s="35"/>
-      <c r="BG3" s="35"/>
-      <c r="BH3" s="35"/>
-      <c r="BI3" s="35"/>
-      <c r="BJ3" s="35"/>
-      <c r="BK3" s="35"/>
-      <c r="BL3" s="35"/>
-      <c r="BM3" s="35"/>
-      <c r="BN3" s="35"/>
-      <c r="BO3" s="35"/>
-      <c r="BP3" s="35"/>
-      <c r="BQ3" s="35"/>
-      <c r="BR3" s="35"/>
-      <c r="BS3" s="35"/>
-      <c r="BT3" s="35"/>
-      <c r="BU3" s="35"/>
-      <c r="BV3" s="35"/>
-      <c r="BW3" s="35"/>
-      <c r="BX3" s="35"/>
-      <c r="BY3" s="35"/>
-      <c r="BZ3" s="35"/>
-      <c r="CA3" s="35"/>
-      <c r="CB3" s="35"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27"/>
+      <c r="K3" s="27"/>
+      <c r="L3" s="27"/>
+      <c r="M3" s="27"/>
+      <c r="N3" s="27"/>
+      <c r="O3" s="27"/>
+      <c r="P3" s="27"/>
+      <c r="Q3" s="27"/>
+      <c r="R3" s="27"/>
+      <c r="S3" s="27"/>
+      <c r="T3" s="27"/>
+      <c r="U3" s="27"/>
+      <c r="V3" s="27"/>
+      <c r="W3" s="27"/>
+      <c r="X3" s="27"/>
+      <c r="Y3" s="27"/>
+      <c r="Z3" s="27"/>
+      <c r="AA3" s="27"/>
+      <c r="AB3" s="27"/>
+      <c r="AC3" s="27"/>
+      <c r="AD3" s="27"/>
+      <c r="AE3" s="27"/>
+      <c r="AF3" s="27"/>
+      <c r="AG3" s="27"/>
+      <c r="AH3" s="27"/>
+      <c r="AI3" s="27"/>
+      <c r="AJ3" s="27"/>
+      <c r="AK3" s="27"/>
+      <c r="AL3" s="27"/>
+      <c r="AM3" s="27"/>
+      <c r="AN3" s="27"/>
+      <c r="AO3" s="27"/>
+      <c r="AP3" s="27"/>
+      <c r="AQ3" s="27"/>
+      <c r="AR3" s="27"/>
+      <c r="AS3" s="27"/>
+      <c r="AT3" s="27"/>
+      <c r="AU3" s="27"/>
+      <c r="AV3" s="27"/>
+      <c r="AW3" s="27"/>
+      <c r="AX3" s="27"/>
+      <c r="AY3" s="27"/>
+      <c r="AZ3" s="27"/>
+      <c r="BA3" s="27"/>
+      <c r="BB3" s="27"/>
+      <c r="BC3" s="27"/>
+      <c r="BD3" s="27"/>
+      <c r="BE3" s="27"/>
+      <c r="BF3" s="27"/>
+      <c r="BG3" s="27"/>
+      <c r="BH3" s="27"/>
+      <c r="BI3" s="27"/>
+      <c r="BJ3" s="27"/>
+      <c r="BK3" s="27"/>
+      <c r="BL3" s="27"/>
+      <c r="BM3" s="27"/>
+      <c r="BN3" s="27"/>
+      <c r="BO3" s="27"/>
+      <c r="BP3" s="27"/>
+      <c r="BQ3" s="27"/>
+      <c r="BR3" s="27"/>
+      <c r="BS3" s="27"/>
+      <c r="BT3" s="27"/>
+      <c r="BU3" s="27"/>
+      <c r="BV3" s="27"/>
+      <c r="BW3" s="27"/>
+      <c r="BX3" s="27"/>
+      <c r="BY3" s="27"/>
+      <c r="BZ3" s="27"/>
+      <c r="CA3" s="27"/>
+      <c r="CB3" s="27"/>
     </row>
     <row r="4" spans="1:85" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="50"/>
-      <c r="C4" s="51" t="s">
+      <c r="B4" s="37"/>
+      <c r="C4" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="34"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="35"/>
-      <c r="L4" s="35"/>
-      <c r="M4" s="35"/>
-      <c r="N4" s="35"/>
-      <c r="O4" s="35"/>
-      <c r="P4" s="35"/>
-      <c r="Q4" s="35"/>
-      <c r="R4" s="35"/>
-      <c r="S4" s="35"/>
-      <c r="T4" s="35"/>
-      <c r="U4" s="35"/>
-      <c r="V4" s="35"/>
-      <c r="W4" s="35"/>
-      <c r="X4" s="35"/>
-      <c r="Y4" s="35"/>
-      <c r="Z4" s="35"/>
-      <c r="AA4" s="35"/>
-      <c r="AB4" s="35"/>
-      <c r="AC4" s="35"/>
-      <c r="AD4" s="35"/>
-      <c r="AE4" s="35"/>
-      <c r="AF4" s="35"/>
-      <c r="AG4" s="35"/>
-      <c r="AH4" s="35"/>
-      <c r="AI4" s="35"/>
-      <c r="AJ4" s="35"/>
-      <c r="AK4" s="35"/>
-      <c r="AL4" s="35"/>
-      <c r="AM4" s="35"/>
-      <c r="AN4" s="35"/>
-      <c r="AO4" s="35"/>
-      <c r="AP4" s="35"/>
-      <c r="AQ4" s="35"/>
-      <c r="AR4" s="35"/>
-      <c r="AS4" s="35"/>
-      <c r="AT4" s="35"/>
-      <c r="AU4" s="35"/>
-      <c r="AV4" s="35"/>
-      <c r="AW4" s="35"/>
-      <c r="AX4" s="35"/>
-      <c r="AY4" s="35"/>
-      <c r="AZ4" s="35"/>
-      <c r="BA4" s="35"/>
-      <c r="BB4" s="35"/>
-      <c r="BC4" s="35"/>
-      <c r="BD4" s="35"/>
-      <c r="BE4" s="35"/>
-      <c r="BF4" s="35"/>
-      <c r="BG4" s="35"/>
-      <c r="BH4" s="35"/>
-      <c r="BI4" s="35"/>
-      <c r="BJ4" s="35"/>
-      <c r="BK4" s="35"/>
-      <c r="BL4" s="35"/>
-      <c r="BM4" s="35"/>
-      <c r="BN4" s="35"/>
-      <c r="BO4" s="35"/>
-      <c r="BP4" s="35"/>
-      <c r="BQ4" s="35"/>
-      <c r="BR4" s="35"/>
-      <c r="BS4" s="35"/>
-      <c r="BT4" s="35"/>
-      <c r="BU4" s="35"/>
-      <c r="BV4" s="35"/>
-      <c r="BW4" s="35"/>
-      <c r="BX4" s="35"/>
-      <c r="BY4" s="35"/>
-      <c r="BZ4" s="35"/>
-      <c r="CA4" s="35"/>
-      <c r="CB4" s="35"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="27"/>
+      <c r="S4" s="27"/>
+      <c r="T4" s="27"/>
+      <c r="U4" s="27"/>
+      <c r="V4" s="27"/>
+      <c r="W4" s="27"/>
+      <c r="X4" s="27"/>
+      <c r="Y4" s="27"/>
+      <c r="Z4" s="27"/>
+      <c r="AA4" s="27"/>
+      <c r="AB4" s="27"/>
+      <c r="AC4" s="27"/>
+      <c r="AD4" s="27"/>
+      <c r="AE4" s="27"/>
+      <c r="AF4" s="27"/>
+      <c r="AG4" s="27"/>
+      <c r="AH4" s="27"/>
+      <c r="AI4" s="27"/>
+      <c r="AJ4" s="27"/>
+      <c r="AK4" s="27"/>
+      <c r="AL4" s="27"/>
+      <c r="AM4" s="27"/>
+      <c r="AN4" s="27"/>
+      <c r="AO4" s="27"/>
+      <c r="AP4" s="27"/>
+      <c r="AQ4" s="27"/>
+      <c r="AR4" s="27"/>
+      <c r="AS4" s="27"/>
+      <c r="AT4" s="27"/>
+      <c r="AU4" s="27"/>
+      <c r="AV4" s="27"/>
+      <c r="AW4" s="27"/>
+      <c r="AX4" s="27"/>
+      <c r="AY4" s="27"/>
+      <c r="AZ4" s="27"/>
+      <c r="BA4" s="27"/>
+      <c r="BB4" s="27"/>
+      <c r="BC4" s="27"/>
+      <c r="BD4" s="27"/>
+      <c r="BE4" s="27"/>
+      <c r="BF4" s="27"/>
+      <c r="BG4" s="27"/>
+      <c r="BH4" s="27"/>
+      <c r="BI4" s="27"/>
+      <c r="BJ4" s="27"/>
+      <c r="BK4" s="27"/>
+      <c r="BL4" s="27"/>
+      <c r="BM4" s="27"/>
+      <c r="BN4" s="27"/>
+      <c r="BO4" s="27"/>
+      <c r="BP4" s="27"/>
+      <c r="BQ4" s="27"/>
+      <c r="BR4" s="27"/>
+      <c r="BS4" s="27"/>
+      <c r="BT4" s="27"/>
+      <c r="BU4" s="27"/>
+      <c r="BV4" s="27"/>
+      <c r="BW4" s="27"/>
+      <c r="BX4" s="27"/>
+      <c r="BY4" s="27"/>
+      <c r="BZ4" s="27"/>
+      <c r="CA4" s="27"/>
+      <c r="CB4" s="27"/>
     </row>
     <row r="5" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="52"/>
-      <c r="C5" s="37">
+      <c r="B5" s="40"/>
+      <c r="C5" s="41">
         <v>60</v>
       </c>
-      <c r="D5" s="38"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="35"/>
-      <c r="J5" s="35"/>
-      <c r="K5" s="35"/>
-      <c r="L5" s="35"/>
-      <c r="M5" s="35"/>
-      <c r="N5" s="35"/>
-      <c r="O5" s="35"/>
-      <c r="P5" s="35"/>
-      <c r="Q5" s="35"/>
-      <c r="R5" s="35"/>
-      <c r="S5" s="35"/>
-      <c r="T5" s="35"/>
-      <c r="U5" s="35"/>
-      <c r="V5" s="35"/>
-      <c r="W5" s="35"/>
-      <c r="X5" s="35"/>
-      <c r="Y5" s="35"/>
-      <c r="Z5" s="35"/>
-      <c r="AA5" s="35"/>
-      <c r="AB5" s="35"/>
-      <c r="AC5" s="35"/>
-      <c r="AD5" s="35"/>
-      <c r="AE5" s="35"/>
-      <c r="AF5" s="35"/>
-      <c r="AG5" s="35"/>
-      <c r="AH5" s="35"/>
-      <c r="AI5" s="35"/>
-      <c r="AJ5" s="35"/>
-      <c r="AK5" s="35"/>
-      <c r="AL5" s="35"/>
-      <c r="AM5" s="35"/>
-      <c r="AN5" s="35"/>
-      <c r="AO5" s="35"/>
-      <c r="AP5" s="35"/>
-      <c r="AQ5" s="35"/>
-      <c r="AR5" s="35"/>
-      <c r="AS5" s="35"/>
-      <c r="AT5" s="35"/>
-      <c r="AU5" s="35"/>
-      <c r="AV5" s="35"/>
-      <c r="AW5" s="35"/>
-      <c r="AX5" s="35"/>
-      <c r="AY5" s="35"/>
-      <c r="AZ5" s="35"/>
-      <c r="BA5" s="35"/>
-      <c r="BB5" s="35"/>
-      <c r="BC5" s="35"/>
-      <c r="BD5" s="35"/>
-      <c r="BE5" s="35"/>
-      <c r="BF5" s="35"/>
-      <c r="BG5" s="35"/>
-      <c r="BH5" s="35"/>
-      <c r="BI5" s="35"/>
-      <c r="BJ5" s="35"/>
-      <c r="BK5" s="35"/>
-      <c r="BL5" s="35"/>
-      <c r="BM5" s="35"/>
-      <c r="BN5" s="35"/>
-      <c r="BO5" s="35"/>
-      <c r="BP5" s="35"/>
-      <c r="BQ5" s="35"/>
-      <c r="BR5" s="35"/>
-      <c r="BS5" s="35"/>
-      <c r="BT5" s="35"/>
-      <c r="BU5" s="35"/>
-      <c r="BV5" s="35"/>
-      <c r="BW5" s="35"/>
-      <c r="BX5" s="35"/>
-      <c r="BY5" s="35"/>
-      <c r="BZ5" s="35"/>
-      <c r="CA5" s="35"/>
-      <c r="CB5" s="35"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="27"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="27"/>
+      <c r="M5" s="27"/>
+      <c r="N5" s="27"/>
+      <c r="O5" s="27"/>
+      <c r="P5" s="27"/>
+      <c r="Q5" s="27"/>
+      <c r="R5" s="27"/>
+      <c r="S5" s="27"/>
+      <c r="T5" s="27"/>
+      <c r="U5" s="27"/>
+      <c r="V5" s="27"/>
+      <c r="W5" s="27"/>
+      <c r="X5" s="27"/>
+      <c r="Y5" s="27"/>
+      <c r="Z5" s="27"/>
+      <c r="AA5" s="27"/>
+      <c r="AB5" s="27"/>
+      <c r="AC5" s="27"/>
+      <c r="AD5" s="27"/>
+      <c r="AE5" s="27"/>
+      <c r="AF5" s="27"/>
+      <c r="AG5" s="27"/>
+      <c r="AH5" s="27"/>
+      <c r="AI5" s="27"/>
+      <c r="AJ5" s="27"/>
+      <c r="AK5" s="27"/>
+      <c r="AL5" s="27"/>
+      <c r="AM5" s="27"/>
+      <c r="AN5" s="27"/>
+      <c r="AO5" s="27"/>
+      <c r="AP5" s="27"/>
+      <c r="AQ5" s="27"/>
+      <c r="AR5" s="27"/>
+      <c r="AS5" s="27"/>
+      <c r="AT5" s="27"/>
+      <c r="AU5" s="27"/>
+      <c r="AV5" s="27"/>
+      <c r="AW5" s="27"/>
+      <c r="AX5" s="27"/>
+      <c r="AY5" s="27"/>
+      <c r="AZ5" s="27"/>
+      <c r="BA5" s="27"/>
+      <c r="BB5" s="27"/>
+      <c r="BC5" s="27"/>
+      <c r="BD5" s="27"/>
+      <c r="BE5" s="27"/>
+      <c r="BF5" s="27"/>
+      <c r="BG5" s="27"/>
+      <c r="BH5" s="27"/>
+      <c r="BI5" s="27"/>
+      <c r="BJ5" s="27"/>
+      <c r="BK5" s="27"/>
+      <c r="BL5" s="27"/>
+      <c r="BM5" s="27"/>
+      <c r="BN5" s="27"/>
+      <c r="BO5" s="27"/>
+      <c r="BP5" s="27"/>
+      <c r="BQ5" s="27"/>
+      <c r="BR5" s="27"/>
+      <c r="BS5" s="27"/>
+      <c r="BT5" s="27"/>
+      <c r="BU5" s="27"/>
+      <c r="BV5" s="27"/>
+      <c r="BW5" s="27"/>
+      <c r="BX5" s="27"/>
+      <c r="BY5" s="27"/>
+      <c r="BZ5" s="27"/>
+      <c r="CA5" s="27"/>
+      <c r="CB5" s="27"/>
     </row>
     <row r="6" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="52" t="s">
+      <c r="A6" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="52"/>
-      <c r="C6" s="37">
+      <c r="B6" s="40"/>
+      <c r="C6" s="41">
         <v>6</v>
       </c>
-      <c r="D6" s="38"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="35"/>
-      <c r="J6" s="35"/>
-      <c r="K6" s="35"/>
-      <c r="L6" s="35"/>
-      <c r="M6" s="35"/>
-      <c r="N6" s="35"/>
-      <c r="O6" s="35"/>
-      <c r="P6" s="35"/>
-      <c r="Q6" s="35"/>
-      <c r="R6" s="35"/>
-      <c r="S6" s="35"/>
-      <c r="T6" s="35"/>
-      <c r="U6" s="35"/>
-      <c r="V6" s="35"/>
-      <c r="W6" s="35"/>
-      <c r="X6" s="35"/>
-      <c r="Y6" s="35"/>
-      <c r="Z6" s="35"/>
-      <c r="AA6" s="35"/>
-      <c r="AB6" s="35"/>
-      <c r="AC6" s="35"/>
-      <c r="AD6" s="35"/>
-      <c r="AE6" s="35"/>
-      <c r="AF6" s="35"/>
-      <c r="AG6" s="35"/>
-      <c r="AH6" s="35"/>
-      <c r="AI6" s="35"/>
-      <c r="AJ6" s="35"/>
-      <c r="AK6" s="35"/>
-      <c r="AL6" s="35"/>
-      <c r="AM6" s="35"/>
-      <c r="AN6" s="35"/>
-      <c r="AO6" s="35"/>
-      <c r="AP6" s="35"/>
-      <c r="AQ6" s="35"/>
-      <c r="AR6" s="35"/>
-      <c r="AS6" s="35"/>
-      <c r="AT6" s="35"/>
-      <c r="AU6" s="35"/>
-      <c r="AV6" s="35"/>
-      <c r="AW6" s="35"/>
-      <c r="AX6" s="35"/>
-      <c r="AY6" s="35"/>
-      <c r="AZ6" s="35"/>
-      <c r="BA6" s="35"/>
-      <c r="BB6" s="35"/>
-      <c r="BC6" s="35"/>
-      <c r="BD6" s="35"/>
-      <c r="BE6" s="35"/>
-      <c r="BF6" s="35"/>
-      <c r="BG6" s="35"/>
-      <c r="BH6" s="35"/>
-      <c r="BI6" s="35"/>
-      <c r="BJ6" s="35"/>
-      <c r="BK6" s="35"/>
-      <c r="BL6" s="35"/>
-      <c r="BM6" s="35"/>
-      <c r="BN6" s="35"/>
-      <c r="BO6" s="35"/>
-      <c r="BP6" s="35"/>
-      <c r="BQ6" s="35"/>
-      <c r="BR6" s="35"/>
-      <c r="BS6" s="35"/>
-      <c r="BT6" s="35"/>
-      <c r="BU6" s="35"/>
-      <c r="BV6" s="35"/>
-      <c r="BW6" s="35"/>
-      <c r="BX6" s="35"/>
-      <c r="BY6" s="35"/>
-      <c r="BZ6" s="35"/>
-      <c r="CA6" s="35"/>
-      <c r="CB6" s="35"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="27"/>
+      <c r="L6" s="27"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="27"/>
+      <c r="O6" s="27"/>
+      <c r="P6" s="27"/>
+      <c r="Q6" s="27"/>
+      <c r="R6" s="27"/>
+      <c r="S6" s="27"/>
+      <c r="T6" s="27"/>
+      <c r="U6" s="27"/>
+      <c r="V6" s="27"/>
+      <c r="W6" s="27"/>
+      <c r="X6" s="27"/>
+      <c r="Y6" s="27"/>
+      <c r="Z6" s="27"/>
+      <c r="AA6" s="27"/>
+      <c r="AB6" s="27"/>
+      <c r="AC6" s="27"/>
+      <c r="AD6" s="27"/>
+      <c r="AE6" s="27"/>
+      <c r="AF6" s="27"/>
+      <c r="AG6" s="27"/>
+      <c r="AH6" s="27"/>
+      <c r="AI6" s="27"/>
+      <c r="AJ6" s="27"/>
+      <c r="AK6" s="27"/>
+      <c r="AL6" s="27"/>
+      <c r="AM6" s="27"/>
+      <c r="AN6" s="27"/>
+      <c r="AO6" s="27"/>
+      <c r="AP6" s="27"/>
+      <c r="AQ6" s="27"/>
+      <c r="AR6" s="27"/>
+      <c r="AS6" s="27"/>
+      <c r="AT6" s="27"/>
+      <c r="AU6" s="27"/>
+      <c r="AV6" s="27"/>
+      <c r="AW6" s="27"/>
+      <c r="AX6" s="27"/>
+      <c r="AY6" s="27"/>
+      <c r="AZ6" s="27"/>
+      <c r="BA6" s="27"/>
+      <c r="BB6" s="27"/>
+      <c r="BC6" s="27"/>
+      <c r="BD6" s="27"/>
+      <c r="BE6" s="27"/>
+      <c r="BF6" s="27"/>
+      <c r="BG6" s="27"/>
+      <c r="BH6" s="27"/>
+      <c r="BI6" s="27"/>
+      <c r="BJ6" s="27"/>
+      <c r="BK6" s="27"/>
+      <c r="BL6" s="27"/>
+      <c r="BM6" s="27"/>
+      <c r="BN6" s="27"/>
+      <c r="BO6" s="27"/>
+      <c r="BP6" s="27"/>
+      <c r="BQ6" s="27"/>
+      <c r="BR6" s="27"/>
+      <c r="BS6" s="27"/>
+      <c r="BT6" s="27"/>
+      <c r="BU6" s="27"/>
+      <c r="BV6" s="27"/>
+      <c r="BW6" s="27"/>
+      <c r="BX6" s="27"/>
+      <c r="BY6" s="27"/>
+      <c r="BZ6" s="27"/>
+      <c r="CA6" s="27"/>
+      <c r="CB6" s="27"/>
     </row>
     <row r="7" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="53" t="s">
+      <c r="A7" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="53"/>
-      <c r="C7" s="37">
+      <c r="B7" s="43"/>
+      <c r="C7" s="41">
         <v>9</v>
       </c>
-      <c r="D7" s="38"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="36"/>
-      <c r="J7" s="36"/>
-      <c r="K7" s="36"/>
-      <c r="L7" s="36"/>
-      <c r="M7" s="36"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="36"/>
-      <c r="P7" s="36"/>
-      <c r="Q7" s="36"/>
-      <c r="R7" s="36"/>
-      <c r="S7" s="36"/>
-      <c r="T7" s="36"/>
-      <c r="U7" s="36"/>
-      <c r="V7" s="36"/>
-      <c r="W7" s="36"/>
-      <c r="X7" s="36"/>
-      <c r="Y7" s="36"/>
-      <c r="Z7" s="36"/>
-      <c r="AA7" s="36"/>
-      <c r="AB7" s="36"/>
-      <c r="AC7" s="36"/>
-      <c r="AD7" s="36"/>
-      <c r="AE7" s="36"/>
-      <c r="AF7" s="36"/>
-      <c r="AG7" s="36"/>
-      <c r="AH7" s="36"/>
-      <c r="AI7" s="36"/>
-      <c r="AJ7" s="36"/>
-      <c r="AK7" s="36"/>
-      <c r="AL7" s="36"/>
-      <c r="AM7" s="36"/>
-      <c r="AN7" s="36"/>
-      <c r="AO7" s="36"/>
-      <c r="AP7" s="36"/>
-      <c r="AQ7" s="36"/>
-      <c r="AR7" s="36"/>
-      <c r="AS7" s="36"/>
-      <c r="AT7" s="36"/>
-      <c r="AU7" s="36"/>
-      <c r="AV7" s="36"/>
-      <c r="AW7" s="36"/>
-      <c r="AX7" s="36"/>
-      <c r="AY7" s="36"/>
-      <c r="AZ7" s="36"/>
-      <c r="BA7" s="36"/>
-      <c r="BB7" s="36"/>
-      <c r="BC7" s="36"/>
-      <c r="BD7" s="36"/>
-      <c r="BE7" s="36"/>
-      <c r="BF7" s="36"/>
-      <c r="BG7" s="36"/>
-      <c r="BH7" s="36"/>
-      <c r="BI7" s="36"/>
-      <c r="BJ7" s="36"/>
-      <c r="BK7" s="36"/>
-      <c r="BL7" s="36"/>
-      <c r="BM7" s="36"/>
-      <c r="BN7" s="36"/>
-      <c r="BO7" s="36"/>
-      <c r="BP7" s="36"/>
-      <c r="BQ7" s="36"/>
-      <c r="BR7" s="36"/>
-      <c r="BS7" s="36"/>
-      <c r="BT7" s="36"/>
-      <c r="BU7" s="36"/>
-      <c r="BV7" s="36"/>
-      <c r="BW7" s="36"/>
-      <c r="BX7" s="36"/>
-      <c r="BY7" s="36"/>
-      <c r="BZ7" s="36"/>
-      <c r="CA7" s="36"/>
-      <c r="CB7" s="36"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="28"/>
+      <c r="K7" s="28"/>
+      <c r="L7" s="28"/>
+      <c r="M7" s="28"/>
+      <c r="N7" s="28"/>
+      <c r="O7" s="28"/>
+      <c r="P7" s="28"/>
+      <c r="Q7" s="28"/>
+      <c r="R7" s="28"/>
+      <c r="S7" s="28"/>
+      <c r="T7" s="28"/>
+      <c r="U7" s="28"/>
+      <c r="V7" s="28"/>
+      <c r="W7" s="28"/>
+      <c r="X7" s="28"/>
+      <c r="Y7" s="28"/>
+      <c r="Z7" s="28"/>
+      <c r="AA7" s="28"/>
+      <c r="AB7" s="28"/>
+      <c r="AC7" s="28"/>
+      <c r="AD7" s="28"/>
+      <c r="AE7" s="28"/>
+      <c r="AF7" s="28"/>
+      <c r="AG7" s="28"/>
+      <c r="AH7" s="28"/>
+      <c r="AI7" s="28"/>
+      <c r="AJ7" s="28"/>
+      <c r="AK7" s="28"/>
+      <c r="AL7" s="28"/>
+      <c r="AM7" s="28"/>
+      <c r="AN7" s="28"/>
+      <c r="AO7" s="28"/>
+      <c r="AP7" s="28"/>
+      <c r="AQ7" s="28"/>
+      <c r="AR7" s="28"/>
+      <c r="AS7" s="28"/>
+      <c r="AT7" s="28"/>
+      <c r="AU7" s="28"/>
+      <c r="AV7" s="28"/>
+      <c r="AW7" s="28"/>
+      <c r="AX7" s="28"/>
+      <c r="AY7" s="28"/>
+      <c r="AZ7" s="28"/>
+      <c r="BA7" s="28"/>
+      <c r="BB7" s="28"/>
+      <c r="BC7" s="28"/>
+      <c r="BD7" s="28"/>
+      <c r="BE7" s="28"/>
+      <c r="BF7" s="28"/>
+      <c r="BG7" s="28"/>
+      <c r="BH7" s="28"/>
+      <c r="BI7" s="28"/>
+      <c r="BJ7" s="28"/>
+      <c r="BK7" s="28"/>
+      <c r="BL7" s="28"/>
+      <c r="BM7" s="28"/>
+      <c r="BN7" s="28"/>
+      <c r="BO7" s="28"/>
+      <c r="BP7" s="28"/>
+      <c r="BQ7" s="28"/>
+      <c r="BR7" s="28"/>
+      <c r="BS7" s="28"/>
+      <c r="BT7" s="28"/>
+      <c r="BU7" s="28"/>
+      <c r="BV7" s="28"/>
+      <c r="BW7" s="28"/>
+      <c r="BX7" s="28"/>
+      <c r="BY7" s="28"/>
+      <c r="BZ7" s="28"/>
+      <c r="CA7" s="28"/>
+      <c r="CB7" s="28"/>
     </row>
     <row r="8" spans="1:85" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="32" t="s">
+      <c r="A8" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="32"/>
-      <c r="C8" s="33">
+      <c r="B8" s="44"/>
+      <c r="C8" s="45">
         <f>SUM(C5:D7)</f>
         <v>75</v>
       </c>
-      <c r="D8" s="34"/>
+      <c r="D8" s="39"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="24">
-        <v>1</v>
-      </c>
-      <c r="G8" s="24">
+      <c r="F8" s="46">
+        <v>1</v>
+      </c>
+      <c r="G8" s="46">
         <v>2</v>
       </c>
-      <c r="H8" s="24">
+      <c r="H8" s="46">
         <v>3</v>
       </c>
-      <c r="I8" s="24">
+      <c r="I8" s="46">
         <v>4</v>
       </c>
-      <c r="J8" s="24">
+      <c r="J8" s="46">
         <v>5</v>
       </c>
-      <c r="K8" s="24">
+      <c r="K8" s="46">
         <v>6</v>
       </c>
-      <c r="L8" s="24">
+      <c r="L8" s="46">
         <v>7</v>
       </c>
-      <c r="M8" s="24">
+      <c r="M8" s="46">
         <v>8</v>
       </c>
-      <c r="N8" s="24">
+      <c r="N8" s="46">
         <v>9</v>
       </c>
-      <c r="O8" s="24">
+      <c r="O8" s="46">
         <v>10</v>
       </c>
-      <c r="P8" s="24">
+      <c r="P8" s="46">
         <v>11</v>
       </c>
-      <c r="Q8" s="24">
+      <c r="Q8" s="46">
         <v>12</v>
       </c>
-      <c r="R8" s="24">
+      <c r="R8" s="46">
         <v>13</v>
       </c>
-      <c r="S8" s="24">
+      <c r="S8" s="46">
         <v>14</v>
       </c>
-      <c r="T8" s="24">
+      <c r="T8" s="46">
         <v>15</v>
       </c>
-      <c r="U8" s="24">
+      <c r="U8" s="46">
         <v>16</v>
       </c>
-      <c r="V8" s="24">
+      <c r="V8" s="46">
         <v>17</v>
       </c>
-      <c r="W8" s="24">
+      <c r="W8" s="46">
         <v>18</v>
       </c>
-      <c r="X8" s="24">
+      <c r="X8" s="46">
         <v>19</v>
       </c>
-      <c r="Y8" s="24">
+      <c r="Y8" s="46">
         <v>20</v>
       </c>
-      <c r="Z8" s="24">
+      <c r="Z8" s="46">
         <v>21</v>
       </c>
-      <c r="AA8" s="24">
+      <c r="AA8" s="46">
         <v>22</v>
       </c>
-      <c r="AB8" s="24">
+      <c r="AB8" s="46">
         <v>23</v>
       </c>
-      <c r="AC8" s="24">
+      <c r="AC8" s="46">
         <v>24</v>
       </c>
-      <c r="AD8" s="24">
+      <c r="AD8" s="46">
         <v>25</v>
       </c>
-      <c r="AE8" s="24">
+      <c r="AE8" s="46">
         <v>26</v>
       </c>
-      <c r="AF8" s="24">
+      <c r="AF8" s="46">
         <v>27</v>
       </c>
-      <c r="AG8" s="24">
+      <c r="AG8" s="46">
         <v>28</v>
       </c>
-      <c r="AH8" s="24">
+      <c r="AH8" s="46">
         <v>29</v>
       </c>
-      <c r="AI8" s="24">
+      <c r="AI8" s="46">
         <v>30</v>
       </c>
-      <c r="AJ8" s="24">
+      <c r="AJ8" s="46">
         <v>31</v>
       </c>
-      <c r="AK8" s="24">
+      <c r="AK8" s="46">
         <v>32</v>
       </c>
-      <c r="AL8" s="24">
+      <c r="AL8" s="46">
         <v>33</v>
       </c>
-      <c r="AM8" s="24">
+      <c r="AM8" s="46">
         <v>34</v>
       </c>
-      <c r="AN8" s="24">
+      <c r="AN8" s="46">
         <v>35</v>
       </c>
-      <c r="AO8" s="24">
+      <c r="AO8" s="46">
         <v>36</v>
       </c>
-      <c r="AP8" s="24">
+      <c r="AP8" s="46">
         <v>37</v>
       </c>
-      <c r="AQ8" s="24">
+      <c r="AQ8" s="46">
         <v>38</v>
       </c>
-      <c r="AR8" s="24">
+      <c r="AR8" s="46">
         <v>39</v>
       </c>
-      <c r="AS8" s="24">
+      <c r="AS8" s="46">
         <v>40</v>
       </c>
-      <c r="AT8" s="24">
+      <c r="AT8" s="46">
         <v>41</v>
       </c>
-      <c r="AU8" s="24">
+      <c r="AU8" s="46">
         <v>42</v>
       </c>
-      <c r="AV8" s="24">
+      <c r="AV8" s="46">
         <v>43</v>
       </c>
-      <c r="AW8" s="24">
+      <c r="AW8" s="46">
         <v>44</v>
       </c>
-      <c r="AX8" s="24">
+      <c r="AX8" s="46">
         <v>45</v>
       </c>
-      <c r="AY8" s="24">
+      <c r="AY8" s="46">
         <v>46</v>
       </c>
-      <c r="AZ8" s="24">
+      <c r="AZ8" s="46">
         <v>47</v>
       </c>
-      <c r="BA8" s="24">
+      <c r="BA8" s="46">
         <v>48</v>
       </c>
-      <c r="BB8" s="24">
+      <c r="BB8" s="46">
         <v>49</v>
       </c>
-      <c r="BC8" s="24">
+      <c r="BC8" s="46">
         <v>50</v>
       </c>
-      <c r="BD8" s="24">
+      <c r="BD8" s="46">
         <v>51</v>
       </c>
-      <c r="BE8" s="24">
+      <c r="BE8" s="46">
         <v>52</v>
       </c>
-      <c r="BF8" s="24">
+      <c r="BF8" s="46">
         <v>53</v>
       </c>
-      <c r="BG8" s="24">
+      <c r="BG8" s="46">
         <v>54</v>
       </c>
-      <c r="BH8" s="24">
+      <c r="BH8" s="46">
         <v>55</v>
       </c>
-      <c r="BI8" s="24">
+      <c r="BI8" s="46">
         <v>56</v>
       </c>
-      <c r="BJ8" s="24">
+      <c r="BJ8" s="46">
         <v>57</v>
       </c>
-      <c r="BK8" s="24">
+      <c r="BK8" s="46">
         <v>58</v>
       </c>
-      <c r="BL8" s="24">
+      <c r="BL8" s="46">
         <v>59</v>
       </c>
-      <c r="BM8" s="24">
+      <c r="BM8" s="46">
         <v>60</v>
       </c>
-      <c r="BN8" s="24">
+      <c r="BN8" s="46">
         <v>61</v>
       </c>
-      <c r="BO8" s="24">
+      <c r="BO8" s="46">
         <v>62</v>
       </c>
-      <c r="BP8" s="24">
+      <c r="BP8" s="46">
         <v>63</v>
       </c>
-      <c r="BQ8" s="24">
+      <c r="BQ8" s="46">
         <v>64</v>
       </c>
-      <c r="BR8" s="24">
+      <c r="BR8" s="46">
         <v>65</v>
       </c>
-      <c r="BS8" s="24">
+      <c r="BS8" s="46">
         <v>66</v>
       </c>
-      <c r="BT8" s="24">
+      <c r="BT8" s="46">
         <v>67</v>
       </c>
-      <c r="BU8" s="24">
+      <c r="BU8" s="46">
         <v>68</v>
       </c>
-      <c r="BV8" s="24">
+      <c r="BV8" s="46">
         <v>69</v>
       </c>
-      <c r="BW8" s="24">
+      <c r="BW8" s="46">
         <v>70</v>
       </c>
-      <c r="BX8" s="24">
+      <c r="BX8" s="46">
         <v>71</v>
       </c>
-      <c r="BY8" s="24">
+      <c r="BY8" s="46">
         <v>72</v>
       </c>
-      <c r="BZ8" s="24">
+      <c r="BZ8" s="46">
         <v>73</v>
       </c>
-      <c r="CA8" s="24">
+      <c r="CA8" s="46">
         <v>74</v>
       </c>
-      <c r="CB8" s="24">
+      <c r="CB8" s="46">
         <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="31" t="s">
+      <c r="C9" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="30"/>
+      <c r="D9" s="49"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="25"/>
-      <c r="I9" s="25"/>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="25"/>
-      <c r="M9" s="25"/>
-      <c r="N9" s="25"/>
-      <c r="O9" s="25"/>
-      <c r="P9" s="25"/>
-      <c r="Q9" s="25"/>
-      <c r="R9" s="25"/>
-      <c r="S9" s="25"/>
-      <c r="T9" s="25"/>
-      <c r="U9" s="25"/>
-      <c r="V9" s="25"/>
-      <c r="W9" s="25"/>
-      <c r="X9" s="25"/>
-      <c r="Y9" s="25"/>
-      <c r="Z9" s="25"/>
-      <c r="AA9" s="25"/>
-      <c r="AB9" s="25"/>
-      <c r="AC9" s="25"/>
-      <c r="AD9" s="25"/>
-      <c r="AE9" s="25"/>
-      <c r="AF9" s="25"/>
-      <c r="AG9" s="25"/>
-      <c r="AH9" s="25"/>
-      <c r="AI9" s="25"/>
-      <c r="AJ9" s="25"/>
-      <c r="AK9" s="25"/>
-      <c r="AL9" s="25"/>
-      <c r="AM9" s="25"/>
-      <c r="AN9" s="25"/>
-      <c r="AO9" s="25"/>
-      <c r="AP9" s="25"/>
-      <c r="AQ9" s="25"/>
-      <c r="AR9" s="25"/>
-      <c r="AS9" s="25"/>
-      <c r="AT9" s="25"/>
-      <c r="AU9" s="25"/>
-      <c r="AV9" s="25"/>
-      <c r="AW9" s="25"/>
-      <c r="AX9" s="25"/>
-      <c r="AY9" s="25"/>
-      <c r="AZ9" s="25"/>
-      <c r="BA9" s="25"/>
-      <c r="BB9" s="25"/>
-      <c r="BC9" s="25"/>
-      <c r="BD9" s="25"/>
-      <c r="BE9" s="25"/>
-      <c r="BF9" s="25"/>
-      <c r="BG9" s="25"/>
-      <c r="BH9" s="25"/>
-      <c r="BI9" s="25"/>
-      <c r="BJ9" s="25"/>
-      <c r="BK9" s="25"/>
-      <c r="BL9" s="25"/>
-      <c r="BM9" s="25"/>
-      <c r="BN9" s="25"/>
-      <c r="BO9" s="25"/>
-      <c r="BP9" s="25"/>
-      <c r="BQ9" s="25"/>
-      <c r="BR9" s="25"/>
-      <c r="BS9" s="25"/>
-      <c r="BT9" s="25"/>
-      <c r="BU9" s="25"/>
-      <c r="BV9" s="25"/>
-      <c r="BW9" s="25"/>
-      <c r="BX9" s="25"/>
-      <c r="BY9" s="25"/>
-      <c r="BZ9" s="25"/>
-      <c r="CA9" s="25"/>
-      <c r="CB9" s="25"/>
+      <c r="F9" s="47"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="47"/>
+      <c r="I9" s="47"/>
+      <c r="J9" s="47"/>
+      <c r="K9" s="47"/>
+      <c r="L9" s="47"/>
+      <c r="M9" s="47"/>
+      <c r="N9" s="47"/>
+      <c r="O9" s="47"/>
+      <c r="P9" s="47"/>
+      <c r="Q9" s="47"/>
+      <c r="R9" s="47"/>
+      <c r="S9" s="47"/>
+      <c r="T9" s="47"/>
+      <c r="U9" s="47"/>
+      <c r="V9" s="47"/>
+      <c r="W9" s="47"/>
+      <c r="X9" s="47"/>
+      <c r="Y9" s="47"/>
+      <c r="Z9" s="47"/>
+      <c r="AA9" s="47"/>
+      <c r="AB9" s="47"/>
+      <c r="AC9" s="47"/>
+      <c r="AD9" s="47"/>
+      <c r="AE9" s="47"/>
+      <c r="AF9" s="47"/>
+      <c r="AG9" s="47"/>
+      <c r="AH9" s="47"/>
+      <c r="AI9" s="47"/>
+      <c r="AJ9" s="47"/>
+      <c r="AK9" s="47"/>
+      <c r="AL9" s="47"/>
+      <c r="AM9" s="47"/>
+      <c r="AN9" s="47"/>
+      <c r="AO9" s="47"/>
+      <c r="AP9" s="47"/>
+      <c r="AQ9" s="47"/>
+      <c r="AR9" s="47"/>
+      <c r="AS9" s="47"/>
+      <c r="AT9" s="47"/>
+      <c r="AU9" s="47"/>
+      <c r="AV9" s="47"/>
+      <c r="AW9" s="47"/>
+      <c r="AX9" s="47"/>
+      <c r="AY9" s="47"/>
+      <c r="AZ9" s="47"/>
+      <c r="BA9" s="47"/>
+      <c r="BB9" s="47"/>
+      <c r="BC9" s="47"/>
+      <c r="BD9" s="47"/>
+      <c r="BE9" s="47"/>
+      <c r="BF9" s="47"/>
+      <c r="BG9" s="47"/>
+      <c r="BH9" s="47"/>
+      <c r="BI9" s="47"/>
+      <c r="BJ9" s="47"/>
+      <c r="BK9" s="47"/>
+      <c r="BL9" s="47"/>
+      <c r="BM9" s="47"/>
+      <c r="BN9" s="47"/>
+      <c r="BO9" s="47"/>
+      <c r="BP9" s="47"/>
+      <c r="BQ9" s="47"/>
+      <c r="BR9" s="47"/>
+      <c r="BS9" s="47"/>
+      <c r="BT9" s="47"/>
+      <c r="BU9" s="47"/>
+      <c r="BV9" s="47"/>
+      <c r="BW9" s="47"/>
+      <c r="BX9" s="47"/>
+      <c r="BY9" s="47"/>
+      <c r="BZ9" s="47"/>
+      <c r="CA9" s="47"/>
+      <c r="CB9" s="47"/>
     </row>
     <row r="10" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="29"/>
-      <c r="B10" s="30"/>
+      <c r="A10" s="48"/>
+      <c r="B10" s="49"/>
       <c r="C10" s="6"/>
       <c r="D10" s="4" t="s">
         <v>12</v>
@@ -2355,7 +2369,7 @@
       </c>
       <c r="D11" s="11">
         <f t="shared" ref="D11:D28" si="0">COUNT(F11:CB11)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" s="12"/>
       <c r="F11" s="8"/>
@@ -2396,7 +2410,9 @@
       <c r="AM11" s="8"/>
       <c r="AN11" s="8"/>
       <c r="AO11" s="8"/>
-      <c r="AP11" s="8"/>
+      <c r="AP11" s="8">
+        <v>0</v>
+      </c>
       <c r="AQ11" s="8"/>
       <c r="AR11" s="8"/>
       <c r="AS11" s="8"/>
@@ -2539,7 +2555,7 @@
       </c>
       <c r="D13" s="11">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E13" s="12"/>
       <c r="F13" s="8"/>
@@ -2602,7 +2618,9 @@
       <c r="AM13" s="8"/>
       <c r="AN13" s="8"/>
       <c r="AO13" s="8"/>
-      <c r="AP13" s="8"/>
+      <c r="AP13" s="8">
+        <v>0</v>
+      </c>
       <c r="AQ13" s="8"/>
       <c r="AR13" s="8"/>
       <c r="AS13" s="8"/>
@@ -2926,7 +2944,7 @@
       </c>
       <c r="D16" s="11">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E16" s="12"/>
       <c r="F16" s="8"/>
@@ -2975,7 +2993,9 @@
       <c r="AM16" s="8"/>
       <c r="AN16" s="8"/>
       <c r="AO16" s="8"/>
-      <c r="AP16" s="8"/>
+      <c r="AP16" s="8">
+        <v>0</v>
+      </c>
       <c r="AQ16" s="8"/>
       <c r="AR16" s="8"/>
       <c r="AS16" s="8"/>
@@ -3063,72 +3083,72 @@
       <c r="P17" s="8">
         <v>0</v>
       </c>
-      <c r="Q17" s="21" t="s">
+      <c r="Q17" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="R17" s="22"/>
-      <c r="S17" s="22"/>
-      <c r="T17" s="22"/>
-      <c r="U17" s="22"/>
-      <c r="V17" s="22"/>
-      <c r="W17" s="22"/>
-      <c r="X17" s="22"/>
-      <c r="Y17" s="22"/>
-      <c r="Z17" s="22"/>
-      <c r="AA17" s="22"/>
-      <c r="AB17" s="22"/>
-      <c r="AC17" s="22"/>
-      <c r="AD17" s="22"/>
-      <c r="AE17" s="22"/>
-      <c r="AF17" s="22"/>
-      <c r="AG17" s="22"/>
-      <c r="AH17" s="22"/>
-      <c r="AI17" s="22"/>
-      <c r="AJ17" s="22"/>
-      <c r="AK17" s="22"/>
-      <c r="AL17" s="22"/>
-      <c r="AM17" s="22"/>
-      <c r="AN17" s="22"/>
-      <c r="AO17" s="22"/>
-      <c r="AP17" s="22"/>
-      <c r="AQ17" s="22"/>
-      <c r="AR17" s="22"/>
-      <c r="AS17" s="22"/>
-      <c r="AT17" s="22"/>
-      <c r="AU17" s="22"/>
-      <c r="AV17" s="22"/>
-      <c r="AW17" s="22"/>
-      <c r="AX17" s="22"/>
-      <c r="AY17" s="22"/>
-      <c r="AZ17" s="22"/>
-      <c r="BA17" s="22"/>
-      <c r="BB17" s="22"/>
-      <c r="BC17" s="22"/>
-      <c r="BD17" s="22"/>
-      <c r="BE17" s="22"/>
-      <c r="BF17" s="22"/>
-      <c r="BG17" s="22"/>
-      <c r="BH17" s="22"/>
-      <c r="BI17" s="22"/>
-      <c r="BJ17" s="22"/>
-      <c r="BK17" s="22"/>
-      <c r="BL17" s="22"/>
-      <c r="BM17" s="22"/>
-      <c r="BN17" s="22"/>
-      <c r="BO17" s="22"/>
-      <c r="BP17" s="22"/>
-      <c r="BQ17" s="22"/>
-      <c r="BR17" s="22"/>
-      <c r="BS17" s="22"/>
-      <c r="BT17" s="22"/>
-      <c r="BU17" s="22"/>
-      <c r="BV17" s="22"/>
-      <c r="BW17" s="22"/>
-      <c r="BX17" s="22"/>
-      <c r="BY17" s="22"/>
-      <c r="BZ17" s="22"/>
-      <c r="CA17" s="22"/>
-      <c r="CB17" s="23"/>
+      <c r="R17" s="25"/>
+      <c r="S17" s="25"/>
+      <c r="T17" s="25"/>
+      <c r="U17" s="25"/>
+      <c r="V17" s="25"/>
+      <c r="W17" s="25"/>
+      <c r="X17" s="25"/>
+      <c r="Y17" s="25"/>
+      <c r="Z17" s="25"/>
+      <c r="AA17" s="25"/>
+      <c r="AB17" s="25"/>
+      <c r="AC17" s="25"/>
+      <c r="AD17" s="25"/>
+      <c r="AE17" s="25"/>
+      <c r="AF17" s="25"/>
+      <c r="AG17" s="25"/>
+      <c r="AH17" s="25"/>
+      <c r="AI17" s="25"/>
+      <c r="AJ17" s="25"/>
+      <c r="AK17" s="25"/>
+      <c r="AL17" s="25"/>
+      <c r="AM17" s="25"/>
+      <c r="AN17" s="25"/>
+      <c r="AO17" s="25"/>
+      <c r="AP17" s="25"/>
+      <c r="AQ17" s="25"/>
+      <c r="AR17" s="25"/>
+      <c r="AS17" s="25"/>
+      <c r="AT17" s="25"/>
+      <c r="AU17" s="25"/>
+      <c r="AV17" s="25"/>
+      <c r="AW17" s="25"/>
+      <c r="AX17" s="25"/>
+      <c r="AY17" s="25"/>
+      <c r="AZ17" s="25"/>
+      <c r="BA17" s="25"/>
+      <c r="BB17" s="25"/>
+      <c r="BC17" s="25"/>
+      <c r="BD17" s="25"/>
+      <c r="BE17" s="25"/>
+      <c r="BF17" s="25"/>
+      <c r="BG17" s="25"/>
+      <c r="BH17" s="25"/>
+      <c r="BI17" s="25"/>
+      <c r="BJ17" s="25"/>
+      <c r="BK17" s="25"/>
+      <c r="BL17" s="25"/>
+      <c r="BM17" s="25"/>
+      <c r="BN17" s="25"/>
+      <c r="BO17" s="25"/>
+      <c r="BP17" s="25"/>
+      <c r="BQ17" s="25"/>
+      <c r="BR17" s="25"/>
+      <c r="BS17" s="25"/>
+      <c r="BT17" s="25"/>
+      <c r="BU17" s="25"/>
+      <c r="BV17" s="25"/>
+      <c r="BW17" s="25"/>
+      <c r="BX17" s="25"/>
+      <c r="BY17" s="25"/>
+      <c r="BZ17" s="25"/>
+      <c r="CA17" s="25"/>
+      <c r="CB17" s="26"/>
     </row>
     <row r="18" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
@@ -3560,57 +3580,57 @@
       <c r="AE21" s="8">
         <v>0</v>
       </c>
-      <c r="AF21" s="21" t="s">
+      <c r="AF21" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="AG21" s="22"/>
-      <c r="AH21" s="22"/>
-      <c r="AI21" s="22"/>
-      <c r="AJ21" s="22"/>
-      <c r="AK21" s="22"/>
-      <c r="AL21" s="22"/>
-      <c r="AM21" s="22"/>
-      <c r="AN21" s="22"/>
-      <c r="AO21" s="22"/>
-      <c r="AP21" s="22"/>
-      <c r="AQ21" s="22"/>
-      <c r="AR21" s="22"/>
-      <c r="AS21" s="22"/>
-      <c r="AT21" s="22"/>
-      <c r="AU21" s="22"/>
-      <c r="AV21" s="22"/>
-      <c r="AW21" s="22"/>
-      <c r="AX21" s="22"/>
-      <c r="AY21" s="22"/>
-      <c r="AZ21" s="22"/>
-      <c r="BA21" s="22"/>
-      <c r="BB21" s="22"/>
-      <c r="BC21" s="22"/>
-      <c r="BD21" s="22"/>
-      <c r="BE21" s="22"/>
-      <c r="BF21" s="22"/>
-      <c r="BG21" s="22"/>
-      <c r="BH21" s="22"/>
-      <c r="BI21" s="22"/>
-      <c r="BJ21" s="22"/>
-      <c r="BK21" s="22"/>
-      <c r="BL21" s="22"/>
-      <c r="BM21" s="22"/>
-      <c r="BN21" s="22"/>
-      <c r="BO21" s="22"/>
-      <c r="BP21" s="22"/>
-      <c r="BQ21" s="22"/>
-      <c r="BR21" s="22"/>
-      <c r="BS21" s="22"/>
-      <c r="BT21" s="22"/>
-      <c r="BU21" s="22"/>
-      <c r="BV21" s="22"/>
-      <c r="BW21" s="22"/>
-      <c r="BX21" s="22"/>
-      <c r="BY21" s="22"/>
-      <c r="BZ21" s="22"/>
-      <c r="CA21" s="22"/>
-      <c r="CB21" s="23"/>
+      <c r="AG21" s="25"/>
+      <c r="AH21" s="25"/>
+      <c r="AI21" s="25"/>
+      <c r="AJ21" s="25"/>
+      <c r="AK21" s="25"/>
+      <c r="AL21" s="25"/>
+      <c r="AM21" s="25"/>
+      <c r="AN21" s="25"/>
+      <c r="AO21" s="25"/>
+      <c r="AP21" s="25"/>
+      <c r="AQ21" s="25"/>
+      <c r="AR21" s="25"/>
+      <c r="AS21" s="25"/>
+      <c r="AT21" s="25"/>
+      <c r="AU21" s="25"/>
+      <c r="AV21" s="25"/>
+      <c r="AW21" s="25"/>
+      <c r="AX21" s="25"/>
+      <c r="AY21" s="25"/>
+      <c r="AZ21" s="25"/>
+      <c r="BA21" s="25"/>
+      <c r="BB21" s="25"/>
+      <c r="BC21" s="25"/>
+      <c r="BD21" s="25"/>
+      <c r="BE21" s="25"/>
+      <c r="BF21" s="25"/>
+      <c r="BG21" s="25"/>
+      <c r="BH21" s="25"/>
+      <c r="BI21" s="25"/>
+      <c r="BJ21" s="25"/>
+      <c r="BK21" s="25"/>
+      <c r="BL21" s="25"/>
+      <c r="BM21" s="25"/>
+      <c r="BN21" s="25"/>
+      <c r="BO21" s="25"/>
+      <c r="BP21" s="25"/>
+      <c r="BQ21" s="25"/>
+      <c r="BR21" s="25"/>
+      <c r="BS21" s="25"/>
+      <c r="BT21" s="25"/>
+      <c r="BU21" s="25"/>
+      <c r="BV21" s="25"/>
+      <c r="BW21" s="25"/>
+      <c r="BX21" s="25"/>
+      <c r="BY21" s="25"/>
+      <c r="BZ21" s="25"/>
+      <c r="CA21" s="25"/>
+      <c r="CB21" s="26"/>
     </row>
     <row r="22" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9">
@@ -3808,57 +3828,57 @@
       <c r="AE23" s="8">
         <v>0</v>
       </c>
-      <c r="AF23" s="21" t="s">
+      <c r="AF23" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="AG23" s="22"/>
-      <c r="AH23" s="22"/>
-      <c r="AI23" s="22"/>
-      <c r="AJ23" s="22"/>
-      <c r="AK23" s="22"/>
-      <c r="AL23" s="22"/>
-      <c r="AM23" s="22"/>
-      <c r="AN23" s="22"/>
-      <c r="AO23" s="22"/>
-      <c r="AP23" s="22"/>
-      <c r="AQ23" s="22"/>
-      <c r="AR23" s="22"/>
-      <c r="AS23" s="22"/>
-      <c r="AT23" s="22"/>
-      <c r="AU23" s="22"/>
-      <c r="AV23" s="22"/>
-      <c r="AW23" s="22"/>
-      <c r="AX23" s="22"/>
-      <c r="AY23" s="22"/>
-      <c r="AZ23" s="22"/>
-      <c r="BA23" s="22"/>
-      <c r="BB23" s="22"/>
-      <c r="BC23" s="22"/>
-      <c r="BD23" s="22"/>
-      <c r="BE23" s="22"/>
-      <c r="BF23" s="22"/>
-      <c r="BG23" s="22"/>
-      <c r="BH23" s="22"/>
-      <c r="BI23" s="22"/>
-      <c r="BJ23" s="22"/>
-      <c r="BK23" s="22"/>
-      <c r="BL23" s="22"/>
-      <c r="BM23" s="22"/>
-      <c r="BN23" s="22"/>
-      <c r="BO23" s="22"/>
-      <c r="BP23" s="22"/>
-      <c r="BQ23" s="22"/>
-      <c r="BR23" s="22"/>
-      <c r="BS23" s="22"/>
-      <c r="BT23" s="22"/>
-      <c r="BU23" s="22"/>
-      <c r="BV23" s="22"/>
-      <c r="BW23" s="22"/>
-      <c r="BX23" s="22"/>
-      <c r="BY23" s="22"/>
-      <c r="BZ23" s="22"/>
-      <c r="CA23" s="22"/>
-      <c r="CB23" s="23"/>
+      <c r="AG23" s="25"/>
+      <c r="AH23" s="25"/>
+      <c r="AI23" s="25"/>
+      <c r="AJ23" s="25"/>
+      <c r="AK23" s="25"/>
+      <c r="AL23" s="25"/>
+      <c r="AM23" s="25"/>
+      <c r="AN23" s="25"/>
+      <c r="AO23" s="25"/>
+      <c r="AP23" s="25"/>
+      <c r="AQ23" s="25"/>
+      <c r="AR23" s="25"/>
+      <c r="AS23" s="25"/>
+      <c r="AT23" s="25"/>
+      <c r="AU23" s="25"/>
+      <c r="AV23" s="25"/>
+      <c r="AW23" s="25"/>
+      <c r="AX23" s="25"/>
+      <c r="AY23" s="25"/>
+      <c r="AZ23" s="25"/>
+      <c r="BA23" s="25"/>
+      <c r="BB23" s="25"/>
+      <c r="BC23" s="25"/>
+      <c r="BD23" s="25"/>
+      <c r="BE23" s="25"/>
+      <c r="BF23" s="25"/>
+      <c r="BG23" s="25"/>
+      <c r="BH23" s="25"/>
+      <c r="BI23" s="25"/>
+      <c r="BJ23" s="25"/>
+      <c r="BK23" s="25"/>
+      <c r="BL23" s="25"/>
+      <c r="BM23" s="25"/>
+      <c r="BN23" s="25"/>
+      <c r="BO23" s="25"/>
+      <c r="BP23" s="25"/>
+      <c r="BQ23" s="25"/>
+      <c r="BR23" s="25"/>
+      <c r="BS23" s="25"/>
+      <c r="BT23" s="25"/>
+      <c r="BU23" s="25"/>
+      <c r="BV23" s="25"/>
+      <c r="BW23" s="25"/>
+      <c r="BX23" s="25"/>
+      <c r="BY23" s="25"/>
+      <c r="BZ23" s="25"/>
+      <c r="CA23" s="25"/>
+      <c r="CB23" s="26"/>
     </row>
     <row r="24" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="9">
@@ -3991,7 +4011,7 @@
       </c>
       <c r="D25" s="11">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E25" s="12"/>
       <c r="F25" s="8">
@@ -4069,8 +4089,12 @@
       <c r="AL25" s="8"/>
       <c r="AM25" s="8"/>
       <c r="AN25" s="8"/>
-      <c r="AO25" s="8"/>
-      <c r="AP25" s="8"/>
+      <c r="AO25" s="8">
+        <v>0</v>
+      </c>
+      <c r="AP25" s="8">
+        <v>0</v>
+      </c>
       <c r="AQ25" s="8"/>
       <c r="AR25" s="8"/>
       <c r="AS25" s="8"/>
@@ -4122,7 +4146,7 @@
       </c>
       <c r="D26" s="11">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E26" s="12"/>
       <c r="F26" s="8">
@@ -4204,8 +4228,12 @@
       <c r="AL26" s="8"/>
       <c r="AM26" s="8"/>
       <c r="AN26" s="8"/>
-      <c r="AO26" s="8"/>
-      <c r="AP26" s="8"/>
+      <c r="AO26" s="8">
+        <v>0</v>
+      </c>
+      <c r="AP26" s="8">
+        <v>0</v>
+      </c>
       <c r="AQ26" s="8"/>
       <c r="AR26" s="8"/>
       <c r="AS26" s="8"/>
@@ -4257,7 +4285,7 @@
       </c>
       <c r="D27" s="11">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E27" s="15"/>
       <c r="F27" s="8">
@@ -4357,8 +4385,12 @@
       <c r="AL27" s="8"/>
       <c r="AM27" s="8"/>
       <c r="AN27" s="8"/>
-      <c r="AO27" s="8"/>
-      <c r="AP27" s="8"/>
+      <c r="AO27" s="8">
+        <v>0</v>
+      </c>
+      <c r="AP27" s="8">
+        <v>0</v>
+      </c>
       <c r="AQ27" s="8"/>
       <c r="AR27" s="8"/>
       <c r="AS27" s="8"/>
@@ -4412,87 +4444,242 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E28" s="26" t="s">
+      <c r="E28" s="51" t="s">
         <v>48</v>
       </c>
-      <c r="F28" s="26"/>
-      <c r="G28" s="26"/>
-      <c r="H28" s="26"/>
-      <c r="I28" s="26"/>
-      <c r="J28" s="26"/>
-      <c r="K28" s="26"/>
-      <c r="L28" s="26"/>
-      <c r="M28" s="26"/>
-      <c r="N28" s="26"/>
-      <c r="O28" s="26"/>
-      <c r="P28" s="26"/>
-      <c r="Q28" s="26"/>
-      <c r="R28" s="26"/>
-      <c r="S28" s="26"/>
-      <c r="T28" s="26"/>
-      <c r="U28" s="26"/>
-      <c r="V28" s="26"/>
-      <c r="W28" s="26"/>
-      <c r="X28" s="26"/>
-      <c r="Y28" s="26"/>
-      <c r="Z28" s="26"/>
-      <c r="AA28" s="26"/>
-      <c r="AB28" s="26"/>
-      <c r="AC28" s="26"/>
-      <c r="AD28" s="26"/>
-      <c r="AE28" s="26"/>
-      <c r="AF28" s="26"/>
-      <c r="AG28" s="26"/>
-      <c r="AH28" s="26"/>
-      <c r="AI28" s="26"/>
-      <c r="AJ28" s="26"/>
-      <c r="AK28" s="26"/>
-      <c r="AL28" s="26"/>
-      <c r="AM28" s="26"/>
-      <c r="AN28" s="26"/>
-      <c r="AO28" s="26"/>
-      <c r="AP28" s="26"/>
-      <c r="AQ28" s="26"/>
-      <c r="AR28" s="26"/>
-      <c r="AS28" s="26"/>
-      <c r="AT28" s="26"/>
-      <c r="AU28" s="26"/>
-      <c r="AV28" s="26"/>
-      <c r="AW28" s="26"/>
-      <c r="AX28" s="26"/>
-      <c r="AY28" s="26"/>
-      <c r="AZ28" s="26"/>
-      <c r="BA28" s="26"/>
-      <c r="BB28" s="26"/>
-      <c r="BC28" s="26"/>
-      <c r="BD28" s="26"/>
-      <c r="BE28" s="26"/>
-      <c r="BF28" s="26"/>
-      <c r="BG28" s="26"/>
-      <c r="BH28" s="26"/>
-      <c r="BI28" s="26"/>
-      <c r="BJ28" s="26"/>
-      <c r="BK28" s="26"/>
-      <c r="BL28" s="26"/>
-      <c r="BM28" s="26"/>
-      <c r="BN28" s="26"/>
-      <c r="BO28" s="26"/>
-      <c r="BP28" s="26"/>
-      <c r="BQ28" s="26"/>
-      <c r="BR28" s="26"/>
-      <c r="BS28" s="26"/>
-      <c r="BT28" s="26"/>
-      <c r="BU28" s="26"/>
-      <c r="BV28" s="26"/>
-      <c r="BW28" s="26"/>
-      <c r="BX28" s="26"/>
-      <c r="BY28" s="26"/>
-      <c r="BZ28" s="26"/>
-      <c r="CA28" s="26"/>
-      <c r="CB28" s="26"/>
+      <c r="F28" s="51"/>
+      <c r="G28" s="51"/>
+      <c r="H28" s="51"/>
+      <c r="I28" s="51"/>
+      <c r="J28" s="51"/>
+      <c r="K28" s="51"/>
+      <c r="L28" s="51"/>
+      <c r="M28" s="51"/>
+      <c r="N28" s="51"/>
+      <c r="O28" s="51"/>
+      <c r="P28" s="51"/>
+      <c r="Q28" s="51"/>
+      <c r="R28" s="51"/>
+      <c r="S28" s="51"/>
+      <c r="T28" s="51"/>
+      <c r="U28" s="51"/>
+      <c r="V28" s="51"/>
+      <c r="W28" s="51"/>
+      <c r="X28" s="51"/>
+      <c r="Y28" s="51"/>
+      <c r="Z28" s="51"/>
+      <c r="AA28" s="51"/>
+      <c r="AB28" s="51"/>
+      <c r="AC28" s="51"/>
+      <c r="AD28" s="51"/>
+      <c r="AE28" s="51"/>
+      <c r="AF28" s="51"/>
+      <c r="AG28" s="51"/>
+      <c r="AH28" s="51"/>
+      <c r="AI28" s="51"/>
+      <c r="AJ28" s="51"/>
+      <c r="AK28" s="51"/>
+      <c r="AL28" s="51"/>
+      <c r="AM28" s="51"/>
+      <c r="AN28" s="51"/>
+      <c r="AO28" s="51"/>
+      <c r="AP28" s="51"/>
+      <c r="AQ28" s="51"/>
+      <c r="AR28" s="51"/>
+      <c r="AS28" s="51"/>
+      <c r="AT28" s="51"/>
+      <c r="AU28" s="51"/>
+      <c r="AV28" s="51"/>
+      <c r="AW28" s="51"/>
+      <c r="AX28" s="51"/>
+      <c r="AY28" s="51"/>
+      <c r="AZ28" s="51"/>
+      <c r="BA28" s="51"/>
+      <c r="BB28" s="51"/>
+      <c r="BC28" s="51"/>
+      <c r="BD28" s="51"/>
+      <c r="BE28" s="51"/>
+      <c r="BF28" s="51"/>
+      <c r="BG28" s="51"/>
+      <c r="BH28" s="51"/>
+      <c r="BI28" s="51"/>
+      <c r="BJ28" s="51"/>
+      <c r="BK28" s="51"/>
+      <c r="BL28" s="51"/>
+      <c r="BM28" s="51"/>
+      <c r="BN28" s="51"/>
+      <c r="BO28" s="51"/>
+      <c r="BP28" s="51"/>
+      <c r="BQ28" s="51"/>
+      <c r="BR28" s="51"/>
+      <c r="BS28" s="51"/>
+      <c r="BT28" s="51"/>
+      <c r="BU28" s="51"/>
+      <c r="BV28" s="51"/>
+      <c r="BW28" s="51"/>
+      <c r="BX28" s="51"/>
+      <c r="BY28" s="51"/>
+      <c r="BZ28" s="51"/>
+      <c r="CA28" s="51"/>
+      <c r="CB28" s="51"/>
     </row>
   </sheetData>
-  <mergeCells count="178">
+  <mergeCells count="179">
+    <mergeCell ref="E28:CB28"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="BU8:BU9"/>
+    <mergeCell ref="BV8:BV9"/>
+    <mergeCell ref="BW8:BW9"/>
+    <mergeCell ref="BC8:BC9"/>
+    <mergeCell ref="BD8:BD9"/>
+    <mergeCell ref="BE8:BE9"/>
+    <mergeCell ref="AN8:AN9"/>
+    <mergeCell ref="AO8:AO9"/>
+    <mergeCell ref="AP8:AP9"/>
+    <mergeCell ref="AQ8:AQ9"/>
+    <mergeCell ref="AR8:AR9"/>
+    <mergeCell ref="AS8:AS9"/>
+    <mergeCell ref="AT8:AT9"/>
+    <mergeCell ref="AU8:AU9"/>
+    <mergeCell ref="AV8:AV9"/>
+    <mergeCell ref="AK1:AP1"/>
+    <mergeCell ref="AW8:AW9"/>
+    <mergeCell ref="AX8:AX9"/>
+    <mergeCell ref="AY8:AY9"/>
+    <mergeCell ref="AZ8:AZ9"/>
+    <mergeCell ref="BA8:BA9"/>
+    <mergeCell ref="BB8:BB9"/>
+    <mergeCell ref="AF23:CB23"/>
+    <mergeCell ref="Q17:CB17"/>
+    <mergeCell ref="BX8:BX9"/>
+    <mergeCell ref="BY8:BY9"/>
+    <mergeCell ref="BZ8:BZ9"/>
+    <mergeCell ref="CA8:CA9"/>
+    <mergeCell ref="CB8:CB9"/>
+    <mergeCell ref="BO8:BO9"/>
+    <mergeCell ref="BP8:BP9"/>
+    <mergeCell ref="BQ8:BQ9"/>
+    <mergeCell ref="BR8:BR9"/>
+    <mergeCell ref="BS8:BS9"/>
+    <mergeCell ref="BT8:BT9"/>
+    <mergeCell ref="BF8:BF9"/>
+    <mergeCell ref="BG8:BG9"/>
+    <mergeCell ref="BH8:BH9"/>
+    <mergeCell ref="BI8:BI9"/>
+    <mergeCell ref="BJ8:BJ9"/>
+    <mergeCell ref="BK8:BK9"/>
+    <mergeCell ref="BL8:BL9"/>
+    <mergeCell ref="BM8:BM9"/>
+    <mergeCell ref="BN8:BN9"/>
+    <mergeCell ref="AE8:AE9"/>
+    <mergeCell ref="AF8:AF9"/>
+    <mergeCell ref="AG8:AG9"/>
+    <mergeCell ref="AH8:AH9"/>
+    <mergeCell ref="AI8:AI9"/>
+    <mergeCell ref="AJ8:AJ9"/>
+    <mergeCell ref="AK8:AK9"/>
+    <mergeCell ref="AL8:AL9"/>
+    <mergeCell ref="AM8:AM9"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="W8:W9"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AD8:AD9"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="BU2:BU7"/>
+    <mergeCell ref="BV2:BV7"/>
+    <mergeCell ref="BW2:BW7"/>
+    <mergeCell ref="BX2:BX7"/>
+    <mergeCell ref="BY2:BY7"/>
+    <mergeCell ref="BZ2:BZ7"/>
+    <mergeCell ref="CA2:CA7"/>
+    <mergeCell ref="CB2:CB7"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="BL2:BL7"/>
+    <mergeCell ref="BM2:BM7"/>
+    <mergeCell ref="BN2:BN7"/>
+    <mergeCell ref="BO2:BO7"/>
+    <mergeCell ref="BP2:BP7"/>
+    <mergeCell ref="BQ2:BQ7"/>
+    <mergeCell ref="BR2:BR7"/>
+    <mergeCell ref="BS2:BS7"/>
+    <mergeCell ref="BT2:BT7"/>
+    <mergeCell ref="BC2:BC7"/>
+    <mergeCell ref="BD2:BD7"/>
+    <mergeCell ref="BE2:BE7"/>
+    <mergeCell ref="BF2:BF7"/>
+    <mergeCell ref="BG2:BG7"/>
+    <mergeCell ref="BH2:BH7"/>
+    <mergeCell ref="BI2:BI7"/>
+    <mergeCell ref="BJ2:BJ7"/>
+    <mergeCell ref="BK2:BK7"/>
+    <mergeCell ref="AT2:AT7"/>
+    <mergeCell ref="AU2:AU7"/>
+    <mergeCell ref="AV2:AV7"/>
+    <mergeCell ref="AW2:AW7"/>
+    <mergeCell ref="AX2:AX7"/>
+    <mergeCell ref="AY2:AY7"/>
+    <mergeCell ref="AZ2:AZ7"/>
+    <mergeCell ref="BA2:BA7"/>
+    <mergeCell ref="BB2:BB7"/>
+    <mergeCell ref="AK2:AK7"/>
+    <mergeCell ref="AL2:AL7"/>
+    <mergeCell ref="AM2:AM7"/>
+    <mergeCell ref="AN2:AN7"/>
+    <mergeCell ref="AO2:AO7"/>
+    <mergeCell ref="AP2:AP7"/>
+    <mergeCell ref="AQ2:AQ7"/>
+    <mergeCell ref="AR2:AR7"/>
+    <mergeCell ref="AS2:AS7"/>
+    <mergeCell ref="AG2:AG7"/>
+    <mergeCell ref="AD2:AD7"/>
+    <mergeCell ref="AE2:AE7"/>
+    <mergeCell ref="AF2:AF7"/>
+    <mergeCell ref="AB2:AB7"/>
+    <mergeCell ref="AC2:AC7"/>
+    <mergeCell ref="AH2:AH7"/>
+    <mergeCell ref="AI2:AI7"/>
+    <mergeCell ref="AJ2:AJ7"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="V1:Z1"/>
+    <mergeCell ref="L1:P1"/>
+    <mergeCell ref="AA2:AA7"/>
+    <mergeCell ref="N2:N7"/>
+    <mergeCell ref="O2:O7"/>
+    <mergeCell ref="P2:P7"/>
+    <mergeCell ref="Q2:Q7"/>
+    <mergeCell ref="R2:R7"/>
+    <mergeCell ref="S2:S7"/>
+    <mergeCell ref="T2:T7"/>
+    <mergeCell ref="U2:U7"/>
+    <mergeCell ref="V2:V7"/>
+    <mergeCell ref="Q1:U1"/>
+    <mergeCell ref="AA1:AE1"/>
     <mergeCell ref="AF1:AJ1"/>
     <mergeCell ref="AF21:CB21"/>
     <mergeCell ref="J1:K1"/>
@@ -4517,160 +4704,6 @@
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="V1:Z1"/>
-    <mergeCell ref="L1:P1"/>
-    <mergeCell ref="AA2:AA7"/>
-    <mergeCell ref="N2:N7"/>
-    <mergeCell ref="O2:O7"/>
-    <mergeCell ref="P2:P7"/>
-    <mergeCell ref="Q2:Q7"/>
-    <mergeCell ref="R2:R7"/>
-    <mergeCell ref="S2:S7"/>
-    <mergeCell ref="T2:T7"/>
-    <mergeCell ref="U2:U7"/>
-    <mergeCell ref="V2:V7"/>
-    <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="AA1:AE1"/>
-    <mergeCell ref="AG2:AG7"/>
-    <mergeCell ref="AD2:AD7"/>
-    <mergeCell ref="AE2:AE7"/>
-    <mergeCell ref="AF2:AF7"/>
-    <mergeCell ref="AB2:AB7"/>
-    <mergeCell ref="AC2:AC7"/>
-    <mergeCell ref="AH2:AH7"/>
-    <mergeCell ref="AI2:AI7"/>
-    <mergeCell ref="AJ2:AJ7"/>
-    <mergeCell ref="AK2:AK7"/>
-    <mergeCell ref="AL2:AL7"/>
-    <mergeCell ref="AM2:AM7"/>
-    <mergeCell ref="AN2:AN7"/>
-    <mergeCell ref="AO2:AO7"/>
-    <mergeCell ref="AP2:AP7"/>
-    <mergeCell ref="AQ2:AQ7"/>
-    <mergeCell ref="AR2:AR7"/>
-    <mergeCell ref="AS2:AS7"/>
-    <mergeCell ref="BH2:BH7"/>
-    <mergeCell ref="BI2:BI7"/>
-    <mergeCell ref="BJ2:BJ7"/>
-    <mergeCell ref="BK2:BK7"/>
-    <mergeCell ref="AT2:AT7"/>
-    <mergeCell ref="AU2:AU7"/>
-    <mergeCell ref="AV2:AV7"/>
-    <mergeCell ref="AW2:AW7"/>
-    <mergeCell ref="AX2:AX7"/>
-    <mergeCell ref="AY2:AY7"/>
-    <mergeCell ref="AZ2:AZ7"/>
-    <mergeCell ref="BA2:BA7"/>
-    <mergeCell ref="BB2:BB7"/>
-    <mergeCell ref="BU2:BU7"/>
-    <mergeCell ref="BV2:BV7"/>
-    <mergeCell ref="BW2:BW7"/>
-    <mergeCell ref="BX2:BX7"/>
-    <mergeCell ref="BY2:BY7"/>
-    <mergeCell ref="BZ2:BZ7"/>
-    <mergeCell ref="CA2:CA7"/>
-    <mergeCell ref="CB2:CB7"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="BL2:BL7"/>
-    <mergeCell ref="BM2:BM7"/>
-    <mergeCell ref="BN2:BN7"/>
-    <mergeCell ref="BO2:BO7"/>
-    <mergeCell ref="BP2:BP7"/>
-    <mergeCell ref="BQ2:BQ7"/>
-    <mergeCell ref="BR2:BR7"/>
-    <mergeCell ref="BS2:BS7"/>
-    <mergeCell ref="BT2:BT7"/>
-    <mergeCell ref="BC2:BC7"/>
-    <mergeCell ref="BD2:BD7"/>
-    <mergeCell ref="BE2:BE7"/>
-    <mergeCell ref="BF2:BF7"/>
-    <mergeCell ref="BG2:BG7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="V8:V9"/>
-    <mergeCell ref="W8:W9"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AD8:AD9"/>
-    <mergeCell ref="AE8:AE9"/>
-    <mergeCell ref="AF8:AF9"/>
-    <mergeCell ref="AG8:AG9"/>
-    <mergeCell ref="AH8:AH9"/>
-    <mergeCell ref="AI8:AI9"/>
-    <mergeCell ref="AJ8:AJ9"/>
-    <mergeCell ref="AK8:AK9"/>
-    <mergeCell ref="AL8:AL9"/>
-    <mergeCell ref="AM8:AM9"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="BO8:BO9"/>
-    <mergeCell ref="BP8:BP9"/>
-    <mergeCell ref="BQ8:BQ9"/>
-    <mergeCell ref="BR8:BR9"/>
-    <mergeCell ref="BS8:BS9"/>
-    <mergeCell ref="BT8:BT9"/>
-    <mergeCell ref="BF8:BF9"/>
-    <mergeCell ref="BG8:BG9"/>
-    <mergeCell ref="BH8:BH9"/>
-    <mergeCell ref="BI8:BI9"/>
-    <mergeCell ref="BJ8:BJ9"/>
-    <mergeCell ref="BK8:BK9"/>
-    <mergeCell ref="BL8:BL9"/>
-    <mergeCell ref="BM8:BM9"/>
-    <mergeCell ref="BN8:BN9"/>
-    <mergeCell ref="AW8:AW9"/>
-    <mergeCell ref="AX8:AX9"/>
-    <mergeCell ref="AY8:AY9"/>
-    <mergeCell ref="AZ8:AZ9"/>
-    <mergeCell ref="BA8:BA9"/>
-    <mergeCell ref="BB8:BB9"/>
-    <mergeCell ref="AF23:CB23"/>
-    <mergeCell ref="Q17:CB17"/>
-    <mergeCell ref="BX8:BX9"/>
-    <mergeCell ref="BY8:BY9"/>
-    <mergeCell ref="BZ8:BZ9"/>
-    <mergeCell ref="CA8:CA9"/>
-    <mergeCell ref="CB8:CB9"/>
-    <mergeCell ref="E28:CB28"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="BU8:BU9"/>
-    <mergeCell ref="BV8:BV9"/>
-    <mergeCell ref="BW8:BW9"/>
-    <mergeCell ref="BC8:BC9"/>
-    <mergeCell ref="BD8:BD9"/>
-    <mergeCell ref="BE8:BE9"/>
-    <mergeCell ref="AN8:AN9"/>
-    <mergeCell ref="AO8:AO9"/>
-    <mergeCell ref="AP8:AP9"/>
-    <mergeCell ref="AQ8:AQ9"/>
-    <mergeCell ref="AR8:AR9"/>
-    <mergeCell ref="AS8:AS9"/>
-    <mergeCell ref="AT8:AT9"/>
-    <mergeCell ref="AU8:AU9"/>
-    <mergeCell ref="AV8:AV9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" verticalDpi="0"/>

--- a/ჟურნალი/5. N301 front-end დეველოპმენტი (ინტეგრირებული მიდგომით) - Git.xlsx
+++ b/ჟურნალი/5. N301 front-end დეველოპმენტი (ინტეგრირებული მიდგომით) - Git.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\designer\Desktop\Front\01. - Front-end-docs\ჟურნალი\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45870C8D-CA3E-4307-B6B2-F826904F6D0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B876E7E-4178-4456-9066-E035F6671C50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -520,7 +520,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -548,6 +548,12 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -732,7 +738,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -783,10 +789,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -878,6 +884,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1123,52 +1135,54 @@
       <c r="J1" s="21">
         <v>2</v>
       </c>
-      <c r="K1" s="23"/>
+      <c r="K1" s="22"/>
       <c r="L1" s="21">
         <v>5</v>
       </c>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
-      <c r="O1" s="22"/>
-      <c r="P1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
+      <c r="P1" s="22"/>
       <c r="Q1" s="21">
         <v>5</v>
       </c>
-      <c r="R1" s="22"/>
-      <c r="S1" s="22"/>
-      <c r="T1" s="22"/>
-      <c r="U1" s="23"/>
+      <c r="R1" s="23"/>
+      <c r="S1" s="23"/>
+      <c r="T1" s="23"/>
+      <c r="U1" s="22"/>
       <c r="V1" s="21">
         <v>5</v>
       </c>
-      <c r="W1" s="22"/>
-      <c r="X1" s="22"/>
-      <c r="Y1" s="22"/>
-      <c r="Z1" s="23"/>
+      <c r="W1" s="23"/>
+      <c r="X1" s="23"/>
+      <c r="Y1" s="23"/>
+      <c r="Z1" s="22"/>
       <c r="AA1" s="21">
         <v>5</v>
       </c>
-      <c r="AB1" s="22"/>
-      <c r="AC1" s="22"/>
-      <c r="AD1" s="22"/>
-      <c r="AE1" s="23"/>
+      <c r="AB1" s="23"/>
+      <c r="AC1" s="23"/>
+      <c r="AD1" s="23"/>
+      <c r="AE1" s="22"/>
       <c r="AF1" s="21">
         <v>5</v>
       </c>
-      <c r="AG1" s="22"/>
-      <c r="AH1" s="22"/>
-      <c r="AI1" s="22"/>
-      <c r="AJ1" s="23"/>
+      <c r="AG1" s="23"/>
+      <c r="AH1" s="23"/>
+      <c r="AI1" s="23"/>
+      <c r="AJ1" s="22"/>
       <c r="AK1" s="21">
         <v>6</v>
       </c>
-      <c r="AL1" s="22"/>
-      <c r="AM1" s="22"/>
-      <c r="AN1" s="22"/>
-      <c r="AO1" s="22"/>
-      <c r="AP1" s="23"/>
-      <c r="AQ1" s="17"/>
-      <c r="AR1" s="17"/>
+      <c r="AL1" s="23"/>
+      <c r="AM1" s="23"/>
+      <c r="AN1" s="23"/>
+      <c r="AO1" s="23"/>
+      <c r="AP1" s="22"/>
+      <c r="AQ1" s="21">
+        <v>2</v>
+      </c>
+      <c r="AR1" s="22"/>
       <c r="AS1" s="18"/>
       <c r="AT1" s="19"/>
       <c r="AU1" s="19"/>
@@ -1207,7 +1221,7 @@
       <c r="CB1" s="17"/>
       <c r="CC1" s="1">
         <f>SUM(E1:CB1)</f>
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:85" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1290,10 +1304,10 @@
       <c r="AC2" s="27">
         <v>46230</v>
       </c>
-      <c r="AD2" s="27">
+      <c r="AD2" s="54">
         <v>46230</v>
       </c>
-      <c r="AE2" s="27">
+      <c r="AE2" s="54">
         <v>46230</v>
       </c>
       <c r="AF2" s="27">
@@ -1329,8 +1343,12 @@
       <c r="AP2" s="27">
         <v>46286</v>
       </c>
-      <c r="AQ2" s="27"/>
-      <c r="AR2" s="27"/>
+      <c r="AQ2" s="27">
+        <v>46290</v>
+      </c>
+      <c r="AR2" s="27">
+        <v>46290</v>
+      </c>
       <c r="AS2" s="27"/>
       <c r="AT2" s="27"/>
       <c r="AU2" s="27"/>
@@ -1400,8 +1418,8 @@
       <c r="AA3" s="27"/>
       <c r="AB3" s="27"/>
       <c r="AC3" s="27"/>
-      <c r="AD3" s="27"/>
-      <c r="AE3" s="27"/>
+      <c r="AD3" s="54"/>
+      <c r="AE3" s="54"/>
       <c r="AF3" s="27"/>
       <c r="AG3" s="27"/>
       <c r="AH3" s="27"/>
@@ -1486,8 +1504,8 @@
       <c r="AA4" s="27"/>
       <c r="AB4" s="27"/>
       <c r="AC4" s="27"/>
-      <c r="AD4" s="27"/>
-      <c r="AE4" s="27"/>
+      <c r="AD4" s="54"/>
+      <c r="AE4" s="54"/>
       <c r="AF4" s="27"/>
       <c r="AG4" s="27"/>
       <c r="AH4" s="27"/>
@@ -1572,8 +1590,8 @@
       <c r="AA5" s="27"/>
       <c r="AB5" s="27"/>
       <c r="AC5" s="27"/>
-      <c r="AD5" s="27"/>
-      <c r="AE5" s="27"/>
+      <c r="AD5" s="54"/>
+      <c r="AE5" s="54"/>
       <c r="AF5" s="27"/>
       <c r="AG5" s="27"/>
       <c r="AH5" s="27"/>
@@ -1658,8 +1676,8 @@
       <c r="AA6" s="27"/>
       <c r="AB6" s="27"/>
       <c r="AC6" s="27"/>
-      <c r="AD6" s="27"/>
-      <c r="AE6" s="27"/>
+      <c r="AD6" s="54"/>
+      <c r="AE6" s="54"/>
       <c r="AF6" s="27"/>
       <c r="AG6" s="27"/>
       <c r="AH6" s="27"/>
@@ -1744,8 +1762,8 @@
       <c r="AA7" s="28"/>
       <c r="AB7" s="28"/>
       <c r="AC7" s="28"/>
-      <c r="AD7" s="28"/>
-      <c r="AE7" s="28"/>
+      <c r="AD7" s="55"/>
+      <c r="AE7" s="55"/>
       <c r="AF7" s="28"/>
       <c r="AG7" s="28"/>
       <c r="AH7" s="28"/>
@@ -4524,7 +4542,7 @@
       <c r="CB28" s="51"/>
     </row>
   </sheetData>
-  <mergeCells count="179">
+  <mergeCells count="180">
     <mergeCell ref="E28:CB28"/>
     <mergeCell ref="F1:I1"/>
     <mergeCell ref="BU8:BU9"/>
@@ -4665,6 +4683,7 @@
     <mergeCell ref="AH2:AH7"/>
     <mergeCell ref="AI2:AI7"/>
     <mergeCell ref="AJ2:AJ7"/>
+    <mergeCell ref="A6:B6"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="V1:Z1"/>
     <mergeCell ref="L1:P1"/>
@@ -4680,6 +4699,7 @@
     <mergeCell ref="V2:V7"/>
     <mergeCell ref="Q1:U1"/>
     <mergeCell ref="AA1:AE1"/>
+    <mergeCell ref="AQ1:AR1"/>
     <mergeCell ref="AF1:AJ1"/>
     <mergeCell ref="AF21:CB21"/>
     <mergeCell ref="J1:K1"/>
@@ -4703,7 +4723,6 @@
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A6:B6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" verticalDpi="0"/>

--- a/ჟურნალი/5. N301 front-end დეველოპმენტი (ინტეგრირებული მიდგომით) - Git.xlsx
+++ b/ჟურნალი/5. N301 front-end დეველოპმენტი (ინტეგრირებული მიდგომით) - Git.xlsx
@@ -1,34 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21126"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\designer\Desktop\Front\01. - Front-end-docs\ჟურნალი\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\3Daudiece\Desktop\Front-end!!\0. ready\ჟურნალი\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B876E7E-4178-4456-9066-E035F6671C50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A84EC8A-B26F-4F5A-BA57-C7EF1627D62E}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-122" yWindow="-122" windowWidth="29045" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="301 ინტეგრირებული" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -520,7 +507,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -542,12 +529,6 @@
       <patternFill patternType="solid">
         <fgColor indexed="2"/>
         <bgColor indexed="2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="5"/>
       </patternFill>
     </fill>
     <fill>
@@ -738,7 +719,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -781,18 +762,29 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -804,11 +796,47 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
@@ -839,57 +867,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1108,87 +1085,89 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:CG28"/>
-  <sheetFormatPr defaultColWidth="3.5703125" defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="3.625" defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.5703125" style="2"/>
+    <col min="1" max="1" width="3.625" style="2"/>
     <col min="2" max="3" width="21" style="1" customWidth="1"/>
     <col min="4" max="4" width="8" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.5703125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="3.5703125" style="1"/>
+    <col min="5" max="5" width="5.625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="3.625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="30"/>
-      <c r="D1" s="31"/>
-      <c r="F1" s="52">
+      <c r="A1" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="45"/>
+      <c r="D1" s="46"/>
+      <c r="F1" s="20">
         <v>4</v>
       </c>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="21">
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="24">
         <v>2</v>
       </c>
-      <c r="K1" s="22"/>
-      <c r="L1" s="21">
+      <c r="K1" s="26"/>
+      <c r="L1" s="24">
         <v>5</v>
       </c>
-      <c r="M1" s="23"/>
-      <c r="N1" s="23"/>
-      <c r="O1" s="23"/>
-      <c r="P1" s="22"/>
-      <c r="Q1" s="21">
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="24">
         <v>5</v>
       </c>
-      <c r="R1" s="23"/>
-      <c r="S1" s="23"/>
-      <c r="T1" s="23"/>
-      <c r="U1" s="22"/>
-      <c r="V1" s="21">
+      <c r="R1" s="25"/>
+      <c r="S1" s="25"/>
+      <c r="T1" s="25"/>
+      <c r="U1" s="26"/>
+      <c r="V1" s="24">
         <v>5</v>
       </c>
-      <c r="W1" s="23"/>
-      <c r="X1" s="23"/>
-      <c r="Y1" s="23"/>
-      <c r="Z1" s="22"/>
-      <c r="AA1" s="21">
+      <c r="W1" s="25"/>
+      <c r="X1" s="25"/>
+      <c r="Y1" s="25"/>
+      <c r="Z1" s="26"/>
+      <c r="AA1" s="24">
         <v>5</v>
       </c>
-      <c r="AB1" s="23"/>
-      <c r="AC1" s="23"/>
-      <c r="AD1" s="23"/>
-      <c r="AE1" s="22"/>
-      <c r="AF1" s="21">
+      <c r="AB1" s="25"/>
+      <c r="AC1" s="25"/>
+      <c r="AD1" s="25"/>
+      <c r="AE1" s="26"/>
+      <c r="AF1" s="24">
         <v>5</v>
       </c>
-      <c r="AG1" s="23"/>
-      <c r="AH1" s="23"/>
-      <c r="AI1" s="23"/>
-      <c r="AJ1" s="22"/>
-      <c r="AK1" s="21">
+      <c r="AG1" s="25"/>
+      <c r="AH1" s="25"/>
+      <c r="AI1" s="25"/>
+      <c r="AJ1" s="26"/>
+      <c r="AK1" s="24">
         <v>6</v>
       </c>
-      <c r="AL1" s="23"/>
-      <c r="AM1" s="23"/>
-      <c r="AN1" s="23"/>
-      <c r="AO1" s="23"/>
-      <c r="AP1" s="22"/>
-      <c r="AQ1" s="21">
+      <c r="AL1" s="25"/>
+      <c r="AM1" s="25"/>
+      <c r="AN1" s="25"/>
+      <c r="AO1" s="25"/>
+      <c r="AP1" s="26"/>
+      <c r="AQ1" s="24">
         <v>2</v>
       </c>
-      <c r="AR1" s="22"/>
-      <c r="AS1" s="18"/>
-      <c r="AT1" s="19"/>
-      <c r="AU1" s="19"/>
-      <c r="AV1" s="19"/>
-      <c r="AW1" s="19"/>
-      <c r="AX1" s="17"/>
+      <c r="AR1" s="26"/>
+      <c r="AS1" s="24">
+        <v>6</v>
+      </c>
+      <c r="AT1" s="25"/>
+      <c r="AU1" s="25"/>
+      <c r="AV1" s="25"/>
+      <c r="AW1" s="25"/>
+      <c r="AX1" s="26"/>
       <c r="AY1" s="17"/>
       <c r="AZ1" s="17"/>
       <c r="BA1" s="17"/>
@@ -1206,9 +1185,9 @@
       <c r="BM1" s="17"/>
       <c r="BN1" s="17"/>
       <c r="BO1" s="17"/>
-      <c r="BP1" s="20"/>
-      <c r="BQ1" s="20"/>
-      <c r="BR1" s="20"/>
+      <c r="BP1" s="18"/>
+      <c r="BQ1" s="18"/>
+      <c r="BR1" s="18"/>
       <c r="BS1" s="17"/>
       <c r="BT1" s="17"/>
       <c r="BU1" s="17"/>
@@ -1221,927 +1200,939 @@
       <c r="CB1" s="17"/>
       <c r="CC1" s="1">
         <f>SUM(E1:CB1)</f>
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:85" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="29"/>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="34" t="s">
+      <c r="A2" s="44"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="27">
+      <c r="F2" s="36">
         <v>46202</v>
       </c>
-      <c r="G2" s="27">
+      <c r="G2" s="36">
         <v>46202</v>
       </c>
-      <c r="H2" s="27">
+      <c r="H2" s="36">
         <v>46202</v>
       </c>
-      <c r="I2" s="27">
+      <c r="I2" s="36">
         <v>46202</v>
       </c>
-      <c r="J2" s="27">
+      <c r="J2" s="36">
         <v>46206</v>
       </c>
-      <c r="K2" s="27">
+      <c r="K2" s="36">
         <v>46206</v>
       </c>
-      <c r="L2" s="27">
+      <c r="L2" s="36">
         <v>46209</v>
       </c>
-      <c r="M2" s="27">
+      <c r="M2" s="36">
         <v>46209</v>
       </c>
-      <c r="N2" s="27">
+      <c r="N2" s="36">
         <v>46209</v>
       </c>
-      <c r="O2" s="27">
+      <c r="O2" s="36">
         <v>46209</v>
       </c>
-      <c r="P2" s="27">
+      <c r="P2" s="36">
         <v>46209</v>
       </c>
-      <c r="Q2" s="27">
+      <c r="Q2" s="36">
         <v>46216</v>
       </c>
-      <c r="R2" s="27">
+      <c r="R2" s="36">
         <v>46216</v>
       </c>
-      <c r="S2" s="27">
+      <c r="S2" s="36">
         <v>46216</v>
       </c>
-      <c r="T2" s="27">
+      <c r="T2" s="36">
         <v>46216</v>
       </c>
-      <c r="U2" s="27">
+      <c r="U2" s="36">
         <v>46216</v>
       </c>
-      <c r="V2" s="27">
+      <c r="V2" s="36">
         <v>46223</v>
       </c>
-      <c r="W2" s="27">
+      <c r="W2" s="36">
         <v>46223</v>
       </c>
-      <c r="X2" s="27">
+      <c r="X2" s="36">
         <v>46223</v>
       </c>
-      <c r="Y2" s="27">
+      <c r="Y2" s="36">
         <v>46223</v>
       </c>
-      <c r="Z2" s="27">
+      <c r="Z2" s="36">
         <v>46223</v>
       </c>
-      <c r="AA2" s="27">
+      <c r="AA2" s="36">
         <v>46230</v>
       </c>
-      <c r="AB2" s="27">
+      <c r="AB2" s="36">
         <v>46230</v>
       </c>
-      <c r="AC2" s="27">
+      <c r="AC2" s="36">
         <v>46230</v>
       </c>
-      <c r="AD2" s="54">
+      <c r="AD2" s="40">
         <v>46230</v>
       </c>
-      <c r="AE2" s="54">
+      <c r="AE2" s="40">
         <v>46230</v>
       </c>
-      <c r="AF2" s="27">
+      <c r="AF2" s="36">
         <v>46279</v>
       </c>
-      <c r="AG2" s="27">
+      <c r="AG2" s="36">
         <v>46279</v>
       </c>
-      <c r="AH2" s="27">
+      <c r="AH2" s="36">
         <v>46279</v>
       </c>
-      <c r="AI2" s="27">
+      <c r="AI2" s="36">
         <v>46279</v>
       </c>
-      <c r="AJ2" s="27">
+      <c r="AJ2" s="36">
         <v>46279</v>
       </c>
-      <c r="AK2" s="27">
+      <c r="AK2" s="36">
         <v>46286</v>
       </c>
-      <c r="AL2" s="27">
+      <c r="AL2" s="36">
         <v>46286</v>
       </c>
-      <c r="AM2" s="27">
+      <c r="AM2" s="36">
         <v>46286</v>
       </c>
-      <c r="AN2" s="27">
+      <c r="AN2" s="36">
         <v>46286</v>
       </c>
-      <c r="AO2" s="27">
+      <c r="AO2" s="36">
         <v>46286</v>
       </c>
-      <c r="AP2" s="27">
+      <c r="AP2" s="36">
         <v>46286</v>
       </c>
-      <c r="AQ2" s="27">
+      <c r="AQ2" s="36">
         <v>46290</v>
       </c>
-      <c r="AR2" s="27">
+      <c r="AR2" s="36">
         <v>46290</v>
       </c>
-      <c r="AS2" s="27"/>
-      <c r="AT2" s="27"/>
-      <c r="AU2" s="27"/>
-      <c r="AV2" s="27"/>
-      <c r="AW2" s="27"/>
-      <c r="AX2" s="27"/>
-      <c r="AY2" s="27"/>
-      <c r="AZ2" s="27"/>
-      <c r="BA2" s="27"/>
-      <c r="BB2" s="27"/>
-      <c r="BC2" s="27"/>
-      <c r="BD2" s="27"/>
-      <c r="BE2" s="27"/>
-      <c r="BF2" s="27"/>
-      <c r="BG2" s="27"/>
-      <c r="BH2" s="27"/>
-      <c r="BI2" s="27"/>
-      <c r="BJ2" s="27"/>
-      <c r="BK2" s="27"/>
-      <c r="BL2" s="27"/>
-      <c r="BM2" s="27"/>
-      <c r="BN2" s="27"/>
-      <c r="BO2" s="27"/>
-      <c r="BP2" s="27"/>
-      <c r="BQ2" s="27"/>
-      <c r="BR2" s="27"/>
-      <c r="BS2" s="27"/>
-      <c r="BT2" s="27"/>
-      <c r="BU2" s="27"/>
-      <c r="BV2" s="27"/>
-      <c r="BW2" s="27"/>
-      <c r="BX2" s="27"/>
-      <c r="BY2" s="27"/>
-      <c r="BZ2" s="27"/>
-      <c r="CA2" s="27"/>
-      <c r="CB2" s="27"/>
+      <c r="AS2" s="36">
+        <v>46293</v>
+      </c>
+      <c r="AT2" s="36">
+        <v>46293</v>
+      </c>
+      <c r="AU2" s="36">
+        <v>46293</v>
+      </c>
+      <c r="AV2" s="36">
+        <v>46293</v>
+      </c>
+      <c r="AW2" s="36">
+        <v>46293</v>
+      </c>
+      <c r="AX2" s="36">
+        <v>46293</v>
+      </c>
+      <c r="AY2" s="36"/>
+      <c r="AZ2" s="36"/>
+      <c r="BA2" s="36"/>
+      <c r="BB2" s="36"/>
+      <c r="BC2" s="36"/>
+      <c r="BD2" s="36"/>
+      <c r="BE2" s="36"/>
+      <c r="BF2" s="36"/>
+      <c r="BG2" s="36"/>
+      <c r="BH2" s="36"/>
+      <c r="BI2" s="36"/>
+      <c r="BJ2" s="36"/>
+      <c r="BK2" s="36"/>
+      <c r="BL2" s="36"/>
+      <c r="BM2" s="36"/>
+      <c r="BN2" s="36"/>
+      <c r="BO2" s="36"/>
+      <c r="BP2" s="36"/>
+      <c r="BQ2" s="36"/>
+      <c r="BR2" s="36"/>
+      <c r="BS2" s="36"/>
+      <c r="BT2" s="36"/>
+      <c r="BU2" s="36"/>
+      <c r="BV2" s="36"/>
+      <c r="BW2" s="36"/>
+      <c r="BX2" s="36"/>
+      <c r="BY2" s="36"/>
+      <c r="BZ2" s="36"/>
+      <c r="CA2" s="36"/>
+      <c r="CB2" s="36"/>
     </row>
-    <row r="3" spans="1:85" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="37" t="s">
+    <row r="3" spans="1:85" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="52" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="37"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
-      <c r="J3" s="27"/>
-      <c r="K3" s="27"/>
-      <c r="L3" s="27"/>
-      <c r="M3" s="27"/>
-      <c r="N3" s="27"/>
-      <c r="O3" s="27"/>
-      <c r="P3" s="27"/>
-      <c r="Q3" s="27"/>
-      <c r="R3" s="27"/>
-      <c r="S3" s="27"/>
-      <c r="T3" s="27"/>
-      <c r="U3" s="27"/>
-      <c r="V3" s="27"/>
-      <c r="W3" s="27"/>
-      <c r="X3" s="27"/>
-      <c r="Y3" s="27"/>
-      <c r="Z3" s="27"/>
-      <c r="AA3" s="27"/>
-      <c r="AB3" s="27"/>
-      <c r="AC3" s="27"/>
-      <c r="AD3" s="54"/>
-      <c r="AE3" s="54"/>
-      <c r="AF3" s="27"/>
-      <c r="AG3" s="27"/>
-      <c r="AH3" s="27"/>
-      <c r="AI3" s="27"/>
-      <c r="AJ3" s="27"/>
-      <c r="AK3" s="27"/>
-      <c r="AL3" s="27"/>
-      <c r="AM3" s="27"/>
-      <c r="AN3" s="27"/>
-      <c r="AO3" s="27"/>
-      <c r="AP3" s="27"/>
-      <c r="AQ3" s="27"/>
-      <c r="AR3" s="27"/>
-      <c r="AS3" s="27"/>
-      <c r="AT3" s="27"/>
-      <c r="AU3" s="27"/>
-      <c r="AV3" s="27"/>
-      <c r="AW3" s="27"/>
-      <c r="AX3" s="27"/>
-      <c r="AY3" s="27"/>
-      <c r="AZ3" s="27"/>
-      <c r="BA3" s="27"/>
-      <c r="BB3" s="27"/>
-      <c r="BC3" s="27"/>
-      <c r="BD3" s="27"/>
-      <c r="BE3" s="27"/>
-      <c r="BF3" s="27"/>
-      <c r="BG3" s="27"/>
-      <c r="BH3" s="27"/>
-      <c r="BI3" s="27"/>
-      <c r="BJ3" s="27"/>
-      <c r="BK3" s="27"/>
-      <c r="BL3" s="27"/>
-      <c r="BM3" s="27"/>
-      <c r="BN3" s="27"/>
-      <c r="BO3" s="27"/>
-      <c r="BP3" s="27"/>
-      <c r="BQ3" s="27"/>
-      <c r="BR3" s="27"/>
-      <c r="BS3" s="27"/>
-      <c r="BT3" s="27"/>
-      <c r="BU3" s="27"/>
-      <c r="BV3" s="27"/>
-      <c r="BW3" s="27"/>
-      <c r="BX3" s="27"/>
-      <c r="BY3" s="27"/>
-      <c r="BZ3" s="27"/>
-      <c r="CA3" s="27"/>
-      <c r="CB3" s="27"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="36"/>
+      <c r="J3" s="36"/>
+      <c r="K3" s="36"/>
+      <c r="L3" s="36"/>
+      <c r="M3" s="36"/>
+      <c r="N3" s="36"/>
+      <c r="O3" s="36"/>
+      <c r="P3" s="36"/>
+      <c r="Q3" s="36"/>
+      <c r="R3" s="36"/>
+      <c r="S3" s="36"/>
+      <c r="T3" s="36"/>
+      <c r="U3" s="36"/>
+      <c r="V3" s="36"/>
+      <c r="W3" s="36"/>
+      <c r="X3" s="36"/>
+      <c r="Y3" s="36"/>
+      <c r="Z3" s="36"/>
+      <c r="AA3" s="36"/>
+      <c r="AB3" s="36"/>
+      <c r="AC3" s="36"/>
+      <c r="AD3" s="40"/>
+      <c r="AE3" s="40"/>
+      <c r="AF3" s="36"/>
+      <c r="AG3" s="36"/>
+      <c r="AH3" s="36"/>
+      <c r="AI3" s="36"/>
+      <c r="AJ3" s="36"/>
+      <c r="AK3" s="36"/>
+      <c r="AL3" s="36"/>
+      <c r="AM3" s="36"/>
+      <c r="AN3" s="36"/>
+      <c r="AO3" s="36"/>
+      <c r="AP3" s="36"/>
+      <c r="AQ3" s="36"/>
+      <c r="AR3" s="36"/>
+      <c r="AS3" s="36"/>
+      <c r="AT3" s="36"/>
+      <c r="AU3" s="36"/>
+      <c r="AV3" s="36"/>
+      <c r="AW3" s="36"/>
+      <c r="AX3" s="36"/>
+      <c r="AY3" s="36"/>
+      <c r="AZ3" s="36"/>
+      <c r="BA3" s="36"/>
+      <c r="BB3" s="36"/>
+      <c r="BC3" s="36"/>
+      <c r="BD3" s="36"/>
+      <c r="BE3" s="36"/>
+      <c r="BF3" s="36"/>
+      <c r="BG3" s="36"/>
+      <c r="BH3" s="36"/>
+      <c r="BI3" s="36"/>
+      <c r="BJ3" s="36"/>
+      <c r="BK3" s="36"/>
+      <c r="BL3" s="36"/>
+      <c r="BM3" s="36"/>
+      <c r="BN3" s="36"/>
+      <c r="BO3" s="36"/>
+      <c r="BP3" s="36"/>
+      <c r="BQ3" s="36"/>
+      <c r="BR3" s="36"/>
+      <c r="BS3" s="36"/>
+      <c r="BT3" s="36"/>
+      <c r="BU3" s="36"/>
+      <c r="BV3" s="36"/>
+      <c r="BW3" s="36"/>
+      <c r="BX3" s="36"/>
+      <c r="BY3" s="36"/>
+      <c r="BZ3" s="36"/>
+      <c r="CA3" s="36"/>
+      <c r="CB3" s="36"/>
     </row>
-    <row r="4" spans="1:85" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="37" t="s">
+    <row r="4" spans="1:85" ht="24.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="37"/>
-      <c r="C4" s="38" t="s">
+      <c r="B4" s="52"/>
+      <c r="C4" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="39"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-      <c r="J4" s="27"/>
-      <c r="K4" s="27"/>
-      <c r="L4" s="27"/>
-      <c r="M4" s="27"/>
-      <c r="N4" s="27"/>
-      <c r="O4" s="27"/>
-      <c r="P4" s="27"/>
-      <c r="Q4" s="27"/>
-      <c r="R4" s="27"/>
-      <c r="S4" s="27"/>
-      <c r="T4" s="27"/>
-      <c r="U4" s="27"/>
-      <c r="V4" s="27"/>
-      <c r="W4" s="27"/>
-      <c r="X4" s="27"/>
-      <c r="Y4" s="27"/>
-      <c r="Z4" s="27"/>
-      <c r="AA4" s="27"/>
-      <c r="AB4" s="27"/>
-      <c r="AC4" s="27"/>
-      <c r="AD4" s="54"/>
-      <c r="AE4" s="54"/>
-      <c r="AF4" s="27"/>
-      <c r="AG4" s="27"/>
-      <c r="AH4" s="27"/>
-      <c r="AI4" s="27"/>
-      <c r="AJ4" s="27"/>
-      <c r="AK4" s="27"/>
-      <c r="AL4" s="27"/>
-      <c r="AM4" s="27"/>
-      <c r="AN4" s="27"/>
-      <c r="AO4" s="27"/>
-      <c r="AP4" s="27"/>
-      <c r="AQ4" s="27"/>
-      <c r="AR4" s="27"/>
-      <c r="AS4" s="27"/>
-      <c r="AT4" s="27"/>
-      <c r="AU4" s="27"/>
-      <c r="AV4" s="27"/>
-      <c r="AW4" s="27"/>
-      <c r="AX4" s="27"/>
-      <c r="AY4" s="27"/>
-      <c r="AZ4" s="27"/>
-      <c r="BA4" s="27"/>
-      <c r="BB4" s="27"/>
-      <c r="BC4" s="27"/>
-      <c r="BD4" s="27"/>
-      <c r="BE4" s="27"/>
-      <c r="BF4" s="27"/>
-      <c r="BG4" s="27"/>
-      <c r="BH4" s="27"/>
-      <c r="BI4" s="27"/>
-      <c r="BJ4" s="27"/>
-      <c r="BK4" s="27"/>
-      <c r="BL4" s="27"/>
-      <c r="BM4" s="27"/>
-      <c r="BN4" s="27"/>
-      <c r="BO4" s="27"/>
-      <c r="BP4" s="27"/>
-      <c r="BQ4" s="27"/>
-      <c r="BR4" s="27"/>
-      <c r="BS4" s="27"/>
-      <c r="BT4" s="27"/>
-      <c r="BU4" s="27"/>
-      <c r="BV4" s="27"/>
-      <c r="BW4" s="27"/>
-      <c r="BX4" s="27"/>
-      <c r="BY4" s="27"/>
-      <c r="BZ4" s="27"/>
-      <c r="CA4" s="27"/>
-      <c r="CB4" s="27"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="36"/>
+      <c r="K4" s="36"/>
+      <c r="L4" s="36"/>
+      <c r="M4" s="36"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
+      <c r="S4" s="36"/>
+      <c r="T4" s="36"/>
+      <c r="U4" s="36"/>
+      <c r="V4" s="36"/>
+      <c r="W4" s="36"/>
+      <c r="X4" s="36"/>
+      <c r="Y4" s="36"/>
+      <c r="Z4" s="36"/>
+      <c r="AA4" s="36"/>
+      <c r="AB4" s="36"/>
+      <c r="AC4" s="36"/>
+      <c r="AD4" s="40"/>
+      <c r="AE4" s="40"/>
+      <c r="AF4" s="36"/>
+      <c r="AG4" s="36"/>
+      <c r="AH4" s="36"/>
+      <c r="AI4" s="36"/>
+      <c r="AJ4" s="36"/>
+      <c r="AK4" s="36"/>
+      <c r="AL4" s="36"/>
+      <c r="AM4" s="36"/>
+      <c r="AN4" s="36"/>
+      <c r="AO4" s="36"/>
+      <c r="AP4" s="36"/>
+      <c r="AQ4" s="36"/>
+      <c r="AR4" s="36"/>
+      <c r="AS4" s="36"/>
+      <c r="AT4" s="36"/>
+      <c r="AU4" s="36"/>
+      <c r="AV4" s="36"/>
+      <c r="AW4" s="36"/>
+      <c r="AX4" s="36"/>
+      <c r="AY4" s="36"/>
+      <c r="AZ4" s="36"/>
+      <c r="BA4" s="36"/>
+      <c r="BB4" s="36"/>
+      <c r="BC4" s="36"/>
+      <c r="BD4" s="36"/>
+      <c r="BE4" s="36"/>
+      <c r="BF4" s="36"/>
+      <c r="BG4" s="36"/>
+      <c r="BH4" s="36"/>
+      <c r="BI4" s="36"/>
+      <c r="BJ4" s="36"/>
+      <c r="BK4" s="36"/>
+      <c r="BL4" s="36"/>
+      <c r="BM4" s="36"/>
+      <c r="BN4" s="36"/>
+      <c r="BO4" s="36"/>
+      <c r="BP4" s="36"/>
+      <c r="BQ4" s="36"/>
+      <c r="BR4" s="36"/>
+      <c r="BS4" s="36"/>
+      <c r="BT4" s="36"/>
+      <c r="BU4" s="36"/>
+      <c r="BV4" s="36"/>
+      <c r="BW4" s="36"/>
+      <c r="BX4" s="36"/>
+      <c r="BY4" s="36"/>
+      <c r="BZ4" s="36"/>
+      <c r="CA4" s="36"/>
+      <c r="CB4" s="36"/>
     </row>
-    <row r="5" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="40" t="s">
+    <row r="5" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="40"/>
-      <c r="C5" s="41">
+      <c r="B5" s="42"/>
+      <c r="C5" s="38">
         <v>60</v>
       </c>
-      <c r="D5" s="42"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="27"/>
-      <c r="K5" s="27"/>
-      <c r="L5" s="27"/>
-      <c r="M5" s="27"/>
-      <c r="N5" s="27"/>
-      <c r="O5" s="27"/>
-      <c r="P5" s="27"/>
-      <c r="Q5" s="27"/>
-      <c r="R5" s="27"/>
-      <c r="S5" s="27"/>
-      <c r="T5" s="27"/>
-      <c r="U5" s="27"/>
-      <c r="V5" s="27"/>
-      <c r="W5" s="27"/>
-      <c r="X5" s="27"/>
-      <c r="Y5" s="27"/>
-      <c r="Z5" s="27"/>
-      <c r="AA5" s="27"/>
-      <c r="AB5" s="27"/>
-      <c r="AC5" s="27"/>
-      <c r="AD5" s="54"/>
-      <c r="AE5" s="54"/>
-      <c r="AF5" s="27"/>
-      <c r="AG5" s="27"/>
-      <c r="AH5" s="27"/>
-      <c r="AI5" s="27"/>
-      <c r="AJ5" s="27"/>
-      <c r="AK5" s="27"/>
-      <c r="AL5" s="27"/>
-      <c r="AM5" s="27"/>
-      <c r="AN5" s="27"/>
-      <c r="AO5" s="27"/>
-      <c r="AP5" s="27"/>
-      <c r="AQ5" s="27"/>
-      <c r="AR5" s="27"/>
-      <c r="AS5" s="27"/>
-      <c r="AT5" s="27"/>
-      <c r="AU5" s="27"/>
-      <c r="AV5" s="27"/>
-      <c r="AW5" s="27"/>
-      <c r="AX5" s="27"/>
-      <c r="AY5" s="27"/>
-      <c r="AZ5" s="27"/>
-      <c r="BA5" s="27"/>
-      <c r="BB5" s="27"/>
-      <c r="BC5" s="27"/>
-      <c r="BD5" s="27"/>
-      <c r="BE5" s="27"/>
-      <c r="BF5" s="27"/>
-      <c r="BG5" s="27"/>
-      <c r="BH5" s="27"/>
-      <c r="BI5" s="27"/>
-      <c r="BJ5" s="27"/>
-      <c r="BK5" s="27"/>
-      <c r="BL5" s="27"/>
-      <c r="BM5" s="27"/>
-      <c r="BN5" s="27"/>
-      <c r="BO5" s="27"/>
-      <c r="BP5" s="27"/>
-      <c r="BQ5" s="27"/>
-      <c r="BR5" s="27"/>
-      <c r="BS5" s="27"/>
-      <c r="BT5" s="27"/>
-      <c r="BU5" s="27"/>
-      <c r="BV5" s="27"/>
-      <c r="BW5" s="27"/>
-      <c r="BX5" s="27"/>
-      <c r="BY5" s="27"/>
-      <c r="BZ5" s="27"/>
-      <c r="CA5" s="27"/>
-      <c r="CB5" s="27"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="36"/>
+      <c r="J5" s="36"/>
+      <c r="K5" s="36"/>
+      <c r="L5" s="36"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="36"/>
+      <c r="S5" s="36"/>
+      <c r="T5" s="36"/>
+      <c r="U5" s="36"/>
+      <c r="V5" s="36"/>
+      <c r="W5" s="36"/>
+      <c r="X5" s="36"/>
+      <c r="Y5" s="36"/>
+      <c r="Z5" s="36"/>
+      <c r="AA5" s="36"/>
+      <c r="AB5" s="36"/>
+      <c r="AC5" s="36"/>
+      <c r="AD5" s="40"/>
+      <c r="AE5" s="40"/>
+      <c r="AF5" s="36"/>
+      <c r="AG5" s="36"/>
+      <c r="AH5" s="36"/>
+      <c r="AI5" s="36"/>
+      <c r="AJ5" s="36"/>
+      <c r="AK5" s="36"/>
+      <c r="AL5" s="36"/>
+      <c r="AM5" s="36"/>
+      <c r="AN5" s="36"/>
+      <c r="AO5" s="36"/>
+      <c r="AP5" s="36"/>
+      <c r="AQ5" s="36"/>
+      <c r="AR5" s="36"/>
+      <c r="AS5" s="36"/>
+      <c r="AT5" s="36"/>
+      <c r="AU5" s="36"/>
+      <c r="AV5" s="36"/>
+      <c r="AW5" s="36"/>
+      <c r="AX5" s="36"/>
+      <c r="AY5" s="36"/>
+      <c r="AZ5" s="36"/>
+      <c r="BA5" s="36"/>
+      <c r="BB5" s="36"/>
+      <c r="BC5" s="36"/>
+      <c r="BD5" s="36"/>
+      <c r="BE5" s="36"/>
+      <c r="BF5" s="36"/>
+      <c r="BG5" s="36"/>
+      <c r="BH5" s="36"/>
+      <c r="BI5" s="36"/>
+      <c r="BJ5" s="36"/>
+      <c r="BK5" s="36"/>
+      <c r="BL5" s="36"/>
+      <c r="BM5" s="36"/>
+      <c r="BN5" s="36"/>
+      <c r="BO5" s="36"/>
+      <c r="BP5" s="36"/>
+      <c r="BQ5" s="36"/>
+      <c r="BR5" s="36"/>
+      <c r="BS5" s="36"/>
+      <c r="BT5" s="36"/>
+      <c r="BU5" s="36"/>
+      <c r="BV5" s="36"/>
+      <c r="BW5" s="36"/>
+      <c r="BX5" s="36"/>
+      <c r="BY5" s="36"/>
+      <c r="BZ5" s="36"/>
+      <c r="CA5" s="36"/>
+      <c r="CB5" s="36"/>
     </row>
-    <row r="6" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="40" t="s">
+    <row r="6" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="40"/>
-      <c r="C6" s="41">
+      <c r="B6" s="42"/>
+      <c r="C6" s="38">
         <v>6</v>
       </c>
-      <c r="D6" s="42"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27"/>
-      <c r="H6" s="27"/>
-      <c r="I6" s="27"/>
-      <c r="J6" s="27"/>
-      <c r="K6" s="27"/>
-      <c r="L6" s="27"/>
-      <c r="M6" s="27"/>
-      <c r="N6" s="27"/>
-      <c r="O6" s="27"/>
-      <c r="P6" s="27"/>
-      <c r="Q6" s="27"/>
-      <c r="R6" s="27"/>
-      <c r="S6" s="27"/>
-      <c r="T6" s="27"/>
-      <c r="U6" s="27"/>
-      <c r="V6" s="27"/>
-      <c r="W6" s="27"/>
-      <c r="X6" s="27"/>
-      <c r="Y6" s="27"/>
-      <c r="Z6" s="27"/>
-      <c r="AA6" s="27"/>
-      <c r="AB6" s="27"/>
-      <c r="AC6" s="27"/>
-      <c r="AD6" s="54"/>
-      <c r="AE6" s="54"/>
-      <c r="AF6" s="27"/>
-      <c r="AG6" s="27"/>
-      <c r="AH6" s="27"/>
-      <c r="AI6" s="27"/>
-      <c r="AJ6" s="27"/>
-      <c r="AK6" s="27"/>
-      <c r="AL6" s="27"/>
-      <c r="AM6" s="27"/>
-      <c r="AN6" s="27"/>
-      <c r="AO6" s="27"/>
-      <c r="AP6" s="27"/>
-      <c r="AQ6" s="27"/>
-      <c r="AR6" s="27"/>
-      <c r="AS6" s="27"/>
-      <c r="AT6" s="27"/>
-      <c r="AU6" s="27"/>
-      <c r="AV6" s="27"/>
-      <c r="AW6" s="27"/>
-      <c r="AX6" s="27"/>
-      <c r="AY6" s="27"/>
-      <c r="AZ6" s="27"/>
-      <c r="BA6" s="27"/>
-      <c r="BB6" s="27"/>
-      <c r="BC6" s="27"/>
-      <c r="BD6" s="27"/>
-      <c r="BE6" s="27"/>
-      <c r="BF6" s="27"/>
-      <c r="BG6" s="27"/>
-      <c r="BH6" s="27"/>
-      <c r="BI6" s="27"/>
-      <c r="BJ6" s="27"/>
-      <c r="BK6" s="27"/>
-      <c r="BL6" s="27"/>
-      <c r="BM6" s="27"/>
-      <c r="BN6" s="27"/>
-      <c r="BO6" s="27"/>
-      <c r="BP6" s="27"/>
-      <c r="BQ6" s="27"/>
-      <c r="BR6" s="27"/>
-      <c r="BS6" s="27"/>
-      <c r="BT6" s="27"/>
-      <c r="BU6" s="27"/>
-      <c r="BV6" s="27"/>
-      <c r="BW6" s="27"/>
-      <c r="BX6" s="27"/>
-      <c r="BY6" s="27"/>
-      <c r="BZ6" s="27"/>
-      <c r="CA6" s="27"/>
-      <c r="CB6" s="27"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="50"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="36"/>
+      <c r="H6" s="36"/>
+      <c r="I6" s="36"/>
+      <c r="J6" s="36"/>
+      <c r="K6" s="36"/>
+      <c r="L6" s="36"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
+      <c r="S6" s="36"/>
+      <c r="T6" s="36"/>
+      <c r="U6" s="36"/>
+      <c r="V6" s="36"/>
+      <c r="W6" s="36"/>
+      <c r="X6" s="36"/>
+      <c r="Y6" s="36"/>
+      <c r="Z6" s="36"/>
+      <c r="AA6" s="36"/>
+      <c r="AB6" s="36"/>
+      <c r="AC6" s="36"/>
+      <c r="AD6" s="40"/>
+      <c r="AE6" s="40"/>
+      <c r="AF6" s="36"/>
+      <c r="AG6" s="36"/>
+      <c r="AH6" s="36"/>
+      <c r="AI6" s="36"/>
+      <c r="AJ6" s="36"/>
+      <c r="AK6" s="36"/>
+      <c r="AL6" s="36"/>
+      <c r="AM6" s="36"/>
+      <c r="AN6" s="36"/>
+      <c r="AO6" s="36"/>
+      <c r="AP6" s="36"/>
+      <c r="AQ6" s="36"/>
+      <c r="AR6" s="36"/>
+      <c r="AS6" s="36"/>
+      <c r="AT6" s="36"/>
+      <c r="AU6" s="36"/>
+      <c r="AV6" s="36"/>
+      <c r="AW6" s="36"/>
+      <c r="AX6" s="36"/>
+      <c r="AY6" s="36"/>
+      <c r="AZ6" s="36"/>
+      <c r="BA6" s="36"/>
+      <c r="BB6" s="36"/>
+      <c r="BC6" s="36"/>
+      <c r="BD6" s="36"/>
+      <c r="BE6" s="36"/>
+      <c r="BF6" s="36"/>
+      <c r="BG6" s="36"/>
+      <c r="BH6" s="36"/>
+      <c r="BI6" s="36"/>
+      <c r="BJ6" s="36"/>
+      <c r="BK6" s="36"/>
+      <c r="BL6" s="36"/>
+      <c r="BM6" s="36"/>
+      <c r="BN6" s="36"/>
+      <c r="BO6" s="36"/>
+      <c r="BP6" s="36"/>
+      <c r="BQ6" s="36"/>
+      <c r="BR6" s="36"/>
+      <c r="BS6" s="36"/>
+      <c r="BT6" s="36"/>
+      <c r="BU6" s="36"/>
+      <c r="BV6" s="36"/>
+      <c r="BW6" s="36"/>
+      <c r="BX6" s="36"/>
+      <c r="BY6" s="36"/>
+      <c r="BZ6" s="36"/>
+      <c r="CA6" s="36"/>
+      <c r="CB6" s="36"/>
     </row>
-    <row r="7" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="43" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="43"/>
-      <c r="C7" s="41">
+      <c r="C7" s="38">
         <v>9</v>
       </c>
-      <c r="D7" s="42"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="28"/>
-      <c r="J7" s="28"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="28"/>
-      <c r="M7" s="28"/>
-      <c r="N7" s="28"/>
-      <c r="O7" s="28"/>
-      <c r="P7" s="28"/>
-      <c r="Q7" s="28"/>
-      <c r="R7" s="28"/>
-      <c r="S7" s="28"/>
-      <c r="T7" s="28"/>
-      <c r="U7" s="28"/>
-      <c r="V7" s="28"/>
-      <c r="W7" s="28"/>
-      <c r="X7" s="28"/>
-      <c r="Y7" s="28"/>
-      <c r="Z7" s="28"/>
-      <c r="AA7" s="28"/>
-      <c r="AB7" s="28"/>
-      <c r="AC7" s="28"/>
-      <c r="AD7" s="55"/>
-      <c r="AE7" s="55"/>
-      <c r="AF7" s="28"/>
-      <c r="AG7" s="28"/>
-      <c r="AH7" s="28"/>
-      <c r="AI7" s="28"/>
-      <c r="AJ7" s="28"/>
-      <c r="AK7" s="28"/>
-      <c r="AL7" s="28"/>
-      <c r="AM7" s="28"/>
-      <c r="AN7" s="28"/>
-      <c r="AO7" s="28"/>
-      <c r="AP7" s="28"/>
-      <c r="AQ7" s="28"/>
-      <c r="AR7" s="28"/>
-      <c r="AS7" s="28"/>
-      <c r="AT7" s="28"/>
-      <c r="AU7" s="28"/>
-      <c r="AV7" s="28"/>
-      <c r="AW7" s="28"/>
-      <c r="AX7" s="28"/>
-      <c r="AY7" s="28"/>
-      <c r="AZ7" s="28"/>
-      <c r="BA7" s="28"/>
-      <c r="BB7" s="28"/>
-      <c r="BC7" s="28"/>
-      <c r="BD7" s="28"/>
-      <c r="BE7" s="28"/>
-      <c r="BF7" s="28"/>
-      <c r="BG7" s="28"/>
-      <c r="BH7" s="28"/>
-      <c r="BI7" s="28"/>
-      <c r="BJ7" s="28"/>
-      <c r="BK7" s="28"/>
-      <c r="BL7" s="28"/>
-      <c r="BM7" s="28"/>
-      <c r="BN7" s="28"/>
-      <c r="BO7" s="28"/>
-      <c r="BP7" s="28"/>
-      <c r="BQ7" s="28"/>
-      <c r="BR7" s="28"/>
-      <c r="BS7" s="28"/>
-      <c r="BT7" s="28"/>
-      <c r="BU7" s="28"/>
-      <c r="BV7" s="28"/>
-      <c r="BW7" s="28"/>
-      <c r="BX7" s="28"/>
-      <c r="BY7" s="28"/>
-      <c r="BZ7" s="28"/>
-      <c r="CA7" s="28"/>
-      <c r="CB7" s="28"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="51"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="37"/>
+      <c r="I7" s="37"/>
+      <c r="J7" s="37"/>
+      <c r="K7" s="37"/>
+      <c r="L7" s="37"/>
+      <c r="M7" s="37"/>
+      <c r="N7" s="37"/>
+      <c r="O7" s="37"/>
+      <c r="P7" s="37"/>
+      <c r="Q7" s="37"/>
+      <c r="R7" s="37"/>
+      <c r="S7" s="37"/>
+      <c r="T7" s="37"/>
+      <c r="U7" s="37"/>
+      <c r="V7" s="37"/>
+      <c r="W7" s="37"/>
+      <c r="X7" s="37"/>
+      <c r="Y7" s="37"/>
+      <c r="Z7" s="37"/>
+      <c r="AA7" s="37"/>
+      <c r="AB7" s="37"/>
+      <c r="AC7" s="37"/>
+      <c r="AD7" s="41"/>
+      <c r="AE7" s="41"/>
+      <c r="AF7" s="37"/>
+      <c r="AG7" s="37"/>
+      <c r="AH7" s="37"/>
+      <c r="AI7" s="37"/>
+      <c r="AJ7" s="37"/>
+      <c r="AK7" s="37"/>
+      <c r="AL7" s="37"/>
+      <c r="AM7" s="37"/>
+      <c r="AN7" s="37"/>
+      <c r="AO7" s="37"/>
+      <c r="AP7" s="37"/>
+      <c r="AQ7" s="37"/>
+      <c r="AR7" s="37"/>
+      <c r="AS7" s="37"/>
+      <c r="AT7" s="37"/>
+      <c r="AU7" s="37"/>
+      <c r="AV7" s="37"/>
+      <c r="AW7" s="37"/>
+      <c r="AX7" s="37"/>
+      <c r="AY7" s="37"/>
+      <c r="AZ7" s="37"/>
+      <c r="BA7" s="37"/>
+      <c r="BB7" s="37"/>
+      <c r="BC7" s="37"/>
+      <c r="BD7" s="37"/>
+      <c r="BE7" s="37"/>
+      <c r="BF7" s="37"/>
+      <c r="BG7" s="37"/>
+      <c r="BH7" s="37"/>
+      <c r="BI7" s="37"/>
+      <c r="BJ7" s="37"/>
+      <c r="BK7" s="37"/>
+      <c r="BL7" s="37"/>
+      <c r="BM7" s="37"/>
+      <c r="BN7" s="37"/>
+      <c r="BO7" s="37"/>
+      <c r="BP7" s="37"/>
+      <c r="BQ7" s="37"/>
+      <c r="BR7" s="37"/>
+      <c r="BS7" s="37"/>
+      <c r="BT7" s="37"/>
+      <c r="BU7" s="37"/>
+      <c r="BV7" s="37"/>
+      <c r="BW7" s="37"/>
+      <c r="BX7" s="37"/>
+      <c r="BY7" s="37"/>
+      <c r="BZ7" s="37"/>
+      <c r="CA7" s="37"/>
+      <c r="CB7" s="37"/>
     </row>
-    <row r="8" spans="1:85" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="44" t="s">
+    <row r="8" spans="1:85" ht="23.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="44"/>
-      <c r="C8" s="45">
+      <c r="B8" s="30"/>
+      <c r="C8" s="31">
         <f>SUM(C5:D7)</f>
         <v>75</v>
       </c>
-      <c r="D8" s="39"/>
+      <c r="D8" s="32"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="46">
-        <v>1</v>
-      </c>
-      <c r="G8" s="46">
+      <c r="F8" s="22">
+        <v>1</v>
+      </c>
+      <c r="G8" s="22">
         <v>2</v>
       </c>
-      <c r="H8" s="46">
+      <c r="H8" s="22">
         <v>3</v>
       </c>
-      <c r="I8" s="46">
+      <c r="I8" s="22">
         <v>4</v>
       </c>
-      <c r="J8" s="46">
+      <c r="J8" s="22">
         <v>5</v>
       </c>
-      <c r="K8" s="46">
+      <c r="K8" s="22">
         <v>6</v>
       </c>
-      <c r="L8" s="46">
+      <c r="L8" s="22">
         <v>7</v>
       </c>
-      <c r="M8" s="46">
+      <c r="M8" s="22">
         <v>8</v>
       </c>
-      <c r="N8" s="46">
+      <c r="N8" s="22">
         <v>9</v>
       </c>
-      <c r="O8" s="46">
+      <c r="O8" s="22">
         <v>10</v>
       </c>
-      <c r="P8" s="46">
+      <c r="P8" s="22">
         <v>11</v>
       </c>
-      <c r="Q8" s="46">
+      <c r="Q8" s="22">
         <v>12</v>
       </c>
-      <c r="R8" s="46">
+      <c r="R8" s="22">
         <v>13</v>
       </c>
-      <c r="S8" s="46">
+      <c r="S8" s="22">
         <v>14</v>
       </c>
-      <c r="T8" s="46">
+      <c r="T8" s="22">
         <v>15</v>
       </c>
-      <c r="U8" s="46">
+      <c r="U8" s="22">
         <v>16</v>
       </c>
-      <c r="V8" s="46">
+      <c r="V8" s="22">
         <v>17</v>
       </c>
-      <c r="W8" s="46">
+      <c r="W8" s="22">
         <v>18</v>
       </c>
-      <c r="X8" s="46">
+      <c r="X8" s="22">
         <v>19</v>
       </c>
-      <c r="Y8" s="46">
+      <c r="Y8" s="22">
         <v>20</v>
       </c>
-      <c r="Z8" s="46">
+      <c r="Z8" s="22">
         <v>21</v>
       </c>
-      <c r="AA8" s="46">
+      <c r="AA8" s="22">
         <v>22</v>
       </c>
-      <c r="AB8" s="46">
+      <c r="AB8" s="22">
         <v>23</v>
       </c>
-      <c r="AC8" s="46">
+      <c r="AC8" s="22">
         <v>24</v>
       </c>
-      <c r="AD8" s="46">
+      <c r="AD8" s="22">
         <v>25</v>
       </c>
-      <c r="AE8" s="46">
+      <c r="AE8" s="22">
         <v>26</v>
       </c>
-      <c r="AF8" s="46">
+      <c r="AF8" s="22">
         <v>27</v>
       </c>
-      <c r="AG8" s="46">
+      <c r="AG8" s="22">
         <v>28</v>
       </c>
-      <c r="AH8" s="46">
+      <c r="AH8" s="22">
         <v>29</v>
       </c>
-      <c r="AI8" s="46">
+      <c r="AI8" s="22">
         <v>30</v>
       </c>
-      <c r="AJ8" s="46">
+      <c r="AJ8" s="22">
         <v>31</v>
       </c>
-      <c r="AK8" s="46">
+      <c r="AK8" s="22">
         <v>32</v>
       </c>
-      <c r="AL8" s="46">
+      <c r="AL8" s="22">
         <v>33</v>
       </c>
-      <c r="AM8" s="46">
+      <c r="AM8" s="22">
         <v>34</v>
       </c>
-      <c r="AN8" s="46">
+      <c r="AN8" s="22">
         <v>35</v>
       </c>
-      <c r="AO8" s="46">
+      <c r="AO8" s="22">
         <v>36</v>
       </c>
-      <c r="AP8" s="46">
+      <c r="AP8" s="22">
         <v>37</v>
       </c>
-      <c r="AQ8" s="46">
+      <c r="AQ8" s="22">
         <v>38</v>
       </c>
-      <c r="AR8" s="46">
+      <c r="AR8" s="22">
         <v>39</v>
       </c>
-      <c r="AS8" s="46">
+      <c r="AS8" s="22">
         <v>40</v>
       </c>
-      <c r="AT8" s="46">
+      <c r="AT8" s="22">
         <v>41</v>
       </c>
-      <c r="AU8" s="46">
+      <c r="AU8" s="22">
         <v>42</v>
       </c>
-      <c r="AV8" s="46">
+      <c r="AV8" s="22">
         <v>43</v>
       </c>
-      <c r="AW8" s="46">
+      <c r="AW8" s="22">
         <v>44</v>
       </c>
-      <c r="AX8" s="46">
+      <c r="AX8" s="22">
         <v>45</v>
       </c>
-      <c r="AY8" s="46">
+      <c r="AY8" s="22">
         <v>46</v>
       </c>
-      <c r="AZ8" s="46">
+      <c r="AZ8" s="22">
         <v>47</v>
       </c>
-      <c r="BA8" s="46">
+      <c r="BA8" s="22">
         <v>48</v>
       </c>
-      <c r="BB8" s="46">
+      <c r="BB8" s="22">
         <v>49</v>
       </c>
-      <c r="BC8" s="46">
+      <c r="BC8" s="22">
         <v>50</v>
       </c>
-      <c r="BD8" s="46">
+      <c r="BD8" s="22">
         <v>51</v>
       </c>
-      <c r="BE8" s="46">
+      <c r="BE8" s="22">
         <v>52</v>
       </c>
-      <c r="BF8" s="46">
+      <c r="BF8" s="22">
         <v>53</v>
       </c>
-      <c r="BG8" s="46">
+      <c r="BG8" s="22">
         <v>54</v>
       </c>
-      <c r="BH8" s="46">
+      <c r="BH8" s="22">
         <v>55</v>
       </c>
-      <c r="BI8" s="46">
+      <c r="BI8" s="22">
         <v>56</v>
       </c>
-      <c r="BJ8" s="46">
+      <c r="BJ8" s="22">
         <v>57</v>
       </c>
-      <c r="BK8" s="46">
+      <c r="BK8" s="22">
         <v>58</v>
       </c>
-      <c r="BL8" s="46">
+      <c r="BL8" s="22">
         <v>59</v>
       </c>
-      <c r="BM8" s="46">
+      <c r="BM8" s="22">
         <v>60</v>
       </c>
-      <c r="BN8" s="46">
+      <c r="BN8" s="22">
         <v>61</v>
       </c>
-      <c r="BO8" s="46">
+      <c r="BO8" s="22">
         <v>62</v>
       </c>
-      <c r="BP8" s="46">
+      <c r="BP8" s="22">
         <v>63</v>
       </c>
-      <c r="BQ8" s="46">
+      <c r="BQ8" s="22">
         <v>64</v>
       </c>
-      <c r="BR8" s="46">
+      <c r="BR8" s="22">
         <v>65</v>
       </c>
-      <c r="BS8" s="46">
+      <c r="BS8" s="22">
         <v>66</v>
       </c>
-      <c r="BT8" s="46">
+      <c r="BT8" s="22">
         <v>67</v>
       </c>
-      <c r="BU8" s="46">
+      <c r="BU8" s="22">
         <v>68</v>
       </c>
-      <c r="BV8" s="46">
+      <c r="BV8" s="22">
         <v>69</v>
       </c>
-      <c r="BW8" s="46">
+      <c r="BW8" s="22">
         <v>70</v>
       </c>
-      <c r="BX8" s="46">
+      <c r="BX8" s="22">
         <v>71</v>
       </c>
-      <c r="BY8" s="46">
+      <c r="BY8" s="22">
         <v>72</v>
       </c>
-      <c r="BZ8" s="46">
+      <c r="BZ8" s="22">
         <v>73</v>
       </c>
-      <c r="CA8" s="46">
+      <c r="CA8" s="22">
         <v>74</v>
       </c>
-      <c r="CB8" s="46">
+      <c r="CB8" s="22">
         <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="48" t="s">
+      <c r="A9" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="49" t="s">
+      <c r="B9" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="50" t="s">
+      <c r="C9" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="49"/>
+      <c r="D9" s="34"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="47"/>
-      <c r="G9" s="47"/>
-      <c r="H9" s="47"/>
-      <c r="I9" s="47"/>
-      <c r="J9" s="47"/>
-      <c r="K9" s="47"/>
-      <c r="L9" s="47"/>
-      <c r="M9" s="47"/>
-      <c r="N9" s="47"/>
-      <c r="O9" s="47"/>
-      <c r="P9" s="47"/>
-      <c r="Q9" s="47"/>
-      <c r="R9" s="47"/>
-      <c r="S9" s="47"/>
-      <c r="T9" s="47"/>
-      <c r="U9" s="47"/>
-      <c r="V9" s="47"/>
-      <c r="W9" s="47"/>
-      <c r="X9" s="47"/>
-      <c r="Y9" s="47"/>
-      <c r="Z9" s="47"/>
-      <c r="AA9" s="47"/>
-      <c r="AB9" s="47"/>
-      <c r="AC9" s="47"/>
-      <c r="AD9" s="47"/>
-      <c r="AE9" s="47"/>
-      <c r="AF9" s="47"/>
-      <c r="AG9" s="47"/>
-      <c r="AH9" s="47"/>
-      <c r="AI9" s="47"/>
-      <c r="AJ9" s="47"/>
-      <c r="AK9" s="47"/>
-      <c r="AL9" s="47"/>
-      <c r="AM9" s="47"/>
-      <c r="AN9" s="47"/>
-      <c r="AO9" s="47"/>
-      <c r="AP9" s="47"/>
-      <c r="AQ9" s="47"/>
-      <c r="AR9" s="47"/>
-      <c r="AS9" s="47"/>
-      <c r="AT9" s="47"/>
-      <c r="AU9" s="47"/>
-      <c r="AV9" s="47"/>
-      <c r="AW9" s="47"/>
-      <c r="AX9" s="47"/>
-      <c r="AY9" s="47"/>
-      <c r="AZ9" s="47"/>
-      <c r="BA9" s="47"/>
-      <c r="BB9" s="47"/>
-      <c r="BC9" s="47"/>
-      <c r="BD9" s="47"/>
-      <c r="BE9" s="47"/>
-      <c r="BF9" s="47"/>
-      <c r="BG9" s="47"/>
-      <c r="BH9" s="47"/>
-      <c r="BI9" s="47"/>
-      <c r="BJ9" s="47"/>
-      <c r="BK9" s="47"/>
-      <c r="BL9" s="47"/>
-      <c r="BM9" s="47"/>
-      <c r="BN9" s="47"/>
-      <c r="BO9" s="47"/>
-      <c r="BP9" s="47"/>
-      <c r="BQ9" s="47"/>
-      <c r="BR9" s="47"/>
-      <c r="BS9" s="47"/>
-      <c r="BT9" s="47"/>
-      <c r="BU9" s="47"/>
-      <c r="BV9" s="47"/>
-      <c r="BW9" s="47"/>
-      <c r="BX9" s="47"/>
-      <c r="BY9" s="47"/>
-      <c r="BZ9" s="47"/>
-      <c r="CA9" s="47"/>
-      <c r="CB9" s="47"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="23"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="23"/>
+      <c r="K9" s="23"/>
+      <c r="L9" s="23"/>
+      <c r="M9" s="23"/>
+      <c r="N9" s="23"/>
+      <c r="O9" s="23"/>
+      <c r="P9" s="23"/>
+      <c r="Q9" s="23"/>
+      <c r="R9" s="23"/>
+      <c r="S9" s="23"/>
+      <c r="T9" s="23"/>
+      <c r="U9" s="23"/>
+      <c r="V9" s="23"/>
+      <c r="W9" s="23"/>
+      <c r="X9" s="23"/>
+      <c r="Y9" s="23"/>
+      <c r="Z9" s="23"/>
+      <c r="AA9" s="23"/>
+      <c r="AB9" s="23"/>
+      <c r="AC9" s="23"/>
+      <c r="AD9" s="23"/>
+      <c r="AE9" s="23"/>
+      <c r="AF9" s="23"/>
+      <c r="AG9" s="23"/>
+      <c r="AH9" s="23"/>
+      <c r="AI9" s="23"/>
+      <c r="AJ9" s="23"/>
+      <c r="AK9" s="23"/>
+      <c r="AL9" s="23"/>
+      <c r="AM9" s="23"/>
+      <c r="AN9" s="23"/>
+      <c r="AO9" s="23"/>
+      <c r="AP9" s="23"/>
+      <c r="AQ9" s="23"/>
+      <c r="AR9" s="23"/>
+      <c r="AS9" s="23"/>
+      <c r="AT9" s="23"/>
+      <c r="AU9" s="23"/>
+      <c r="AV9" s="23"/>
+      <c r="AW9" s="23"/>
+      <c r="AX9" s="23"/>
+      <c r="AY9" s="23"/>
+      <c r="AZ9" s="23"/>
+      <c r="BA9" s="23"/>
+      <c r="BB9" s="23"/>
+      <c r="BC9" s="23"/>
+      <c r="BD9" s="23"/>
+      <c r="BE9" s="23"/>
+      <c r="BF9" s="23"/>
+      <c r="BG9" s="23"/>
+      <c r="BH9" s="23"/>
+      <c r="BI9" s="23"/>
+      <c r="BJ9" s="23"/>
+      <c r="BK9" s="23"/>
+      <c r="BL9" s="23"/>
+      <c r="BM9" s="23"/>
+      <c r="BN9" s="23"/>
+      <c r="BO9" s="23"/>
+      <c r="BP9" s="23"/>
+      <c r="BQ9" s="23"/>
+      <c r="BR9" s="23"/>
+      <c r="BS9" s="23"/>
+      <c r="BT9" s="23"/>
+      <c r="BU9" s="23"/>
+      <c r="BV9" s="23"/>
+      <c r="BW9" s="23"/>
+      <c r="BX9" s="23"/>
+      <c r="BY9" s="23"/>
+      <c r="BZ9" s="23"/>
+      <c r="CA9" s="23"/>
+      <c r="CB9" s="23"/>
     </row>
     <row r="10" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="48"/>
-      <c r="B10" s="49"/>
+      <c r="A10" s="33"/>
+      <c r="B10" s="34"/>
       <c r="C10" s="6"/>
       <c r="D10" s="4" t="s">
         <v>12</v>
@@ -2375,7 +2366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="9">
         <v>1</v>
       </c>
@@ -2470,7 +2461,7 @@
       <c r="CA11" s="8"/>
       <c r="CB11" s="8"/>
     </row>
-    <row r="12" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9">
         <v>2</v>
       </c>
@@ -2561,7 +2552,7 @@
       <c r="CA12" s="8"/>
       <c r="CB12" s="8"/>
     </row>
-    <row r="13" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="9">
         <v>3</v>
       </c>
@@ -2682,7 +2673,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="9">
         <v>4</v>
       </c>
@@ -2817,7 +2808,7 @@
       <c r="CA14" s="8"/>
       <c r="CB14" s="8"/>
     </row>
-    <row r="15" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="9">
         <v>5</v>
       </c>
@@ -2950,7 +2941,7 @@
       <c r="CA15" s="8"/>
       <c r="CB15" s="8"/>
     </row>
-    <row r="16" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:85" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9">
         <v>6</v>
       </c>
@@ -3053,7 +3044,7 @@
       <c r="CA16" s="8"/>
       <c r="CB16" s="8"/>
     </row>
-    <row r="17" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="9">
         <v>7</v>
       </c>
@@ -3101,74 +3092,74 @@
       <c r="P17" s="8">
         <v>0</v>
       </c>
-      <c r="Q17" s="24" t="s">
+      <c r="Q17" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="R17" s="25"/>
-      <c r="S17" s="25"/>
-      <c r="T17" s="25"/>
-      <c r="U17" s="25"/>
-      <c r="V17" s="25"/>
-      <c r="W17" s="25"/>
-      <c r="X17" s="25"/>
-      <c r="Y17" s="25"/>
-      <c r="Z17" s="25"/>
-      <c r="AA17" s="25"/>
-      <c r="AB17" s="25"/>
-      <c r="AC17" s="25"/>
-      <c r="AD17" s="25"/>
-      <c r="AE17" s="25"/>
-      <c r="AF17" s="25"/>
-      <c r="AG17" s="25"/>
-      <c r="AH17" s="25"/>
-      <c r="AI17" s="25"/>
-      <c r="AJ17" s="25"/>
-      <c r="AK17" s="25"/>
-      <c r="AL17" s="25"/>
-      <c r="AM17" s="25"/>
-      <c r="AN17" s="25"/>
-      <c r="AO17" s="25"/>
-      <c r="AP17" s="25"/>
-      <c r="AQ17" s="25"/>
-      <c r="AR17" s="25"/>
-      <c r="AS17" s="25"/>
-      <c r="AT17" s="25"/>
-      <c r="AU17" s="25"/>
-      <c r="AV17" s="25"/>
-      <c r="AW17" s="25"/>
-      <c r="AX17" s="25"/>
-      <c r="AY17" s="25"/>
-      <c r="AZ17" s="25"/>
-      <c r="BA17" s="25"/>
-      <c r="BB17" s="25"/>
-      <c r="BC17" s="25"/>
-      <c r="BD17" s="25"/>
-      <c r="BE17" s="25"/>
-      <c r="BF17" s="25"/>
-      <c r="BG17" s="25"/>
-      <c r="BH17" s="25"/>
-      <c r="BI17" s="25"/>
-      <c r="BJ17" s="25"/>
-      <c r="BK17" s="25"/>
-      <c r="BL17" s="25"/>
-      <c r="BM17" s="25"/>
-      <c r="BN17" s="25"/>
-      <c r="BO17" s="25"/>
-      <c r="BP17" s="25"/>
-      <c r="BQ17" s="25"/>
-      <c r="BR17" s="25"/>
-      <c r="BS17" s="25"/>
-      <c r="BT17" s="25"/>
-      <c r="BU17" s="25"/>
-      <c r="BV17" s="25"/>
-      <c r="BW17" s="25"/>
-      <c r="BX17" s="25"/>
-      <c r="BY17" s="25"/>
-      <c r="BZ17" s="25"/>
-      <c r="CA17" s="25"/>
-      <c r="CB17" s="26"/>
+      <c r="R17" s="28"/>
+      <c r="S17" s="28"/>
+      <c r="T17" s="28"/>
+      <c r="U17" s="28"/>
+      <c r="V17" s="28"/>
+      <c r="W17" s="28"/>
+      <c r="X17" s="28"/>
+      <c r="Y17" s="28"/>
+      <c r="Z17" s="28"/>
+      <c r="AA17" s="28"/>
+      <c r="AB17" s="28"/>
+      <c r="AC17" s="28"/>
+      <c r="AD17" s="28"/>
+      <c r="AE17" s="28"/>
+      <c r="AF17" s="28"/>
+      <c r="AG17" s="28"/>
+      <c r="AH17" s="28"/>
+      <c r="AI17" s="28"/>
+      <c r="AJ17" s="28"/>
+      <c r="AK17" s="28"/>
+      <c r="AL17" s="28"/>
+      <c r="AM17" s="28"/>
+      <c r="AN17" s="28"/>
+      <c r="AO17" s="28"/>
+      <c r="AP17" s="28"/>
+      <c r="AQ17" s="28"/>
+      <c r="AR17" s="28"/>
+      <c r="AS17" s="28"/>
+      <c r="AT17" s="28"/>
+      <c r="AU17" s="28"/>
+      <c r="AV17" s="28"/>
+      <c r="AW17" s="28"/>
+      <c r="AX17" s="28"/>
+      <c r="AY17" s="28"/>
+      <c r="AZ17" s="28"/>
+      <c r="BA17" s="28"/>
+      <c r="BB17" s="28"/>
+      <c r="BC17" s="28"/>
+      <c r="BD17" s="28"/>
+      <c r="BE17" s="28"/>
+      <c r="BF17" s="28"/>
+      <c r="BG17" s="28"/>
+      <c r="BH17" s="28"/>
+      <c r="BI17" s="28"/>
+      <c r="BJ17" s="28"/>
+      <c r="BK17" s="28"/>
+      <c r="BL17" s="28"/>
+      <c r="BM17" s="28"/>
+      <c r="BN17" s="28"/>
+      <c r="BO17" s="28"/>
+      <c r="BP17" s="28"/>
+      <c r="BQ17" s="28"/>
+      <c r="BR17" s="28"/>
+      <c r="BS17" s="28"/>
+      <c r="BT17" s="28"/>
+      <c r="BU17" s="28"/>
+      <c r="BV17" s="28"/>
+      <c r="BW17" s="28"/>
+      <c r="BX17" s="28"/>
+      <c r="BY17" s="28"/>
+      <c r="BZ17" s="28"/>
+      <c r="CA17" s="28"/>
+      <c r="CB17" s="29"/>
     </row>
-    <row r="18" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9">
         <v>8</v>
       </c>
@@ -3275,7 +3266,7 @@
       <c r="CA18" s="8"/>
       <c r="CB18" s="8"/>
     </row>
-    <row r="19" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9">
         <v>9</v>
       </c>
@@ -3392,7 +3383,7 @@
       <c r="CA19" s="8"/>
       <c r="CB19" s="8"/>
     </row>
-    <row r="20" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9">
         <v>10</v>
       </c>
@@ -3505,7 +3496,7 @@
       <c r="CA20" s="8"/>
       <c r="CB20" s="8"/>
     </row>
-    <row r="21" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="9">
         <v>11</v>
       </c>
@@ -3598,59 +3589,59 @@
       <c r="AE21" s="8">
         <v>0</v>
       </c>
-      <c r="AF21" s="24" t="s">
+      <c r="AF21" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="AG21" s="25"/>
-      <c r="AH21" s="25"/>
-      <c r="AI21" s="25"/>
-      <c r="AJ21" s="25"/>
-      <c r="AK21" s="25"/>
-      <c r="AL21" s="25"/>
-      <c r="AM21" s="25"/>
-      <c r="AN21" s="25"/>
-      <c r="AO21" s="25"/>
-      <c r="AP21" s="25"/>
-      <c r="AQ21" s="25"/>
-      <c r="AR21" s="25"/>
-      <c r="AS21" s="25"/>
-      <c r="AT21" s="25"/>
-      <c r="AU21" s="25"/>
-      <c r="AV21" s="25"/>
-      <c r="AW21" s="25"/>
-      <c r="AX21" s="25"/>
-      <c r="AY21" s="25"/>
-      <c r="AZ21" s="25"/>
-      <c r="BA21" s="25"/>
-      <c r="BB21" s="25"/>
-      <c r="BC21" s="25"/>
-      <c r="BD21" s="25"/>
-      <c r="BE21" s="25"/>
-      <c r="BF21" s="25"/>
-      <c r="BG21" s="25"/>
-      <c r="BH21" s="25"/>
-      <c r="BI21" s="25"/>
-      <c r="BJ21" s="25"/>
-      <c r="BK21" s="25"/>
-      <c r="BL21" s="25"/>
-      <c r="BM21" s="25"/>
-      <c r="BN21" s="25"/>
-      <c r="BO21" s="25"/>
-      <c r="BP21" s="25"/>
-      <c r="BQ21" s="25"/>
-      <c r="BR21" s="25"/>
-      <c r="BS21" s="25"/>
-      <c r="BT21" s="25"/>
-      <c r="BU21" s="25"/>
-      <c r="BV21" s="25"/>
-      <c r="BW21" s="25"/>
-      <c r="BX21" s="25"/>
-      <c r="BY21" s="25"/>
-      <c r="BZ21" s="25"/>
-      <c r="CA21" s="25"/>
-      <c r="CB21" s="26"/>
+      <c r="AG21" s="28"/>
+      <c r="AH21" s="28"/>
+      <c r="AI21" s="28"/>
+      <c r="AJ21" s="28"/>
+      <c r="AK21" s="28"/>
+      <c r="AL21" s="28"/>
+      <c r="AM21" s="28"/>
+      <c r="AN21" s="28"/>
+      <c r="AO21" s="28"/>
+      <c r="AP21" s="28"/>
+      <c r="AQ21" s="28"/>
+      <c r="AR21" s="28"/>
+      <c r="AS21" s="28"/>
+      <c r="AT21" s="28"/>
+      <c r="AU21" s="28"/>
+      <c r="AV21" s="28"/>
+      <c r="AW21" s="28"/>
+      <c r="AX21" s="28"/>
+      <c r="AY21" s="28"/>
+      <c r="AZ21" s="28"/>
+      <c r="BA21" s="28"/>
+      <c r="BB21" s="28"/>
+      <c r="BC21" s="28"/>
+      <c r="BD21" s="28"/>
+      <c r="BE21" s="28"/>
+      <c r="BF21" s="28"/>
+      <c r="BG21" s="28"/>
+      <c r="BH21" s="28"/>
+      <c r="BI21" s="28"/>
+      <c r="BJ21" s="28"/>
+      <c r="BK21" s="28"/>
+      <c r="BL21" s="28"/>
+      <c r="BM21" s="28"/>
+      <c r="BN21" s="28"/>
+      <c r="BO21" s="28"/>
+      <c r="BP21" s="28"/>
+      <c r="BQ21" s="28"/>
+      <c r="BR21" s="28"/>
+      <c r="BS21" s="28"/>
+      <c r="BT21" s="28"/>
+      <c r="BU21" s="28"/>
+      <c r="BV21" s="28"/>
+      <c r="BW21" s="28"/>
+      <c r="BX21" s="28"/>
+      <c r="BY21" s="28"/>
+      <c r="BZ21" s="28"/>
+      <c r="CA21" s="28"/>
+      <c r="CB21" s="29"/>
     </row>
-    <row r="22" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="9">
         <v>12</v>
       </c>
@@ -3753,7 +3744,7 @@
       <c r="CA22" s="8"/>
       <c r="CB22" s="8"/>
     </row>
-    <row r="23" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="9">
         <v>13</v>
       </c>
@@ -3846,59 +3837,59 @@
       <c r="AE23" s="8">
         <v>0</v>
       </c>
-      <c r="AF23" s="24" t="s">
+      <c r="AF23" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="AG23" s="25"/>
-      <c r="AH23" s="25"/>
-      <c r="AI23" s="25"/>
-      <c r="AJ23" s="25"/>
-      <c r="AK23" s="25"/>
-      <c r="AL23" s="25"/>
-      <c r="AM23" s="25"/>
-      <c r="AN23" s="25"/>
-      <c r="AO23" s="25"/>
-      <c r="AP23" s="25"/>
-      <c r="AQ23" s="25"/>
-      <c r="AR23" s="25"/>
-      <c r="AS23" s="25"/>
-      <c r="AT23" s="25"/>
-      <c r="AU23" s="25"/>
-      <c r="AV23" s="25"/>
-      <c r="AW23" s="25"/>
-      <c r="AX23" s="25"/>
-      <c r="AY23" s="25"/>
-      <c r="AZ23" s="25"/>
-      <c r="BA23" s="25"/>
-      <c r="BB23" s="25"/>
-      <c r="BC23" s="25"/>
-      <c r="BD23" s="25"/>
-      <c r="BE23" s="25"/>
-      <c r="BF23" s="25"/>
-      <c r="BG23" s="25"/>
-      <c r="BH23" s="25"/>
-      <c r="BI23" s="25"/>
-      <c r="BJ23" s="25"/>
-      <c r="BK23" s="25"/>
-      <c r="BL23" s="25"/>
-      <c r="BM23" s="25"/>
-      <c r="BN23" s="25"/>
-      <c r="BO23" s="25"/>
-      <c r="BP23" s="25"/>
-      <c r="BQ23" s="25"/>
-      <c r="BR23" s="25"/>
-      <c r="BS23" s="25"/>
-      <c r="BT23" s="25"/>
-      <c r="BU23" s="25"/>
-      <c r="BV23" s="25"/>
-      <c r="BW23" s="25"/>
-      <c r="BX23" s="25"/>
-      <c r="BY23" s="25"/>
-      <c r="BZ23" s="25"/>
-      <c r="CA23" s="25"/>
-      <c r="CB23" s="26"/>
+      <c r="AG23" s="28"/>
+      <c r="AH23" s="28"/>
+      <c r="AI23" s="28"/>
+      <c r="AJ23" s="28"/>
+      <c r="AK23" s="28"/>
+      <c r="AL23" s="28"/>
+      <c r="AM23" s="28"/>
+      <c r="AN23" s="28"/>
+      <c r="AO23" s="28"/>
+      <c r="AP23" s="28"/>
+      <c r="AQ23" s="28"/>
+      <c r="AR23" s="28"/>
+      <c r="AS23" s="28"/>
+      <c r="AT23" s="28"/>
+      <c r="AU23" s="28"/>
+      <c r="AV23" s="28"/>
+      <c r="AW23" s="28"/>
+      <c r="AX23" s="28"/>
+      <c r="AY23" s="28"/>
+      <c r="AZ23" s="28"/>
+      <c r="BA23" s="28"/>
+      <c r="BB23" s="28"/>
+      <c r="BC23" s="28"/>
+      <c r="BD23" s="28"/>
+      <c r="BE23" s="28"/>
+      <c r="BF23" s="28"/>
+      <c r="BG23" s="28"/>
+      <c r="BH23" s="28"/>
+      <c r="BI23" s="28"/>
+      <c r="BJ23" s="28"/>
+      <c r="BK23" s="28"/>
+      <c r="BL23" s="28"/>
+      <c r="BM23" s="28"/>
+      <c r="BN23" s="28"/>
+      <c r="BO23" s="28"/>
+      <c r="BP23" s="28"/>
+      <c r="BQ23" s="28"/>
+      <c r="BR23" s="28"/>
+      <c r="BS23" s="28"/>
+      <c r="BT23" s="28"/>
+      <c r="BU23" s="28"/>
+      <c r="BV23" s="28"/>
+      <c r="BW23" s="28"/>
+      <c r="BX23" s="28"/>
+      <c r="BY23" s="28"/>
+      <c r="BZ23" s="28"/>
+      <c r="CA23" s="28"/>
+      <c r="CB23" s="29"/>
     </row>
-    <row r="24" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="9">
         <v>14</v>
       </c>
@@ -4017,7 +4008,7 @@
       <c r="CA24" s="8"/>
       <c r="CB24" s="8"/>
     </row>
-    <row r="25" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="9">
         <v>15</v>
       </c>
@@ -4152,7 +4143,7 @@
       <c r="CA25" s="8"/>
       <c r="CB25" s="8"/>
     </row>
-    <row r="26" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="9">
         <v>16</v>
       </c>
@@ -4291,7 +4282,7 @@
       <c r="CA26" s="8"/>
       <c r="CB26" s="8"/>
     </row>
-    <row r="27" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="9">
         <v>17</v>
       </c>
@@ -4448,7 +4439,7 @@
       <c r="CA27" s="8"/>
       <c r="CB27" s="8"/>
     </row>
-    <row r="28" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:80" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="9">
         <v>18</v>
       </c>
@@ -4462,87 +4453,244 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E28" s="51" t="s">
+      <c r="E28" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="F28" s="51"/>
-      <c r="G28" s="51"/>
-      <c r="H28" s="51"/>
-      <c r="I28" s="51"/>
-      <c r="J28" s="51"/>
-      <c r="K28" s="51"/>
-      <c r="L28" s="51"/>
-      <c r="M28" s="51"/>
-      <c r="N28" s="51"/>
-      <c r="O28" s="51"/>
-      <c r="P28" s="51"/>
-      <c r="Q28" s="51"/>
-      <c r="R28" s="51"/>
-      <c r="S28" s="51"/>
-      <c r="T28" s="51"/>
-      <c r="U28" s="51"/>
-      <c r="V28" s="51"/>
-      <c r="W28" s="51"/>
-      <c r="X28" s="51"/>
-      <c r="Y28" s="51"/>
-      <c r="Z28" s="51"/>
-      <c r="AA28" s="51"/>
-      <c r="AB28" s="51"/>
-      <c r="AC28" s="51"/>
-      <c r="AD28" s="51"/>
-      <c r="AE28" s="51"/>
-      <c r="AF28" s="51"/>
-      <c r="AG28" s="51"/>
-      <c r="AH28" s="51"/>
-      <c r="AI28" s="51"/>
-      <c r="AJ28" s="51"/>
-      <c r="AK28" s="51"/>
-      <c r="AL28" s="51"/>
-      <c r="AM28" s="51"/>
-      <c r="AN28" s="51"/>
-      <c r="AO28" s="51"/>
-      <c r="AP28" s="51"/>
-      <c r="AQ28" s="51"/>
-      <c r="AR28" s="51"/>
-      <c r="AS28" s="51"/>
-      <c r="AT28" s="51"/>
-      <c r="AU28" s="51"/>
-      <c r="AV28" s="51"/>
-      <c r="AW28" s="51"/>
-      <c r="AX28" s="51"/>
-      <c r="AY28" s="51"/>
-      <c r="AZ28" s="51"/>
-      <c r="BA28" s="51"/>
-      <c r="BB28" s="51"/>
-      <c r="BC28" s="51"/>
-      <c r="BD28" s="51"/>
-      <c r="BE28" s="51"/>
-      <c r="BF28" s="51"/>
-      <c r="BG28" s="51"/>
-      <c r="BH28" s="51"/>
-      <c r="BI28" s="51"/>
-      <c r="BJ28" s="51"/>
-      <c r="BK28" s="51"/>
-      <c r="BL28" s="51"/>
-      <c r="BM28" s="51"/>
-      <c r="BN28" s="51"/>
-      <c r="BO28" s="51"/>
-      <c r="BP28" s="51"/>
-      <c r="BQ28" s="51"/>
-      <c r="BR28" s="51"/>
-      <c r="BS28" s="51"/>
-      <c r="BT28" s="51"/>
-      <c r="BU28" s="51"/>
-      <c r="BV28" s="51"/>
-      <c r="BW28" s="51"/>
-      <c r="BX28" s="51"/>
-      <c r="BY28" s="51"/>
-      <c r="BZ28" s="51"/>
-      <c r="CA28" s="51"/>
-      <c r="CB28" s="51"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="19"/>
+      <c r="Q28" s="19"/>
+      <c r="R28" s="19"/>
+      <c r="S28" s="19"/>
+      <c r="T28" s="19"/>
+      <c r="U28" s="19"/>
+      <c r="V28" s="19"/>
+      <c r="W28" s="19"/>
+      <c r="X28" s="19"/>
+      <c r="Y28" s="19"/>
+      <c r="Z28" s="19"/>
+      <c r="AA28" s="19"/>
+      <c r="AB28" s="19"/>
+      <c r="AC28" s="19"/>
+      <c r="AD28" s="19"/>
+      <c r="AE28" s="19"/>
+      <c r="AF28" s="19"/>
+      <c r="AG28" s="19"/>
+      <c r="AH28" s="19"/>
+      <c r="AI28" s="19"/>
+      <c r="AJ28" s="19"/>
+      <c r="AK28" s="19"/>
+      <c r="AL28" s="19"/>
+      <c r="AM28" s="19"/>
+      <c r="AN28" s="19"/>
+      <c r="AO28" s="19"/>
+      <c r="AP28" s="19"/>
+      <c r="AQ28" s="19"/>
+      <c r="AR28" s="19"/>
+      <c r="AS28" s="19"/>
+      <c r="AT28" s="19"/>
+      <c r="AU28" s="19"/>
+      <c r="AV28" s="19"/>
+      <c r="AW28" s="19"/>
+      <c r="AX28" s="19"/>
+      <c r="AY28" s="19"/>
+      <c r="AZ28" s="19"/>
+      <c r="BA28" s="19"/>
+      <c r="BB28" s="19"/>
+      <c r="BC28" s="19"/>
+      <c r="BD28" s="19"/>
+      <c r="BE28" s="19"/>
+      <c r="BF28" s="19"/>
+      <c r="BG28" s="19"/>
+      <c r="BH28" s="19"/>
+      <c r="BI28" s="19"/>
+      <c r="BJ28" s="19"/>
+      <c r="BK28" s="19"/>
+      <c r="BL28" s="19"/>
+      <c r="BM28" s="19"/>
+      <c r="BN28" s="19"/>
+      <c r="BO28" s="19"/>
+      <c r="BP28" s="19"/>
+      <c r="BQ28" s="19"/>
+      <c r="BR28" s="19"/>
+      <c r="BS28" s="19"/>
+      <c r="BT28" s="19"/>
+      <c r="BU28" s="19"/>
+      <c r="BV28" s="19"/>
+      <c r="BW28" s="19"/>
+      <c r="BX28" s="19"/>
+      <c r="BY28" s="19"/>
+      <c r="BZ28" s="19"/>
+      <c r="CA28" s="19"/>
+      <c r="CB28" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="180">
+  <mergeCells count="181">
+    <mergeCell ref="AS1:AX1"/>
+    <mergeCell ref="AQ1:AR1"/>
+    <mergeCell ref="AF1:AJ1"/>
+    <mergeCell ref="AF21:CB21"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="W2:W7"/>
+    <mergeCell ref="X2:X7"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:D2"/>
+    <mergeCell ref="Y2:Y7"/>
+    <mergeCell ref="Z2:Z7"/>
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="F2:F7"/>
+    <mergeCell ref="G2:G7"/>
+    <mergeCell ref="H2:H7"/>
+    <mergeCell ref="I2:I7"/>
+    <mergeCell ref="J2:J7"/>
+    <mergeCell ref="K2:K7"/>
+    <mergeCell ref="L2:L7"/>
+    <mergeCell ref="M2:M7"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="V1:Z1"/>
+    <mergeCell ref="L1:P1"/>
+    <mergeCell ref="AA2:AA7"/>
+    <mergeCell ref="N2:N7"/>
+    <mergeCell ref="O2:O7"/>
+    <mergeCell ref="P2:P7"/>
+    <mergeCell ref="Q2:Q7"/>
+    <mergeCell ref="R2:R7"/>
+    <mergeCell ref="S2:S7"/>
+    <mergeCell ref="T2:T7"/>
+    <mergeCell ref="U2:U7"/>
+    <mergeCell ref="V2:V7"/>
+    <mergeCell ref="Q1:U1"/>
+    <mergeCell ref="AA1:AE1"/>
+    <mergeCell ref="AG2:AG7"/>
+    <mergeCell ref="AD2:AD7"/>
+    <mergeCell ref="AE2:AE7"/>
+    <mergeCell ref="AF2:AF7"/>
+    <mergeCell ref="AB2:AB7"/>
+    <mergeCell ref="AC2:AC7"/>
+    <mergeCell ref="AH2:AH7"/>
+    <mergeCell ref="AI2:AI7"/>
+    <mergeCell ref="AJ2:AJ7"/>
+    <mergeCell ref="AK2:AK7"/>
+    <mergeCell ref="AL2:AL7"/>
+    <mergeCell ref="AM2:AM7"/>
+    <mergeCell ref="AN2:AN7"/>
+    <mergeCell ref="AO2:AO7"/>
+    <mergeCell ref="AP2:AP7"/>
+    <mergeCell ref="AQ2:AQ7"/>
+    <mergeCell ref="AR2:AR7"/>
+    <mergeCell ref="AS2:AS7"/>
+    <mergeCell ref="BH2:BH7"/>
+    <mergeCell ref="BI2:BI7"/>
+    <mergeCell ref="BJ2:BJ7"/>
+    <mergeCell ref="BK2:BK7"/>
+    <mergeCell ref="AT2:AT7"/>
+    <mergeCell ref="AU2:AU7"/>
+    <mergeCell ref="AV2:AV7"/>
+    <mergeCell ref="AW2:AW7"/>
+    <mergeCell ref="AX2:AX7"/>
+    <mergeCell ref="AY2:AY7"/>
+    <mergeCell ref="AZ2:AZ7"/>
+    <mergeCell ref="BA2:BA7"/>
+    <mergeCell ref="BB2:BB7"/>
+    <mergeCell ref="BU2:BU7"/>
+    <mergeCell ref="BV2:BV7"/>
+    <mergeCell ref="BW2:BW7"/>
+    <mergeCell ref="BX2:BX7"/>
+    <mergeCell ref="BY2:BY7"/>
+    <mergeCell ref="BZ2:BZ7"/>
+    <mergeCell ref="CA2:CA7"/>
+    <mergeCell ref="CB2:CB7"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="BL2:BL7"/>
+    <mergeCell ref="BM2:BM7"/>
+    <mergeCell ref="BN2:BN7"/>
+    <mergeCell ref="BO2:BO7"/>
+    <mergeCell ref="BP2:BP7"/>
+    <mergeCell ref="BQ2:BQ7"/>
+    <mergeCell ref="BR2:BR7"/>
+    <mergeCell ref="BS2:BS7"/>
+    <mergeCell ref="BT2:BT7"/>
+    <mergeCell ref="BC2:BC7"/>
+    <mergeCell ref="BD2:BD7"/>
+    <mergeCell ref="BE2:BE7"/>
+    <mergeCell ref="BF2:BF7"/>
+    <mergeCell ref="BG2:BG7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="AG8:AG9"/>
+    <mergeCell ref="AH8:AH9"/>
+    <mergeCell ref="AI8:AI9"/>
+    <mergeCell ref="AJ8:AJ9"/>
+    <mergeCell ref="AK8:AK9"/>
+    <mergeCell ref="AL8:AL9"/>
+    <mergeCell ref="AM8:AM9"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="W8:W9"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="Z8:Z9"/>
+    <mergeCell ref="AA8:AA9"/>
+    <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="AC8:AC9"/>
+    <mergeCell ref="AD8:AD9"/>
+    <mergeCell ref="AF23:CB23"/>
+    <mergeCell ref="Q17:CB17"/>
+    <mergeCell ref="BX8:BX9"/>
+    <mergeCell ref="BY8:BY9"/>
+    <mergeCell ref="BZ8:BZ9"/>
+    <mergeCell ref="CA8:CA9"/>
+    <mergeCell ref="CB8:CB9"/>
+    <mergeCell ref="BO8:BO9"/>
+    <mergeCell ref="BP8:BP9"/>
+    <mergeCell ref="BQ8:BQ9"/>
+    <mergeCell ref="BR8:BR9"/>
+    <mergeCell ref="BS8:BS9"/>
+    <mergeCell ref="BT8:BT9"/>
+    <mergeCell ref="BF8:BF9"/>
+    <mergeCell ref="BG8:BG9"/>
+    <mergeCell ref="BH8:BH9"/>
+    <mergeCell ref="BI8:BI9"/>
+    <mergeCell ref="BJ8:BJ9"/>
+    <mergeCell ref="BK8:BK9"/>
+    <mergeCell ref="BL8:BL9"/>
+    <mergeCell ref="BM8:BM9"/>
+    <mergeCell ref="BN8:BN9"/>
+    <mergeCell ref="AE8:AE9"/>
+    <mergeCell ref="AF8:AF9"/>
     <mergeCell ref="E28:CB28"/>
     <mergeCell ref="F1:I1"/>
     <mergeCell ref="BU8:BU9"/>
@@ -4567,162 +4715,6 @@
     <mergeCell ref="AZ8:AZ9"/>
     <mergeCell ref="BA8:BA9"/>
     <mergeCell ref="BB8:BB9"/>
-    <mergeCell ref="AF23:CB23"/>
-    <mergeCell ref="Q17:CB17"/>
-    <mergeCell ref="BX8:BX9"/>
-    <mergeCell ref="BY8:BY9"/>
-    <mergeCell ref="BZ8:BZ9"/>
-    <mergeCell ref="CA8:CA9"/>
-    <mergeCell ref="CB8:CB9"/>
-    <mergeCell ref="BO8:BO9"/>
-    <mergeCell ref="BP8:BP9"/>
-    <mergeCell ref="BQ8:BQ9"/>
-    <mergeCell ref="BR8:BR9"/>
-    <mergeCell ref="BS8:BS9"/>
-    <mergeCell ref="BT8:BT9"/>
-    <mergeCell ref="BF8:BF9"/>
-    <mergeCell ref="BG8:BG9"/>
-    <mergeCell ref="BH8:BH9"/>
-    <mergeCell ref="BI8:BI9"/>
-    <mergeCell ref="BJ8:BJ9"/>
-    <mergeCell ref="BK8:BK9"/>
-    <mergeCell ref="BL8:BL9"/>
-    <mergeCell ref="BM8:BM9"/>
-    <mergeCell ref="BN8:BN9"/>
-    <mergeCell ref="AE8:AE9"/>
-    <mergeCell ref="AF8:AF9"/>
-    <mergeCell ref="AG8:AG9"/>
-    <mergeCell ref="AH8:AH9"/>
-    <mergeCell ref="AI8:AI9"/>
-    <mergeCell ref="AJ8:AJ9"/>
-    <mergeCell ref="AK8:AK9"/>
-    <mergeCell ref="AL8:AL9"/>
-    <mergeCell ref="AM8:AM9"/>
-    <mergeCell ref="V8:V9"/>
-    <mergeCell ref="W8:W9"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="AC8:AC9"/>
-    <mergeCell ref="AD8:AD9"/>
-    <mergeCell ref="M8:M9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="BU2:BU7"/>
-    <mergeCell ref="BV2:BV7"/>
-    <mergeCell ref="BW2:BW7"/>
-    <mergeCell ref="BX2:BX7"/>
-    <mergeCell ref="BY2:BY7"/>
-    <mergeCell ref="BZ2:BZ7"/>
-    <mergeCell ref="CA2:CA7"/>
-    <mergeCell ref="CB2:CB7"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="BL2:BL7"/>
-    <mergeCell ref="BM2:BM7"/>
-    <mergeCell ref="BN2:BN7"/>
-    <mergeCell ref="BO2:BO7"/>
-    <mergeCell ref="BP2:BP7"/>
-    <mergeCell ref="BQ2:BQ7"/>
-    <mergeCell ref="BR2:BR7"/>
-    <mergeCell ref="BS2:BS7"/>
-    <mergeCell ref="BT2:BT7"/>
-    <mergeCell ref="BC2:BC7"/>
-    <mergeCell ref="BD2:BD7"/>
-    <mergeCell ref="BE2:BE7"/>
-    <mergeCell ref="BF2:BF7"/>
-    <mergeCell ref="BG2:BG7"/>
-    <mergeCell ref="BH2:BH7"/>
-    <mergeCell ref="BI2:BI7"/>
-    <mergeCell ref="BJ2:BJ7"/>
-    <mergeCell ref="BK2:BK7"/>
-    <mergeCell ref="AT2:AT7"/>
-    <mergeCell ref="AU2:AU7"/>
-    <mergeCell ref="AV2:AV7"/>
-    <mergeCell ref="AW2:AW7"/>
-    <mergeCell ref="AX2:AX7"/>
-    <mergeCell ref="AY2:AY7"/>
-    <mergeCell ref="AZ2:AZ7"/>
-    <mergeCell ref="BA2:BA7"/>
-    <mergeCell ref="BB2:BB7"/>
-    <mergeCell ref="AK2:AK7"/>
-    <mergeCell ref="AL2:AL7"/>
-    <mergeCell ref="AM2:AM7"/>
-    <mergeCell ref="AN2:AN7"/>
-    <mergeCell ref="AO2:AO7"/>
-    <mergeCell ref="AP2:AP7"/>
-    <mergeCell ref="AQ2:AQ7"/>
-    <mergeCell ref="AR2:AR7"/>
-    <mergeCell ref="AS2:AS7"/>
-    <mergeCell ref="AG2:AG7"/>
-    <mergeCell ref="AD2:AD7"/>
-    <mergeCell ref="AE2:AE7"/>
-    <mergeCell ref="AF2:AF7"/>
-    <mergeCell ref="AB2:AB7"/>
-    <mergeCell ref="AC2:AC7"/>
-    <mergeCell ref="AH2:AH7"/>
-    <mergeCell ref="AI2:AI7"/>
-    <mergeCell ref="AJ2:AJ7"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="V1:Z1"/>
-    <mergeCell ref="L1:P1"/>
-    <mergeCell ref="AA2:AA7"/>
-    <mergeCell ref="N2:N7"/>
-    <mergeCell ref="O2:O7"/>
-    <mergeCell ref="P2:P7"/>
-    <mergeCell ref="Q2:Q7"/>
-    <mergeCell ref="R2:R7"/>
-    <mergeCell ref="S2:S7"/>
-    <mergeCell ref="T2:T7"/>
-    <mergeCell ref="U2:U7"/>
-    <mergeCell ref="V2:V7"/>
-    <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="AA1:AE1"/>
-    <mergeCell ref="AQ1:AR1"/>
-    <mergeCell ref="AF1:AJ1"/>
-    <mergeCell ref="AF21:CB21"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="W2:W7"/>
-    <mergeCell ref="X2:X7"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:D2"/>
-    <mergeCell ref="Y2:Y7"/>
-    <mergeCell ref="Z2:Z7"/>
-    <mergeCell ref="E2:E7"/>
-    <mergeCell ref="F2:F7"/>
-    <mergeCell ref="G2:G7"/>
-    <mergeCell ref="H2:H7"/>
-    <mergeCell ref="I2:I7"/>
-    <mergeCell ref="J2:J7"/>
-    <mergeCell ref="K2:K7"/>
-    <mergeCell ref="L2:L7"/>
-    <mergeCell ref="M2:M7"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" verticalDpi="0"/>
